--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -20,15 +20,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
     <numFmt numFmtId="167" formatCode="\+0.000;\-0.000;\-"/>
     <numFmt numFmtId="168" formatCode="\+0.0%;\-0.0%;\-"/>
     <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="170" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="171" formatCode="+0.000;-0.000;&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -305,8 +308,34 @@
       <color rgb="FF15803D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="009CA3AF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -415,8 +444,13 @@
         <bgColor rgb="FFECFEFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -601,6 +635,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -612,7 +660,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1223,6 +1271,23 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="39" fillId="19" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="39" fillId="19" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="40" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="40" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="39" fillId="19" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1445,7 +1510,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1467,7 +1532,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1489,7 +1554,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1511,7 +1576,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1533,7 +1598,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1555,7 +1620,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1577,7 +1642,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -1597,7 +1662,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1685,7 +1750,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1764,7 +1829,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -3263,7 +3328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3400,244 +3465,259 @@
       <c r="O4" s="102" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
-      <c r="A5" s="166" t="n">
+      <c r="A5" s="211" t="n">
+        <v>46093.77185422383</v>
+      </c>
+      <c r="B5" s="212" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C5" s="213" t="n"/>
+      <c r="D5" s="214" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E5" s="215">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="216" t="n"/>
+      <c r="G5" s="217">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H5" s="218">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I5" s="216" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J5" s="219" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K5" s="214" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L5" s="215">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M5" s="220" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE,SE</t>
+        </is>
+      </c>
+      <c r="N5" s="221" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="101">
+      <c r="A6" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B5" s="167" t="inlineStr">
+      <c r="B6" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C5" s="168" t="n"/>
-      <c r="D5" s="169" t="n"/>
-      <c r="E5" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="171" t="n"/>
-      <c r="G5" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I5" s="171" t="n"/>
-      <c r="J5" s="174" t="n"/>
-      <c r="K5" s="169" t="n"/>
-      <c r="L5" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M5" s="175" t="n"/>
-      <c r="N5" s="176" t="n"/>
-      <c r="O5" s="102" t="n"/>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B6" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C6" s="168" t="n"/>
       <c r="D6" s="169" t="n"/>
-      <c r="E6" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E6" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F6" s="171" t="n"/>
-      <c r="G6" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G6" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I6" s="171" t="n"/>
       <c r="J6" s="174" t="n"/>
       <c r="K6" s="169" t="n"/>
-      <c r="L6" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M6" s="182" t="n"/>
-      <c r="N6" s="183" t="n"/>
+      <c r="L6" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="175" t="n"/>
+      <c r="N6" s="176" t="n"/>
       <c r="O6" s="102" t="n"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B7" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A7" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B7" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C7" s="168" t="n"/>
       <c r="D7" s="169" t="n"/>
-      <c r="E7" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E7" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F7" s="171" t="n"/>
-      <c r="G7" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G7" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I7" s="171" t="n"/>
       <c r="J7" s="174" t="n"/>
       <c r="K7" s="169" t="n"/>
-      <c r="L7" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M7" s="175" t="n"/>
-      <c r="N7" s="176" t="n"/>
+      <c r="L7" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="182" t="n"/>
+      <c r="N7" s="183" t="n"/>
       <c r="O7" s="102" t="n"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B8" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A8" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B8" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C8" s="168" t="n"/>
       <c r="D8" s="169" t="n"/>
-      <c r="E8" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E8" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F8" s="171" t="n"/>
-      <c r="G8" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G8" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I8" s="171" t="n"/>
       <c r="J8" s="174" t="n"/>
       <c r="K8" s="169" t="n"/>
-      <c r="L8" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="182" t="n"/>
-      <c r="N8" s="183" t="n"/>
+      <c r="L8" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="175" t="n"/>
+      <c r="N8" s="176" t="n"/>
       <c r="O8" s="102" t="n"/>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B9" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A9" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B9" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C9" s="168" t="n"/>
       <c r="D9" s="169" t="n"/>
-      <c r="E9" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E9" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F9" s="171" t="n"/>
-      <c r="G9" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G9" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I9" s="171" t="n"/>
       <c r="J9" s="174" t="n"/>
       <c r="K9" s="169" t="n"/>
-      <c r="L9" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="175" t="n"/>
-      <c r="N9" s="176" t="n"/>
+      <c r="L9" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="182" t="n"/>
+      <c r="N9" s="183" t="n"/>
       <c r="O9" s="102" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B10" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A10" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B10" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C10" s="168" t="n"/>
       <c r="D10" s="169" t="n"/>
-      <c r="E10" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E10" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F10" s="171" t="n"/>
-      <c r="G10" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G10" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I10" s="171" t="n"/>
       <c r="J10" s="174" t="n"/>
       <c r="K10" s="169" t="n"/>
-      <c r="L10" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="189" t="n"/>
-      <c r="N10" s="190" t="n"/>
+      <c r="L10" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="175" t="n"/>
+      <c r="N10" s="176" t="n"/>
       <c r="O10" s="102" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
       <c r="A11" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B11" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C11" s="168" t="n"/>
       <c r="D11" s="169" t="n"/>
       <c r="E11" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
       <c r="G11" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H11" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I11" s="171" t="n"/>
       <c r="J11" s="174" t="n"/>
       <c r="K11" s="169" t="n"/>
       <c r="L11" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M11" s="189" t="n"/>
@@ -3645,244 +3725,244 @@
       <c r="O11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B12" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A12" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B12" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
-      <c r="E12" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E12" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G12" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
-      <c r="L12" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="182" t="n"/>
-      <c r="N12" s="183" t="n"/>
+      <c r="L12" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="189" t="n"/>
+      <c r="N12" s="190" t="n"/>
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B13" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A13" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B13" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E13" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G13" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="175" t="n"/>
-      <c r="N13" s="176" t="n"/>
+      <c r="L13" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="182" t="n"/>
+      <c r="N13" s="183" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B14" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A14" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B14" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E14" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G14" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="182" t="n"/>
-      <c r="N14" s="183" t="n"/>
+      <c r="L14" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="176" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B15" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A15" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B15" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E15" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G15" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="175" t="n"/>
-      <c r="N15" s="176" t="n"/>
+      <c r="L15" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="182" t="n"/>
+      <c r="N15" s="183" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B16" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A16" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B16" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E16" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G16" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="182" t="n"/>
-      <c r="N16" s="183" t="n"/>
+      <c r="L16" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="175" t="n"/>
+      <c r="N16" s="176" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B17" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A17" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B17" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E17" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G17" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="189" t="n"/>
-      <c r="N17" s="190" t="n"/>
+      <c r="L17" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="182" t="n"/>
+      <c r="N17" s="183" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
       <c r="A18" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B18" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
       <c r="E18" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
       <c r="G18" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H18" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
       <c r="L18" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M18" s="189" t="n"/>
@@ -3890,244 +3970,244 @@
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B19" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A19" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B19" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E19" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G19" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="175" t="n"/>
-      <c r="N19" s="176" t="n"/>
+      <c r="L19" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="189" t="n"/>
+      <c r="N19" s="190" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B20" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A20" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B20" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E20" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G20" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="182" t="n"/>
-      <c r="N20" s="183" t="n"/>
+      <c r="L20" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="175" t="n"/>
+      <c r="N20" s="176" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B21" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A21" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B21" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E21" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G21" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="175" t="n"/>
-      <c r="N21" s="176" t="n"/>
+      <c r="L21" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="182" t="n"/>
+      <c r="N21" s="183" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B22" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A22" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B22" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E22" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G22" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="182" t="n"/>
-      <c r="N22" s="183" t="n"/>
+      <c r="L22" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="175" t="n"/>
+      <c r="N22" s="176" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B23" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A23" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B23" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E23" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G23" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="175" t="n"/>
-      <c r="N23" s="176" t="n"/>
+      <c r="L23" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="182" t="n"/>
+      <c r="N23" s="183" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B24" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A24" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E24" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G24" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="189" t="n"/>
-      <c r="N24" s="190" t="n"/>
+      <c r="L24" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="175" t="n"/>
+      <c r="N24" s="176" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
       <c r="A25" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B25" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
       <c r="E25" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
       <c r="G25" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H25" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
       <c r="L25" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M25" s="189" t="n"/>
@@ -4135,244 +4215,244 @@
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B26" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A26" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B26" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E26" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G26" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="182" t="n"/>
-      <c r="N26" s="183" t="n"/>
+      <c r="L26" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="189" t="n"/>
+      <c r="N26" s="190" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B27" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A27" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B27" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E27" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G27" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="175" t="n"/>
-      <c r="N27" s="176" t="n"/>
+      <c r="L27" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="182" t="n"/>
+      <c r="N27" s="183" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B28" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A28" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B28" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E28" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G28" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="182" t="n"/>
-      <c r="N28" s="183" t="n"/>
+      <c r="L28" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="175" t="n"/>
+      <c r="N28" s="176" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B29" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A29" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B29" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E29" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G29" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="175" t="n"/>
-      <c r="N29" s="176" t="n"/>
+      <c r="L29" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="182" t="n"/>
+      <c r="N29" s="183" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B30" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A30" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B30" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E30" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G30" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="182" t="n"/>
-      <c r="N30" s="183" t="n"/>
+      <c r="L30" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="175" t="n"/>
+      <c r="N30" s="176" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B31" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A31" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B31" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E31" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G31" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="189" t="n"/>
-      <c r="N31" s="190" t="n"/>
+      <c r="L31" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="182" t="n"/>
+      <c r="N31" s="183" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
       <c r="A32" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B32" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
       <c r="E32" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
       <c r="G32" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H32" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
       <c r="L32" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M32" s="189" t="n"/>
@@ -4380,244 +4460,244 @@
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B33" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A33" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B33" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E33" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G33" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="175" t="n"/>
-      <c r="N33" s="176" t="n"/>
+      <c r="L33" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="189" t="n"/>
+      <c r="N33" s="190" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B34" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A34" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B34" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E34" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G34" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="182" t="n"/>
-      <c r="N34" s="183" t="n"/>
+      <c r="L34" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="175" t="n"/>
+      <c r="N34" s="176" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B35" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A35" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B35" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E35" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G35" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="175" t="n"/>
-      <c r="N35" s="176" t="n"/>
+      <c r="L35" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="182" t="n"/>
+      <c r="N35" s="183" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B36" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A36" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B36" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E36" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G36" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="182" t="n"/>
-      <c r="N36" s="183" t="n"/>
+      <c r="L36" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="175" t="n"/>
+      <c r="N36" s="176" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B37" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A37" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B37" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E37" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G37" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="175" t="n"/>
-      <c r="N37" s="176" t="n"/>
+      <c r="L37" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="182" t="n"/>
+      <c r="N37" s="183" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B38" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A38" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B38" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E38" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G38" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="189" t="n"/>
-      <c r="N38" s="190" t="n"/>
+      <c r="L38" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="175" t="n"/>
+      <c r="N38" s="176" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
       <c r="A39" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B39" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
       <c r="E39" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
       <c r="G39" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H39" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
       <c r="L39" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M39" s="189" t="n"/>
@@ -4625,244 +4705,244 @@
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B40" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A40" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B40" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E40" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G40" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="182" t="n"/>
-      <c r="N40" s="183" t="n"/>
+      <c r="L40" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="189" t="n"/>
+      <c r="N40" s="190" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B41" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A41" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B41" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E41" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G41" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="175" t="n"/>
-      <c r="N41" s="176" t="n"/>
+      <c r="L41" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="182" t="n"/>
+      <c r="N41" s="183" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B42" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A42" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B42" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E42" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G42" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="182" t="n"/>
-      <c r="N42" s="183" t="n"/>
+      <c r="L42" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="175" t="n"/>
+      <c r="N42" s="176" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B43" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A43" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B43" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E43" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G43" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="175" t="n"/>
-      <c r="N43" s="176" t="n"/>
+      <c r="L43" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="182" t="n"/>
+      <c r="N43" s="183" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B44" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A44" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B44" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E44" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G44" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="182" t="n"/>
-      <c r="N44" s="183" t="n"/>
+      <c r="L44" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="175" t="n"/>
+      <c r="N44" s="176" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B45" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A45" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B45" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E45" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G45" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="189" t="n"/>
-      <c r="N45" s="190" t="n"/>
+      <c r="L45" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="182" t="n"/>
+      <c r="N45" s="183" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
       <c r="A46" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B46" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
       <c r="E46" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
       <c r="G46" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H46" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
       <c r="L46" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M46" s="189" t="n"/>
@@ -4870,244 +4950,244 @@
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B47" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A47" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B47" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E47" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G47" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="175" t="n"/>
-      <c r="N47" s="176" t="n"/>
+      <c r="L47" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="189" t="n"/>
+      <c r="N47" s="190" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B48" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A48" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B48" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E48" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G48" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="182" t="n"/>
-      <c r="N48" s="183" t="n"/>
+      <c r="L48" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="175" t="n"/>
+      <c r="N48" s="176" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B49" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A49" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B49" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E49" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G49" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="175" t="n"/>
-      <c r="N49" s="176" t="n"/>
+      <c r="L49" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="182" t="n"/>
+      <c r="N49" s="183" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B50" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A50" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B50" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E50" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G50" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="182" t="n"/>
-      <c r="N50" s="183" t="n"/>
+      <c r="L50" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="175" t="n"/>
+      <c r="N50" s="176" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B51" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A51" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B51" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E51" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G51" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="175" t="n"/>
-      <c r="N51" s="176" t="n"/>
+      <c r="L51" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="182" t="n"/>
+      <c r="N51" s="183" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B52" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A52" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B52" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E52" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G52" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="189" t="n"/>
-      <c r="N52" s="190" t="n"/>
+      <c r="L52" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="175" t="n"/>
+      <c r="N52" s="176" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
       <c r="A53" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B53" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
       <c r="E53" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
       <c r="G53" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H53" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
       <c r="L53" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M53" s="189" t="n"/>
@@ -5115,244 +5195,244 @@
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B54" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A54" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B54" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E54" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G54" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="182" t="n"/>
-      <c r="N54" s="183" t="n"/>
+      <c r="L54" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="189" t="n"/>
+      <c r="N54" s="190" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B55" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A55" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B55" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E55" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G55" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="175" t="n"/>
-      <c r="N55" s="176" t="n"/>
+      <c r="L55" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="182" t="n"/>
+      <c r="N55" s="183" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B56" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A56" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B56" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E56" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G56" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="182" t="n"/>
-      <c r="N56" s="183" t="n"/>
+      <c r="L56" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="175" t="n"/>
+      <c r="N56" s="176" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B57" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A57" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B57" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E57" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G57" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="175" t="n"/>
-      <c r="N57" s="176" t="n"/>
+      <c r="L57" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="182" t="n"/>
+      <c r="N57" s="183" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B58" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A58" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B58" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E58" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G58" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="182" t="n"/>
-      <c r="N58" s="183" t="n"/>
+      <c r="L58" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="175" t="n"/>
+      <c r="N58" s="176" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B59" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A59" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B59" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E59" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G59" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="189" t="n"/>
-      <c r="N59" s="190" t="n"/>
+      <c r="L59" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="182" t="n"/>
+      <c r="N59" s="183" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
       <c r="A60" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B60" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
       <c r="E60" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
       <c r="G60" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H60" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
       <c r="L60" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M60" s="189" t="n"/>
@@ -5360,184 +5440,202 @@
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B61" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A61" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B61" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E61" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G61" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="175" t="n"/>
-      <c r="N61" s="176" t="n"/>
+      <c r="L61" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="189" t="n"/>
+      <c r="N61" s="190" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B62" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A62" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B62" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E62" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G62" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="182" t="n"/>
-      <c r="N62" s="183" t="n"/>
+      <c r="L62" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="175" t="n"/>
+      <c r="N62" s="176" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B63" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A63" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B63" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E63" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G63" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="175" t="n"/>
-      <c r="N63" s="176" t="n"/>
+      <c r="L63" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="182" t="n"/>
+      <c r="N63" s="183" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B64" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A64" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B64" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E64" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G64" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="179">
+      <c r="L64" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="175" t="n"/>
+      <c r="N64" s="176" t="n"/>
+      <c r="O64" s="102" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="101">
+      <c r="A65" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B65" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C65" s="168" t="n"/>
+      <c r="D65" s="169" t="n"/>
+      <c r="E65" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F65" s="171" t="n"/>
+      <c r="G65" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I65" s="171" t="n"/>
+      <c r="J65" s="174" t="n"/>
+      <c r="K65" s="169" t="n"/>
+      <c r="L65" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M64" s="182" t="n"/>
-      <c r="N64" s="183" t="n"/>
-      <c r="O64" s="102" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="191" t="n">
+      <c r="M65" s="182" t="n"/>
+      <c r="N65" s="183" t="n"/>
+      <c r="O65" s="102" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="101">
+      <c r="A66" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B65" s="102" t="n"/>
-      <c r="C65" s="102" t="n"/>
-      <c r="D65" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E65" s="102" t="n"/>
-      <c r="F65" s="102" t="n"/>
-      <c r="G65" s="102" t="n"/>
-      <c r="H65" s="102" t="n"/>
-      <c r="I65" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J65" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K65" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L65" s="102" t="n"/>
-      <c r="M65" s="102" t="n"/>
-      <c r="N65" s="102" t="n"/>
-      <c r="O65" s="102" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="102" t="n"/>
       <c r="B66" s="102" t="n"/>
       <c r="C66" s="102" t="n"/>
-      <c r="D66" s="102" t="n"/>
+      <c r="D66" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E66" s="102" t="n"/>
       <c r="F66" s="102" t="n"/>
       <c r="G66" s="102" t="n"/>
       <c r="H66" s="102" t="n"/>
-      <c r="I66" s="102" t="n"/>
-      <c r="J66" s="102" t="n"/>
-      <c r="K66" s="102" t="n"/>
+      <c r="I66" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J66" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K66" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L66" s="102" t="n"/>
       <c r="M66" s="102" t="n"/>
       <c r="N66" s="102" t="n"/>
@@ -5593,6 +5691,23 @@
       <c r="M69" s="102" t="n"/>
       <c r="N69" s="102" t="n"/>
       <c r="O69" s="102" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="102" t="n"/>
+      <c r="B70" s="102" t="n"/>
+      <c r="C70" s="102" t="n"/>
+      <c r="D70" s="102" t="n"/>
+      <c r="E70" s="102" t="n"/>
+      <c r="F70" s="102" t="n"/>
+      <c r="G70" s="102" t="n"/>
+      <c r="H70" s="102" t="n"/>
+      <c r="I70" s="102" t="n"/>
+      <c r="J70" s="102" t="n"/>
+      <c r="K70" s="102" t="n"/>
+      <c r="L70" s="102" t="n"/>
+      <c r="M70" s="102" t="n"/>
+      <c r="N70" s="102" t="n"/>
+      <c r="O70" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -660,7 +660,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1288,6 +1288,39 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="37" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="39" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="40" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="40" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="39" fillId="19" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -3328,7 +3361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O70"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3465,294 +3498,313 @@
       <c r="O4" s="102" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
-      <c r="A5" s="211" t="n">
-        <v>46093.77185422383</v>
-      </c>
-      <c r="B5" s="212" t="inlineStr">
+      <c r="A5" s="222" t="n">
+        <v>46093.78404205589</v>
+      </c>
+      <c r="B5" s="223" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C5" s="213" t="n"/>
-      <c r="D5" s="214" t="n">
+      <c r="C5" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D5" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E5" s="215">
+      <c r="E5" s="226">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F5" s="216" t="n"/>
-      <c r="G5" s="217">
+      <c r="F5" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G5" s="228">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H5" s="218">
+      <c r="H5" s="229">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I5" s="216" t="n">
+      <c r="I5" s="227" t="n">
         <v>2.086</v>
       </c>
-      <c r="J5" s="219" t="n">
+      <c r="J5" s="230" t="n">
         <v>20.49</v>
       </c>
-      <c r="K5" s="214" t="n">
+      <c r="K5" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="215">
+      <c r="L5" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M5" s="220" t="inlineStr">
+      <c r="M5" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N5" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="101">
+      <c r="A6" s="211" t="n">
+        <v>46093.77185422453</v>
+      </c>
+      <c r="B6" s="212" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C6" s="213" t="n"/>
+      <c r="D6" s="214" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E6" s="215">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="216" t="n"/>
+      <c r="G6" s="217">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="218">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="216" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J6" s="219" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K6" s="214" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L6" s="215">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N5" s="221" t="inlineStr">
+      <c r="N6" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="166" t="n">
+    <row r="7" ht="21.75" customHeight="1" s="101">
+      <c r="A7" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B6" s="167" t="inlineStr">
+      <c r="B7" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C6" s="168" t="n"/>
-      <c r="D6" s="169" t="n"/>
-      <c r="E6" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="171" t="n"/>
-      <c r="G6" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I6" s="171" t="n"/>
-      <c r="J6" s="174" t="n"/>
-      <c r="K6" s="169" t="n"/>
-      <c r="L6" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M6" s="175" t="n"/>
-      <c r="N6" s="176" t="n"/>
-      <c r="O6" s="102" t="n"/>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B7" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C7" s="168" t="n"/>
       <c r="D7" s="169" t="n"/>
-      <c r="E7" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E7" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F7" s="171" t="n"/>
-      <c r="G7" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G7" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I7" s="171" t="n"/>
       <c r="J7" s="174" t="n"/>
       <c r="K7" s="169" t="n"/>
-      <c r="L7" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M7" s="182" t="n"/>
-      <c r="N7" s="183" t="n"/>
+      <c r="L7" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="175" t="n"/>
+      <c r="N7" s="176" t="n"/>
       <c r="O7" s="102" t="n"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B8" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A8" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B8" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C8" s="168" t="n"/>
       <c r="D8" s="169" t="n"/>
-      <c r="E8" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E8" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F8" s="171" t="n"/>
-      <c r="G8" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G8" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I8" s="171" t="n"/>
       <c r="J8" s="174" t="n"/>
       <c r="K8" s="169" t="n"/>
-      <c r="L8" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="175" t="n"/>
-      <c r="N8" s="176" t="n"/>
+      <c r="L8" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="182" t="n"/>
+      <c r="N8" s="183" t="n"/>
       <c r="O8" s="102" t="n"/>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B9" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A9" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B9" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C9" s="168" t="n"/>
       <c r="D9" s="169" t="n"/>
-      <c r="E9" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E9" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F9" s="171" t="n"/>
-      <c r="G9" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G9" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I9" s="171" t="n"/>
       <c r="J9" s="174" t="n"/>
       <c r="K9" s="169" t="n"/>
-      <c r="L9" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="182" t="n"/>
-      <c r="N9" s="183" t="n"/>
+      <c r="L9" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="175" t="n"/>
+      <c r="N9" s="176" t="n"/>
       <c r="O9" s="102" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B10" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A10" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B10" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C10" s="168" t="n"/>
       <c r="D10" s="169" t="n"/>
-      <c r="E10" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E10" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F10" s="171" t="n"/>
-      <c r="G10" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G10" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I10" s="171" t="n"/>
       <c r="J10" s="174" t="n"/>
       <c r="K10" s="169" t="n"/>
-      <c r="L10" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="175" t="n"/>
-      <c r="N10" s="176" t="n"/>
+      <c r="L10" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="182" t="n"/>
+      <c r="N10" s="183" t="n"/>
       <c r="O10" s="102" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B11" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A11" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B11" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C11" s="168" t="n"/>
       <c r="D11" s="169" t="n"/>
-      <c r="E11" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E11" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
-      <c r="G11" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G11" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I11" s="171" t="n"/>
       <c r="J11" s="174" t="n"/>
       <c r="K11" s="169" t="n"/>
-      <c r="L11" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="189" t="n"/>
-      <c r="N11" s="190" t="n"/>
+      <c r="L11" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="175" t="n"/>
+      <c r="N11" s="176" t="n"/>
       <c r="O11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
       <c r="A12" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B12" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
       <c r="E12" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
       <c r="G12" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H12" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
       <c r="L12" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M12" s="189" t="n"/>
@@ -3760,244 +3812,244 @@
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B13" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A13" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B13" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E13" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G13" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="182" t="n"/>
-      <c r="N13" s="183" t="n"/>
+      <c r="L13" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="189" t="n"/>
+      <c r="N13" s="190" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B14" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A14" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B14" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E14" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G14" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="175" t="n"/>
-      <c r="N14" s="176" t="n"/>
+      <c r="L14" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="182" t="n"/>
+      <c r="N14" s="183" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B15" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A15" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B15" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E15" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G15" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="182" t="n"/>
-      <c r="N15" s="183" t="n"/>
+      <c r="L15" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="175" t="n"/>
+      <c r="N15" s="176" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B16" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A16" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B16" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E16" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G16" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="175" t="n"/>
-      <c r="N16" s="176" t="n"/>
+      <c r="L16" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="182" t="n"/>
+      <c r="N16" s="183" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B17" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A17" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B17" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E17" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G17" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="182" t="n"/>
-      <c r="N17" s="183" t="n"/>
+      <c r="L17" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="175" t="n"/>
+      <c r="N17" s="176" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B18" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A18" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B18" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E18" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G18" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="189" t="n"/>
-      <c r="N18" s="190" t="n"/>
+      <c r="L18" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="182" t="n"/>
+      <c r="N18" s="183" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
       <c r="A19" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B19" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
       <c r="E19" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
       <c r="G19" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H19" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
       <c r="L19" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M19" s="189" t="n"/>
@@ -4005,244 +4057,244 @@
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A20" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B20" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E20" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G20" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="175" t="n"/>
-      <c r="N20" s="176" t="n"/>
+      <c r="L20" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="189" t="n"/>
+      <c r="N20" s="190" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B21" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A21" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B21" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E21" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G21" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="182" t="n"/>
-      <c r="N21" s="183" t="n"/>
+      <c r="L21" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="175" t="n"/>
+      <c r="N21" s="176" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B22" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A22" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B22" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E22" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G22" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="175" t="n"/>
-      <c r="N22" s="176" t="n"/>
+      <c r="L22" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="182" t="n"/>
+      <c r="N22" s="183" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B23" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A23" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B23" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E23" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G23" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="182" t="n"/>
-      <c r="N23" s="183" t="n"/>
+      <c r="L23" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="175" t="n"/>
+      <c r="N23" s="176" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B24" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A24" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B24" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E24" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G24" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="175" t="n"/>
-      <c r="N24" s="176" t="n"/>
+      <c r="L24" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="182" t="n"/>
+      <c r="N24" s="183" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B25" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A25" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B25" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E25" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G25" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="189" t="n"/>
-      <c r="N25" s="190" t="n"/>
+      <c r="L25" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="175" t="n"/>
+      <c r="N25" s="176" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
       <c r="A26" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B26" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
       <c r="E26" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
       <c r="G26" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H26" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
       <c r="L26" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M26" s="189" t="n"/>
@@ -4250,244 +4302,244 @@
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B27" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A27" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B27" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E27" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G27" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="182" t="n"/>
-      <c r="N27" s="183" t="n"/>
+      <c r="L27" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="189" t="n"/>
+      <c r="N27" s="190" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B28" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A28" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B28" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E28" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G28" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="175" t="n"/>
-      <c r="N28" s="176" t="n"/>
+      <c r="L28" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="182" t="n"/>
+      <c r="N28" s="183" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B29" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A29" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B29" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E29" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G29" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="182" t="n"/>
-      <c r="N29" s="183" t="n"/>
+      <c r="L29" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="175" t="n"/>
+      <c r="N29" s="176" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B30" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A30" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B30" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E30" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G30" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="175" t="n"/>
-      <c r="N30" s="176" t="n"/>
+      <c r="L30" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="182" t="n"/>
+      <c r="N30" s="183" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B31" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A31" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B31" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E31" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G31" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="182" t="n"/>
-      <c r="N31" s="183" t="n"/>
+      <c r="L31" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="175" t="n"/>
+      <c r="N31" s="176" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B32" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A32" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B32" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E32" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G32" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="189" t="n"/>
-      <c r="N32" s="190" t="n"/>
+      <c r="L32" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="182" t="n"/>
+      <c r="N32" s="183" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
       <c r="A33" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B33" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
       <c r="E33" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
       <c r="G33" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H33" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
       <c r="L33" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M33" s="189" t="n"/>
@@ -4495,244 +4547,244 @@
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B34" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A34" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B34" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E34" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G34" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="175" t="n"/>
-      <c r="N34" s="176" t="n"/>
+      <c r="L34" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="189" t="n"/>
+      <c r="N34" s="190" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B35" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A35" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B35" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E35" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G35" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="182" t="n"/>
-      <c r="N35" s="183" t="n"/>
+      <c r="L35" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="175" t="n"/>
+      <c r="N35" s="176" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B36" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A36" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B36" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E36" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G36" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="175" t="n"/>
-      <c r="N36" s="176" t="n"/>
+      <c r="L36" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="182" t="n"/>
+      <c r="N36" s="183" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B37" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A37" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B37" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E37" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G37" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="182" t="n"/>
-      <c r="N37" s="183" t="n"/>
+      <c r="L37" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="175" t="n"/>
+      <c r="N37" s="176" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B38" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A38" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B38" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E38" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G38" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="175" t="n"/>
-      <c r="N38" s="176" t="n"/>
+      <c r="L38" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="182" t="n"/>
+      <c r="N38" s="183" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B39" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A39" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B39" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E39" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G39" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="189" t="n"/>
-      <c r="N39" s="190" t="n"/>
+      <c r="L39" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="175" t="n"/>
+      <c r="N39" s="176" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
       <c r="A40" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B40" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
       <c r="E40" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
       <c r="G40" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H40" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
       <c r="L40" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M40" s="189" t="n"/>
@@ -4740,244 +4792,244 @@
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B41" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A41" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B41" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E41" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G41" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="182" t="n"/>
-      <c r="N41" s="183" t="n"/>
+      <c r="L41" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="189" t="n"/>
+      <c r="N41" s="190" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B42" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A42" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B42" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E42" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G42" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="175" t="n"/>
-      <c r="N42" s="176" t="n"/>
+      <c r="L42" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="182" t="n"/>
+      <c r="N42" s="183" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B43" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A43" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B43" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E43" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G43" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="182" t="n"/>
-      <c r="N43" s="183" t="n"/>
+      <c r="L43" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="175" t="n"/>
+      <c r="N43" s="176" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B44" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A44" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B44" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E44" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G44" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="175" t="n"/>
-      <c r="N44" s="176" t="n"/>
+      <c r="L44" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="182" t="n"/>
+      <c r="N44" s="183" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B45" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A45" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B45" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E45" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G45" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="182" t="n"/>
-      <c r="N45" s="183" t="n"/>
+      <c r="L45" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="175" t="n"/>
+      <c r="N45" s="176" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B46" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A46" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B46" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E46" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G46" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="189" t="n"/>
-      <c r="N46" s="190" t="n"/>
+      <c r="L46" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="182" t="n"/>
+      <c r="N46" s="183" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
       <c r="A47" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B47" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
       <c r="E47" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
       <c r="G47" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H47" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
       <c r="L47" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M47" s="189" t="n"/>
@@ -4985,244 +5037,244 @@
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B48" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A48" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B48" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E48" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G48" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="175" t="n"/>
-      <c r="N48" s="176" t="n"/>
+      <c r="L48" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="189" t="n"/>
+      <c r="N48" s="190" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B49" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A49" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B49" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E49" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G49" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="182" t="n"/>
-      <c r="N49" s="183" t="n"/>
+      <c r="L49" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="175" t="n"/>
+      <c r="N49" s="176" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B50" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A50" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B50" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E50" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G50" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="175" t="n"/>
-      <c r="N50" s="176" t="n"/>
+      <c r="L50" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="182" t="n"/>
+      <c r="N50" s="183" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B51" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A51" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B51" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E51" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G51" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="182" t="n"/>
-      <c r="N51" s="183" t="n"/>
+      <c r="L51" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="175" t="n"/>
+      <c r="N51" s="176" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B52" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A52" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B52" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E52" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G52" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="175" t="n"/>
-      <c r="N52" s="176" t="n"/>
+      <c r="L52" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="182" t="n"/>
+      <c r="N52" s="183" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B53" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A53" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B53" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E53" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G53" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="189" t="n"/>
-      <c r="N53" s="190" t="n"/>
+      <c r="L53" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="175" t="n"/>
+      <c r="N53" s="176" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
       <c r="A54" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B54" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
       <c r="E54" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
       <c r="G54" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H54" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
       <c r="L54" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M54" s="189" t="n"/>
@@ -5230,244 +5282,244 @@
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B55" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A55" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B55" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E55" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G55" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="182" t="n"/>
-      <c r="N55" s="183" t="n"/>
+      <c r="L55" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="189" t="n"/>
+      <c r="N55" s="190" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B56" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A56" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B56" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E56" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G56" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="175" t="n"/>
-      <c r="N56" s="176" t="n"/>
+      <c r="L56" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="182" t="n"/>
+      <c r="N56" s="183" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B57" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A57" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B57" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E57" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G57" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="182" t="n"/>
-      <c r="N57" s="183" t="n"/>
+      <c r="L57" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="175" t="n"/>
+      <c r="N57" s="176" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B58" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A58" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B58" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E58" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G58" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="175" t="n"/>
-      <c r="N58" s="176" t="n"/>
+      <c r="L58" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="182" t="n"/>
+      <c r="N58" s="183" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B59" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A59" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B59" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E59" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G59" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="182" t="n"/>
-      <c r="N59" s="183" t="n"/>
+      <c r="L59" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="175" t="n"/>
+      <c r="N59" s="176" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B60" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A60" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B60" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E60" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G60" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="189" t="n"/>
-      <c r="N60" s="190" t="n"/>
+      <c r="L60" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="182" t="n"/>
+      <c r="N60" s="183" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
       <c r="A61" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B61" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
       <c r="E61" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
       <c r="G61" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H61" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
       <c r="L61" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M61" s="189" t="n"/>
@@ -5475,184 +5527,202 @@
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B62" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A62" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B62" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E62" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G62" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="175" t="n"/>
-      <c r="N62" s="176" t="n"/>
+      <c r="L62" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="189" t="n"/>
+      <c r="N62" s="190" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B63" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A63" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B63" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E63" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G63" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="182" t="n"/>
-      <c r="N63" s="183" t="n"/>
+      <c r="L63" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="175" t="n"/>
+      <c r="N63" s="176" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B64" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A64" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B64" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E64" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G64" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="175" t="n"/>
-      <c r="N64" s="176" t="n"/>
+      <c r="L64" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="182" t="n"/>
+      <c r="N64" s="183" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B65" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A65" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B65" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E65" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G65" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="179">
+      <c r="L65" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="175" t="n"/>
+      <c r="N65" s="176" t="n"/>
+      <c r="O65" s="102" t="n"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="101">
+      <c r="A66" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B66" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C66" s="168" t="n"/>
+      <c r="D66" s="169" t="n"/>
+      <c r="E66" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F66" s="171" t="n"/>
+      <c r="G66" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I66" s="171" t="n"/>
+      <c r="J66" s="174" t="n"/>
+      <c r="K66" s="169" t="n"/>
+      <c r="L66" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M65" s="182" t="n"/>
-      <c r="N65" s="183" t="n"/>
-      <c r="O65" s="102" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="191" t="n">
+      <c r="M66" s="182" t="n"/>
+      <c r="N66" s="183" t="n"/>
+      <c r="O66" s="102" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="101">
+      <c r="A67" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B66" s="102" t="n"/>
-      <c r="C66" s="102" t="n"/>
-      <c r="D66" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E66" s="102" t="n"/>
-      <c r="F66" s="102" t="n"/>
-      <c r="G66" s="102" t="n"/>
-      <c r="H66" s="102" t="n"/>
-      <c r="I66" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J66" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K66" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L66" s="102" t="n"/>
-      <c r="M66" s="102" t="n"/>
-      <c r="N66" s="102" t="n"/>
-      <c r="O66" s="102" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="102" t="n"/>
       <c r="B67" s="102" t="n"/>
       <c r="C67" s="102" t="n"/>
-      <c r="D67" s="102" t="n"/>
+      <c r="D67" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E67" s="102" t="n"/>
       <c r="F67" s="102" t="n"/>
       <c r="G67" s="102" t="n"/>
       <c r="H67" s="102" t="n"/>
-      <c r="I67" s="102" t="n"/>
-      <c r="J67" s="102" t="n"/>
-      <c r="K67" s="102" t="n"/>
+      <c r="I67" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J67" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K67" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L67" s="102" t="n"/>
       <c r="M67" s="102" t="n"/>
       <c r="N67" s="102" t="n"/>
@@ -5708,6 +5778,23 @@
       <c r="M70" s="102" t="n"/>
       <c r="N70" s="102" t="n"/>
       <c r="O70" s="102" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="102" t="n"/>
+      <c r="B71" s="102" t="n"/>
+      <c r="C71" s="102" t="n"/>
+      <c r="D71" s="102" t="n"/>
+      <c r="E71" s="102" t="n"/>
+      <c r="F71" s="102" t="n"/>
+      <c r="G71" s="102" t="n"/>
+      <c r="H71" s="102" t="n"/>
+      <c r="I71" s="102" t="n"/>
+      <c r="J71" s="102" t="n"/>
+      <c r="K71" s="102" t="n"/>
+      <c r="L71" s="102" t="n"/>
+      <c r="M71" s="102" t="n"/>
+      <c r="N71" s="102" t="n"/>
+      <c r="O71" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3361,7 +3361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.78404205589</v>
+        <v>46093.79037730218</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3512,20 +3512,17 @@
       <c r="D5" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E5" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E5" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F5" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G5" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H5" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G5" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H5" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I5" s="227" t="n">
         <v>2.086</v>
@@ -3536,310 +3533,328 @@
       <c r="K5" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="226">
+      <c r="L5" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M5" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N5" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="101">
+      <c r="A6" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B6" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C6" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D6" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E6" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G6" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I6" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J6" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K6" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L6" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M5" s="231" t="inlineStr">
+      <c r="M6" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N5" s="232" t="inlineStr">
+      <c r="N6" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="211" t="n">
+    <row r="7" ht="21.75" customHeight="1" s="101">
+      <c r="A7" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B6" s="212" t="inlineStr">
+      <c r="B7" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C6" s="213" t="n"/>
-      <c r="D6" s="214" t="n">
+      <c r="C7" s="213" t="n"/>
+      <c r="D7" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E6" s="215">
+      <c r="E7" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F6" s="216" t="n"/>
-      <c r="G6" s="217">
+      <c r="F7" s="216" t="n"/>
+      <c r="G7" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H6" s="218">
+      <c r="H7" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I6" s="216" t="n">
+      <c r="I7" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J6" s="219" t="n">
+      <c r="J7" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K6" s="214" t="n">
+      <c r="K7" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L6" s="215">
+      <c r="L7" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M6" s="220" t="inlineStr">
+      <c r="M7" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N6" s="221" t="inlineStr">
+      <c r="N7" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="166" t="n">
+    <row r="8" ht="21.75" customHeight="1" s="101">
+      <c r="A8" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B7" s="167" t="inlineStr">
+      <c r="B8" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C7" s="168" t="n"/>
-      <c r="D7" s="169" t="n"/>
-      <c r="E7" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="171" t="n"/>
-      <c r="G7" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I7" s="171" t="n"/>
-      <c r="J7" s="174" t="n"/>
-      <c r="K7" s="169" t="n"/>
-      <c r="L7" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M7" s="175" t="n"/>
-      <c r="N7" s="176" t="n"/>
-      <c r="O7" s="102" t="n"/>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B8" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C8" s="168" t="n"/>
       <c r="D8" s="169" t="n"/>
-      <c r="E8" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E8" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F8" s="171" t="n"/>
-      <c r="G8" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G8" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I8" s="171" t="n"/>
       <c r="J8" s="174" t="n"/>
       <c r="K8" s="169" t="n"/>
-      <c r="L8" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="182" t="n"/>
-      <c r="N8" s="183" t="n"/>
+      <c r="L8" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="175" t="n"/>
+      <c r="N8" s="176" t="n"/>
       <c r="O8" s="102" t="n"/>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B9" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A9" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B9" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C9" s="168" t="n"/>
       <c r="D9" s="169" t="n"/>
-      <c r="E9" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E9" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F9" s="171" t="n"/>
-      <c r="G9" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G9" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I9" s="171" t="n"/>
       <c r="J9" s="174" t="n"/>
       <c r="K9" s="169" t="n"/>
-      <c r="L9" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="175" t="n"/>
-      <c r="N9" s="176" t="n"/>
+      <c r="L9" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="182" t="n"/>
+      <c r="N9" s="183" t="n"/>
       <c r="O9" s="102" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B10" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A10" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B10" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C10" s="168" t="n"/>
       <c r="D10" s="169" t="n"/>
-      <c r="E10" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E10" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F10" s="171" t="n"/>
-      <c r="G10" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G10" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I10" s="171" t="n"/>
       <c r="J10" s="174" t="n"/>
       <c r="K10" s="169" t="n"/>
-      <c r="L10" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="182" t="n"/>
-      <c r="N10" s="183" t="n"/>
+      <c r="L10" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="175" t="n"/>
+      <c r="N10" s="176" t="n"/>
       <c r="O10" s="102" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B11" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A11" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B11" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C11" s="168" t="n"/>
       <c r="D11" s="169" t="n"/>
-      <c r="E11" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E11" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
-      <c r="G11" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G11" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I11" s="171" t="n"/>
       <c r="J11" s="174" t="n"/>
       <c r="K11" s="169" t="n"/>
-      <c r="L11" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="175" t="n"/>
-      <c r="N11" s="176" t="n"/>
+      <c r="L11" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="182" t="n"/>
+      <c r="N11" s="183" t="n"/>
       <c r="O11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B12" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A12" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B12" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
-      <c r="E12" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E12" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G12" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
-      <c r="L12" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="189" t="n"/>
-      <c r="N12" s="190" t="n"/>
+      <c r="L12" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="175" t="n"/>
+      <c r="N12" s="176" t="n"/>
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
       <c r="A13" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B13" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
       <c r="E13" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
       <c r="G13" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H13" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
       <c r="L13" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M13" s="189" t="n"/>
@@ -3847,244 +3862,244 @@
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B14" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A14" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B14" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E14" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G14" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="182" t="n"/>
-      <c r="N14" s="183" t="n"/>
+      <c r="L14" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="189" t="n"/>
+      <c r="N14" s="190" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B15" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A15" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B15" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E15" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G15" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="175" t="n"/>
-      <c r="N15" s="176" t="n"/>
+      <c r="L15" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="182" t="n"/>
+      <c r="N15" s="183" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B16" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A16" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B16" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E16" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G16" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="182" t="n"/>
-      <c r="N16" s="183" t="n"/>
+      <c r="L16" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="175" t="n"/>
+      <c r="N16" s="176" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B17" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A17" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B17" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E17" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G17" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="175" t="n"/>
-      <c r="N17" s="176" t="n"/>
+      <c r="L17" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="182" t="n"/>
+      <c r="N17" s="183" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B18" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A18" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B18" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E18" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G18" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="182" t="n"/>
-      <c r="N18" s="183" t="n"/>
+      <c r="L18" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="175" t="n"/>
+      <c r="N18" s="176" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B19" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A19" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B19" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E19" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G19" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="189" t="n"/>
-      <c r="N19" s="190" t="n"/>
+      <c r="L19" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="182" t="n"/>
+      <c r="N19" s="183" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
       <c r="A20" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B20" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
       <c r="E20" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
       <c r="G20" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H20" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
       <c r="L20" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M20" s="189" t="n"/>
@@ -4092,244 +4107,244 @@
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B21" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A21" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B21" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E21" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G21" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="175" t="n"/>
-      <c r="N21" s="176" t="n"/>
+      <c r="L21" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="189" t="n"/>
+      <c r="N21" s="190" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B22" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A22" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B22" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E22" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G22" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="182" t="n"/>
-      <c r="N22" s="183" t="n"/>
+      <c r="L22" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="175" t="n"/>
+      <c r="N22" s="176" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B23" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A23" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B23" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E23" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G23" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="175" t="n"/>
-      <c r="N23" s="176" t="n"/>
+      <c r="L23" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="182" t="n"/>
+      <c r="N23" s="183" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B24" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A24" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E24" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G24" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="182" t="n"/>
-      <c r="N24" s="183" t="n"/>
+      <c r="L24" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="175" t="n"/>
+      <c r="N24" s="176" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B25" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A25" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B25" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E25" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G25" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="175" t="n"/>
-      <c r="N25" s="176" t="n"/>
+      <c r="L25" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="182" t="n"/>
+      <c r="N25" s="183" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B26" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A26" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B26" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E26" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G26" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="189" t="n"/>
-      <c r="N26" s="190" t="n"/>
+      <c r="L26" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="175" t="n"/>
+      <c r="N26" s="176" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
       <c r="A27" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B27" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
       <c r="E27" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
       <c r="G27" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H27" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
       <c r="L27" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M27" s="189" t="n"/>
@@ -4337,244 +4352,244 @@
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B28" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A28" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B28" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E28" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G28" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="182" t="n"/>
-      <c r="N28" s="183" t="n"/>
+      <c r="L28" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="189" t="n"/>
+      <c r="N28" s="190" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B29" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A29" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B29" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E29" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G29" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="175" t="n"/>
-      <c r="N29" s="176" t="n"/>
+      <c r="L29" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="182" t="n"/>
+      <c r="N29" s="183" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B30" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A30" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B30" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E30" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G30" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="182" t="n"/>
-      <c r="N30" s="183" t="n"/>
+      <c r="L30" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="175" t="n"/>
+      <c r="N30" s="176" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B31" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A31" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B31" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E31" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G31" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="175" t="n"/>
-      <c r="N31" s="176" t="n"/>
+      <c r="L31" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="182" t="n"/>
+      <c r="N31" s="183" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B32" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A32" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B32" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E32" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G32" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="182" t="n"/>
-      <c r="N32" s="183" t="n"/>
+      <c r="L32" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="175" t="n"/>
+      <c r="N32" s="176" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B33" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A33" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B33" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E33" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G33" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="189" t="n"/>
-      <c r="N33" s="190" t="n"/>
+      <c r="L33" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="182" t="n"/>
+      <c r="N33" s="183" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
       <c r="A34" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B34" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
       <c r="E34" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
       <c r="G34" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H34" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
       <c r="L34" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M34" s="189" t="n"/>
@@ -4582,244 +4597,244 @@
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B35" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A35" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B35" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E35" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G35" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="175" t="n"/>
-      <c r="N35" s="176" t="n"/>
+      <c r="L35" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="189" t="n"/>
+      <c r="N35" s="190" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B36" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A36" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B36" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E36" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G36" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="182" t="n"/>
-      <c r="N36" s="183" t="n"/>
+      <c r="L36" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="175" t="n"/>
+      <c r="N36" s="176" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B37" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A37" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B37" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E37" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G37" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="175" t="n"/>
-      <c r="N37" s="176" t="n"/>
+      <c r="L37" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="182" t="n"/>
+      <c r="N37" s="183" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B38" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A38" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B38" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E38" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G38" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="182" t="n"/>
-      <c r="N38" s="183" t="n"/>
+      <c r="L38" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="175" t="n"/>
+      <c r="N38" s="176" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B39" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A39" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B39" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E39" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G39" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="175" t="n"/>
-      <c r="N39" s="176" t="n"/>
+      <c r="L39" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="182" t="n"/>
+      <c r="N39" s="183" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B40" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A40" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B40" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E40" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G40" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="189" t="n"/>
-      <c r="N40" s="190" t="n"/>
+      <c r="L40" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="175" t="n"/>
+      <c r="N40" s="176" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
       <c r="A41" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B41" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
       <c r="E41" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
       <c r="G41" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H41" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
       <c r="L41" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M41" s="189" t="n"/>
@@ -4827,244 +4842,244 @@
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B42" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A42" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B42" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E42" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G42" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="182" t="n"/>
-      <c r="N42" s="183" t="n"/>
+      <c r="L42" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="189" t="n"/>
+      <c r="N42" s="190" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B43" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A43" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B43" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E43" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G43" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="175" t="n"/>
-      <c r="N43" s="176" t="n"/>
+      <c r="L43" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="182" t="n"/>
+      <c r="N43" s="183" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B44" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A44" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B44" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E44" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G44" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="182" t="n"/>
-      <c r="N44" s="183" t="n"/>
+      <c r="L44" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="175" t="n"/>
+      <c r="N44" s="176" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B45" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A45" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B45" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E45" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G45" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="175" t="n"/>
-      <c r="N45" s="176" t="n"/>
+      <c r="L45" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="182" t="n"/>
+      <c r="N45" s="183" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B46" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A46" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B46" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E46" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G46" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="182" t="n"/>
-      <c r="N46" s="183" t="n"/>
+      <c r="L46" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="175" t="n"/>
+      <c r="N46" s="176" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B47" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A47" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B47" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E47" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G47" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="189" t="n"/>
-      <c r="N47" s="190" t="n"/>
+      <c r="L47" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="182" t="n"/>
+      <c r="N47" s="183" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
       <c r="A48" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B48" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
       <c r="E48" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
       <c r="G48" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H48" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
       <c r="L48" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M48" s="189" t="n"/>
@@ -5072,244 +5087,244 @@
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B49" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A49" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B49" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E49" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G49" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="175" t="n"/>
-      <c r="N49" s="176" t="n"/>
+      <c r="L49" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="189" t="n"/>
+      <c r="N49" s="190" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B50" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A50" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B50" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E50" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G50" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="182" t="n"/>
-      <c r="N50" s="183" t="n"/>
+      <c r="L50" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="175" t="n"/>
+      <c r="N50" s="176" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B51" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A51" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B51" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E51" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G51" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="175" t="n"/>
-      <c r="N51" s="176" t="n"/>
+      <c r="L51" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="182" t="n"/>
+      <c r="N51" s="183" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B52" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A52" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B52" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E52" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G52" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="182" t="n"/>
-      <c r="N52" s="183" t="n"/>
+      <c r="L52" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="175" t="n"/>
+      <c r="N52" s="176" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B53" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A53" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B53" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E53" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G53" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="175" t="n"/>
-      <c r="N53" s="176" t="n"/>
+      <c r="L53" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="182" t="n"/>
+      <c r="N53" s="183" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B54" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A54" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B54" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E54" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G54" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="189" t="n"/>
-      <c r="N54" s="190" t="n"/>
+      <c r="L54" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="175" t="n"/>
+      <c r="N54" s="176" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
       <c r="A55" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B55" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
       <c r="E55" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
       <c r="G55" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H55" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
       <c r="L55" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M55" s="189" t="n"/>
@@ -5317,244 +5332,244 @@
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B56" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A56" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B56" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E56" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G56" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="182" t="n"/>
-      <c r="N56" s="183" t="n"/>
+      <c r="L56" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="189" t="n"/>
+      <c r="N56" s="190" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B57" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A57" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B57" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E57" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G57" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="175" t="n"/>
-      <c r="N57" s="176" t="n"/>
+      <c r="L57" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="182" t="n"/>
+      <c r="N57" s="183" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B58" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A58" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B58" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E58" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G58" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="182" t="n"/>
-      <c r="N58" s="183" t="n"/>
+      <c r="L58" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="175" t="n"/>
+      <c r="N58" s="176" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B59" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A59" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B59" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E59" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G59" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="175" t="n"/>
-      <c r="N59" s="176" t="n"/>
+      <c r="L59" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="182" t="n"/>
+      <c r="N59" s="183" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B60" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A60" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B60" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E60" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G60" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="182" t="n"/>
-      <c r="N60" s="183" t="n"/>
+      <c r="L60" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="175" t="n"/>
+      <c r="N60" s="176" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B61" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A61" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B61" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E61" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G61" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="189" t="n"/>
-      <c r="N61" s="190" t="n"/>
+      <c r="L61" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="182" t="n"/>
+      <c r="N61" s="183" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
       <c r="A62" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B62" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
       <c r="E62" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
       <c r="G62" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H62" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
       <c r="L62" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M62" s="189" t="n"/>
@@ -5562,184 +5577,202 @@
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B63" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A63" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B63" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E63" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G63" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="175" t="n"/>
-      <c r="N63" s="176" t="n"/>
+      <c r="L63" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="189" t="n"/>
+      <c r="N63" s="190" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B64" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A64" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B64" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E64" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G64" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="182" t="n"/>
-      <c r="N64" s="183" t="n"/>
+      <c r="L64" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="175" t="n"/>
+      <c r="N64" s="176" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B65" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A65" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B65" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E65" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G65" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="175" t="n"/>
-      <c r="N65" s="176" t="n"/>
+      <c r="L65" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="182" t="n"/>
+      <c r="N65" s="183" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B66" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A66" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B66" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E66" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G66" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="179">
+      <c r="L66" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="175" t="n"/>
+      <c r="N66" s="176" t="n"/>
+      <c r="O66" s="102" t="n"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="101">
+      <c r="A67" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B67" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C67" s="168" t="n"/>
+      <c r="D67" s="169" t="n"/>
+      <c r="E67" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="171" t="n"/>
+      <c r="G67" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I67" s="171" t="n"/>
+      <c r="J67" s="174" t="n"/>
+      <c r="K67" s="169" t="n"/>
+      <c r="L67" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M66" s="182" t="n"/>
-      <c r="N66" s="183" t="n"/>
-      <c r="O66" s="102" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="191" t="n">
+      <c r="M67" s="182" t="n"/>
+      <c r="N67" s="183" t="n"/>
+      <c r="O67" s="102" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="101">
+      <c r="A68" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B67" s="102" t="n"/>
-      <c r="C67" s="102" t="n"/>
-      <c r="D67" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E67" s="102" t="n"/>
-      <c r="F67" s="102" t="n"/>
-      <c r="G67" s="102" t="n"/>
-      <c r="H67" s="102" t="n"/>
-      <c r="I67" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J67" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K67" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L67" s="102" t="n"/>
-      <c r="M67" s="102" t="n"/>
-      <c r="N67" s="102" t="n"/>
-      <c r="O67" s="102" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="102" t="n"/>
       <c r="B68" s="102" t="n"/>
       <c r="C68" s="102" t="n"/>
-      <c r="D68" s="102" t="n"/>
+      <c r="D68" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E68" s="102" t="n"/>
       <c r="F68" s="102" t="n"/>
       <c r="G68" s="102" t="n"/>
       <c r="H68" s="102" t="n"/>
-      <c r="I68" s="102" t="n"/>
-      <c r="J68" s="102" t="n"/>
-      <c r="K68" s="102" t="n"/>
+      <c r="I68" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J68" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K68" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L68" s="102" t="n"/>
       <c r="M68" s="102" t="n"/>
       <c r="N68" s="102" t="n"/>
@@ -5795,6 +5828,23 @@
       <c r="M71" s="102" t="n"/>
       <c r="N71" s="102" t="n"/>
       <c r="O71" s="102" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="102" t="n"/>
+      <c r="B72" s="102" t="n"/>
+      <c r="C72" s="102" t="n"/>
+      <c r="D72" s="102" t="n"/>
+      <c r="E72" s="102" t="n"/>
+      <c r="F72" s="102" t="n"/>
+      <c r="G72" s="102" t="n"/>
+      <c r="H72" s="102" t="n"/>
+      <c r="I72" s="102" t="n"/>
+      <c r="J72" s="102" t="n"/>
+      <c r="K72" s="102" t="n"/>
+      <c r="L72" s="102" t="n"/>
+      <c r="M72" s="102" t="n"/>
+      <c r="N72" s="102" t="n"/>
+      <c r="O72" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -660,7 +660,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1322,6 +1322,9 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3361,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3499,7 +3502,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.79037730218</v>
+        <v>46093.80209267978</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3513,19 +3516,13 @@
         <v>4.2578</v>
       </c>
       <c r="E5" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F5" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G5" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H5" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F5" s="227" t="n"/>
+      <c r="G5" s="228" t="n"/>
+      <c r="H5" s="229" t="n"/>
       <c r="I5" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J5" s="230" t="n">
         <v>20.49</v>
@@ -3534,11 +3531,11 @@
         <v>10.7108</v>
       </c>
       <c r="L5" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M5" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N5" s="232" t="inlineStr">
@@ -3549,7 +3546,7 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3562,20 +3559,17 @@
       <c r="D6" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E6" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E6" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F6" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G6" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G6" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H6" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I6" s="227" t="n">
         <v>2.086</v>
@@ -3586,310 +3580,328 @@
       <c r="K6" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L6" s="226">
+      <c r="L6" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M6" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N6" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" s="101">
+      <c r="A7" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B7" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C7" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D7" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E7" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G7" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I7" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J7" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K7" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L7" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M6" s="231" t="inlineStr">
+      <c r="M7" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N6" s="232" t="inlineStr">
+      <c r="N7" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="211" t="n">
+    <row r="8" ht="21.75" customHeight="1" s="101">
+      <c r="A8" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B7" s="212" t="inlineStr">
+      <c r="B8" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C7" s="213" t="n"/>
-      <c r="D7" s="214" t="n">
+      <c r="C8" s="213" t="n"/>
+      <c r="D8" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E7" s="215">
+      <c r="E8" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F7" s="216" t="n"/>
-      <c r="G7" s="217">
+      <c r="F8" s="216" t="n"/>
+      <c r="G8" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H7" s="218">
+      <c r="H8" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I7" s="216" t="n">
+      <c r="I8" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J7" s="219" t="n">
+      <c r="J8" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K7" s="214" t="n">
+      <c r="K8" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L7" s="215">
+      <c r="L8" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M7" s="220" t="inlineStr">
+      <c r="M8" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N7" s="221" t="inlineStr">
+      <c r="N8" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="166" t="n">
+    <row r="9" ht="21.75" customHeight="1" s="101">
+      <c r="A9" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B8" s="167" t="inlineStr">
+      <c r="B9" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C8" s="168" t="n"/>
-      <c r="D8" s="169" t="n"/>
-      <c r="E8" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="171" t="n"/>
-      <c r="G8" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I8" s="171" t="n"/>
-      <c r="J8" s="174" t="n"/>
-      <c r="K8" s="169" t="n"/>
-      <c r="L8" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="175" t="n"/>
-      <c r="N8" s="176" t="n"/>
-      <c r="O8" s="102" t="n"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B9" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C9" s="168" t="n"/>
       <c r="D9" s="169" t="n"/>
-      <c r="E9" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E9" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F9" s="171" t="n"/>
-      <c r="G9" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G9" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I9" s="171" t="n"/>
       <c r="J9" s="174" t="n"/>
       <c r="K9" s="169" t="n"/>
-      <c r="L9" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="182" t="n"/>
-      <c r="N9" s="183" t="n"/>
+      <c r="L9" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="175" t="n"/>
+      <c r="N9" s="176" t="n"/>
       <c r="O9" s="102" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B10" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A10" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B10" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C10" s="168" t="n"/>
       <c r="D10" s="169" t="n"/>
-      <c r="E10" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E10" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F10" s="171" t="n"/>
-      <c r="G10" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G10" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I10" s="171" t="n"/>
       <c r="J10" s="174" t="n"/>
       <c r="K10" s="169" t="n"/>
-      <c r="L10" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="175" t="n"/>
-      <c r="N10" s="176" t="n"/>
+      <c r="L10" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="182" t="n"/>
+      <c r="N10" s="183" t="n"/>
       <c r="O10" s="102" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B11" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A11" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B11" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C11" s="168" t="n"/>
       <c r="D11" s="169" t="n"/>
-      <c r="E11" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E11" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
-      <c r="G11" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G11" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I11" s="171" t="n"/>
       <c r="J11" s="174" t="n"/>
       <c r="K11" s="169" t="n"/>
-      <c r="L11" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="182" t="n"/>
-      <c r="N11" s="183" t="n"/>
+      <c r="L11" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="175" t="n"/>
+      <c r="N11" s="176" t="n"/>
       <c r="O11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B12" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A12" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B12" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
-      <c r="E12" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E12" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G12" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
-      <c r="L12" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="175" t="n"/>
-      <c r="N12" s="176" t="n"/>
+      <c r="L12" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="182" t="n"/>
+      <c r="N12" s="183" t="n"/>
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B13" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A13" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B13" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E13" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G13" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="189" t="n"/>
-      <c r="N13" s="190" t="n"/>
+      <c r="L13" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="175" t="n"/>
+      <c r="N13" s="176" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
       <c r="A14" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B14" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
       <c r="E14" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
       <c r="G14" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H14" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
       <c r="L14" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M14" s="189" t="n"/>
@@ -3897,244 +3909,244 @@
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B15" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A15" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B15" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E15" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G15" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="182" t="n"/>
-      <c r="N15" s="183" t="n"/>
+      <c r="L15" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="189" t="n"/>
+      <c r="N15" s="190" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B16" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A16" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B16" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E16" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G16" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="175" t="n"/>
-      <c r="N16" s="176" t="n"/>
+      <c r="L16" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="182" t="n"/>
+      <c r="N16" s="183" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B17" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A17" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B17" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E17" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G17" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="182" t="n"/>
-      <c r="N17" s="183" t="n"/>
+      <c r="L17" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="175" t="n"/>
+      <c r="N17" s="176" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B18" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A18" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B18" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E18" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G18" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="175" t="n"/>
-      <c r="N18" s="176" t="n"/>
+      <c r="L18" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="182" t="n"/>
+      <c r="N18" s="183" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B19" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A19" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B19" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E19" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G19" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="182" t="n"/>
-      <c r="N19" s="183" t="n"/>
+      <c r="L19" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="175" t="n"/>
+      <c r="N19" s="176" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B20" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A20" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B20" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E20" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G20" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="189" t="n"/>
-      <c r="N20" s="190" t="n"/>
+      <c r="L20" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="182" t="n"/>
+      <c r="N20" s="183" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
       <c r="A21" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B21" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
       <c r="E21" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
       <c r="G21" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H21" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
       <c r="L21" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M21" s="189" t="n"/>
@@ -4142,244 +4154,244 @@
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B22" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A22" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B22" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E22" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G22" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="175" t="n"/>
-      <c r="N22" s="176" t="n"/>
+      <c r="L22" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="189" t="n"/>
+      <c r="N22" s="190" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B23" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A23" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B23" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E23" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G23" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="182" t="n"/>
-      <c r="N23" s="183" t="n"/>
+      <c r="L23" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="175" t="n"/>
+      <c r="N23" s="176" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B24" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A24" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B24" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E24" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G24" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="175" t="n"/>
-      <c r="N24" s="176" t="n"/>
+      <c r="L24" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="182" t="n"/>
+      <c r="N24" s="183" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B25" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A25" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B25" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E25" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G25" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="182" t="n"/>
-      <c r="N25" s="183" t="n"/>
+      <c r="L25" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="175" t="n"/>
+      <c r="N25" s="176" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B26" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A26" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B26" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E26" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G26" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="175" t="n"/>
-      <c r="N26" s="176" t="n"/>
+      <c r="L26" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="182" t="n"/>
+      <c r="N26" s="183" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B27" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A27" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B27" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E27" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G27" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="189" t="n"/>
-      <c r="N27" s="190" t="n"/>
+      <c r="L27" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="175" t="n"/>
+      <c r="N27" s="176" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
       <c r="A28" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B28" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
       <c r="E28" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
       <c r="G28" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H28" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
       <c r="L28" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M28" s="189" t="n"/>
@@ -4387,244 +4399,244 @@
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B29" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A29" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B29" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E29" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G29" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="182" t="n"/>
-      <c r="N29" s="183" t="n"/>
+      <c r="L29" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="189" t="n"/>
+      <c r="N29" s="190" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B30" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A30" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B30" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E30" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G30" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="175" t="n"/>
-      <c r="N30" s="176" t="n"/>
+      <c r="L30" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="182" t="n"/>
+      <c r="N30" s="183" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B31" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A31" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B31" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E31" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G31" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="182" t="n"/>
-      <c r="N31" s="183" t="n"/>
+      <c r="L31" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="175" t="n"/>
+      <c r="N31" s="176" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B32" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A32" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B32" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E32" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G32" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="175" t="n"/>
-      <c r="N32" s="176" t="n"/>
+      <c r="L32" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="182" t="n"/>
+      <c r="N32" s="183" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B33" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A33" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B33" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E33" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G33" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="182" t="n"/>
-      <c r="N33" s="183" t="n"/>
+      <c r="L33" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="175" t="n"/>
+      <c r="N33" s="176" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B34" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A34" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B34" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E34" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G34" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="189" t="n"/>
-      <c r="N34" s="190" t="n"/>
+      <c r="L34" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="182" t="n"/>
+      <c r="N34" s="183" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
       <c r="A35" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B35" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
       <c r="E35" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
       <c r="G35" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H35" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
       <c r="L35" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M35" s="189" t="n"/>
@@ -4632,244 +4644,244 @@
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B36" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A36" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B36" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E36" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G36" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="175" t="n"/>
-      <c r="N36" s="176" t="n"/>
+      <c r="L36" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="189" t="n"/>
+      <c r="N36" s="190" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B37" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A37" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B37" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E37" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G37" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="182" t="n"/>
-      <c r="N37" s="183" t="n"/>
+      <c r="L37" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="175" t="n"/>
+      <c r="N37" s="176" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B38" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A38" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B38" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E38" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G38" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="175" t="n"/>
-      <c r="N38" s="176" t="n"/>
+      <c r="L38" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="182" t="n"/>
+      <c r="N38" s="183" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B39" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A39" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B39" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E39" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G39" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="182" t="n"/>
-      <c r="N39" s="183" t="n"/>
+      <c r="L39" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="175" t="n"/>
+      <c r="N39" s="176" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B40" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A40" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B40" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E40" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G40" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="175" t="n"/>
-      <c r="N40" s="176" t="n"/>
+      <c r="L40" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="182" t="n"/>
+      <c r="N40" s="183" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B41" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A41" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B41" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E41" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G41" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="189" t="n"/>
-      <c r="N41" s="190" t="n"/>
+      <c r="L41" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="175" t="n"/>
+      <c r="N41" s="176" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
       <c r="A42" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B42" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
       <c r="E42" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
       <c r="G42" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H42" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
       <c r="L42" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M42" s="189" t="n"/>
@@ -4877,244 +4889,244 @@
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B43" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A43" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B43" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E43" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G43" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="182" t="n"/>
-      <c r="N43" s="183" t="n"/>
+      <c r="L43" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="189" t="n"/>
+      <c r="N43" s="190" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B44" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A44" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B44" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E44" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G44" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="175" t="n"/>
-      <c r="N44" s="176" t="n"/>
+      <c r="L44" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="182" t="n"/>
+      <c r="N44" s="183" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B45" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A45" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B45" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E45" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G45" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="182" t="n"/>
-      <c r="N45" s="183" t="n"/>
+      <c r="L45" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="175" t="n"/>
+      <c r="N45" s="176" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B46" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A46" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B46" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E46" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G46" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="175" t="n"/>
-      <c r="N46" s="176" t="n"/>
+      <c r="L46" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="182" t="n"/>
+      <c r="N46" s="183" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B47" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A47" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B47" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E47" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G47" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="182" t="n"/>
-      <c r="N47" s="183" t="n"/>
+      <c r="L47" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="175" t="n"/>
+      <c r="N47" s="176" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B48" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A48" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B48" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E48" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G48" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="189" t="n"/>
-      <c r="N48" s="190" t="n"/>
+      <c r="L48" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="182" t="n"/>
+      <c r="N48" s="183" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
       <c r="A49" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B49" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
       <c r="E49" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
       <c r="G49" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H49" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
       <c r="L49" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M49" s="189" t="n"/>
@@ -5122,244 +5134,244 @@
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B50" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A50" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B50" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E50" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G50" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="175" t="n"/>
-      <c r="N50" s="176" t="n"/>
+      <c r="L50" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="189" t="n"/>
+      <c r="N50" s="190" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B51" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A51" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B51" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E51" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G51" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="182" t="n"/>
-      <c r="N51" s="183" t="n"/>
+      <c r="L51" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="175" t="n"/>
+      <c r="N51" s="176" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B52" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A52" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B52" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E52" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G52" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="175" t="n"/>
-      <c r="N52" s="176" t="n"/>
+      <c r="L52" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="182" t="n"/>
+      <c r="N52" s="183" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B53" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A53" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B53" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E53" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G53" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="182" t="n"/>
-      <c r="N53" s="183" t="n"/>
+      <c r="L53" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="175" t="n"/>
+      <c r="N53" s="176" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B54" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A54" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B54" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E54" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G54" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="175" t="n"/>
-      <c r="N54" s="176" t="n"/>
+      <c r="L54" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="182" t="n"/>
+      <c r="N54" s="183" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B55" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A55" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B55" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E55" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G55" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="189" t="n"/>
-      <c r="N55" s="190" t="n"/>
+      <c r="L55" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="175" t="n"/>
+      <c r="N55" s="176" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
       <c r="A56" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B56" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
       <c r="E56" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
       <c r="G56" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H56" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
       <c r="L56" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M56" s="189" t="n"/>
@@ -5367,244 +5379,244 @@
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B57" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A57" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B57" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E57" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G57" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="182" t="n"/>
-      <c r="N57" s="183" t="n"/>
+      <c r="L57" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="189" t="n"/>
+      <c r="N57" s="190" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B58" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A58" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B58" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E58" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G58" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="175" t="n"/>
-      <c r="N58" s="176" t="n"/>
+      <c r="L58" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="182" t="n"/>
+      <c r="N58" s="183" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B59" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A59" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B59" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E59" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G59" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="182" t="n"/>
-      <c r="N59" s="183" t="n"/>
+      <c r="L59" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="175" t="n"/>
+      <c r="N59" s="176" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B60" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A60" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B60" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E60" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G60" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="175" t="n"/>
-      <c r="N60" s="176" t="n"/>
+      <c r="L60" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="182" t="n"/>
+      <c r="N60" s="183" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B61" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A61" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B61" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E61" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G61" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="182" t="n"/>
-      <c r="N61" s="183" t="n"/>
+      <c r="L61" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="175" t="n"/>
+      <c r="N61" s="176" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B62" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A62" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B62" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E62" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G62" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="189" t="n"/>
-      <c r="N62" s="190" t="n"/>
+      <c r="L62" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="182" t="n"/>
+      <c r="N62" s="183" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
       <c r="A63" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B63" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
       <c r="E63" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
       <c r="G63" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H63" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
       <c r="L63" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M63" s="189" t="n"/>
@@ -5612,184 +5624,202 @@
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B64" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A64" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B64" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E64" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G64" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="175" t="n"/>
-      <c r="N64" s="176" t="n"/>
+      <c r="L64" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="189" t="n"/>
+      <c r="N64" s="190" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B65" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A65" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B65" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E65" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G65" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="182" t="n"/>
-      <c r="N65" s="183" t="n"/>
+      <c r="L65" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="175" t="n"/>
+      <c r="N65" s="176" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B66" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A66" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B66" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E66" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G66" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="175" t="n"/>
-      <c r="N66" s="176" t="n"/>
+      <c r="L66" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="182" t="n"/>
+      <c r="N66" s="183" t="n"/>
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B67" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A67" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B67" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
-      <c r="E67" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E67" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
-      <c r="G67" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G67" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
-      <c r="L67" s="179">
+      <c r="L67" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="175" t="n"/>
+      <c r="N67" s="176" t="n"/>
+      <c r="O67" s="102" t="n"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" s="101">
+      <c r="A68" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B68" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C68" s="168" t="n"/>
+      <c r="D68" s="169" t="n"/>
+      <c r="E68" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F68" s="171" t="n"/>
+      <c r="G68" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I68" s="171" t="n"/>
+      <c r="J68" s="174" t="n"/>
+      <c r="K68" s="169" t="n"/>
+      <c r="L68" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M67" s="182" t="n"/>
-      <c r="N67" s="183" t="n"/>
-      <c r="O67" s="102" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="191" t="n">
+      <c r="M68" s="182" t="n"/>
+      <c r="N68" s="183" t="n"/>
+      <c r="O68" s="102" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="101">
+      <c r="A69" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B68" s="102" t="n"/>
-      <c r="C68" s="102" t="n"/>
-      <c r="D68" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E68" s="102" t="n"/>
-      <c r="F68" s="102" t="n"/>
-      <c r="G68" s="102" t="n"/>
-      <c r="H68" s="102" t="n"/>
-      <c r="I68" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J68" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K68" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L68" s="102" t="n"/>
-      <c r="M68" s="102" t="n"/>
-      <c r="N68" s="102" t="n"/>
-      <c r="O68" s="102" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="102" t="n"/>
       <c r="B69" s="102" t="n"/>
       <c r="C69" s="102" t="n"/>
-      <c r="D69" s="102" t="n"/>
+      <c r="D69" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E69" s="102" t="n"/>
       <c r="F69" s="102" t="n"/>
       <c r="G69" s="102" t="n"/>
       <c r="H69" s="102" t="n"/>
-      <c r="I69" s="102" t="n"/>
-      <c r="J69" s="102" t="n"/>
-      <c r="K69" s="102" t="n"/>
+      <c r="I69" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J69" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K69" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L69" s="102" t="n"/>
       <c r="M69" s="102" t="n"/>
       <c r="N69" s="102" t="n"/>
@@ -5845,6 +5875,23 @@
       <c r="M72" s="102" t="n"/>
       <c r="N72" s="102" t="n"/>
       <c r="O72" s="102" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="102" t="n"/>
+      <c r="B73" s="102" t="n"/>
+      <c r="C73" s="102" t="n"/>
+      <c r="D73" s="102" t="n"/>
+      <c r="E73" s="102" t="n"/>
+      <c r="F73" s="102" t="n"/>
+      <c r="G73" s="102" t="n"/>
+      <c r="H73" s="102" t="n"/>
+      <c r="I73" s="102" t="n"/>
+      <c r="J73" s="102" t="n"/>
+      <c r="K73" s="102" t="n"/>
+      <c r="L73" s="102" t="n"/>
+      <c r="M73" s="102" t="n"/>
+      <c r="N73" s="102" t="n"/>
+      <c r="O73" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -5921,7 +5968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="100" min="1" max="1"/>
@@ -5999,26 +6046,37 @@
       <c r="K3" s="102" t="n"/>
     </row>
     <row r="4" ht="21.75" customHeight="1" s="101">
-      <c r="A4" s="166" t="n">
+      <c r="A4" s="233" t="n">
+        <v>46090.80209267978</v>
+      </c>
+      <c r="B4" s="234" t="n">
+        <v>1.901</v>
+      </c>
+      <c r="C4" s="234" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="D4" s="234" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="E4" s="234" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="F4" s="234" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="G4" s="234" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="H4" s="234" t="n">
+        <v>1.748</v>
+      </c>
+      <c r="I4" s="235" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+    </row>
+    <row r="5" ht="21.75" customHeight="1" s="101">
+      <c r="A5" s="166" t="n">
         <v>45726</v>
-      </c>
-      <c r="B4" s="171" t="n"/>
-      <c r="C4" s="171" t="n"/>
-      <c r="D4" s="171" t="n"/>
-      <c r="E4" s="171" t="n"/>
-      <c r="F4" s="171" t="n"/>
-      <c r="G4" s="171" t="n"/>
-      <c r="H4" s="171" t="n"/>
-      <c r="I4" s="173">
-        <f>IF(AND(B4&lt;&gt;"",H4&lt;&gt;"",H4&lt;&gt;0),(B4-H4)/H4,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="175" t="n"/>
-      <c r="K4" s="102" t="n"/>
-    </row>
-    <row r="5" ht="21.75" customHeight="1" s="101">
-      <c r="A5" s="177" t="n">
-        <v>45719</v>
       </c>
       <c r="B5" s="171" t="n"/>
       <c r="C5" s="171" t="n"/>
@@ -6027,16 +6085,16 @@
       <c r="F5" s="171" t="n"/>
       <c r="G5" s="171" t="n"/>
       <c r="H5" s="171" t="n"/>
-      <c r="I5" s="181">
-        <f>IF(AND(B5&lt;&gt;"",H5&lt;&gt;"",H5&lt;&gt;0),(B5-H5)/H5,"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="182" t="n"/>
+      <c r="I5" s="173">
+        <f>IF(AND(B4&lt;&gt;"",H4&lt;&gt;"",H4&lt;&gt;0),(B4-H4)/H4,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="175" t="n"/>
       <c r="K5" s="102" t="n"/>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="166" t="n">
-        <v>45712</v>
+      <c r="A6" s="177" t="n">
+        <v>45719</v>
       </c>
       <c r="B6" s="171" t="n"/>
       <c r="C6" s="171" t="n"/>
@@ -6045,16 +6103,16 @@
       <c r="F6" s="171" t="n"/>
       <c r="G6" s="171" t="n"/>
       <c r="H6" s="171" t="n"/>
-      <c r="I6" s="173">
-        <f>IF(AND(B6&lt;&gt;"",H6&lt;&gt;"",H6&lt;&gt;0),(B6-H6)/H6,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="175" t="n"/>
+      <c r="I6" s="181">
+        <f>IF(AND(B5&lt;&gt;"",H5&lt;&gt;"",H5&lt;&gt;0),(B5-H5)/H5,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="182" t="n"/>
       <c r="K6" s="102" t="n"/>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="177" t="n">
-        <v>45705</v>
+      <c r="A7" s="166" t="n">
+        <v>45712</v>
       </c>
       <c r="B7" s="171" t="n"/>
       <c r="C7" s="171" t="n"/>
@@ -6063,16 +6121,16 @@
       <c r="F7" s="171" t="n"/>
       <c r="G7" s="171" t="n"/>
       <c r="H7" s="171" t="n"/>
-      <c r="I7" s="181">
-        <f>IF(AND(B7&lt;&gt;"",H7&lt;&gt;"",H7&lt;&gt;0),(B7-H7)/H7,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="182" t="n"/>
+      <c r="I7" s="173">
+        <f>IF(AND(B6&lt;&gt;"",H6&lt;&gt;"",H6&lt;&gt;0),(B6-H6)/H6,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="175" t="n"/>
       <c r="K7" s="102" t="n"/>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="166" t="n">
-        <v>45698</v>
+      <c r="A8" s="177" t="n">
+        <v>45705</v>
       </c>
       <c r="B8" s="171" t="n"/>
       <c r="C8" s="171" t="n"/>
@@ -6081,16 +6139,16 @@
       <c r="F8" s="171" t="n"/>
       <c r="G8" s="171" t="n"/>
       <c r="H8" s="171" t="n"/>
-      <c r="I8" s="173">
-        <f>IF(AND(B8&lt;&gt;"",H8&lt;&gt;"",H8&lt;&gt;0),(B8-H8)/H8,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="175" t="n"/>
+      <c r="I8" s="181">
+        <f>IF(AND(B7&lt;&gt;"",H7&lt;&gt;"",H7&lt;&gt;0),(B7-H7)/H7,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="182" t="n"/>
       <c r="K8" s="102" t="n"/>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="177" t="n">
-        <v>45691</v>
+      <c r="A9" s="166" t="n">
+        <v>45698</v>
       </c>
       <c r="B9" s="171" t="n"/>
       <c r="C9" s="171" t="n"/>
@@ -6099,16 +6157,16 @@
       <c r="F9" s="171" t="n"/>
       <c r="G9" s="171" t="n"/>
       <c r="H9" s="171" t="n"/>
-      <c r="I9" s="181">
-        <f>IF(AND(B9&lt;&gt;"",H9&lt;&gt;"",H9&lt;&gt;0),(B9-H9)/H9,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="182" t="n"/>
+      <c r="I9" s="173">
+        <f>IF(AND(B8&lt;&gt;"",H8&lt;&gt;"",H8&lt;&gt;0),(B8-H8)/H8,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="175" t="n"/>
       <c r="K9" s="102" t="n"/>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="166" t="n">
-        <v>45684</v>
+      <c r="A10" s="177" t="n">
+        <v>45691</v>
       </c>
       <c r="B10" s="171" t="n"/>
       <c r="C10" s="171" t="n"/>
@@ -6117,16 +6175,16 @@
       <c r="F10" s="171" t="n"/>
       <c r="G10" s="171" t="n"/>
       <c r="H10" s="171" t="n"/>
-      <c r="I10" s="173">
-        <f>IF(AND(B10&lt;&gt;"",H10&lt;&gt;"",H10&lt;&gt;0),(B10-H10)/H10,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="175" t="n"/>
+      <c r="I10" s="181">
+        <f>IF(AND(B9&lt;&gt;"",H9&lt;&gt;"",H9&lt;&gt;0),(B9-H9)/H9,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="182" t="n"/>
       <c r="K10" s="102" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="177" t="n">
-        <v>45677</v>
+      <c r="A11" s="166" t="n">
+        <v>45684</v>
       </c>
       <c r="B11" s="171" t="n"/>
       <c r="C11" s="171" t="n"/>
@@ -6135,16 +6193,16 @@
       <c r="F11" s="171" t="n"/>
       <c r="G11" s="171" t="n"/>
       <c r="H11" s="171" t="n"/>
-      <c r="I11" s="181">
-        <f>IF(AND(B11&lt;&gt;"",H11&lt;&gt;"",H11&lt;&gt;0),(B11-H11)/H11,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="182" t="n"/>
+      <c r="I11" s="173">
+        <f>IF(AND(B10&lt;&gt;"",H10&lt;&gt;"",H10&lt;&gt;0),(B10-H10)/H10,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="175" t="n"/>
       <c r="K11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="166" t="n">
-        <v>45670</v>
+      <c r="A12" s="177" t="n">
+        <v>45677</v>
       </c>
       <c r="B12" s="171" t="n"/>
       <c r="C12" s="171" t="n"/>
@@ -6153,16 +6211,16 @@
       <c r="F12" s="171" t="n"/>
       <c r="G12" s="171" t="n"/>
       <c r="H12" s="171" t="n"/>
-      <c r="I12" s="173">
-        <f>IF(AND(B12&lt;&gt;"",H12&lt;&gt;"",H12&lt;&gt;0),(B12-H12)/H12,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="175" t="n"/>
+      <c r="I12" s="181">
+        <f>IF(AND(B11&lt;&gt;"",H11&lt;&gt;"",H11&lt;&gt;0),(B11-H11)/H11,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="182" t="n"/>
       <c r="K12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="177" t="n">
-        <v>45663</v>
+      <c r="A13" s="166" t="n">
+        <v>45670</v>
       </c>
       <c r="B13" s="171" t="n"/>
       <c r="C13" s="171" t="n"/>
@@ -6171,16 +6229,16 @@
       <c r="F13" s="171" t="n"/>
       <c r="G13" s="171" t="n"/>
       <c r="H13" s="171" t="n"/>
-      <c r="I13" s="181">
-        <f>IF(AND(B13&lt;&gt;"",H13&lt;&gt;"",H13&lt;&gt;0),(B13-H13)/H13,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="182" t="n"/>
+      <c r="I13" s="173">
+        <f>IF(AND(B12&lt;&gt;"",H12&lt;&gt;"",H12&lt;&gt;0),(B12-H12)/H12,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="175" t="n"/>
       <c r="K13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="166" t="n">
-        <v>45656</v>
+      <c r="A14" s="177" t="n">
+        <v>45663</v>
       </c>
       <c r="B14" s="171" t="n"/>
       <c r="C14" s="171" t="n"/>
@@ -6189,16 +6247,16 @@
       <c r="F14" s="171" t="n"/>
       <c r="G14" s="171" t="n"/>
       <c r="H14" s="171" t="n"/>
-      <c r="I14" s="173">
-        <f>IF(AND(B14&lt;&gt;"",H14&lt;&gt;"",H14&lt;&gt;0),(B14-H14)/H14,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="175" t="n"/>
+      <c r="I14" s="181">
+        <f>IF(AND(B13&lt;&gt;"",H13&lt;&gt;"",H13&lt;&gt;0),(B13-H13)/H13,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="182" t="n"/>
       <c r="K14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="177" t="n">
-        <v>45649</v>
+      <c r="A15" s="166" t="n">
+        <v>45656</v>
       </c>
       <c r="B15" s="171" t="n"/>
       <c r="C15" s="171" t="n"/>
@@ -6207,16 +6265,16 @@
       <c r="F15" s="171" t="n"/>
       <c r="G15" s="171" t="n"/>
       <c r="H15" s="171" t="n"/>
-      <c r="I15" s="181">
-        <f>IF(AND(B15&lt;&gt;"",H15&lt;&gt;"",H15&lt;&gt;0),(B15-H15)/H15,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="182" t="n"/>
+      <c r="I15" s="173">
+        <f>IF(AND(B14&lt;&gt;"",H14&lt;&gt;"",H14&lt;&gt;0),(B14-H14)/H14,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="175" t="n"/>
       <c r="K15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="166" t="n">
-        <v>45642</v>
+      <c r="A16" s="177" t="n">
+        <v>45649</v>
       </c>
       <c r="B16" s="171" t="n"/>
       <c r="C16" s="171" t="n"/>
@@ -6225,16 +6283,16 @@
       <c r="F16" s="171" t="n"/>
       <c r="G16" s="171" t="n"/>
       <c r="H16" s="171" t="n"/>
-      <c r="I16" s="173">
-        <f>IF(AND(B16&lt;&gt;"",H16&lt;&gt;"",H16&lt;&gt;0),(B16-H16)/H16,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="175" t="n"/>
+      <c r="I16" s="181">
+        <f>IF(AND(B15&lt;&gt;"",H15&lt;&gt;"",H15&lt;&gt;0),(B15-H15)/H15,"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="182" t="n"/>
       <c r="K16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="177" t="n">
-        <v>45635</v>
+      <c r="A17" s="166" t="n">
+        <v>45642</v>
       </c>
       <c r="B17" s="171" t="n"/>
       <c r="C17" s="171" t="n"/>
@@ -6243,16 +6301,16 @@
       <c r="F17" s="171" t="n"/>
       <c r="G17" s="171" t="n"/>
       <c r="H17" s="171" t="n"/>
-      <c r="I17" s="181">
-        <f>IF(AND(B17&lt;&gt;"",H17&lt;&gt;"",H17&lt;&gt;0),(B17-H17)/H17,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="182" t="n"/>
+      <c r="I17" s="173">
+        <f>IF(AND(B16&lt;&gt;"",H16&lt;&gt;"",H16&lt;&gt;0),(B16-H16)/H16,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="175" t="n"/>
       <c r="K17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="166" t="n">
-        <v>45628</v>
+      <c r="A18" s="177" t="n">
+        <v>45635</v>
       </c>
       <c r="B18" s="171" t="n"/>
       <c r="C18" s="171" t="n"/>
@@ -6261,16 +6319,16 @@
       <c r="F18" s="171" t="n"/>
       <c r="G18" s="171" t="n"/>
       <c r="H18" s="171" t="n"/>
-      <c r="I18" s="173">
-        <f>IF(AND(B18&lt;&gt;"",H18&lt;&gt;"",H18&lt;&gt;0),(B18-H18)/H18,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="175" t="n"/>
+      <c r="I18" s="181">
+        <f>IF(AND(B17&lt;&gt;"",H17&lt;&gt;"",H17&lt;&gt;0),(B17-H17)/H17,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="182" t="n"/>
       <c r="K18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="177" t="n">
-        <v>45621</v>
+      <c r="A19" s="166" t="n">
+        <v>45628</v>
       </c>
       <c r="B19" s="171" t="n"/>
       <c r="C19" s="171" t="n"/>
@@ -6279,16 +6337,16 @@
       <c r="F19" s="171" t="n"/>
       <c r="G19" s="171" t="n"/>
       <c r="H19" s="171" t="n"/>
-      <c r="I19" s="181">
-        <f>IF(AND(B19&lt;&gt;"",H19&lt;&gt;"",H19&lt;&gt;0),(B19-H19)/H19,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="182" t="n"/>
+      <c r="I19" s="173">
+        <f>IF(AND(B18&lt;&gt;"",H18&lt;&gt;"",H18&lt;&gt;0),(B18-H18)/H18,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="175" t="n"/>
       <c r="K19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="166" t="n">
-        <v>45614</v>
+      <c r="A20" s="177" t="n">
+        <v>45621</v>
       </c>
       <c r="B20" s="171" t="n"/>
       <c r="C20" s="171" t="n"/>
@@ -6297,16 +6355,16 @@
       <c r="F20" s="171" t="n"/>
       <c r="G20" s="171" t="n"/>
       <c r="H20" s="171" t="n"/>
-      <c r="I20" s="173">
-        <f>IF(AND(B20&lt;&gt;"",H20&lt;&gt;"",H20&lt;&gt;0),(B20-H20)/H20,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="175" t="n"/>
+      <c r="I20" s="181">
+        <f>IF(AND(B19&lt;&gt;"",H19&lt;&gt;"",H19&lt;&gt;0),(B19-H19)/H19,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="182" t="n"/>
       <c r="K20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="177" t="n">
-        <v>45607</v>
+      <c r="A21" s="166" t="n">
+        <v>45614</v>
       </c>
       <c r="B21" s="171" t="n"/>
       <c r="C21" s="171" t="n"/>
@@ -6315,16 +6373,16 @@
       <c r="F21" s="171" t="n"/>
       <c r="G21" s="171" t="n"/>
       <c r="H21" s="171" t="n"/>
-      <c r="I21" s="181">
-        <f>IF(AND(B21&lt;&gt;"",H21&lt;&gt;"",H21&lt;&gt;0),(B21-H21)/H21,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="182" t="n"/>
+      <c r="I21" s="173">
+        <f>IF(AND(B20&lt;&gt;"",H20&lt;&gt;"",H20&lt;&gt;0),(B20-H20)/H20,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="175" t="n"/>
       <c r="K21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="166" t="n">
-        <v>45600</v>
+      <c r="A22" s="177" t="n">
+        <v>45607</v>
       </c>
       <c r="B22" s="171" t="n"/>
       <c r="C22" s="171" t="n"/>
@@ -6333,16 +6391,16 @@
       <c r="F22" s="171" t="n"/>
       <c r="G22" s="171" t="n"/>
       <c r="H22" s="171" t="n"/>
-      <c r="I22" s="173">
-        <f>IF(AND(B22&lt;&gt;"",H22&lt;&gt;"",H22&lt;&gt;0),(B22-H22)/H22,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="175" t="n"/>
+      <c r="I22" s="181">
+        <f>IF(AND(B21&lt;&gt;"",H21&lt;&gt;"",H21&lt;&gt;0),(B21-H21)/H21,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="182" t="n"/>
       <c r="K22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="177" t="n">
-        <v>45593</v>
+      <c r="A23" s="166" t="n">
+        <v>45600</v>
       </c>
       <c r="B23" s="171" t="n"/>
       <c r="C23" s="171" t="n"/>
@@ -6351,16 +6409,16 @@
       <c r="F23" s="171" t="n"/>
       <c r="G23" s="171" t="n"/>
       <c r="H23" s="171" t="n"/>
-      <c r="I23" s="181">
-        <f>IF(AND(B23&lt;&gt;"",H23&lt;&gt;"",H23&lt;&gt;0),(B23-H23)/H23,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="182" t="n"/>
+      <c r="I23" s="173">
+        <f>IF(AND(B22&lt;&gt;"",H22&lt;&gt;"",H22&lt;&gt;0),(B22-H22)/H22,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="175" t="n"/>
       <c r="K23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="166" t="n">
-        <v>45586</v>
+      <c r="A24" s="177" t="n">
+        <v>45593</v>
       </c>
       <c r="B24" s="171" t="n"/>
       <c r="C24" s="171" t="n"/>
@@ -6369,16 +6427,16 @@
       <c r="F24" s="171" t="n"/>
       <c r="G24" s="171" t="n"/>
       <c r="H24" s="171" t="n"/>
-      <c r="I24" s="173">
-        <f>IF(AND(B24&lt;&gt;"",H24&lt;&gt;"",H24&lt;&gt;0),(B24-H24)/H24,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="175" t="n"/>
+      <c r="I24" s="181">
+        <f>IF(AND(B23&lt;&gt;"",H23&lt;&gt;"",H23&lt;&gt;0),(B23-H23)/H23,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="182" t="n"/>
       <c r="K24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="177" t="n">
-        <v>45579</v>
+      <c r="A25" s="166" t="n">
+        <v>45586</v>
       </c>
       <c r="B25" s="171" t="n"/>
       <c r="C25" s="171" t="n"/>
@@ -6387,16 +6445,16 @@
       <c r="F25" s="171" t="n"/>
       <c r="G25" s="171" t="n"/>
       <c r="H25" s="171" t="n"/>
-      <c r="I25" s="181">
-        <f>IF(AND(B25&lt;&gt;"",H25&lt;&gt;"",H25&lt;&gt;0),(B25-H25)/H25,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="182" t="n"/>
+      <c r="I25" s="173">
+        <f>IF(AND(B24&lt;&gt;"",H24&lt;&gt;"",H24&lt;&gt;0),(B24-H24)/H24,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="175" t="n"/>
       <c r="K25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="166" t="n">
-        <v>45572</v>
+      <c r="A26" s="177" t="n">
+        <v>45579</v>
       </c>
       <c r="B26" s="171" t="n"/>
       <c r="C26" s="171" t="n"/>
@@ -6405,16 +6463,16 @@
       <c r="F26" s="171" t="n"/>
       <c r="G26" s="171" t="n"/>
       <c r="H26" s="171" t="n"/>
-      <c r="I26" s="173">
-        <f>IF(AND(B26&lt;&gt;"",H26&lt;&gt;"",H26&lt;&gt;0),(B26-H26)/H26,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="175" t="n"/>
+      <c r="I26" s="181">
+        <f>IF(AND(B25&lt;&gt;"",H25&lt;&gt;"",H25&lt;&gt;0),(B25-H25)/H25,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="182" t="n"/>
       <c r="K26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="177" t="n">
-        <v>45565</v>
+      <c r="A27" s="166" t="n">
+        <v>45572</v>
       </c>
       <c r="B27" s="171" t="n"/>
       <c r="C27" s="171" t="n"/>
@@ -6423,16 +6481,16 @@
       <c r="F27" s="171" t="n"/>
       <c r="G27" s="171" t="n"/>
       <c r="H27" s="171" t="n"/>
-      <c r="I27" s="181">
-        <f>IF(AND(B27&lt;&gt;"",H27&lt;&gt;"",H27&lt;&gt;0),(B27-H27)/H27,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="182" t="n"/>
+      <c r="I27" s="173">
+        <f>IF(AND(B26&lt;&gt;"",H26&lt;&gt;"",H26&lt;&gt;0),(B26-H26)/H26,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="175" t="n"/>
       <c r="K27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="166" t="n">
-        <v>45558</v>
+      <c r="A28" s="177" t="n">
+        <v>45565</v>
       </c>
       <c r="B28" s="171" t="n"/>
       <c r="C28" s="171" t="n"/>
@@ -6441,16 +6499,16 @@
       <c r="F28" s="171" t="n"/>
       <c r="G28" s="171" t="n"/>
       <c r="H28" s="171" t="n"/>
-      <c r="I28" s="173">
-        <f>IF(AND(B28&lt;&gt;"",H28&lt;&gt;"",H28&lt;&gt;0),(B28-H28)/H28,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="175" t="n"/>
+      <c r="I28" s="181">
+        <f>IF(AND(B27&lt;&gt;"",H27&lt;&gt;"",H27&lt;&gt;0),(B27-H27)/H27,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="182" t="n"/>
       <c r="K28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="177" t="n">
-        <v>45551</v>
+      <c r="A29" s="166" t="n">
+        <v>45558</v>
       </c>
       <c r="B29" s="171" t="n"/>
       <c r="C29" s="171" t="n"/>
@@ -6459,16 +6517,16 @@
       <c r="F29" s="171" t="n"/>
       <c r="G29" s="171" t="n"/>
       <c r="H29" s="171" t="n"/>
-      <c r="I29" s="181">
-        <f>IF(AND(B29&lt;&gt;"",H29&lt;&gt;"",H29&lt;&gt;0),(B29-H29)/H29,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="182" t="n"/>
+      <c r="I29" s="173">
+        <f>IF(AND(B28&lt;&gt;"",H28&lt;&gt;"",H28&lt;&gt;0),(B28-H28)/H28,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="175" t="n"/>
       <c r="K29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="166" t="n">
-        <v>45544</v>
+      <c r="A30" s="177" t="n">
+        <v>45551</v>
       </c>
       <c r="B30" s="171" t="n"/>
       <c r="C30" s="171" t="n"/>
@@ -6477,16 +6535,16 @@
       <c r="F30" s="171" t="n"/>
       <c r="G30" s="171" t="n"/>
       <c r="H30" s="171" t="n"/>
-      <c r="I30" s="173">
-        <f>IF(AND(B30&lt;&gt;"",H30&lt;&gt;"",H30&lt;&gt;0),(B30-H30)/H30,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="175" t="n"/>
+      <c r="I30" s="181">
+        <f>IF(AND(B29&lt;&gt;"",H29&lt;&gt;"",H29&lt;&gt;0),(B29-H29)/H29,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="182" t="n"/>
       <c r="K30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="177" t="n">
-        <v>45537</v>
+      <c r="A31" s="166" t="n">
+        <v>45544</v>
       </c>
       <c r="B31" s="171" t="n"/>
       <c r="C31" s="171" t="n"/>
@@ -6495,16 +6553,16 @@
       <c r="F31" s="171" t="n"/>
       <c r="G31" s="171" t="n"/>
       <c r="H31" s="171" t="n"/>
-      <c r="I31" s="181">
-        <f>IF(AND(B31&lt;&gt;"",H31&lt;&gt;"",H31&lt;&gt;0),(B31-H31)/H31,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="182" t="n"/>
+      <c r="I31" s="173">
+        <f>IF(AND(B30&lt;&gt;"",H30&lt;&gt;"",H30&lt;&gt;0),(B30-H30)/H30,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="175" t="n"/>
       <c r="K31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="166" t="n">
-        <v>45530</v>
+      <c r="A32" s="177" t="n">
+        <v>45537</v>
       </c>
       <c r="B32" s="171" t="n"/>
       <c r="C32" s="171" t="n"/>
@@ -6513,16 +6571,16 @@
       <c r="F32" s="171" t="n"/>
       <c r="G32" s="171" t="n"/>
       <c r="H32" s="171" t="n"/>
-      <c r="I32" s="173">
-        <f>IF(AND(B32&lt;&gt;"",H32&lt;&gt;"",H32&lt;&gt;0),(B32-H32)/H32,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="175" t="n"/>
+      <c r="I32" s="181">
+        <f>IF(AND(B31&lt;&gt;"",H31&lt;&gt;"",H31&lt;&gt;0),(B31-H31)/H31,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="182" t="n"/>
       <c r="K32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="177" t="n">
-        <v>45523</v>
+      <c r="A33" s="166" t="n">
+        <v>45530</v>
       </c>
       <c r="B33" s="171" t="n"/>
       <c r="C33" s="171" t="n"/>
@@ -6531,24 +6589,29 @@
       <c r="F33" s="171" t="n"/>
       <c r="G33" s="171" t="n"/>
       <c r="H33" s="171" t="n"/>
-      <c r="I33" s="181">
+      <c r="I33" s="173">
+        <f>IF(AND(B32&lt;&gt;"",H32&lt;&gt;"",H32&lt;&gt;0),(B32-H32)/H32,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="175" t="n"/>
+      <c r="K33" s="102" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="101">
+      <c r="A34" s="177" t="n">
+        <v>45523</v>
+      </c>
+      <c r="B34" s="171" t="n"/>
+      <c r="C34" s="171" t="n"/>
+      <c r="D34" s="171" t="n"/>
+      <c r="E34" s="171" t="n"/>
+      <c r="F34" s="171" t="n"/>
+      <c r="G34" s="171" t="n"/>
+      <c r="H34" s="171" t="n"/>
+      <c r="I34" s="181">
         <f>IF(AND(B33&lt;&gt;"",H33&lt;&gt;"",H33&lt;&gt;0),(B33-H33)/H33,"")</f>
         <v/>
       </c>
-      <c r="J33" s="182" t="n"/>
-      <c r="K33" s="102" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="101">
-      <c r="A34" s="102" t="n"/>
-      <c r="B34" s="102" t="n"/>
-      <c r="C34" s="102" t="n"/>
-      <c r="D34" s="102" t="n"/>
-      <c r="E34" s="102" t="n"/>
-      <c r="F34" s="102" t="n"/>
-      <c r="G34" s="102" t="n"/>
-      <c r="H34" s="102" t="n"/>
-      <c r="I34" s="102" t="n"/>
-      <c r="J34" s="102" t="n"/>
+      <c r="J34" s="182" t="n"/>
       <c r="K34" s="102" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1" s="101">
@@ -6615,6 +6678,19 @@
       <c r="I39" s="102" t="n"/>
       <c r="J39" s="102" t="n"/>
       <c r="K39" s="102" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="102" t="n"/>
+      <c r="B40" s="102" t="n"/>
+      <c r="C40" s="102" t="n"/>
+      <c r="D40" s="102" t="n"/>
+      <c r="E40" s="102" t="n"/>
+      <c r="F40" s="102" t="n"/>
+      <c r="G40" s="102" t="n"/>
+      <c r="H40" s="102" t="n"/>
+      <c r="I40" s="102" t="n"/>
+      <c r="J40" s="102" t="n"/>
+      <c r="K40" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3364,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.80209267978</v>
+        <v>46093.82300822704</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46093.80209268518</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3560,19 +3560,13 @@
         <v>4.2578</v>
       </c>
       <c r="E6" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F6" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G6" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H6" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F6" s="227" t="n"/>
+      <c r="G6" s="228" t="n"/>
+      <c r="H6" s="229" t="n"/>
       <c r="I6" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J6" s="230" t="n">
         <v>20.49</v>
@@ -3581,11 +3575,11 @@
         <v>10.7108</v>
       </c>
       <c r="L6" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M6" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N6" s="232" t="inlineStr">
@@ -3596,7 +3590,7 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
       <c r="A7" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B7" s="223" t="inlineStr">
         <is>
@@ -3609,20 +3603,17 @@
       <c r="D7" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E7" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E7" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F7" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G7" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G7" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H7" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I7" s="227" t="n">
         <v>2.086</v>
@@ -3633,310 +3624,328 @@
       <c r="K7" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L7" s="226">
+      <c r="L7" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M7" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N7" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.75" customHeight="1" s="101">
+      <c r="A8" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B8" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C8" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D8" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E8" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G8" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J8" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K8" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L8" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M7" s="231" t="inlineStr">
+      <c r="M8" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N7" s="232" t="inlineStr">
+      <c r="N8" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="211" t="n">
+    <row r="9" ht="21.75" customHeight="1" s="101">
+      <c r="A9" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B8" s="212" t="inlineStr">
+      <c r="B9" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C8" s="213" t="n"/>
-      <c r="D8" s="214" t="n">
+      <c r="C9" s="213" t="n"/>
+      <c r="D9" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E8" s="215">
+      <c r="E9" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F8" s="216" t="n"/>
-      <c r="G8" s="217">
+      <c r="F9" s="216" t="n"/>
+      <c r="G9" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H8" s="218">
+      <c r="H9" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I8" s="216" t="n">
+      <c r="I9" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J8" s="219" t="n">
+      <c r="J9" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K8" s="214" t="n">
+      <c r="K9" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L8" s="215">
+      <c r="L9" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M8" s="220" t="inlineStr">
+      <c r="M9" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N8" s="221" t="inlineStr">
+      <c r="N9" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="166" t="n">
+    <row r="10" ht="21.75" customHeight="1" s="101">
+      <c r="A10" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B9" s="167" t="inlineStr">
+      <c r="B10" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C9" s="168" t="n"/>
-      <c r="D9" s="169" t="n"/>
-      <c r="E9" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="171" t="n"/>
-      <c r="G9" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I9" s="171" t="n"/>
-      <c r="J9" s="174" t="n"/>
-      <c r="K9" s="169" t="n"/>
-      <c r="L9" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="175" t="n"/>
-      <c r="N9" s="176" t="n"/>
-      <c r="O9" s="102" t="n"/>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B10" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C10" s="168" t="n"/>
       <c r="D10" s="169" t="n"/>
-      <c r="E10" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E10" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F10" s="171" t="n"/>
-      <c r="G10" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G10" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I10" s="171" t="n"/>
       <c r="J10" s="174" t="n"/>
       <c r="K10" s="169" t="n"/>
-      <c r="L10" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="182" t="n"/>
-      <c r="N10" s="183" t="n"/>
+      <c r="L10" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="175" t="n"/>
+      <c r="N10" s="176" t="n"/>
       <c r="O10" s="102" t="n"/>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B11" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A11" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B11" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C11" s="168" t="n"/>
       <c r="D11" s="169" t="n"/>
-      <c r="E11" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E11" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
-      <c r="G11" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G11" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I11" s="171" t="n"/>
       <c r="J11" s="174" t="n"/>
       <c r="K11" s="169" t="n"/>
-      <c r="L11" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="175" t="n"/>
-      <c r="N11" s="176" t="n"/>
+      <c r="L11" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="182" t="n"/>
+      <c r="N11" s="183" t="n"/>
       <c r="O11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B12" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A12" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B12" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
-      <c r="E12" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E12" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G12" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
-      <c r="L12" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="182" t="n"/>
-      <c r="N12" s="183" t="n"/>
+      <c r="L12" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="175" t="n"/>
+      <c r="N12" s="176" t="n"/>
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B13" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A13" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B13" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E13" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G13" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="175" t="n"/>
-      <c r="N13" s="176" t="n"/>
+      <c r="L13" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="182" t="n"/>
+      <c r="N13" s="183" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B14" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A14" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B14" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E14" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G14" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="189" t="n"/>
-      <c r="N14" s="190" t="n"/>
+      <c r="L14" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="176" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
       <c r="A15" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B15" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
       <c r="E15" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
       <c r="G15" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H15" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
       <c r="L15" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M15" s="189" t="n"/>
@@ -3944,244 +3953,244 @@
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B16" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A16" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B16" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E16" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G16" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="182" t="n"/>
-      <c r="N16" s="183" t="n"/>
+      <c r="L16" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="189" t="n"/>
+      <c r="N16" s="190" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B17" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A17" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B17" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E17" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G17" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="175" t="n"/>
-      <c r="N17" s="176" t="n"/>
+      <c r="L17" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="182" t="n"/>
+      <c r="N17" s="183" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B18" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A18" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B18" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E18" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G18" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="182" t="n"/>
-      <c r="N18" s="183" t="n"/>
+      <c r="L18" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="175" t="n"/>
+      <c r="N18" s="176" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B19" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A19" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B19" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E19" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G19" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="175" t="n"/>
-      <c r="N19" s="176" t="n"/>
+      <c r="L19" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="182" t="n"/>
+      <c r="N19" s="183" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B20" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A20" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B20" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E20" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G20" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="182" t="n"/>
-      <c r="N20" s="183" t="n"/>
+      <c r="L20" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="175" t="n"/>
+      <c r="N20" s="176" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B21" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A21" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B21" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E21" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G21" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="189" t="n"/>
-      <c r="N21" s="190" t="n"/>
+      <c r="L21" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="182" t="n"/>
+      <c r="N21" s="183" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
       <c r="A22" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B22" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
       <c r="E22" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
       <c r="G22" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H22" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
       <c r="L22" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M22" s="189" t="n"/>
@@ -4189,244 +4198,244 @@
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B23" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A23" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B23" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E23" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G23" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="175" t="n"/>
-      <c r="N23" s="176" t="n"/>
+      <c r="L23" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="189" t="n"/>
+      <c r="N23" s="190" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B24" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A24" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E24" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G24" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="182" t="n"/>
-      <c r="N24" s="183" t="n"/>
+      <c r="L24" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="175" t="n"/>
+      <c r="N24" s="176" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B25" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A25" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B25" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E25" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G25" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="175" t="n"/>
-      <c r="N25" s="176" t="n"/>
+      <c r="L25" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="182" t="n"/>
+      <c r="N25" s="183" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B26" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A26" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B26" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E26" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G26" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="182" t="n"/>
-      <c r="N26" s="183" t="n"/>
+      <c r="L26" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="175" t="n"/>
+      <c r="N26" s="176" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B27" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A27" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B27" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E27" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G27" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="175" t="n"/>
-      <c r="N27" s="176" t="n"/>
+      <c r="L27" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="182" t="n"/>
+      <c r="N27" s="183" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B28" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A28" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B28" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E28" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G28" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="189" t="n"/>
-      <c r="N28" s="190" t="n"/>
+      <c r="L28" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="175" t="n"/>
+      <c r="N28" s="176" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
       <c r="A29" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B29" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
       <c r="E29" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
       <c r="G29" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H29" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
       <c r="L29" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M29" s="189" t="n"/>
@@ -4434,244 +4443,244 @@
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B30" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A30" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B30" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E30" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G30" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="182" t="n"/>
-      <c r="N30" s="183" t="n"/>
+      <c r="L30" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="189" t="n"/>
+      <c r="N30" s="190" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B31" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A31" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B31" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E31" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G31" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="175" t="n"/>
-      <c r="N31" s="176" t="n"/>
+      <c r="L31" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="182" t="n"/>
+      <c r="N31" s="183" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B32" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A32" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B32" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E32" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G32" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="182" t="n"/>
-      <c r="N32" s="183" t="n"/>
+      <c r="L32" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="175" t="n"/>
+      <c r="N32" s="176" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B33" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A33" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B33" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E33" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G33" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="175" t="n"/>
-      <c r="N33" s="176" t="n"/>
+      <c r="L33" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="182" t="n"/>
+      <c r="N33" s="183" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B34" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A34" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B34" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E34" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G34" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="182" t="n"/>
-      <c r="N34" s="183" t="n"/>
+      <c r="L34" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="175" t="n"/>
+      <c r="N34" s="176" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B35" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A35" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B35" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E35" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G35" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="189" t="n"/>
-      <c r="N35" s="190" t="n"/>
+      <c r="L35" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="182" t="n"/>
+      <c r="N35" s="183" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
       <c r="A36" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B36" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
       <c r="E36" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
       <c r="G36" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H36" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
       <c r="L36" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M36" s="189" t="n"/>
@@ -4679,244 +4688,244 @@
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B37" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A37" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B37" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E37" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G37" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="175" t="n"/>
-      <c r="N37" s="176" t="n"/>
+      <c r="L37" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="189" t="n"/>
+      <c r="N37" s="190" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B38" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A38" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B38" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E38" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G38" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="182" t="n"/>
-      <c r="N38" s="183" t="n"/>
+      <c r="L38" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="175" t="n"/>
+      <c r="N38" s="176" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B39" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A39" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B39" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E39" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G39" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="175" t="n"/>
-      <c r="N39" s="176" t="n"/>
+      <c r="L39" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="182" t="n"/>
+      <c r="N39" s="183" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B40" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A40" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B40" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E40" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G40" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="182" t="n"/>
-      <c r="N40" s="183" t="n"/>
+      <c r="L40" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="175" t="n"/>
+      <c r="N40" s="176" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B41" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A41" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B41" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E41" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G41" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="175" t="n"/>
-      <c r="N41" s="176" t="n"/>
+      <c r="L41" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="182" t="n"/>
+      <c r="N41" s="183" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B42" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A42" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B42" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E42" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G42" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="189" t="n"/>
-      <c r="N42" s="190" t="n"/>
+      <c r="L42" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="175" t="n"/>
+      <c r="N42" s="176" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
       <c r="A43" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B43" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
       <c r="E43" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
       <c r="G43" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H43" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
       <c r="L43" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M43" s="189" t="n"/>
@@ -4924,244 +4933,244 @@
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B44" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A44" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B44" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E44" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G44" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="182" t="n"/>
-      <c r="N44" s="183" t="n"/>
+      <c r="L44" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="189" t="n"/>
+      <c r="N44" s="190" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B45" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A45" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B45" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E45" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G45" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="175" t="n"/>
-      <c r="N45" s="176" t="n"/>
+      <c r="L45" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="182" t="n"/>
+      <c r="N45" s="183" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B46" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A46" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B46" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E46" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G46" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="182" t="n"/>
-      <c r="N46" s="183" t="n"/>
+      <c r="L46" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="175" t="n"/>
+      <c r="N46" s="176" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B47" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A47" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B47" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E47" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G47" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="175" t="n"/>
-      <c r="N47" s="176" t="n"/>
+      <c r="L47" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="182" t="n"/>
+      <c r="N47" s="183" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B48" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A48" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B48" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E48" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G48" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="182" t="n"/>
-      <c r="N48" s="183" t="n"/>
+      <c r="L48" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="175" t="n"/>
+      <c r="N48" s="176" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B49" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A49" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B49" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E49" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G49" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="189" t="n"/>
-      <c r="N49" s="190" t="n"/>
+      <c r="L49" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="182" t="n"/>
+      <c r="N49" s="183" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
       <c r="A50" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B50" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
       <c r="E50" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
       <c r="G50" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H50" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
       <c r="L50" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M50" s="189" t="n"/>
@@ -5169,244 +5178,244 @@
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B51" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A51" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B51" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E51" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G51" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="175" t="n"/>
-      <c r="N51" s="176" t="n"/>
+      <c r="L51" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="189" t="n"/>
+      <c r="N51" s="190" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B52" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A52" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B52" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E52" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G52" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="182" t="n"/>
-      <c r="N52" s="183" t="n"/>
+      <c r="L52" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="175" t="n"/>
+      <c r="N52" s="176" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B53" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A53" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B53" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E53" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G53" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="175" t="n"/>
-      <c r="N53" s="176" t="n"/>
+      <c r="L53" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="182" t="n"/>
+      <c r="N53" s="183" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B54" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A54" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B54" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E54" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G54" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="182" t="n"/>
-      <c r="N54" s="183" t="n"/>
+      <c r="L54" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="175" t="n"/>
+      <c r="N54" s="176" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B55" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A55" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B55" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E55" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G55" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="175" t="n"/>
-      <c r="N55" s="176" t="n"/>
+      <c r="L55" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="182" t="n"/>
+      <c r="N55" s="183" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B56" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A56" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B56" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E56" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G56" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="189" t="n"/>
-      <c r="N56" s="190" t="n"/>
+      <c r="L56" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="175" t="n"/>
+      <c r="N56" s="176" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
       <c r="A57" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B57" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
       <c r="E57" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
       <c r="G57" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H57" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
       <c r="L57" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M57" s="189" t="n"/>
@@ -5414,244 +5423,244 @@
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B58" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A58" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B58" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E58" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G58" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="182" t="n"/>
-      <c r="N58" s="183" t="n"/>
+      <c r="L58" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="189" t="n"/>
+      <c r="N58" s="190" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B59" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A59" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B59" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E59" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G59" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="175" t="n"/>
-      <c r="N59" s="176" t="n"/>
+      <c r="L59" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="182" t="n"/>
+      <c r="N59" s="183" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B60" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A60" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B60" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E60" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G60" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="182" t="n"/>
-      <c r="N60" s="183" t="n"/>
+      <c r="L60" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="175" t="n"/>
+      <c r="N60" s="176" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B61" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A61" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B61" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E61" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G61" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="175" t="n"/>
-      <c r="N61" s="176" t="n"/>
+      <c r="L61" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="182" t="n"/>
+      <c r="N61" s="183" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B62" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A62" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B62" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E62" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G62" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="182" t="n"/>
-      <c r="N62" s="183" t="n"/>
+      <c r="L62" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="175" t="n"/>
+      <c r="N62" s="176" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B63" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A63" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B63" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E63" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G63" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="189" t="n"/>
-      <c r="N63" s="190" t="n"/>
+      <c r="L63" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="182" t="n"/>
+      <c r="N63" s="183" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
       <c r="A64" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B64" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
       <c r="E64" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
       <c r="G64" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H64" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
       <c r="L64" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M64" s="189" t="n"/>
@@ -5659,184 +5668,202 @@
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B65" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A65" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B65" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E65" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G65" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="175" t="n"/>
-      <c r="N65" s="176" t="n"/>
+      <c r="L65" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="189" t="n"/>
+      <c r="N65" s="190" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B66" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A66" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B66" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E66" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G66" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="182" t="n"/>
-      <c r="N66" s="183" t="n"/>
+      <c r="L66" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="175" t="n"/>
+      <c r="N66" s="176" t="n"/>
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B67" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A67" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B67" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
-      <c r="E67" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E67" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
-      <c r="G67" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G67" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
-      <c r="L67" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="175" t="n"/>
-      <c r="N67" s="176" t="n"/>
+      <c r="L67" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="182" t="n"/>
+      <c r="N67" s="183" t="n"/>
       <c r="O67" s="102" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B68" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A68" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B68" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C68" s="168" t="n"/>
       <c r="D68" s="169" t="n"/>
-      <c r="E68" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E68" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F68" s="171" t="n"/>
-      <c r="G68" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G68" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I68" s="171" t="n"/>
       <c r="J68" s="174" t="n"/>
       <c r="K68" s="169" t="n"/>
-      <c r="L68" s="179">
+      <c r="L68" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M68" s="175" t="n"/>
+      <c r="N68" s="176" t="n"/>
+      <c r="O68" s="102" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" s="101">
+      <c r="A69" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B69" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C69" s="168" t="n"/>
+      <c r="D69" s="169" t="n"/>
+      <c r="E69" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F69" s="171" t="n"/>
+      <c r="G69" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="171" t="n"/>
+      <c r="J69" s="174" t="n"/>
+      <c r="K69" s="169" t="n"/>
+      <c r="L69" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M68" s="182" t="n"/>
-      <c r="N68" s="183" t="n"/>
-      <c r="O68" s="102" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="191" t="n">
+      <c r="M69" s="182" t="n"/>
+      <c r="N69" s="183" t="n"/>
+      <c r="O69" s="102" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B69" s="102" t="n"/>
-      <c r="C69" s="102" t="n"/>
-      <c r="D69" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E69" s="102" t="n"/>
-      <c r="F69" s="102" t="n"/>
-      <c r="G69" s="102" t="n"/>
-      <c r="H69" s="102" t="n"/>
-      <c r="I69" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J69" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K69" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L69" s="102" t="n"/>
-      <c r="M69" s="102" t="n"/>
-      <c r="N69" s="102" t="n"/>
-      <c r="O69" s="102" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="102" t="n"/>
       <c r="B70" s="102" t="n"/>
       <c r="C70" s="102" t="n"/>
-      <c r="D70" s="102" t="n"/>
+      <c r="D70" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E70" s="102" t="n"/>
       <c r="F70" s="102" t="n"/>
       <c r="G70" s="102" t="n"/>
       <c r="H70" s="102" t="n"/>
-      <c r="I70" s="102" t="n"/>
-      <c r="J70" s="102" t="n"/>
-      <c r="K70" s="102" t="n"/>
+      <c r="I70" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J70" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K70" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L70" s="102" t="n"/>
       <c r="M70" s="102" t="n"/>
       <c r="N70" s="102" t="n"/>
@@ -5892,6 +5919,23 @@
       <c r="M73" s="102" t="n"/>
       <c r="N73" s="102" t="n"/>
       <c r="O73" s="102" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="102" t="n"/>
+      <c r="B74" s="102" t="n"/>
+      <c r="C74" s="102" t="n"/>
+      <c r="D74" s="102" t="n"/>
+      <c r="E74" s="102" t="n"/>
+      <c r="F74" s="102" t="n"/>
+      <c r="G74" s="102" t="n"/>
+      <c r="H74" s="102" t="n"/>
+      <c r="I74" s="102" t="n"/>
+      <c r="J74" s="102" t="n"/>
+      <c r="K74" s="102" t="n"/>
+      <c r="L74" s="102" t="n"/>
+      <c r="M74" s="102" t="n"/>
+      <c r="N74" s="102" t="n"/>
+      <c r="O74" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6047,7 +6091,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="101">
       <c r="A4" s="233" t="n">
-        <v>46090.80209267978</v>
+        <v>46090.80209268518</v>
       </c>
       <c r="B4" s="234" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3364,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.82300822704</v>
+        <v>46093.82653238095</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3521,21 +3521,15 @@
       <c r="F5" s="227" t="n"/>
       <c r="G5" s="228" t="n"/>
       <c r="H5" s="229" t="n"/>
-      <c r="I5" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J5" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="I5" s="227" t="n"/>
+      <c r="J5" s="230" t="n"/>
       <c r="K5" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="226" t="n">
-        <v>1.913</v>
-      </c>
+      <c r="L5" s="226" t="n"/>
       <c r="M5" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL</t>
         </is>
       </c>
       <c r="N5" s="232" t="inlineStr">
@@ -3546,7 +3540,7 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.80209268518</v>
+        <v>46093.82300822917</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3590,7 +3584,7 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
       <c r="A7" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46093.80209268518</v>
       </c>
       <c r="B7" s="223" t="inlineStr">
         <is>
@@ -3604,19 +3598,13 @@
         <v>4.2578</v>
       </c>
       <c r="E7" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F7" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G7" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H7" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F7" s="227" t="n"/>
+      <c r="G7" s="228" t="n"/>
+      <c r="H7" s="229" t="n"/>
       <c r="I7" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J7" s="230" t="n">
         <v>20.49</v>
@@ -3625,11 +3613,11 @@
         <v>10.7108</v>
       </c>
       <c r="L7" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M7" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N7" s="232" t="inlineStr">
@@ -3640,7 +3628,7 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
@@ -3653,20 +3641,17 @@
       <c r="D8" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E8" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E8" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F8" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G8" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G8" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H8" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I8" s="227" t="n">
         <v>2.086</v>
@@ -3677,310 +3662,328 @@
       <c r="K8" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L8" s="226">
+      <c r="L8" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M8" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N8" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="101">
+      <c r="A9" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B9" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C9" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D9" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E9" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G9" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I9" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J9" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K9" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L9" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M8" s="231" t="inlineStr">
+      <c r="M9" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N8" s="232" t="inlineStr">
+      <c r="N9" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="211" t="n">
+    <row r="10" ht="21.75" customHeight="1" s="101">
+      <c r="A10" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B9" s="212" t="inlineStr">
+      <c r="B10" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C9" s="213" t="n"/>
-      <c r="D9" s="214" t="n">
+      <c r="C10" s="213" t="n"/>
+      <c r="D10" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E9" s="215">
+      <c r="E10" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F9" s="216" t="n"/>
-      <c r="G9" s="217">
+      <c r="F10" s="216" t="n"/>
+      <c r="G10" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H9" s="218">
+      <c r="H10" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I9" s="216" t="n">
+      <c r="I10" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J9" s="219" t="n">
+      <c r="J10" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K9" s="214" t="n">
+      <c r="K10" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L9" s="215">
+      <c r="L10" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M9" s="220" t="inlineStr">
+      <c r="M10" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N9" s="221" t="inlineStr">
+      <c r="N10" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="166" t="n">
+    <row r="11" ht="21.75" customHeight="1" s="101">
+      <c r="A11" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B10" s="167" t="inlineStr">
+      <c r="B11" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C10" s="168" t="n"/>
-      <c r="D10" s="169" t="n"/>
-      <c r="E10" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="171" t="n"/>
-      <c r="G10" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I10" s="171" t="n"/>
-      <c r="J10" s="174" t="n"/>
-      <c r="K10" s="169" t="n"/>
-      <c r="L10" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="175" t="n"/>
-      <c r="N10" s="176" t="n"/>
-      <c r="O10" s="102" t="n"/>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B11" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C11" s="168" t="n"/>
       <c r="D11" s="169" t="n"/>
-      <c r="E11" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E11" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F11" s="171" t="n"/>
-      <c r="G11" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G11" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I11" s="171" t="n"/>
       <c r="J11" s="174" t="n"/>
       <c r="K11" s="169" t="n"/>
-      <c r="L11" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="182" t="n"/>
-      <c r="N11" s="183" t="n"/>
+      <c r="L11" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M11" s="175" t="n"/>
+      <c r="N11" s="176" t="n"/>
       <c r="O11" s="102" t="n"/>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B12" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A12" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B12" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
-      <c r="E12" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E12" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G12" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
-      <c r="L12" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="175" t="n"/>
-      <c r="N12" s="176" t="n"/>
+      <c r="L12" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="182" t="n"/>
+      <c r="N12" s="183" t="n"/>
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B13" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A13" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B13" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E13" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G13" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="182" t="n"/>
-      <c r="N13" s="183" t="n"/>
+      <c r="L13" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="175" t="n"/>
+      <c r="N13" s="176" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B14" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A14" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B14" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E14" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G14" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="175" t="n"/>
-      <c r="N14" s="176" t="n"/>
+      <c r="L14" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="182" t="n"/>
+      <c r="N14" s="183" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B15" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A15" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B15" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E15" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G15" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="189" t="n"/>
-      <c r="N15" s="190" t="n"/>
+      <c r="L15" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="175" t="n"/>
+      <c r="N15" s="176" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
       <c r="A16" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B16" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
       <c r="E16" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
       <c r="G16" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H16" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
       <c r="L16" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M16" s="189" t="n"/>
@@ -3988,244 +3991,244 @@
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B17" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A17" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B17" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E17" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G17" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="182" t="n"/>
-      <c r="N17" s="183" t="n"/>
+      <c r="L17" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="189" t="n"/>
+      <c r="N17" s="190" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B18" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A18" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B18" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E18" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G18" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="175" t="n"/>
-      <c r="N18" s="176" t="n"/>
+      <c r="L18" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="182" t="n"/>
+      <c r="N18" s="183" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B19" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A19" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B19" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E19" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G19" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="182" t="n"/>
-      <c r="N19" s="183" t="n"/>
+      <c r="L19" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="175" t="n"/>
+      <c r="N19" s="176" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A20" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B20" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E20" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G20" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="175" t="n"/>
-      <c r="N20" s="176" t="n"/>
+      <c r="L20" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="182" t="n"/>
+      <c r="N20" s="183" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B21" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A21" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B21" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E21" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G21" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="182" t="n"/>
-      <c r="N21" s="183" t="n"/>
+      <c r="L21" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="175" t="n"/>
+      <c r="N21" s="176" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B22" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A22" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B22" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E22" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G22" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="189" t="n"/>
-      <c r="N22" s="190" t="n"/>
+      <c r="L22" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="182" t="n"/>
+      <c r="N22" s="183" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
       <c r="A23" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B23" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
       <c r="E23" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
       <c r="G23" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H23" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
       <c r="L23" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M23" s="189" t="n"/>
@@ -4233,244 +4236,244 @@
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B24" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A24" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B24" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E24" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G24" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="175" t="n"/>
-      <c r="N24" s="176" t="n"/>
+      <c r="L24" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="189" t="n"/>
+      <c r="N24" s="190" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B25" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A25" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B25" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E25" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G25" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="182" t="n"/>
-      <c r="N25" s="183" t="n"/>
+      <c r="L25" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="175" t="n"/>
+      <c r="N25" s="176" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B26" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A26" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B26" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E26" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G26" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="175" t="n"/>
-      <c r="N26" s="176" t="n"/>
+      <c r="L26" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="182" t="n"/>
+      <c r="N26" s="183" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B27" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A27" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B27" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E27" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G27" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="182" t="n"/>
-      <c r="N27" s="183" t="n"/>
+      <c r="L27" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="175" t="n"/>
+      <c r="N27" s="176" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B28" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A28" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B28" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E28" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G28" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="175" t="n"/>
-      <c r="N28" s="176" t="n"/>
+      <c r="L28" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="182" t="n"/>
+      <c r="N28" s="183" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B29" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A29" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B29" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E29" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G29" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="189" t="n"/>
-      <c r="N29" s="190" t="n"/>
+      <c r="L29" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="175" t="n"/>
+      <c r="N29" s="176" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
       <c r="A30" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B30" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
       <c r="E30" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
       <c r="G30" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H30" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
       <c r="L30" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M30" s="189" t="n"/>
@@ -4478,244 +4481,244 @@
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B31" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A31" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B31" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E31" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G31" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="182" t="n"/>
-      <c r="N31" s="183" t="n"/>
+      <c r="L31" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="189" t="n"/>
+      <c r="N31" s="190" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B32" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A32" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B32" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E32" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G32" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="175" t="n"/>
-      <c r="N32" s="176" t="n"/>
+      <c r="L32" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="182" t="n"/>
+      <c r="N32" s="183" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B33" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A33" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B33" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E33" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G33" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="182" t="n"/>
-      <c r="N33" s="183" t="n"/>
+      <c r="L33" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="175" t="n"/>
+      <c r="N33" s="176" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B34" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A34" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B34" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E34" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G34" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="175" t="n"/>
-      <c r="N34" s="176" t="n"/>
+      <c r="L34" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="182" t="n"/>
+      <c r="N34" s="183" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B35" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A35" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B35" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E35" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G35" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="182" t="n"/>
-      <c r="N35" s="183" t="n"/>
+      <c r="L35" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="175" t="n"/>
+      <c r="N35" s="176" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B36" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A36" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B36" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E36" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G36" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="189" t="n"/>
-      <c r="N36" s="190" t="n"/>
+      <c r="L36" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="182" t="n"/>
+      <c r="N36" s="183" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
       <c r="A37" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B37" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
       <c r="E37" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
       <c r="G37" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H37" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
       <c r="L37" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M37" s="189" t="n"/>
@@ -4723,244 +4726,244 @@
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B38" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A38" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B38" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E38" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G38" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="175" t="n"/>
-      <c r="N38" s="176" t="n"/>
+      <c r="L38" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="189" t="n"/>
+      <c r="N38" s="190" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B39" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A39" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B39" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E39" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G39" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="182" t="n"/>
-      <c r="N39" s="183" t="n"/>
+      <c r="L39" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="175" t="n"/>
+      <c r="N39" s="176" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B40" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A40" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B40" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E40" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G40" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="175" t="n"/>
-      <c r="N40" s="176" t="n"/>
+      <c r="L40" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="182" t="n"/>
+      <c r="N40" s="183" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B41" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A41" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B41" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E41" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G41" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="182" t="n"/>
-      <c r="N41" s="183" t="n"/>
+      <c r="L41" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="175" t="n"/>
+      <c r="N41" s="176" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B42" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A42" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B42" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E42" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G42" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="175" t="n"/>
-      <c r="N42" s="176" t="n"/>
+      <c r="L42" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="182" t="n"/>
+      <c r="N42" s="183" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B43" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A43" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B43" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E43" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G43" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="189" t="n"/>
-      <c r="N43" s="190" t="n"/>
+      <c r="L43" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="175" t="n"/>
+      <c r="N43" s="176" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
       <c r="A44" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B44" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
       <c r="E44" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
       <c r="G44" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H44" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
       <c r="L44" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M44" s="189" t="n"/>
@@ -4968,244 +4971,244 @@
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B45" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A45" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B45" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E45" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G45" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="182" t="n"/>
-      <c r="N45" s="183" t="n"/>
+      <c r="L45" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="189" t="n"/>
+      <c r="N45" s="190" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B46" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A46" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B46" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E46" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G46" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="175" t="n"/>
-      <c r="N46" s="176" t="n"/>
+      <c r="L46" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="182" t="n"/>
+      <c r="N46" s="183" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B47" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A47" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B47" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E47" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G47" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="182" t="n"/>
-      <c r="N47" s="183" t="n"/>
+      <c r="L47" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="175" t="n"/>
+      <c r="N47" s="176" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B48" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A48" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B48" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E48" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G48" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="175" t="n"/>
-      <c r="N48" s="176" t="n"/>
+      <c r="L48" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="182" t="n"/>
+      <c r="N48" s="183" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B49" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A49" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B49" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E49" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G49" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="182" t="n"/>
-      <c r="N49" s="183" t="n"/>
+      <c r="L49" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="175" t="n"/>
+      <c r="N49" s="176" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B50" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A50" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B50" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E50" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G50" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="189" t="n"/>
-      <c r="N50" s="190" t="n"/>
+      <c r="L50" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="182" t="n"/>
+      <c r="N50" s="183" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
       <c r="A51" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B51" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
       <c r="E51" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
       <c r="G51" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H51" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
       <c r="L51" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M51" s="189" t="n"/>
@@ -5213,244 +5216,244 @@
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B52" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A52" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B52" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E52" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G52" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="175" t="n"/>
-      <c r="N52" s="176" t="n"/>
+      <c r="L52" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="189" t="n"/>
+      <c r="N52" s="190" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B53" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A53" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B53" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E53" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G53" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="182" t="n"/>
-      <c r="N53" s="183" t="n"/>
+      <c r="L53" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="175" t="n"/>
+      <c r="N53" s="176" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B54" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A54" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B54" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E54" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G54" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="175" t="n"/>
-      <c r="N54" s="176" t="n"/>
+      <c r="L54" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="182" t="n"/>
+      <c r="N54" s="183" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B55" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A55" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B55" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E55" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G55" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="182" t="n"/>
-      <c r="N55" s="183" t="n"/>
+      <c r="L55" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="175" t="n"/>
+      <c r="N55" s="176" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B56" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A56" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B56" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E56" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G56" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="175" t="n"/>
-      <c r="N56" s="176" t="n"/>
+      <c r="L56" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="182" t="n"/>
+      <c r="N56" s="183" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B57" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A57" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B57" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E57" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G57" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="189" t="n"/>
-      <c r="N57" s="190" t="n"/>
+      <c r="L57" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="175" t="n"/>
+      <c r="N57" s="176" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
       <c r="A58" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B58" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
       <c r="E58" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
       <c r="G58" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H58" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
       <c r="L58" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M58" s="189" t="n"/>
@@ -5458,244 +5461,244 @@
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B59" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A59" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B59" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E59" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G59" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="182" t="n"/>
-      <c r="N59" s="183" t="n"/>
+      <c r="L59" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="189" t="n"/>
+      <c r="N59" s="190" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B60" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A60" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B60" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E60" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G60" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="175" t="n"/>
-      <c r="N60" s="176" t="n"/>
+      <c r="L60" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="182" t="n"/>
+      <c r="N60" s="183" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B61" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A61" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B61" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E61" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G61" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="182" t="n"/>
-      <c r="N61" s="183" t="n"/>
+      <c r="L61" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="175" t="n"/>
+      <c r="N61" s="176" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B62" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A62" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B62" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E62" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G62" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="175" t="n"/>
-      <c r="N62" s="176" t="n"/>
+      <c r="L62" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="182" t="n"/>
+      <c r="N62" s="183" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B63" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A63" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B63" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E63" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G63" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="182" t="n"/>
-      <c r="N63" s="183" t="n"/>
+      <c r="L63" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="175" t="n"/>
+      <c r="N63" s="176" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B64" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A64" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B64" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E64" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G64" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="189" t="n"/>
-      <c r="N64" s="190" t="n"/>
+      <c r="L64" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="182" t="n"/>
+      <c r="N64" s="183" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
       <c r="A65" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B65" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
       <c r="E65" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
       <c r="G65" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H65" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
       <c r="L65" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M65" s="189" t="n"/>
@@ -5703,184 +5706,202 @@
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B66" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A66" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B66" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E66" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G66" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="175" t="n"/>
-      <c r="N66" s="176" t="n"/>
+      <c r="L66" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="189" t="n"/>
+      <c r="N66" s="190" t="n"/>
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B67" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A67" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B67" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
-      <c r="E67" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E67" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
-      <c r="G67" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G67" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
-      <c r="L67" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="182" t="n"/>
-      <c r="N67" s="183" t="n"/>
+      <c r="L67" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="175" t="n"/>
+      <c r="N67" s="176" t="n"/>
       <c r="O67" s="102" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B68" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A68" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B68" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C68" s="168" t="n"/>
       <c r="D68" s="169" t="n"/>
-      <c r="E68" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E68" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F68" s="171" t="n"/>
-      <c r="G68" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G68" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I68" s="171" t="n"/>
       <c r="J68" s="174" t="n"/>
       <c r="K68" s="169" t="n"/>
-      <c r="L68" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M68" s="175" t="n"/>
-      <c r="N68" s="176" t="n"/>
+      <c r="L68" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M68" s="182" t="n"/>
+      <c r="N68" s="183" t="n"/>
       <c r="O68" s="102" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B69" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A69" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B69" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C69" s="168" t="n"/>
       <c r="D69" s="169" t="n"/>
-      <c r="E69" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E69" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F69" s="171" t="n"/>
-      <c r="G69" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G69" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I69" s="171" t="n"/>
       <c r="J69" s="174" t="n"/>
       <c r="K69" s="169" t="n"/>
-      <c r="L69" s="179">
+      <c r="L69" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M69" s="175" t="n"/>
+      <c r="N69" s="176" t="n"/>
+      <c r="O69" s="102" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B70" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C70" s="168" t="n"/>
+      <c r="D70" s="169" t="n"/>
+      <c r="E70" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F70" s="171" t="n"/>
+      <c r="G70" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I70" s="171" t="n"/>
+      <c r="J70" s="174" t="n"/>
+      <c r="K70" s="169" t="n"/>
+      <c r="L70" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M69" s="182" t="n"/>
-      <c r="N69" s="183" t="n"/>
-      <c r="O69" s="102" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="191" t="n">
+      <c r="M70" s="182" t="n"/>
+      <c r="N70" s="183" t="n"/>
+      <c r="O70" s="102" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B70" s="102" t="n"/>
-      <c r="C70" s="102" t="n"/>
-      <c r="D70" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E70" s="102" t="n"/>
-      <c r="F70" s="102" t="n"/>
-      <c r="G70" s="102" t="n"/>
-      <c r="H70" s="102" t="n"/>
-      <c r="I70" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J70" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K70" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L70" s="102" t="n"/>
-      <c r="M70" s="102" t="n"/>
-      <c r="N70" s="102" t="n"/>
-      <c r="O70" s="102" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="102" t="n"/>
       <c r="B71" s="102" t="n"/>
       <c r="C71" s="102" t="n"/>
-      <c r="D71" s="102" t="n"/>
+      <c r="D71" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E71" s="102" t="n"/>
       <c r="F71" s="102" t="n"/>
       <c r="G71" s="102" t="n"/>
       <c r="H71" s="102" t="n"/>
-      <c r="I71" s="102" t="n"/>
-      <c r="J71" s="102" t="n"/>
-      <c r="K71" s="102" t="n"/>
+      <c r="I71" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J71" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K71" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L71" s="102" t="n"/>
       <c r="M71" s="102" t="n"/>
       <c r="N71" s="102" t="n"/>
@@ -5936,6 +5957,23 @@
       <c r="M74" s="102" t="n"/>
       <c r="N74" s="102" t="n"/>
       <c r="O74" s="102" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="102" t="n"/>
+      <c r="B75" s="102" t="n"/>
+      <c r="C75" s="102" t="n"/>
+      <c r="D75" s="102" t="n"/>
+      <c r="E75" s="102" t="n"/>
+      <c r="F75" s="102" t="n"/>
+      <c r="G75" s="102" t="n"/>
+      <c r="H75" s="102" t="n"/>
+      <c r="I75" s="102" t="n"/>
+      <c r="J75" s="102" t="n"/>
+      <c r="K75" s="102" t="n"/>
+      <c r="L75" s="102" t="n"/>
+      <c r="M75" s="102" t="n"/>
+      <c r="N75" s="102" t="n"/>
+      <c r="O75" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3364,7 +3364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O76"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3502,7 +3502,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.82653238095</v>
+        <v>46093.82998256211</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3518,18 +3518,30 @@
       <c r="E5" s="226" t="n">
         <v>1.4543</v>
       </c>
-      <c r="F5" s="227" t="n"/>
-      <c r="G5" s="228" t="n"/>
-      <c r="H5" s="229" t="n"/>
-      <c r="I5" s="227" t="n"/>
-      <c r="J5" s="230" t="n"/>
+      <c r="F5" s="227" t="n">
+        <v>6.5536</v>
+      </c>
+      <c r="G5" s="228" t="n">
+        <v>-5.0993</v>
+      </c>
+      <c r="H5" s="229" t="n">
+        <v>-0.7781</v>
+      </c>
+      <c r="I5" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J5" s="230" t="n">
+        <v>20.49</v>
+      </c>
       <c r="K5" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="226" t="n"/>
+      <c r="L5" s="226" t="n">
+        <v>1.913</v>
+      </c>
       <c r="M5" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N5" s="232" t="inlineStr">
@@ -3540,7 +3552,7 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.82300822917</v>
+        <v>46093.82653238426</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3559,21 +3571,15 @@
       <c r="F6" s="227" t="n"/>
       <c r="G6" s="228" t="n"/>
       <c r="H6" s="229" t="n"/>
-      <c r="I6" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J6" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="I6" s="227" t="n"/>
+      <c r="J6" s="230" t="n"/>
       <c r="K6" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L6" s="226" t="n">
-        <v>1.913</v>
-      </c>
+      <c r="L6" s="226" t="n"/>
       <c r="M6" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL</t>
         </is>
       </c>
       <c r="N6" s="232" t="inlineStr">
@@ -3584,7 +3590,7 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
       <c r="A7" s="222" t="n">
-        <v>46093.80209268518</v>
+        <v>46093.82300822917</v>
       </c>
       <c r="B7" s="223" t="inlineStr">
         <is>
@@ -3628,7 +3634,7 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46093.80209268518</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
@@ -3642,19 +3648,13 @@
         <v>4.2578</v>
       </c>
       <c r="E8" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F8" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G8" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H8" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F8" s="227" t="n"/>
+      <c r="G8" s="228" t="n"/>
+      <c r="H8" s="229" t="n"/>
       <c r="I8" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J8" s="230" t="n">
         <v>20.49</v>
@@ -3663,11 +3663,11 @@
         <v>10.7108</v>
       </c>
       <c r="L8" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M8" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N8" s="232" t="inlineStr">
@@ -3678,7 +3678,7 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
       <c r="A9" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B9" s="223" t="inlineStr">
         <is>
@@ -3691,20 +3691,17 @@
       <c r="D9" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E9" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E9" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F9" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G9" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G9" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H9" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I9" s="227" t="n">
         <v>2.086</v>
@@ -3715,310 +3712,328 @@
       <c r="K9" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L9" s="226">
+      <c r="L9" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M9" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N9" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="101">
+      <c r="A10" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B10" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C10" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D10" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E10" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G10" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I10" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J10" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K10" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L10" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M9" s="231" t="inlineStr">
+      <c r="M10" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N9" s="232" t="inlineStr">
+      <c r="N10" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="211" t="n">
+    <row r="11" ht="21.75" customHeight="1" s="101">
+      <c r="A11" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B10" s="212" t="inlineStr">
+      <c r="B11" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C10" s="213" t="n"/>
-      <c r="D10" s="214" t="n">
+      <c r="C11" s="213" t="n"/>
+      <c r="D11" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E10" s="215">
+      <c r="E11" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F10" s="216" t="n"/>
-      <c r="G10" s="217">
+      <c r="F11" s="216" t="n"/>
+      <c r="G11" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H10" s="218">
+      <c r="H11" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I10" s="216" t="n">
+      <c r="I11" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J10" s="219" t="n">
+      <c r="J11" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K10" s="214" t="n">
+      <c r="K11" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L10" s="215">
+      <c r="L11" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M10" s="220" t="inlineStr">
+      <c r="M11" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N10" s="221" t="inlineStr">
+      <c r="N11" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="166" t="n">
+    <row r="12" ht="21.75" customHeight="1" s="101">
+      <c r="A12" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B11" s="167" t="inlineStr">
+      <c r="B12" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C11" s="168" t="n"/>
-      <c r="D11" s="169" t="n"/>
-      <c r="E11" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="171" t="n"/>
-      <c r="G11" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I11" s="171" t="n"/>
-      <c r="J11" s="174" t="n"/>
-      <c r="K11" s="169" t="n"/>
-      <c r="L11" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="175" t="n"/>
-      <c r="N11" s="176" t="n"/>
-      <c r="O11" s="102" t="n"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B12" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C12" s="168" t="n"/>
       <c r="D12" s="169" t="n"/>
-      <c r="E12" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E12" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F12" s="171" t="n"/>
-      <c r="G12" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G12" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I12" s="171" t="n"/>
       <c r="J12" s="174" t="n"/>
       <c r="K12" s="169" t="n"/>
-      <c r="L12" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="182" t="n"/>
-      <c r="N12" s="183" t="n"/>
+      <c r="L12" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="175" t="n"/>
+      <c r="N12" s="176" t="n"/>
       <c r="O12" s="102" t="n"/>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B13" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A13" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B13" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E13" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G13" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="175" t="n"/>
-      <c r="N13" s="176" t="n"/>
+      <c r="L13" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="182" t="n"/>
+      <c r="N13" s="183" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B14" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A14" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B14" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E14" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G14" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="182" t="n"/>
-      <c r="N14" s="183" t="n"/>
+      <c r="L14" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="176" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B15" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A15" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B15" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E15" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G15" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="175" t="n"/>
-      <c r="N15" s="176" t="n"/>
+      <c r="L15" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="182" t="n"/>
+      <c r="N15" s="183" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B16" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A16" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B16" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E16" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G16" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="189" t="n"/>
-      <c r="N16" s="190" t="n"/>
+      <c r="L16" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="175" t="n"/>
+      <c r="N16" s="176" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
       <c r="A17" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B17" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
       <c r="E17" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
       <c r="G17" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H17" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
       <c r="L17" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M17" s="189" t="n"/>
@@ -4026,244 +4041,244 @@
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B18" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A18" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B18" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E18" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G18" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="182" t="n"/>
-      <c r="N18" s="183" t="n"/>
+      <c r="L18" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="189" t="n"/>
+      <c r="N18" s="190" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B19" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A19" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B19" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E19" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G19" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="175" t="n"/>
-      <c r="N19" s="176" t="n"/>
+      <c r="L19" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="182" t="n"/>
+      <c r="N19" s="183" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B20" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A20" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B20" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E20" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G20" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="182" t="n"/>
-      <c r="N20" s="183" t="n"/>
+      <c r="L20" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="175" t="n"/>
+      <c r="N20" s="176" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B21" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A21" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B21" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E21" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G21" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="175" t="n"/>
-      <c r="N21" s="176" t="n"/>
+      <c r="L21" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="182" t="n"/>
+      <c r="N21" s="183" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B22" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A22" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B22" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E22" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G22" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="182" t="n"/>
-      <c r="N22" s="183" t="n"/>
+      <c r="L22" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="175" t="n"/>
+      <c r="N22" s="176" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B23" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A23" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B23" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E23" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G23" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="189" t="n"/>
-      <c r="N23" s="190" t="n"/>
+      <c r="L23" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="182" t="n"/>
+      <c r="N23" s="183" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
       <c r="A24" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B24" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
       <c r="E24" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
       <c r="G24" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H24" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
       <c r="L24" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M24" s="189" t="n"/>
@@ -4271,244 +4286,244 @@
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B25" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A25" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B25" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E25" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G25" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="175" t="n"/>
-      <c r="N25" s="176" t="n"/>
+      <c r="L25" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="189" t="n"/>
+      <c r="N25" s="190" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B26" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A26" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B26" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E26" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G26" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="182" t="n"/>
-      <c r="N26" s="183" t="n"/>
+      <c r="L26" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="175" t="n"/>
+      <c r="N26" s="176" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B27" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A27" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B27" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E27" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G27" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="175" t="n"/>
-      <c r="N27" s="176" t="n"/>
+      <c r="L27" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="182" t="n"/>
+      <c r="N27" s="183" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B28" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A28" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B28" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E28" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G28" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="182" t="n"/>
-      <c r="N28" s="183" t="n"/>
+      <c r="L28" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="175" t="n"/>
+      <c r="N28" s="176" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B29" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A29" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B29" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E29" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G29" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="175" t="n"/>
-      <c r="N29" s="176" t="n"/>
+      <c r="L29" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="182" t="n"/>
+      <c r="N29" s="183" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B30" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A30" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B30" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E30" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G30" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="189" t="n"/>
-      <c r="N30" s="190" t="n"/>
+      <c r="L30" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="175" t="n"/>
+      <c r="N30" s="176" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
       <c r="A31" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B31" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
       <c r="E31" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
       <c r="G31" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H31" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
       <c r="L31" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M31" s="189" t="n"/>
@@ -4516,244 +4531,244 @@
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B32" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A32" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B32" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E32" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G32" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="182" t="n"/>
-      <c r="N32" s="183" t="n"/>
+      <c r="L32" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="189" t="n"/>
+      <c r="N32" s="190" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B33" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A33" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B33" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E33" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G33" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="175" t="n"/>
-      <c r="N33" s="176" t="n"/>
+      <c r="L33" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="182" t="n"/>
+      <c r="N33" s="183" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B34" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A34" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B34" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E34" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G34" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="182" t="n"/>
-      <c r="N34" s="183" t="n"/>
+      <c r="L34" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="175" t="n"/>
+      <c r="N34" s="176" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B35" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A35" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B35" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E35" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G35" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="175" t="n"/>
-      <c r="N35" s="176" t="n"/>
+      <c r="L35" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="182" t="n"/>
+      <c r="N35" s="183" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B36" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A36" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B36" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E36" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G36" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="182" t="n"/>
-      <c r="N36" s="183" t="n"/>
+      <c r="L36" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="175" t="n"/>
+      <c r="N36" s="176" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B37" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A37" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B37" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E37" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G37" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="189" t="n"/>
-      <c r="N37" s="190" t="n"/>
+      <c r="L37" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="182" t="n"/>
+      <c r="N37" s="183" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
       <c r="A38" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B38" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
       <c r="E38" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
       <c r="G38" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H38" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
       <c r="L38" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M38" s="189" t="n"/>
@@ -4761,244 +4776,244 @@
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B39" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A39" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B39" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E39" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G39" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="175" t="n"/>
-      <c r="N39" s="176" t="n"/>
+      <c r="L39" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="189" t="n"/>
+      <c r="N39" s="190" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B40" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A40" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B40" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E40" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G40" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="182" t="n"/>
-      <c r="N40" s="183" t="n"/>
+      <c r="L40" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="175" t="n"/>
+      <c r="N40" s="176" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B41" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A41" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B41" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E41" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G41" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="175" t="n"/>
-      <c r="N41" s="176" t="n"/>
+      <c r="L41" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="182" t="n"/>
+      <c r="N41" s="183" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B42" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A42" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B42" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E42" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G42" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="182" t="n"/>
-      <c r="N42" s="183" t="n"/>
+      <c r="L42" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="175" t="n"/>
+      <c r="N42" s="176" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B43" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A43" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B43" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E43" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G43" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="175" t="n"/>
-      <c r="N43" s="176" t="n"/>
+      <c r="L43" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="182" t="n"/>
+      <c r="N43" s="183" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B44" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A44" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B44" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E44" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G44" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="189" t="n"/>
-      <c r="N44" s="190" t="n"/>
+      <c r="L44" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="175" t="n"/>
+      <c r="N44" s="176" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
       <c r="A45" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B45" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
       <c r="E45" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
       <c r="G45" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H45" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
       <c r="L45" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M45" s="189" t="n"/>
@@ -5006,244 +5021,244 @@
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B46" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A46" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B46" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E46" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G46" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="182" t="n"/>
-      <c r="N46" s="183" t="n"/>
+      <c r="L46" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="189" t="n"/>
+      <c r="N46" s="190" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B47" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A47" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B47" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E47" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G47" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="175" t="n"/>
-      <c r="N47" s="176" t="n"/>
+      <c r="L47" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="182" t="n"/>
+      <c r="N47" s="183" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B48" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A48" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B48" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E48" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G48" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="182" t="n"/>
-      <c r="N48" s="183" t="n"/>
+      <c r="L48" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="175" t="n"/>
+      <c r="N48" s="176" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B49" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A49" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B49" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E49" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G49" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="175" t="n"/>
-      <c r="N49" s="176" t="n"/>
+      <c r="L49" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="182" t="n"/>
+      <c r="N49" s="183" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B50" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A50" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B50" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E50" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G50" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="182" t="n"/>
-      <c r="N50" s="183" t="n"/>
+      <c r="L50" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="175" t="n"/>
+      <c r="N50" s="176" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B51" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A51" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B51" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E51" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G51" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="189" t="n"/>
-      <c r="N51" s="190" t="n"/>
+      <c r="L51" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="182" t="n"/>
+      <c r="N51" s="183" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
       <c r="A52" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B52" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
       <c r="E52" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
       <c r="G52" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H52" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
       <c r="L52" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M52" s="189" t="n"/>
@@ -5251,244 +5266,244 @@
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B53" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A53" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B53" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E53" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G53" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="175" t="n"/>
-      <c r="N53" s="176" t="n"/>
+      <c r="L53" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="189" t="n"/>
+      <c r="N53" s="190" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B54" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A54" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B54" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E54" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G54" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="182" t="n"/>
-      <c r="N54" s="183" t="n"/>
+      <c r="L54" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="175" t="n"/>
+      <c r="N54" s="176" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B55" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A55" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B55" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E55" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G55" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="175" t="n"/>
-      <c r="N55" s="176" t="n"/>
+      <c r="L55" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="182" t="n"/>
+      <c r="N55" s="183" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B56" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A56" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B56" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E56" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G56" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="182" t="n"/>
-      <c r="N56" s="183" t="n"/>
+      <c r="L56" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="175" t="n"/>
+      <c r="N56" s="176" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B57" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A57" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B57" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E57" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G57" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="175" t="n"/>
-      <c r="N57" s="176" t="n"/>
+      <c r="L57" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="182" t="n"/>
+      <c r="N57" s="183" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B58" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A58" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B58" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E58" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G58" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="189" t="n"/>
-      <c r="N58" s="190" t="n"/>
+      <c r="L58" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="175" t="n"/>
+      <c r="N58" s="176" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
       <c r="A59" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B59" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
       <c r="E59" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
       <c r="G59" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H59" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
       <c r="L59" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M59" s="189" t="n"/>
@@ -5496,244 +5511,244 @@
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B60" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A60" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B60" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E60" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G60" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="182" t="n"/>
-      <c r="N60" s="183" t="n"/>
+      <c r="L60" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="189" t="n"/>
+      <c r="N60" s="190" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B61" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A61" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B61" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E61" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G61" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="175" t="n"/>
-      <c r="N61" s="176" t="n"/>
+      <c r="L61" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="182" t="n"/>
+      <c r="N61" s="183" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B62" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A62" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B62" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E62" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G62" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="182" t="n"/>
-      <c r="N62" s="183" t="n"/>
+      <c r="L62" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="175" t="n"/>
+      <c r="N62" s="176" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B63" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A63" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B63" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E63" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G63" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="175" t="n"/>
-      <c r="N63" s="176" t="n"/>
+      <c r="L63" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="182" t="n"/>
+      <c r="N63" s="183" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B64" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A64" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B64" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E64" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G64" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="182" t="n"/>
-      <c r="N64" s="183" t="n"/>
+      <c r="L64" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="175" t="n"/>
+      <c r="N64" s="176" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B65" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A65" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B65" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E65" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G65" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="189" t="n"/>
-      <c r="N65" s="190" t="n"/>
+      <c r="L65" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="182" t="n"/>
+      <c r="N65" s="183" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
       <c r="A66" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B66" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
       <c r="E66" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
       <c r="G66" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H66" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
       <c r="L66" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M66" s="189" t="n"/>
@@ -5741,184 +5756,202 @@
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B67" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A67" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B67" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
-      <c r="E67" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E67" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
-      <c r="G67" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G67" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
-      <c r="L67" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="175" t="n"/>
-      <c r="N67" s="176" t="n"/>
+      <c r="L67" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="189" t="n"/>
+      <c r="N67" s="190" t="n"/>
       <c r="O67" s="102" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B68" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A68" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B68" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C68" s="168" t="n"/>
       <c r="D68" s="169" t="n"/>
-      <c r="E68" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E68" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F68" s="171" t="n"/>
-      <c r="G68" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G68" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I68" s="171" t="n"/>
       <c r="J68" s="174" t="n"/>
       <c r="K68" s="169" t="n"/>
-      <c r="L68" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M68" s="182" t="n"/>
-      <c r="N68" s="183" t="n"/>
+      <c r="L68" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M68" s="175" t="n"/>
+      <c r="N68" s="176" t="n"/>
       <c r="O68" s="102" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B69" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A69" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B69" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C69" s="168" t="n"/>
       <c r="D69" s="169" t="n"/>
-      <c r="E69" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E69" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F69" s="171" t="n"/>
-      <c r="G69" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G69" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I69" s="171" t="n"/>
       <c r="J69" s="174" t="n"/>
       <c r="K69" s="169" t="n"/>
-      <c r="L69" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M69" s="175" t="n"/>
-      <c r="N69" s="176" t="n"/>
+      <c r="L69" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M69" s="182" t="n"/>
+      <c r="N69" s="183" t="n"/>
       <c r="O69" s="102" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B70" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A70" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B70" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C70" s="168" t="n"/>
       <c r="D70" s="169" t="n"/>
-      <c r="E70" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E70" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F70" s="171" t="n"/>
-      <c r="G70" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G70" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I70" s="171" t="n"/>
       <c r="J70" s="174" t="n"/>
       <c r="K70" s="169" t="n"/>
-      <c r="L70" s="179">
+      <c r="L70" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M70" s="175" t="n"/>
+      <c r="N70" s="176" t="n"/>
+      <c r="O70" s="102" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B71" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C71" s="168" t="n"/>
+      <c r="D71" s="169" t="n"/>
+      <c r="E71" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="171" t="n"/>
+      <c r="G71" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I71" s="171" t="n"/>
+      <c r="J71" s="174" t="n"/>
+      <c r="K71" s="169" t="n"/>
+      <c r="L71" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M70" s="182" t="n"/>
-      <c r="N70" s="183" t="n"/>
-      <c r="O70" s="102" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="191" t="n">
+      <c r="M71" s="182" t="n"/>
+      <c r="N71" s="183" t="n"/>
+      <c r="O71" s="102" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B71" s="102" t="n"/>
-      <c r="C71" s="102" t="n"/>
-      <c r="D71" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E71" s="102" t="n"/>
-      <c r="F71" s="102" t="n"/>
-      <c r="G71" s="102" t="n"/>
-      <c r="H71" s="102" t="n"/>
-      <c r="I71" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J71" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K71" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L71" s="102" t="n"/>
-      <c r="M71" s="102" t="n"/>
-      <c r="N71" s="102" t="n"/>
-      <c r="O71" s="102" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="102" t="n"/>
       <c r="B72" s="102" t="n"/>
       <c r="C72" s="102" t="n"/>
-      <c r="D72" s="102" t="n"/>
+      <c r="D72" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E72" s="102" t="n"/>
       <c r="F72" s="102" t="n"/>
       <c r="G72" s="102" t="n"/>
       <c r="H72" s="102" t="n"/>
-      <c r="I72" s="102" t="n"/>
-      <c r="J72" s="102" t="n"/>
-      <c r="K72" s="102" t="n"/>
+      <c r="I72" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J72" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K72" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L72" s="102" t="n"/>
       <c r="M72" s="102" t="n"/>
       <c r="N72" s="102" t="n"/>
@@ -5974,6 +6007,23 @@
       <c r="M75" s="102" t="n"/>
       <c r="N75" s="102" t="n"/>
       <c r="O75" s="102" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="102" t="n"/>
+      <c r="B76" s="102" t="n"/>
+      <c r="C76" s="102" t="n"/>
+      <c r="D76" s="102" t="n"/>
+      <c r="E76" s="102" t="n"/>
+      <c r="F76" s="102" t="n"/>
+      <c r="G76" s="102" t="n"/>
+      <c r="H76" s="102" t="n"/>
+      <c r="I76" s="102" t="n"/>
+      <c r="J76" s="102" t="n"/>
+      <c r="K76" s="102" t="n"/>
+      <c r="L76" s="102" t="n"/>
+      <c r="M76" s="102" t="n"/>
+      <c r="N76" s="102" t="n"/>
+      <c r="O76" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="171" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="172" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -333,6 +333,12 @@
       <name val="Aptos"/>
       <color rgb="009CA3AF"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <color rgb="001D4ED8"/>
     </font>
   </fonts>
   <fills count="20">
@@ -660,7 +666,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="236">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1325,6 +1331,24 @@
     <xf numFmtId="170" fontId="37" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="39" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="43" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="43" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="43" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3364,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3501,58 +3525,38 @@
       <c r="O4" s="102" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
-      <c r="A5" s="222" t="n">
-        <v>46093.82998256211</v>
-      </c>
-      <c r="B5" s="223" t="inlineStr">
+      <c r="A5" s="236" t="n">
+        <v>46093.84472162451</v>
+      </c>
+      <c r="B5" s="237" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C5" s="224" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D5" s="225" t="n">
+      <c r="D5" s="238" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E5" s="226" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F5" s="227" t="n">
-        <v>6.5536</v>
-      </c>
-      <c r="G5" s="228" t="n">
-        <v>-5.0993</v>
-      </c>
-      <c r="H5" s="229" t="n">
-        <v>-0.7781</v>
-      </c>
-      <c r="I5" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J5" s="230" t="n">
+      <c r="I5" s="239" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="J5" s="240" t="n">
         <v>20.49</v>
       </c>
-      <c r="K5" s="225" t="n">
+      <c r="K5" s="238" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="226" t="n">
-        <v>1.913</v>
-      </c>
-      <c r="M5" s="231" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
-        </is>
-      </c>
-      <c r="N5" s="232" t="inlineStr">
-        <is>
-          <t>Auto</t>
+      <c r="L5" s="241" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M5" s="237" t="inlineStr">
+        <is>
+          <t>Auto: FX, DE, SE</t>
         </is>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.82653238426</v>
+        <v>46093.82998255787</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3568,18 +3572,30 @@
       <c r="E6" s="226" t="n">
         <v>1.4543</v>
       </c>
-      <c r="F6" s="227" t="n"/>
-      <c r="G6" s="228" t="n"/>
-      <c r="H6" s="229" t="n"/>
-      <c r="I6" s="227" t="n"/>
-      <c r="J6" s="230" t="n"/>
+      <c r="F6" s="227" t="n">
+        <v>6.5536</v>
+      </c>
+      <c r="G6" s="228" t="n">
+        <v>-5.0993</v>
+      </c>
+      <c r="H6" s="229" t="n">
+        <v>-0.7781</v>
+      </c>
+      <c r="I6" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J6" s="230" t="n">
+        <v>20.49</v>
+      </c>
       <c r="K6" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L6" s="226" t="n"/>
+      <c r="L6" s="226" t="n">
+        <v>1.913</v>
+      </c>
       <c r="M6" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N6" s="232" t="inlineStr">
@@ -3590,7 +3606,7 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
       <c r="A7" s="222" t="n">
-        <v>46093.82300822917</v>
+        <v>46093.82653238426</v>
       </c>
       <c r="B7" s="223" t="inlineStr">
         <is>
@@ -3609,21 +3625,15 @@
       <c r="F7" s="227" t="n"/>
       <c r="G7" s="228" t="n"/>
       <c r="H7" s="229" t="n"/>
-      <c r="I7" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J7" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="I7" s="227" t="n"/>
+      <c r="J7" s="230" t="n"/>
       <c r="K7" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L7" s="226" t="n">
-        <v>1.913</v>
-      </c>
+      <c r="L7" s="226" t="n"/>
       <c r="M7" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL</t>
         </is>
       </c>
       <c r="N7" s="232" t="inlineStr">
@@ -3634,7 +3644,7 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46093.80209268518</v>
+        <v>46093.82300822917</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
@@ -3678,7 +3688,7 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
       <c r="A9" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46093.80209268518</v>
       </c>
       <c r="B9" s="223" t="inlineStr">
         <is>
@@ -3692,19 +3702,13 @@
         <v>4.2578</v>
       </c>
       <c r="E9" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F9" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G9" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H9" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F9" s="227" t="n"/>
+      <c r="G9" s="228" t="n"/>
+      <c r="H9" s="229" t="n"/>
       <c r="I9" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J9" s="230" t="n">
         <v>20.49</v>
@@ -3713,11 +3717,11 @@
         <v>10.7108</v>
       </c>
       <c r="L9" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M9" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N9" s="232" t="inlineStr">
@@ -3728,7 +3732,7 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
       <c r="A10" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B10" s="223" t="inlineStr">
         <is>
@@ -3741,20 +3745,17 @@
       <c r="D10" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E10" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E10" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F10" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G10" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G10" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H10" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I10" s="227" t="n">
         <v>2.086</v>
@@ -3765,310 +3766,328 @@
       <c r="K10" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L10" s="226">
+      <c r="L10" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M10" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N10" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1" s="101">
+      <c r="A11" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B11" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C11" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D11" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E11" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G11" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I11" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J11" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K11" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L11" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M10" s="231" t="inlineStr">
+      <c r="M11" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N10" s="232" t="inlineStr">
+      <c r="N11" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="211" t="n">
+    <row r="12" ht="21.75" customHeight="1" s="101">
+      <c r="A12" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B11" s="212" t="inlineStr">
+      <c r="B12" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C11" s="213" t="n"/>
-      <c r="D11" s="214" t="n">
+      <c r="C12" s="213" t="n"/>
+      <c r="D12" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E11" s="215">
+      <c r="E12" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F11" s="216" t="n"/>
-      <c r="G11" s="217">
+      <c r="F12" s="216" t="n"/>
+      <c r="G12" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H11" s="218">
+      <c r="H12" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I11" s="216" t="n">
+      <c r="I12" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J11" s="219" t="n">
+      <c r="J12" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K11" s="214" t="n">
+      <c r="K12" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L11" s="215">
+      <c r="L12" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M11" s="220" t="inlineStr">
+      <c r="M12" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N11" s="221" t="inlineStr">
+      <c r="N12" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="166" t="n">
+    <row r="13" ht="21.75" customHeight="1" s="101">
+      <c r="A13" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B12" s="167" t="inlineStr">
+      <c r="B13" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C12" s="168" t="n"/>
-      <c r="D12" s="169" t="n"/>
-      <c r="E12" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="171" t="n"/>
-      <c r="G12" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I12" s="171" t="n"/>
-      <c r="J12" s="174" t="n"/>
-      <c r="K12" s="169" t="n"/>
-      <c r="L12" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M12" s="175" t="n"/>
-      <c r="N12" s="176" t="n"/>
-      <c r="O12" s="102" t="n"/>
-    </row>
-    <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B13" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C13" s="168" t="n"/>
       <c r="D13" s="169" t="n"/>
-      <c r="E13" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E13" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F13" s="171" t="n"/>
-      <c r="G13" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G13" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I13" s="171" t="n"/>
       <c r="J13" s="174" t="n"/>
       <c r="K13" s="169" t="n"/>
-      <c r="L13" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="182" t="n"/>
-      <c r="N13" s="183" t="n"/>
+      <c r="L13" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="175" t="n"/>
+      <c r="N13" s="176" t="n"/>
       <c r="O13" s="102" t="n"/>
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B14" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A14" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B14" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E14" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G14" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="175" t="n"/>
-      <c r="N14" s="176" t="n"/>
+      <c r="L14" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="182" t="n"/>
+      <c r="N14" s="183" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B15" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A15" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B15" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E15" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G15" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="182" t="n"/>
-      <c r="N15" s="183" t="n"/>
+      <c r="L15" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="175" t="n"/>
+      <c r="N15" s="176" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B16" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A16" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B16" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E16" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G16" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="175" t="n"/>
-      <c r="N16" s="176" t="n"/>
+      <c r="L16" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="182" t="n"/>
+      <c r="N16" s="183" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B17" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A17" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B17" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E17" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G17" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="189" t="n"/>
-      <c r="N17" s="190" t="n"/>
+      <c r="L17" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="175" t="n"/>
+      <c r="N17" s="176" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
       <c r="A18" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B18" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
       <c r="E18" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
       <c r="G18" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H18" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
       <c r="L18" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M18" s="189" t="n"/>
@@ -4076,244 +4095,244 @@
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B19" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A19" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B19" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E19" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G19" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="182" t="n"/>
-      <c r="N19" s="183" t="n"/>
+      <c r="L19" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="189" t="n"/>
+      <c r="N19" s="190" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A20" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B20" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E20" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G20" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="175" t="n"/>
-      <c r="N20" s="176" t="n"/>
+      <c r="L20" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="182" t="n"/>
+      <c r="N20" s="183" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B21" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A21" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B21" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E21" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G21" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="182" t="n"/>
-      <c r="N21" s="183" t="n"/>
+      <c r="L21" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="175" t="n"/>
+      <c r="N21" s="176" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B22" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A22" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B22" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E22" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G22" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="175" t="n"/>
-      <c r="N22" s="176" t="n"/>
+      <c r="L22" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="182" t="n"/>
+      <c r="N22" s="183" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B23" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A23" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B23" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E23" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G23" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="182" t="n"/>
-      <c r="N23" s="183" t="n"/>
+      <c r="L23" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="175" t="n"/>
+      <c r="N23" s="176" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B24" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A24" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B24" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E24" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G24" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="189" t="n"/>
-      <c r="N24" s="190" t="n"/>
+      <c r="L24" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="182" t="n"/>
+      <c r="N24" s="183" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
       <c r="A25" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B25" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
       <c r="E25" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
       <c r="G25" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H25" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
       <c r="L25" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M25" s="189" t="n"/>
@@ -4321,244 +4340,244 @@
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B26" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A26" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B26" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E26" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G26" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="175" t="n"/>
-      <c r="N26" s="176" t="n"/>
+      <c r="L26" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="189" t="n"/>
+      <c r="N26" s="190" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B27" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A27" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B27" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E27" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G27" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="182" t="n"/>
-      <c r="N27" s="183" t="n"/>
+      <c r="L27" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="175" t="n"/>
+      <c r="N27" s="176" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B28" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A28" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B28" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E28" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G28" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="175" t="n"/>
-      <c r="N28" s="176" t="n"/>
+      <c r="L28" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="182" t="n"/>
+      <c r="N28" s="183" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B29" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A29" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B29" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E29" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G29" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="182" t="n"/>
-      <c r="N29" s="183" t="n"/>
+      <c r="L29" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="175" t="n"/>
+      <c r="N29" s="176" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B30" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A30" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B30" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E30" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G30" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="175" t="n"/>
-      <c r="N30" s="176" t="n"/>
+      <c r="L30" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="182" t="n"/>
+      <c r="N30" s="183" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B31" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A31" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B31" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E31" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G31" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="189" t="n"/>
-      <c r="N31" s="190" t="n"/>
+      <c r="L31" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="175" t="n"/>
+      <c r="N31" s="176" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
       <c r="A32" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B32" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
       <c r="E32" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
       <c r="G32" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H32" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
       <c r="L32" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M32" s="189" t="n"/>
@@ -4566,244 +4585,244 @@
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B33" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A33" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B33" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E33" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G33" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="182" t="n"/>
-      <c r="N33" s="183" t="n"/>
+      <c r="L33" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="189" t="n"/>
+      <c r="N33" s="190" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B34" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A34" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B34" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E34" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G34" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="175" t="n"/>
-      <c r="N34" s="176" t="n"/>
+      <c r="L34" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="182" t="n"/>
+      <c r="N34" s="183" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B35" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A35" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B35" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E35" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G35" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="182" t="n"/>
-      <c r="N35" s="183" t="n"/>
+      <c r="L35" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="175" t="n"/>
+      <c r="N35" s="176" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B36" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A36" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B36" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E36" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G36" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="175" t="n"/>
-      <c r="N36" s="176" t="n"/>
+      <c r="L36" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="182" t="n"/>
+      <c r="N36" s="183" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B37" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A37" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B37" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E37" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G37" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="182" t="n"/>
-      <c r="N37" s="183" t="n"/>
+      <c r="L37" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="175" t="n"/>
+      <c r="N37" s="176" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B38" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A38" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B38" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E38" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G38" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="189" t="n"/>
-      <c r="N38" s="190" t="n"/>
+      <c r="L38" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="182" t="n"/>
+      <c r="N38" s="183" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
       <c r="A39" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B39" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
       <c r="E39" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
       <c r="G39" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H39" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
       <c r="L39" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M39" s="189" t="n"/>
@@ -4811,244 +4830,244 @@
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B40" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A40" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B40" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E40" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G40" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="175" t="n"/>
-      <c r="N40" s="176" t="n"/>
+      <c r="L40" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="189" t="n"/>
+      <c r="N40" s="190" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B41" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A41" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B41" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E41" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G41" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="182" t="n"/>
-      <c r="N41" s="183" t="n"/>
+      <c r="L41" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="175" t="n"/>
+      <c r="N41" s="176" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B42" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A42" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B42" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E42" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G42" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="175" t="n"/>
-      <c r="N42" s="176" t="n"/>
+      <c r="L42" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="182" t="n"/>
+      <c r="N42" s="183" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B43" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A43" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B43" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E43" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G43" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="182" t="n"/>
-      <c r="N43" s="183" t="n"/>
+      <c r="L43" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="175" t="n"/>
+      <c r="N43" s="176" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B44" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A44" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B44" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E44" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G44" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="175" t="n"/>
-      <c r="N44" s="176" t="n"/>
+      <c r="L44" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="182" t="n"/>
+      <c r="N44" s="183" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B45" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A45" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B45" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E45" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G45" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="189" t="n"/>
-      <c r="N45" s="190" t="n"/>
+      <c r="L45" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="175" t="n"/>
+      <c r="N45" s="176" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
       <c r="A46" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B46" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
       <c r="E46" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
       <c r="G46" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H46" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
       <c r="L46" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M46" s="189" t="n"/>
@@ -5056,244 +5075,244 @@
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B47" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A47" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B47" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E47" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G47" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="182" t="n"/>
-      <c r="N47" s="183" t="n"/>
+      <c r="L47" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="189" t="n"/>
+      <c r="N47" s="190" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B48" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A48" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B48" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E48" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G48" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="175" t="n"/>
-      <c r="N48" s="176" t="n"/>
+      <c r="L48" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="182" t="n"/>
+      <c r="N48" s="183" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B49" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A49" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B49" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E49" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G49" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="182" t="n"/>
-      <c r="N49" s="183" t="n"/>
+      <c r="L49" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="175" t="n"/>
+      <c r="N49" s="176" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B50" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A50" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B50" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E50" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G50" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="175" t="n"/>
-      <c r="N50" s="176" t="n"/>
+      <c r="L50" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="182" t="n"/>
+      <c r="N50" s="183" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B51" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A51" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B51" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E51" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G51" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="182" t="n"/>
-      <c r="N51" s="183" t="n"/>
+      <c r="L51" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="175" t="n"/>
+      <c r="N51" s="176" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B52" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A52" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B52" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E52" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G52" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="189" t="n"/>
-      <c r="N52" s="190" t="n"/>
+      <c r="L52" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="182" t="n"/>
+      <c r="N52" s="183" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
       <c r="A53" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B53" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
       <c r="E53" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
       <c r="G53" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H53" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
       <c r="L53" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M53" s="189" t="n"/>
@@ -5301,244 +5320,244 @@
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B54" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A54" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B54" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E54" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G54" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="175" t="n"/>
-      <c r="N54" s="176" t="n"/>
+      <c r="L54" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="189" t="n"/>
+      <c r="N54" s="190" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B55" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A55" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B55" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E55" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G55" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="182" t="n"/>
-      <c r="N55" s="183" t="n"/>
+      <c r="L55" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="175" t="n"/>
+      <c r="N55" s="176" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B56" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A56" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B56" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E56" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G56" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="175" t="n"/>
-      <c r="N56" s="176" t="n"/>
+      <c r="L56" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="182" t="n"/>
+      <c r="N56" s="183" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B57" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A57" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B57" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E57" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G57" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="182" t="n"/>
-      <c r="N57" s="183" t="n"/>
+      <c r="L57" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="175" t="n"/>
+      <c r="N57" s="176" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B58" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A58" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B58" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E58" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G58" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="175" t="n"/>
-      <c r="N58" s="176" t="n"/>
+      <c r="L58" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="182" t="n"/>
+      <c r="N58" s="183" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B59" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A59" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B59" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E59" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G59" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="189" t="n"/>
-      <c r="N59" s="190" t="n"/>
+      <c r="L59" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="175" t="n"/>
+      <c r="N59" s="176" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
       <c r="A60" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B60" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
       <c r="E60" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
       <c r="G60" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H60" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
       <c r="L60" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M60" s="189" t="n"/>
@@ -5546,244 +5565,244 @@
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B61" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A61" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B61" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E61" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G61" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="182" t="n"/>
-      <c r="N61" s="183" t="n"/>
+      <c r="L61" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="189" t="n"/>
+      <c r="N61" s="190" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B62" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A62" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B62" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E62" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G62" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="175" t="n"/>
-      <c r="N62" s="176" t="n"/>
+      <c r="L62" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="182" t="n"/>
+      <c r="N62" s="183" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B63" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A63" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B63" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E63" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G63" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="182" t="n"/>
-      <c r="N63" s="183" t="n"/>
+      <c r="L63" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="175" t="n"/>
+      <c r="N63" s="176" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B64" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A64" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B64" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E64" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G64" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="175" t="n"/>
-      <c r="N64" s="176" t="n"/>
+      <c r="L64" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="182" t="n"/>
+      <c r="N64" s="183" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B65" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A65" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B65" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E65" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G65" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="182" t="n"/>
-      <c r="N65" s="183" t="n"/>
+      <c r="L65" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="175" t="n"/>
+      <c r="N65" s="176" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B66" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A66" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B66" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E66" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G66" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="189" t="n"/>
-      <c r="N66" s="190" t="n"/>
+      <c r="L66" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="182" t="n"/>
+      <c r="N66" s="183" t="n"/>
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
       <c r="A67" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B67" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
       <c r="E67" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
       <c r="G67" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H67" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
       <c r="L67" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M67" s="189" t="n"/>
@@ -5791,184 +5810,202 @@
       <c r="O67" s="102" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B68" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A68" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B68" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C68" s="168" t="n"/>
       <c r="D68" s="169" t="n"/>
-      <c r="E68" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E68" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F68" s="171" t="n"/>
-      <c r="G68" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G68" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I68" s="171" t="n"/>
       <c r="J68" s="174" t="n"/>
       <c r="K68" s="169" t="n"/>
-      <c r="L68" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M68" s="175" t="n"/>
-      <c r="N68" s="176" t="n"/>
+      <c r="L68" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M68" s="189" t="n"/>
+      <c r="N68" s="190" t="n"/>
       <c r="O68" s="102" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B69" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A69" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B69" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C69" s="168" t="n"/>
       <c r="D69" s="169" t="n"/>
-      <c r="E69" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E69" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F69" s="171" t="n"/>
-      <c r="G69" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G69" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I69" s="171" t="n"/>
       <c r="J69" s="174" t="n"/>
       <c r="K69" s="169" t="n"/>
-      <c r="L69" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M69" s="182" t="n"/>
-      <c r="N69" s="183" t="n"/>
+      <c r="L69" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M69" s="175" t="n"/>
+      <c r="N69" s="176" t="n"/>
       <c r="O69" s="102" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B70" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A70" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B70" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C70" s="168" t="n"/>
       <c r="D70" s="169" t="n"/>
-      <c r="E70" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E70" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F70" s="171" t="n"/>
-      <c r="G70" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G70" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I70" s="171" t="n"/>
       <c r="J70" s="174" t="n"/>
       <c r="K70" s="169" t="n"/>
-      <c r="L70" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M70" s="175" t="n"/>
-      <c r="N70" s="176" t="n"/>
+      <c r="L70" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M70" s="182" t="n"/>
+      <c r="N70" s="183" t="n"/>
       <c r="O70" s="102" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B71" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A71" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B71" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C71" s="168" t="n"/>
       <c r="D71" s="169" t="n"/>
-      <c r="E71" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E71" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F71" s="171" t="n"/>
-      <c r="G71" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G71" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I71" s="171" t="n"/>
       <c r="J71" s="174" t="n"/>
       <c r="K71" s="169" t="n"/>
-      <c r="L71" s="179">
+      <c r="L71" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M71" s="175" t="n"/>
+      <c r="N71" s="176" t="n"/>
+      <c r="O71" s="102" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B72" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C72" s="168" t="n"/>
+      <c r="D72" s="169" t="n"/>
+      <c r="E72" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F72" s="171" t="n"/>
+      <c r="G72" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H72" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I72" s="171" t="n"/>
+      <c r="J72" s="174" t="n"/>
+      <c r="K72" s="169" t="n"/>
+      <c r="L72" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M71" s="182" t="n"/>
-      <c r="N71" s="183" t="n"/>
-      <c r="O71" s="102" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="191" t="n">
+      <c r="M72" s="182" t="n"/>
+      <c r="N72" s="183" t="n"/>
+      <c r="O72" s="102" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B72" s="102" t="n"/>
-      <c r="C72" s="102" t="n"/>
-      <c r="D72" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E72" s="102" t="n"/>
-      <c r="F72" s="102" t="n"/>
-      <c r="G72" s="102" t="n"/>
-      <c r="H72" s="102" t="n"/>
-      <c r="I72" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J72" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K72" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L72" s="102" t="n"/>
-      <c r="M72" s="102" t="n"/>
-      <c r="N72" s="102" t="n"/>
-      <c r="O72" s="102" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="102" t="n"/>
       <c r="B73" s="102" t="n"/>
       <c r="C73" s="102" t="n"/>
-      <c r="D73" s="102" t="n"/>
+      <c r="D73" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E73" s="102" t="n"/>
       <c r="F73" s="102" t="n"/>
       <c r="G73" s="102" t="n"/>
       <c r="H73" s="102" t="n"/>
-      <c r="I73" s="102" t="n"/>
-      <c r="J73" s="102" t="n"/>
-      <c r="K73" s="102" t="n"/>
+      <c r="I73" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J73" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K73" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L73" s="102" t="n"/>
       <c r="M73" s="102" t="n"/>
       <c r="N73" s="102" t="n"/>
@@ -6024,6 +6061,23 @@
       <c r="M76" s="102" t="n"/>
       <c r="N76" s="102" t="n"/>
       <c r="O76" s="102" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="102" t="n"/>
+      <c r="B77" s="102" t="n"/>
+      <c r="C77" s="102" t="n"/>
+      <c r="D77" s="102" t="n"/>
+      <c r="E77" s="102" t="n"/>
+      <c r="F77" s="102" t="n"/>
+      <c r="G77" s="102" t="n"/>
+      <c r="H77" s="102" t="n"/>
+      <c r="I77" s="102" t="n"/>
+      <c r="J77" s="102" t="n"/>
+      <c r="K77" s="102" t="n"/>
+      <c r="L77" s="102" t="n"/>
+      <c r="M77" s="102" t="n"/>
+      <c r="N77" s="102" t="n"/>
+      <c r="O77" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3388,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3525,88 +3525,82 @@
       <c r="O4" s="102" t="n"/>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
-      <c r="A5" s="236" t="n">
-        <v>46093.84472162451</v>
-      </c>
-      <c r="B5" s="237" t="inlineStr">
+      <c r="A5" s="222" t="n">
+        <v>46093.84974698354</v>
+      </c>
+      <c r="B5" s="223" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D5" s="238" t="n">
+      <c r="C5" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D5" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="I5" s="239" t="n">
+      <c r="E5" s="226" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="F5" s="227" t="n"/>
+      <c r="G5" s="228" t="n"/>
+      <c r="H5" s="229" t="n"/>
+      <c r="I5" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J5" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K5" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L5" s="226" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="M5" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N5" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="101">
+      <c r="A6" s="236" t="n">
+        <v>46093.84472162037</v>
+      </c>
+      <c r="B6" s="237" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D6" s="238" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="I6" s="239" t="n">
         <v>1.266</v>
       </c>
-      <c r="J5" s="240" t="n">
+      <c r="J6" s="240" t="n">
         <v>20.49</v>
       </c>
-      <c r="K5" s="238" t="n">
+      <c r="K6" s="238" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="241" t="n">
+      <c r="L6" s="241" t="n">
         <v>1.913022369944355</v>
       </c>
-      <c r="M5" s="237" t="inlineStr">
+      <c r="M6" s="237" t="inlineStr">
         <is>
           <t>Auto: FX, DE, SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="222" t="n">
-        <v>46093.82998255787</v>
-      </c>
-      <c r="B6" s="223" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C6" s="224" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D6" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E6" s="226" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F6" s="227" t="n">
-        <v>6.5536</v>
-      </c>
-      <c r="G6" s="228" t="n">
-        <v>-5.0993</v>
-      </c>
-      <c r="H6" s="229" t="n">
-        <v>-0.7781</v>
-      </c>
-      <c r="I6" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J6" s="230" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K6" s="225" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L6" s="226" t="n">
-        <v>1.913</v>
-      </c>
-      <c r="M6" s="231" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
-        </is>
-      </c>
-      <c r="N6" s="232" t="inlineStr">
-        <is>
-          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
       <c r="A7" s="222" t="n">
-        <v>46093.82653238426</v>
+        <v>46093.82998255787</v>
       </c>
       <c r="B7" s="223" t="inlineStr">
         <is>
@@ -3622,18 +3616,30 @@
       <c r="E7" s="226" t="n">
         <v>1.4543</v>
       </c>
-      <c r="F7" s="227" t="n"/>
-      <c r="G7" s="228" t="n"/>
-      <c r="H7" s="229" t="n"/>
-      <c r="I7" s="227" t="n"/>
-      <c r="J7" s="230" t="n"/>
+      <c r="F7" s="227" t="n">
+        <v>6.5536</v>
+      </c>
+      <c r="G7" s="228" t="n">
+        <v>-5.0993</v>
+      </c>
+      <c r="H7" s="229" t="n">
+        <v>-0.7781</v>
+      </c>
+      <c r="I7" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J7" s="230" t="n">
+        <v>20.49</v>
+      </c>
       <c r="K7" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L7" s="226" t="n"/>
+      <c r="L7" s="226" t="n">
+        <v>1.913</v>
+      </c>
       <c r="M7" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N7" s="232" t="inlineStr">
@@ -3644,7 +3650,7 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46093.82300822917</v>
+        <v>46093.82653238426</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
@@ -3663,21 +3669,15 @@
       <c r="F8" s="227" t="n"/>
       <c r="G8" s="228" t="n"/>
       <c r="H8" s="229" t="n"/>
-      <c r="I8" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J8" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="I8" s="227" t="n"/>
+      <c r="J8" s="230" t="n"/>
       <c r="K8" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L8" s="226" t="n">
-        <v>1.913</v>
-      </c>
+      <c r="L8" s="226" t="n"/>
       <c r="M8" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL</t>
         </is>
       </c>
       <c r="N8" s="232" t="inlineStr">
@@ -3688,7 +3688,7 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
       <c r="A9" s="222" t="n">
-        <v>46093.80209268518</v>
+        <v>46093.82300822917</v>
       </c>
       <c r="B9" s="223" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
       <c r="A10" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46093.80209268518</v>
       </c>
       <c r="B10" s="223" t="inlineStr">
         <is>
@@ -3746,19 +3746,13 @@
         <v>4.2578</v>
       </c>
       <c r="E10" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F10" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G10" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H10" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F10" s="227" t="n"/>
+      <c r="G10" s="228" t="n"/>
+      <c r="H10" s="229" t="n"/>
       <c r="I10" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J10" s="230" t="n">
         <v>20.49</v>
@@ -3767,11 +3761,11 @@
         <v>10.7108</v>
       </c>
       <c r="L10" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M10" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N10" s="232" t="inlineStr">
@@ -3782,7 +3776,7 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
       <c r="A11" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B11" s="223" t="inlineStr">
         <is>
@@ -3795,20 +3789,17 @@
       <c r="D11" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E11" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E11" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F11" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G11" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G11" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H11" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I11" s="227" t="n">
         <v>2.086</v>
@@ -3819,310 +3810,328 @@
       <c r="K11" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L11" s="226">
+      <c r="L11" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M11" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N11" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.75" customHeight="1" s="101">
+      <c r="A12" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B12" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C12" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D12" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E12" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G12" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I12" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J12" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K12" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L12" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M11" s="231" t="inlineStr">
+      <c r="M12" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N11" s="232" t="inlineStr">
+      <c r="N12" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="211" t="n">
+    <row r="13" ht="21.75" customHeight="1" s="101">
+      <c r="A13" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B12" s="212" t="inlineStr">
+      <c r="B13" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C12" s="213" t="n"/>
-      <c r="D12" s="214" t="n">
+      <c r="C13" s="213" t="n"/>
+      <c r="D13" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E12" s="215">
+      <c r="E13" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F12" s="216" t="n"/>
-      <c r="G12" s="217">
+      <c r="F13" s="216" t="n"/>
+      <c r="G13" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H12" s="218">
+      <c r="H13" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I12" s="216" t="n">
+      <c r="I13" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J12" s="219" t="n">
+      <c r="J13" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K12" s="214" t="n">
+      <c r="K13" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L12" s="215">
+      <c r="L13" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M12" s="220" t="inlineStr">
+      <c r="M13" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N12" s="221" t="inlineStr">
+      <c r="N13" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="166" t="n">
+    <row r="14" ht="21.75" customHeight="1" s="101">
+      <c r="A14" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B13" s="167" t="inlineStr">
+      <c r="B14" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C13" s="168" t="n"/>
-      <c r="D13" s="169" t="n"/>
-      <c r="E13" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="171" t="n"/>
-      <c r="G13" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="171" t="n"/>
-      <c r="J13" s="174" t="n"/>
-      <c r="K13" s="169" t="n"/>
-      <c r="L13" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="175" t="n"/>
-      <c r="N13" s="176" t="n"/>
-      <c r="O13" s="102" t="n"/>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B14" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C14" s="168" t="n"/>
       <c r="D14" s="169" t="n"/>
-      <c r="E14" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E14" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F14" s="171" t="n"/>
-      <c r="G14" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G14" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I14" s="171" t="n"/>
       <c r="J14" s="174" t="n"/>
       <c r="K14" s="169" t="n"/>
-      <c r="L14" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="182" t="n"/>
-      <c r="N14" s="183" t="n"/>
+      <c r="L14" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M14" s="175" t="n"/>
+      <c r="N14" s="176" t="n"/>
       <c r="O14" s="102" t="n"/>
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B15" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A15" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B15" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E15" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G15" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="175" t="n"/>
-      <c r="N15" s="176" t="n"/>
+      <c r="L15" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="182" t="n"/>
+      <c r="N15" s="183" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B16" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A16" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B16" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E16" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G16" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="182" t="n"/>
-      <c r="N16" s="183" t="n"/>
+      <c r="L16" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="175" t="n"/>
+      <c r="N16" s="176" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B17" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A17" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B17" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E17" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G17" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="175" t="n"/>
-      <c r="N17" s="176" t="n"/>
+      <c r="L17" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="182" t="n"/>
+      <c r="N17" s="183" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B18" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A18" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B18" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E18" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G18" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="189" t="n"/>
-      <c r="N18" s="190" t="n"/>
+      <c r="L18" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="175" t="n"/>
+      <c r="N18" s="176" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
       <c r="A19" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B19" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
       <c r="E19" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
       <c r="G19" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H19" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
       <c r="L19" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M19" s="189" t="n"/>
@@ -4130,244 +4139,244 @@
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B20" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A20" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B20" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
-      <c r="E20" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E20" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
-      <c r="G20" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G20" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H20" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
-      <c r="L20" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="182" t="n"/>
-      <c r="N20" s="183" t="n"/>
+      <c r="L20" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M20" s="189" t="n"/>
+      <c r="N20" s="190" t="n"/>
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B21" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A21" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B21" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E21" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G21" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="175" t="n"/>
-      <c r="N21" s="176" t="n"/>
+      <c r="L21" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="182" t="n"/>
+      <c r="N21" s="183" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B22" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A22" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B22" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E22" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G22" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="182" t="n"/>
-      <c r="N22" s="183" t="n"/>
+      <c r="L22" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="175" t="n"/>
+      <c r="N22" s="176" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B23" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A23" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B23" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E23" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G23" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="175" t="n"/>
-      <c r="N23" s="176" t="n"/>
+      <c r="L23" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="182" t="n"/>
+      <c r="N23" s="183" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B24" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A24" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B24" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E24" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G24" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="182" t="n"/>
-      <c r="N24" s="183" t="n"/>
+      <c r="L24" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="175" t="n"/>
+      <c r="N24" s="176" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B25" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A25" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B25" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E25" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G25" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="189" t="n"/>
-      <c r="N25" s="190" t="n"/>
+      <c r="L25" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="182" t="n"/>
+      <c r="N25" s="183" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
       <c r="A26" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B26" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
       <c r="E26" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
       <c r="G26" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H26" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
       <c r="L26" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M26" s="189" t="n"/>
@@ -4375,244 +4384,244 @@
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B27" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A27" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B27" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
-      <c r="E27" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E27" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
-      <c r="G27" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G27" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
-      <c r="L27" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="175" t="n"/>
-      <c r="N27" s="176" t="n"/>
+      <c r="L27" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M27" s="189" t="n"/>
+      <c r="N27" s="190" t="n"/>
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B28" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A28" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B28" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E28" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G28" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="182" t="n"/>
-      <c r="N28" s="183" t="n"/>
+      <c r="L28" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="175" t="n"/>
+      <c r="N28" s="176" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B29" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A29" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B29" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E29" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G29" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="175" t="n"/>
-      <c r="N29" s="176" t="n"/>
+      <c r="L29" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="182" t="n"/>
+      <c r="N29" s="183" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B30" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A30" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B30" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E30" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G30" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="182" t="n"/>
-      <c r="N30" s="183" t="n"/>
+      <c r="L30" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="175" t="n"/>
+      <c r="N30" s="176" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B31" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A31" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B31" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E31" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G31" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="175" t="n"/>
-      <c r="N31" s="176" t="n"/>
+      <c r="L31" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="182" t="n"/>
+      <c r="N31" s="183" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B32" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A32" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B32" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E32" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G32" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="189" t="n"/>
-      <c r="N32" s="190" t="n"/>
+      <c r="L32" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="175" t="n"/>
+      <c r="N32" s="176" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
       <c r="A33" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B33" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
       <c r="E33" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
       <c r="G33" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H33" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
       <c r="L33" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M33" s="189" t="n"/>
@@ -4620,244 +4629,244 @@
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B34" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A34" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B34" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
-      <c r="E34" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E34" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
-      <c r="G34" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G34" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
-      <c r="L34" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="182" t="n"/>
-      <c r="N34" s="183" t="n"/>
+      <c r="L34" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M34" s="189" t="n"/>
+      <c r="N34" s="190" t="n"/>
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B35" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A35" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B35" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E35" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G35" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="175" t="n"/>
-      <c r="N35" s="176" t="n"/>
+      <c r="L35" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="182" t="n"/>
+      <c r="N35" s="183" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B36" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A36" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B36" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E36" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G36" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="182" t="n"/>
-      <c r="N36" s="183" t="n"/>
+      <c r="L36" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="175" t="n"/>
+      <c r="N36" s="176" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B37" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A37" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B37" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E37" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G37" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="175" t="n"/>
-      <c r="N37" s="176" t="n"/>
+      <c r="L37" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="182" t="n"/>
+      <c r="N37" s="183" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B38" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A38" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B38" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E38" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G38" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="182" t="n"/>
-      <c r="N38" s="183" t="n"/>
+      <c r="L38" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="175" t="n"/>
+      <c r="N38" s="176" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B39" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A39" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B39" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E39" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G39" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="189" t="n"/>
-      <c r="N39" s="190" t="n"/>
+      <c r="L39" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="182" t="n"/>
+      <c r="N39" s="183" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
       <c r="A40" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B40" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
       <c r="E40" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
       <c r="G40" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H40" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
       <c r="L40" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M40" s="189" t="n"/>
@@ -4865,244 +4874,244 @@
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B41" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A41" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B41" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
-      <c r="E41" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E41" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
-      <c r="G41" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G41" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
-      <c r="L41" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="175" t="n"/>
-      <c r="N41" s="176" t="n"/>
+      <c r="L41" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M41" s="189" t="n"/>
+      <c r="N41" s="190" t="n"/>
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B42" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A42" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B42" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E42" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G42" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="182" t="n"/>
-      <c r="N42" s="183" t="n"/>
+      <c r="L42" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="175" t="n"/>
+      <c r="N42" s="176" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B43" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A43" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B43" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E43" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G43" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="175" t="n"/>
-      <c r="N43" s="176" t="n"/>
+      <c r="L43" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="182" t="n"/>
+      <c r="N43" s="183" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B44" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A44" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B44" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E44" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G44" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="182" t="n"/>
-      <c r="N44" s="183" t="n"/>
+      <c r="L44" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="175" t="n"/>
+      <c r="N44" s="176" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B45" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A45" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B45" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E45" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G45" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="175" t="n"/>
-      <c r="N45" s="176" t="n"/>
+      <c r="L45" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="182" t="n"/>
+      <c r="N45" s="183" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B46" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A46" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B46" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E46" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G46" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="189" t="n"/>
-      <c r="N46" s="190" t="n"/>
+      <c r="L46" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="175" t="n"/>
+      <c r="N46" s="176" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
       <c r="A47" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B47" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
       <c r="E47" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
       <c r="G47" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H47" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
       <c r="L47" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M47" s="189" t="n"/>
@@ -5110,244 +5119,244 @@
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B48" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A48" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B48" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
-      <c r="E48" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E48" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
-      <c r="G48" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G48" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
-      <c r="L48" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="182" t="n"/>
-      <c r="N48" s="183" t="n"/>
+      <c r="L48" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M48" s="189" t="n"/>
+      <c r="N48" s="190" t="n"/>
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B49" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A49" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B49" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E49" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G49" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="175" t="n"/>
-      <c r="N49" s="176" t="n"/>
+      <c r="L49" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="182" t="n"/>
+      <c r="N49" s="183" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B50" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A50" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B50" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E50" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G50" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="182" t="n"/>
-      <c r="N50" s="183" t="n"/>
+      <c r="L50" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="175" t="n"/>
+      <c r="N50" s="176" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B51" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A51" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B51" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E51" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G51" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="175" t="n"/>
-      <c r="N51" s="176" t="n"/>
+      <c r="L51" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="182" t="n"/>
+      <c r="N51" s="183" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B52" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A52" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B52" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E52" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G52" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="182" t="n"/>
-      <c r="N52" s="183" t="n"/>
+      <c r="L52" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="175" t="n"/>
+      <c r="N52" s="176" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B53" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A53" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B53" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E53" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G53" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="189" t="n"/>
-      <c r="N53" s="190" t="n"/>
+      <c r="L53" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="182" t="n"/>
+      <c r="N53" s="183" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
       <c r="A54" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B54" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
       <c r="E54" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
       <c r="G54" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H54" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
       <c r="L54" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M54" s="189" t="n"/>
@@ -5355,244 +5364,244 @@
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B55" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A55" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B55" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
-      <c r="E55" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E55" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
-      <c r="G55" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G55" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
-      <c r="L55" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="175" t="n"/>
-      <c r="N55" s="176" t="n"/>
+      <c r="L55" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M55" s="189" t="n"/>
+      <c r="N55" s="190" t="n"/>
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B56" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A56" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B56" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E56" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G56" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="182" t="n"/>
-      <c r="N56" s="183" t="n"/>
+      <c r="L56" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="175" t="n"/>
+      <c r="N56" s="176" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B57" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A57" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B57" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E57" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G57" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="175" t="n"/>
-      <c r="N57" s="176" t="n"/>
+      <c r="L57" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="182" t="n"/>
+      <c r="N57" s="183" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B58" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A58" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B58" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E58" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G58" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="182" t="n"/>
-      <c r="N58" s="183" t="n"/>
+      <c r="L58" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="175" t="n"/>
+      <c r="N58" s="176" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B59" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A59" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B59" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E59" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G59" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="175" t="n"/>
-      <c r="N59" s="176" t="n"/>
+      <c r="L59" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="182" t="n"/>
+      <c r="N59" s="183" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B60" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A60" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B60" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E60" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G60" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="189" t="n"/>
-      <c r="N60" s="190" t="n"/>
+      <c r="L60" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="175" t="n"/>
+      <c r="N60" s="176" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
       <c r="A61" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B61" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
       <c r="E61" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
       <c r="G61" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H61" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
       <c r="L61" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M61" s="189" t="n"/>
@@ -5600,244 +5609,244 @@
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B62" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A62" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B62" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
-      <c r="E62" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E62" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
-      <c r="G62" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G62" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
-      <c r="L62" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="182" t="n"/>
-      <c r="N62" s="183" t="n"/>
+      <c r="L62" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M62" s="189" t="n"/>
+      <c r="N62" s="190" t="n"/>
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B63" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A63" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B63" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E63" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G63" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="175" t="n"/>
-      <c r="N63" s="176" t="n"/>
+      <c r="L63" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="182" t="n"/>
+      <c r="N63" s="183" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B64" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A64" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B64" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E64" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G64" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="182" t="n"/>
-      <c r="N64" s="183" t="n"/>
+      <c r="L64" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="175" t="n"/>
+      <c r="N64" s="176" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B65" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A65" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B65" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E65" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G65" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="175" t="n"/>
-      <c r="N65" s="176" t="n"/>
+      <c r="L65" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="182" t="n"/>
+      <c r="N65" s="183" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B66" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A66" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B66" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E66" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G66" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="182" t="n"/>
-      <c r="N66" s="183" t="n"/>
+      <c r="L66" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="175" t="n"/>
+      <c r="N66" s="176" t="n"/>
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B67" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A67" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B67" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
-      <c r="E67" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E67" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
-      <c r="G67" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G67" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
-      <c r="L67" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="189" t="n"/>
-      <c r="N67" s="190" t="n"/>
+      <c r="L67" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="182" t="n"/>
+      <c r="N67" s="183" t="n"/>
       <c r="O67" s="102" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="101">
       <c r="A68" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B68" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C68" s="168" t="n"/>
       <c r="D68" s="169" t="n"/>
       <c r="E68" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F68" s="171" t="n"/>
       <c r="G68" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H68" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I68" s="171" t="n"/>
       <c r="J68" s="174" t="n"/>
       <c r="K68" s="169" t="n"/>
       <c r="L68" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M68" s="189" t="n"/>
@@ -5845,184 +5854,202 @@
       <c r="O68" s="102" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B69" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A69" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B69" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C69" s="168" t="n"/>
       <c r="D69" s="169" t="n"/>
-      <c r="E69" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E69" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F69" s="171" t="n"/>
-      <c r="G69" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G69" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I69" s="171" t="n"/>
       <c r="J69" s="174" t="n"/>
       <c r="K69" s="169" t="n"/>
-      <c r="L69" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M69" s="175" t="n"/>
-      <c r="N69" s="176" t="n"/>
+      <c r="L69" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M69" s="189" t="n"/>
+      <c r="N69" s="190" t="n"/>
       <c r="O69" s="102" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B70" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A70" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B70" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C70" s="168" t="n"/>
       <c r="D70" s="169" t="n"/>
-      <c r="E70" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E70" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F70" s="171" t="n"/>
-      <c r="G70" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G70" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I70" s="171" t="n"/>
       <c r="J70" s="174" t="n"/>
       <c r="K70" s="169" t="n"/>
-      <c r="L70" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M70" s="182" t="n"/>
-      <c r="N70" s="183" t="n"/>
+      <c r="L70" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M70" s="175" t="n"/>
+      <c r="N70" s="176" t="n"/>
       <c r="O70" s="102" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B71" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A71" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B71" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C71" s="168" t="n"/>
       <c r="D71" s="169" t="n"/>
-      <c r="E71" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E71" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F71" s="171" t="n"/>
-      <c r="G71" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G71" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I71" s="171" t="n"/>
       <c r="J71" s="174" t="n"/>
       <c r="K71" s="169" t="n"/>
-      <c r="L71" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M71" s="175" t="n"/>
-      <c r="N71" s="176" t="n"/>
+      <c r="L71" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M71" s="182" t="n"/>
+      <c r="N71" s="183" t="n"/>
       <c r="O71" s="102" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B72" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A72" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B72" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C72" s="168" t="n"/>
       <c r="D72" s="169" t="n"/>
-      <c r="E72" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E72" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F72" s="171" t="n"/>
-      <c r="G72" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H72" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G72" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H72" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I72" s="171" t="n"/>
       <c r="J72" s="174" t="n"/>
       <c r="K72" s="169" t="n"/>
-      <c r="L72" s="179">
+      <c r="L72" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M72" s="175" t="n"/>
+      <c r="N72" s="176" t="n"/>
+      <c r="O72" s="102" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B73" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C73" s="168" t="n"/>
+      <c r="D73" s="169" t="n"/>
+      <c r="E73" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F73" s="171" t="n"/>
+      <c r="G73" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H73" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I73" s="171" t="n"/>
+      <c r="J73" s="174" t="n"/>
+      <c r="K73" s="169" t="n"/>
+      <c r="L73" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M72" s="182" t="n"/>
-      <c r="N72" s="183" t="n"/>
-      <c r="O72" s="102" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="191" t="n">
+      <c r="M73" s="182" t="n"/>
+      <c r="N73" s="183" t="n"/>
+      <c r="O73" s="102" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B73" s="102" t="n"/>
-      <c r="C73" s="102" t="n"/>
-      <c r="D73" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E73" s="102" t="n"/>
-      <c r="F73" s="102" t="n"/>
-      <c r="G73" s="102" t="n"/>
-      <c r="H73" s="102" t="n"/>
-      <c r="I73" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J73" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K73" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L73" s="102" t="n"/>
-      <c r="M73" s="102" t="n"/>
-      <c r="N73" s="102" t="n"/>
-      <c r="O73" s="102" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="102" t="n"/>
       <c r="B74" s="102" t="n"/>
       <c r="C74" s="102" t="n"/>
-      <c r="D74" s="102" t="n"/>
+      <c r="D74" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E74" s="102" t="n"/>
       <c r="F74" s="102" t="n"/>
       <c r="G74" s="102" t="n"/>
       <c r="H74" s="102" t="n"/>
-      <c r="I74" s="102" t="n"/>
-      <c r="J74" s="102" t="n"/>
-      <c r="K74" s="102" t="n"/>
+      <c r="I74" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J74" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K74" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L74" s="102" t="n"/>
       <c r="M74" s="102" t="n"/>
       <c r="N74" s="102" t="n"/>
@@ -6078,6 +6105,23 @@
       <c r="M77" s="102" t="n"/>
       <c r="N77" s="102" t="n"/>
       <c r="O77" s="102" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="102" t="n"/>
+      <c r="B78" s="102" t="n"/>
+      <c r="C78" s="102" t="n"/>
+      <c r="D78" s="102" t="n"/>
+      <c r="E78" s="102" t="n"/>
+      <c r="F78" s="102" t="n"/>
+      <c r="G78" s="102" t="n"/>
+      <c r="H78" s="102" t="n"/>
+      <c r="I78" s="102" t="n"/>
+      <c r="J78" s="102" t="n"/>
+      <c r="K78" s="102" t="n"/>
+      <c r="L78" s="102" t="n"/>
+      <c r="M78" s="102" t="n"/>
+      <c r="N78" s="102" t="n"/>
+      <c r="O78" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3388,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3526,7 +3526,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.84974698354</v>
+        <v>46093.86089493575</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3569,88 +3569,82 @@
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="236" t="n">
+      <c r="A6" s="222" t="n">
+        <v>46093.84974697917</v>
+      </c>
+      <c r="B6" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C6" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D6" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E6" s="226" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="F6" s="227" t="n"/>
+      <c r="G6" s="228" t="n"/>
+      <c r="H6" s="229" t="n"/>
+      <c r="I6" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J6" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K6" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L6" s="226" t="n">
+        <v>1.913</v>
+      </c>
+      <c r="M6" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N6" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" s="101">
+      <c r="A7" s="236" t="n">
         <v>46093.84472162037</v>
       </c>
-      <c r="B6" s="237" t="inlineStr">
+      <c r="B7" s="237" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D6" s="238" t="n">
+      <c r="D7" s="238" t="n">
         <v>4.2578</v>
       </c>
-      <c r="I6" s="239" t="n">
+      <c r="I7" s="239" t="n">
         <v>1.266</v>
       </c>
-      <c r="J6" s="240" t="n">
+      <c r="J7" s="240" t="n">
         <v>20.49</v>
       </c>
-      <c r="K6" s="238" t="n">
+      <c r="K7" s="238" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L6" s="241" t="n">
+      <c r="L7" s="241" t="n">
         <v>1.913022369944355</v>
       </c>
-      <c r="M6" s="237" t="inlineStr">
+      <c r="M7" s="237" t="inlineStr">
         <is>
           <t>Auto: FX, DE, SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="222" t="n">
-        <v>46093.82998255787</v>
-      </c>
-      <c r="B7" s="223" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C7" s="224" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D7" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E7" s="226" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F7" s="227" t="n">
-        <v>6.5536</v>
-      </c>
-      <c r="G7" s="228" t="n">
-        <v>-5.0993</v>
-      </c>
-      <c r="H7" s="229" t="n">
-        <v>-0.7781</v>
-      </c>
-      <c r="I7" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J7" s="230" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K7" s="225" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L7" s="226" t="n">
-        <v>1.913</v>
-      </c>
-      <c r="M7" s="231" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
-        </is>
-      </c>
-      <c r="N7" s="232" t="inlineStr">
-        <is>
-          <t>Auto</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46093.82653238426</v>
+        <v>46093.82998255787</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
@@ -3666,18 +3660,30 @@
       <c r="E8" s="226" t="n">
         <v>1.4543</v>
       </c>
-      <c r="F8" s="227" t="n"/>
-      <c r="G8" s="228" t="n"/>
-      <c r="H8" s="229" t="n"/>
-      <c r="I8" s="227" t="n"/>
-      <c r="J8" s="230" t="n"/>
+      <c r="F8" s="227" t="n">
+        <v>6.5536</v>
+      </c>
+      <c r="G8" s="228" t="n">
+        <v>-5.0993</v>
+      </c>
+      <c r="H8" s="229" t="n">
+        <v>-0.7781</v>
+      </c>
+      <c r="I8" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J8" s="230" t="n">
+        <v>20.49</v>
+      </c>
       <c r="K8" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L8" s="226" t="n"/>
+      <c r="L8" s="226" t="n">
+        <v>1.913</v>
+      </c>
       <c r="M8" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N8" s="232" t="inlineStr">
@@ -3688,7 +3694,7 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
       <c r="A9" s="222" t="n">
-        <v>46093.82300822917</v>
+        <v>46093.82653238426</v>
       </c>
       <c r="B9" s="223" t="inlineStr">
         <is>
@@ -3707,21 +3713,15 @@
       <c r="F9" s="227" t="n"/>
       <c r="G9" s="228" t="n"/>
       <c r="H9" s="229" t="n"/>
-      <c r="I9" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J9" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="I9" s="227" t="n"/>
+      <c r="J9" s="230" t="n"/>
       <c r="K9" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L9" s="226" t="n">
-        <v>1.913</v>
-      </c>
+      <c r="L9" s="226" t="n"/>
       <c r="M9" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL</t>
         </is>
       </c>
       <c r="N9" s="232" t="inlineStr">
@@ -3732,7 +3732,7 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
       <c r="A10" s="222" t="n">
-        <v>46093.80209268518</v>
+        <v>46093.82300822917</v>
       </c>
       <c r="B10" s="223" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
       <c r="A11" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46093.80209268518</v>
       </c>
       <c r="B11" s="223" t="inlineStr">
         <is>
@@ -3790,19 +3790,13 @@
         <v>4.2578</v>
       </c>
       <c r="E11" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F11" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G11" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H11" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
+        <v>1.4543</v>
+      </c>
+      <c r="F11" s="227" t="n"/>
+      <c r="G11" s="228" t="n"/>
+      <c r="H11" s="229" t="n"/>
       <c r="I11" s="227" t="n">
-        <v>2.086</v>
+        <v>2.163</v>
       </c>
       <c r="J11" s="230" t="n">
         <v>20.49</v>
@@ -3811,11 +3805,11 @@
         <v>10.7108</v>
       </c>
       <c r="L11" s="226" t="n">
-        <v>1.913022369944355</v>
+        <v>1.913</v>
       </c>
       <c r="M11" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N11" s="232" t="inlineStr">
@@ -3826,7 +3820,7 @@
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
       <c r="A12" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46093.79037730324</v>
       </c>
       <c r="B12" s="223" t="inlineStr">
         <is>
@@ -3839,20 +3833,17 @@
       <c r="D12" s="225" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E12" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
+      <c r="E12" s="226" t="n">
+        <v>1.45427215933111</v>
       </c>
       <c r="F12" s="227" t="n">
         <v>1.1128</v>
       </c>
-      <c r="G12" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
+      <c r="G12" s="228" t="n">
+        <v>0.3414721593311101</v>
+      </c>
+      <c r="H12" s="229" t="n">
+        <v>0.3068585184499552</v>
       </c>
       <c r="I12" s="227" t="n">
         <v>2.086</v>
@@ -3863,310 +3854,328 @@
       <c r="K12" s="225" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L12" s="226">
+      <c r="L12" s="226" t="n">
+        <v>1.913022369944355</v>
+      </c>
+      <c r="M12" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N12" s="232" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21.75" customHeight="1" s="101">
+      <c r="A13" s="222" t="n">
+        <v>46093.78404206019</v>
+      </c>
+      <c r="B13" s="223" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C13" s="224" t="n">
+        <v>6192</v>
+      </c>
+      <c r="D13" s="225" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E13" s="226">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="227" t="n">
+        <v>1.1128</v>
+      </c>
+      <c r="G13" s="228">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="229">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
+        <v/>
+      </c>
+      <c r="I13" s="227" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="J13" s="230" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K13" s="225" t="n">
+        <v>10.7108</v>
+      </c>
+      <c r="L13" s="226">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M12" s="231" t="inlineStr">
+      <c r="M13" s="231" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N12" s="232" t="inlineStr">
+      <c r="N13" s="232" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="211" t="n">
+    <row r="14" ht="21.75" customHeight="1" s="101">
+      <c r="A14" s="211" t="n">
         <v>46093.77185422453</v>
       </c>
-      <c r="B13" s="212" t="inlineStr">
+      <c r="B14" s="212" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C13" s="213" t="n"/>
-      <c r="D13" s="214" t="n">
+      <c r="C14" s="213" t="n"/>
+      <c r="D14" s="214" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E13" s="215">
+      <c r="E14" s="215">
         <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
-      <c r="F13" s="216" t="n"/>
-      <c r="G13" s="217">
+      <c r="F14" s="216" t="n"/>
+      <c r="G14" s="217">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
         <v/>
       </c>
-      <c r="H13" s="218">
+      <c r="H14" s="218">
         <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
-      <c r="I13" s="216" t="n">
+      <c r="I14" s="216" t="n">
         <v>2.086</v>
       </c>
-      <c r="J13" s="219" t="n">
+      <c r="J14" s="219" t="n">
         <v>20.49</v>
       </c>
-      <c r="K13" s="214" t="n">
+      <c r="K14" s="214" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L13" s="215">
+      <c r="L14" s="215">
         <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
         <v/>
       </c>
-      <c r="M13" s="220" t="inlineStr">
+      <c r="M14" s="220" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
       </c>
-      <c r="N13" s="221" t="inlineStr">
+      <c r="N14" s="221" t="inlineStr">
         <is>
           <t>Auto</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="166" t="n">
+    <row r="15" ht="21.75" customHeight="1" s="101">
+      <c r="A15" s="166" t="n">
         <v>45730</v>
       </c>
-      <c r="B14" s="167" t="inlineStr">
+      <c r="B15" s="167" t="inlineStr">
         <is>
           <t>Fri</t>
-        </is>
-      </c>
-      <c r="C14" s="168" t="n"/>
-      <c r="D14" s="169" t="n"/>
-      <c r="E14" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="171" t="n"/>
-      <c r="G14" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="171" t="n"/>
-      <c r="J14" s="174" t="n"/>
-      <c r="K14" s="169" t="n"/>
-      <c r="L14" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="175" t="n"/>
-      <c r="N14" s="176" t="n"/>
-      <c r="O14" s="102" t="n"/>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B15" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
         </is>
       </c>
       <c r="C15" s="168" t="n"/>
       <c r="D15" s="169" t="n"/>
-      <c r="E15" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
+      <c r="E15" s="170">
+        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
         <v/>
       </c>
       <c r="F15" s="171" t="n"/>
-      <c r="G15" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
+      <c r="G15" s="172">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="173">
+        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
         <v/>
       </c>
       <c r="I15" s="171" t="n"/>
       <c r="J15" s="174" t="n"/>
       <c r="K15" s="169" t="n"/>
-      <c r="L15" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="182" t="n"/>
-      <c r="N15" s="183" t="n"/>
+      <c r="L15" s="170">
+        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="175" t="n"/>
+      <c r="N15" s="176" t="n"/>
       <c r="O15" s="102" t="n"/>
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B16" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A16" s="177" t="n">
+        <v>45729</v>
+      </c>
+      <c r="B16" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C16" s="168" t="n"/>
       <c r="D16" s="169" t="n"/>
-      <c r="E16" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
+      <c r="E16" s="179">
+        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
         <v/>
       </c>
       <c r="F16" s="171" t="n"/>
-      <c r="G16" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
+      <c r="G16" s="180">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="181">
+        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
         <v/>
       </c>
       <c r="I16" s="171" t="n"/>
       <c r="J16" s="174" t="n"/>
       <c r="K16" s="169" t="n"/>
-      <c r="L16" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="175" t="n"/>
-      <c r="N16" s="176" t="n"/>
+      <c r="L16" s="179">
+        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="182" t="n"/>
+      <c r="N16" s="183" t="n"/>
       <c r="O16" s="102" t="n"/>
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B17" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A17" s="166" t="n">
+        <v>45728</v>
+      </c>
+      <c r="B17" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C17" s="168" t="n"/>
       <c r="D17" s="169" t="n"/>
-      <c r="E17" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
+      <c r="E17" s="170">
+        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
         <v/>
       </c>
       <c r="F17" s="171" t="n"/>
-      <c r="G17" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
+      <c r="G17" s="172">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="173">
+        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
         <v/>
       </c>
       <c r="I17" s="171" t="n"/>
       <c r="J17" s="174" t="n"/>
       <c r="K17" s="169" t="n"/>
-      <c r="L17" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="182" t="n"/>
-      <c r="N17" s="183" t="n"/>
+      <c r="L17" s="170">
+        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
+        <v/>
+      </c>
+      <c r="M17" s="175" t="n"/>
+      <c r="N17" s="176" t="n"/>
       <c r="O17" s="102" t="n"/>
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B18" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A18" s="177" t="n">
+        <v>45727</v>
+      </c>
+      <c r="B18" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C18" s="168" t="n"/>
       <c r="D18" s="169" t="n"/>
-      <c r="E18" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
+      <c r="E18" s="179">
+        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
         <v/>
       </c>
       <c r="F18" s="171" t="n"/>
-      <c r="G18" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
+      <c r="G18" s="180">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H18" s="181">
+        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
         <v/>
       </c>
       <c r="I18" s="171" t="n"/>
       <c r="J18" s="174" t="n"/>
       <c r="K18" s="169" t="n"/>
-      <c r="L18" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="175" t="n"/>
-      <c r="N18" s="176" t="n"/>
+      <c r="L18" s="179">
+        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="182" t="n"/>
+      <c r="N18" s="183" t="n"/>
       <c r="O18" s="102" t="n"/>
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B19" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A19" s="166" t="n">
+        <v>45726</v>
+      </c>
+      <c r="B19" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C19" s="168" t="n"/>
       <c r="D19" s="169" t="n"/>
-      <c r="E19" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
+      <c r="E19" s="170">
+        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
         <v/>
       </c>
       <c r="F19" s="171" t="n"/>
-      <c r="G19" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
+      <c r="G19" s="172">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="173">
+        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
         <v/>
       </c>
       <c r="I19" s="171" t="n"/>
       <c r="J19" s="174" t="n"/>
       <c r="K19" s="169" t="n"/>
-      <c r="L19" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="189" t="n"/>
-      <c r="N19" s="190" t="n"/>
+      <c r="L19" s="170">
+        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="175" t="n"/>
+      <c r="N19" s="176" t="n"/>
       <c r="O19" s="102" t="n"/>
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
       <c r="A20" s="184" t="n">
-        <v>45724</v>
+        <v>45725</v>
       </c>
       <c r="B20" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C20" s="168" t="n"/>
       <c r="D20" s="169" t="n"/>
       <c r="E20" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
+        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
         <v/>
       </c>
       <c r="F20" s="171" t="n"/>
       <c r="G20" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
         <v/>
       </c>
       <c r="H20" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
+        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
         <v/>
       </c>
       <c r="I20" s="171" t="n"/>
       <c r="J20" s="174" t="n"/>
       <c r="K20" s="169" t="n"/>
       <c r="L20" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
         <v/>
       </c>
       <c r="M20" s="189" t="n"/>
@@ -4174,244 +4183,244 @@
       <c r="O20" s="102" t="n"/>
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B21" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A21" s="184" t="n">
+        <v>45724</v>
+      </c>
+      <c r="B21" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C21" s="168" t="n"/>
       <c r="D21" s="169" t="n"/>
-      <c r="E21" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
+      <c r="E21" s="186">
+        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
         <v/>
       </c>
       <c r="F21" s="171" t="n"/>
-      <c r="G21" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
+      <c r="G21" s="187">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="188">
+        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
         <v/>
       </c>
       <c r="I21" s="171" t="n"/>
       <c r="J21" s="174" t="n"/>
       <c r="K21" s="169" t="n"/>
-      <c r="L21" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="182" t="n"/>
-      <c r="N21" s="183" t="n"/>
+      <c r="L21" s="186">
+        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="189" t="n"/>
+      <c r="N21" s="190" t="n"/>
       <c r="O21" s="102" t="n"/>
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B22" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A22" s="177" t="n">
+        <v>45723</v>
+      </c>
+      <c r="B22" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C22" s="168" t="n"/>
       <c r="D22" s="169" t="n"/>
-      <c r="E22" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
+      <c r="E22" s="179">
+        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
         <v/>
       </c>
       <c r="F22" s="171" t="n"/>
-      <c r="G22" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
+      <c r="G22" s="180">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H22" s="181">
+        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
         <v/>
       </c>
       <c r="I22" s="171" t="n"/>
       <c r="J22" s="174" t="n"/>
       <c r="K22" s="169" t="n"/>
-      <c r="L22" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="175" t="n"/>
-      <c r="N22" s="176" t="n"/>
+      <c r="L22" s="179">
+        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="182" t="n"/>
+      <c r="N22" s="183" t="n"/>
       <c r="O22" s="102" t="n"/>
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B23" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A23" s="166" t="n">
+        <v>45722</v>
+      </c>
+      <c r="B23" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C23" s="168" t="n"/>
       <c r="D23" s="169" t="n"/>
-      <c r="E23" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
+      <c r="E23" s="170">
+        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
         <v/>
       </c>
       <c r="F23" s="171" t="n"/>
-      <c r="G23" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
+      <c r="G23" s="172">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="173">
+        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
         <v/>
       </c>
       <c r="I23" s="171" t="n"/>
       <c r="J23" s="174" t="n"/>
       <c r="K23" s="169" t="n"/>
-      <c r="L23" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="182" t="n"/>
-      <c r="N23" s="183" t="n"/>
+      <c r="L23" s="170">
+        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
+        <v/>
+      </c>
+      <c r="M23" s="175" t="n"/>
+      <c r="N23" s="176" t="n"/>
       <c r="O23" s="102" t="n"/>
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B24" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A24" s="177" t="n">
+        <v>45721</v>
+      </c>
+      <c r="B24" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C24" s="168" t="n"/>
       <c r="D24" s="169" t="n"/>
-      <c r="E24" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
+      <c r="E24" s="179">
+        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
         <v/>
       </c>
       <c r="F24" s="171" t="n"/>
-      <c r="G24" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
+      <c r="G24" s="180">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H24" s="181">
+        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
         <v/>
       </c>
       <c r="I24" s="171" t="n"/>
       <c r="J24" s="174" t="n"/>
       <c r="K24" s="169" t="n"/>
-      <c r="L24" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="175" t="n"/>
-      <c r="N24" s="176" t="n"/>
+      <c r="L24" s="179">
+        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
+        <v/>
+      </c>
+      <c r="M24" s="182" t="n"/>
+      <c r="N24" s="183" t="n"/>
       <c r="O24" s="102" t="n"/>
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B25" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A25" s="166" t="n">
+        <v>45720</v>
+      </c>
+      <c r="B25" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C25" s="168" t="n"/>
       <c r="D25" s="169" t="n"/>
-      <c r="E25" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
+      <c r="E25" s="170">
+        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
         <v/>
       </c>
       <c r="F25" s="171" t="n"/>
-      <c r="G25" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
+      <c r="G25" s="172">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="173">
+        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
         <v/>
       </c>
       <c r="I25" s="171" t="n"/>
       <c r="J25" s="174" t="n"/>
       <c r="K25" s="169" t="n"/>
-      <c r="L25" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="182" t="n"/>
-      <c r="N25" s="183" t="n"/>
+      <c r="L25" s="170">
+        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
+        <v/>
+      </c>
+      <c r="M25" s="175" t="n"/>
+      <c r="N25" s="176" t="n"/>
       <c r="O25" s="102" t="n"/>
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B26" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A26" s="177" t="n">
+        <v>45719</v>
+      </c>
+      <c r="B26" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C26" s="168" t="n"/>
       <c r="D26" s="169" t="n"/>
-      <c r="E26" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
+      <c r="E26" s="179">
+        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
         <v/>
       </c>
       <c r="F26" s="171" t="n"/>
-      <c r="G26" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
+      <c r="G26" s="180">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H26" s="181">
+        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
         <v/>
       </c>
       <c r="I26" s="171" t="n"/>
       <c r="J26" s="174" t="n"/>
       <c r="K26" s="169" t="n"/>
-      <c r="L26" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="189" t="n"/>
-      <c r="N26" s="190" t="n"/>
+      <c r="L26" s="179">
+        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
+        <v/>
+      </c>
+      <c r="M26" s="182" t="n"/>
+      <c r="N26" s="183" t="n"/>
       <c r="O26" s="102" t="n"/>
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
       <c r="A27" s="184" t="n">
-        <v>45717</v>
+        <v>45718</v>
       </c>
       <c r="B27" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="169" t="n"/>
       <c r="E27" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
+        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
         <v/>
       </c>
       <c r="F27" s="171" t="n"/>
       <c r="G27" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
         <v/>
       </c>
       <c r="H27" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
+        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
         <v/>
       </c>
       <c r="I27" s="171" t="n"/>
       <c r="J27" s="174" t="n"/>
       <c r="K27" s="169" t="n"/>
       <c r="L27" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
         <v/>
       </c>
       <c r="M27" s="189" t="n"/>
@@ -4419,244 +4428,244 @@
       <c r="O27" s="102" t="n"/>
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B28" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A28" s="184" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B28" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C28" s="168" t="n"/>
       <c r="D28" s="169" t="n"/>
-      <c r="E28" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
+      <c r="E28" s="186">
+        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
         <v/>
       </c>
       <c r="F28" s="171" t="n"/>
-      <c r="G28" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
+      <c r="G28" s="187">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="188">
+        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
         <v/>
       </c>
       <c r="I28" s="171" t="n"/>
       <c r="J28" s="174" t="n"/>
       <c r="K28" s="169" t="n"/>
-      <c r="L28" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="175" t="n"/>
-      <c r="N28" s="176" t="n"/>
+      <c r="L28" s="186">
+        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
+        <v/>
+      </c>
+      <c r="M28" s="189" t="n"/>
+      <c r="N28" s="190" t="n"/>
       <c r="O28" s="102" t="n"/>
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B29" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A29" s="166" t="n">
+        <v>45716</v>
+      </c>
+      <c r="B29" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C29" s="168" t="n"/>
       <c r="D29" s="169" t="n"/>
-      <c r="E29" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
+      <c r="E29" s="170">
+        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
         <v/>
       </c>
       <c r="F29" s="171" t="n"/>
-      <c r="G29" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
+      <c r="G29" s="172">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="173">
+        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
         <v/>
       </c>
       <c r="I29" s="171" t="n"/>
       <c r="J29" s="174" t="n"/>
       <c r="K29" s="169" t="n"/>
-      <c r="L29" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="182" t="n"/>
-      <c r="N29" s="183" t="n"/>
+      <c r="L29" s="170">
+        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
+        <v/>
+      </c>
+      <c r="M29" s="175" t="n"/>
+      <c r="N29" s="176" t="n"/>
       <c r="O29" s="102" t="n"/>
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B30" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A30" s="177" t="n">
+        <v>45715</v>
+      </c>
+      <c r="B30" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C30" s="168" t="n"/>
       <c r="D30" s="169" t="n"/>
-      <c r="E30" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
+      <c r="E30" s="179">
+        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
         <v/>
       </c>
       <c r="F30" s="171" t="n"/>
-      <c r="G30" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
+      <c r="G30" s="180">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
+        <v/>
+      </c>
+      <c r="H30" s="181">
+        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
         <v/>
       </c>
       <c r="I30" s="171" t="n"/>
       <c r="J30" s="174" t="n"/>
       <c r="K30" s="169" t="n"/>
-      <c r="L30" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="175" t="n"/>
-      <c r="N30" s="176" t="n"/>
+      <c r="L30" s="179">
+        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
+        <v/>
+      </c>
+      <c r="M30" s="182" t="n"/>
+      <c r="N30" s="183" t="n"/>
       <c r="O30" s="102" t="n"/>
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B31" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A31" s="166" t="n">
+        <v>45714</v>
+      </c>
+      <c r="B31" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C31" s="168" t="n"/>
       <c r="D31" s="169" t="n"/>
-      <c r="E31" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
+      <c r="E31" s="170">
+        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
         <v/>
       </c>
       <c r="F31" s="171" t="n"/>
-      <c r="G31" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
+      <c r="G31" s="172">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="173">
+        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
         <v/>
       </c>
       <c r="I31" s="171" t="n"/>
       <c r="J31" s="174" t="n"/>
       <c r="K31" s="169" t="n"/>
-      <c r="L31" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="182" t="n"/>
-      <c r="N31" s="183" t="n"/>
+      <c r="L31" s="170">
+        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
+        <v/>
+      </c>
+      <c r="M31" s="175" t="n"/>
+      <c r="N31" s="176" t="n"/>
       <c r="O31" s="102" t="n"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B32" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A32" s="177" t="n">
+        <v>45713</v>
+      </c>
+      <c r="B32" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C32" s="168" t="n"/>
       <c r="D32" s="169" t="n"/>
-      <c r="E32" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
+      <c r="E32" s="179">
+        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
         <v/>
       </c>
       <c r="F32" s="171" t="n"/>
-      <c r="G32" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
+      <c r="G32" s="180">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="181">
+        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
         <v/>
       </c>
       <c r="I32" s="171" t="n"/>
       <c r="J32" s="174" t="n"/>
       <c r="K32" s="169" t="n"/>
-      <c r="L32" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="175" t="n"/>
-      <c r="N32" s="176" t="n"/>
+      <c r="L32" s="179">
+        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
+        <v/>
+      </c>
+      <c r="M32" s="182" t="n"/>
+      <c r="N32" s="183" t="n"/>
       <c r="O32" s="102" t="n"/>
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B33" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A33" s="166" t="n">
+        <v>45712</v>
+      </c>
+      <c r="B33" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C33" s="168" t="n"/>
       <c r="D33" s="169" t="n"/>
-      <c r="E33" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
+      <c r="E33" s="170">
+        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
         <v/>
       </c>
       <c r="F33" s="171" t="n"/>
-      <c r="G33" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
+      <c r="G33" s="172">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="173">
+        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
         <v/>
       </c>
       <c r="I33" s="171" t="n"/>
       <c r="J33" s="174" t="n"/>
       <c r="K33" s="169" t="n"/>
-      <c r="L33" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="189" t="n"/>
-      <c r="N33" s="190" t="n"/>
+      <c r="L33" s="170">
+        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
+        <v/>
+      </c>
+      <c r="M33" s="175" t="n"/>
+      <c r="N33" s="176" t="n"/>
       <c r="O33" s="102" t="n"/>
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
       <c r="A34" s="184" t="n">
-        <v>45710</v>
+        <v>45711</v>
       </c>
       <c r="B34" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C34" s="168" t="n"/>
       <c r="D34" s="169" t="n"/>
       <c r="E34" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
+        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
         <v/>
       </c>
       <c r="F34" s="171" t="n"/>
       <c r="G34" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
         <v/>
       </c>
       <c r="H34" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
+        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
         <v/>
       </c>
       <c r="I34" s="171" t="n"/>
       <c r="J34" s="174" t="n"/>
       <c r="K34" s="169" t="n"/>
       <c r="L34" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
         <v/>
       </c>
       <c r="M34" s="189" t="n"/>
@@ -4664,244 +4673,244 @@
       <c r="O34" s="102" t="n"/>
     </row>
     <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B35" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A35" s="184" t="n">
+        <v>45710</v>
+      </c>
+      <c r="B35" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C35" s="168" t="n"/>
       <c r="D35" s="169" t="n"/>
-      <c r="E35" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
+      <c r="E35" s="186">
+        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
         <v/>
       </c>
       <c r="F35" s="171" t="n"/>
-      <c r="G35" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
+      <c r="G35" s="187">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="188">
+        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
         <v/>
       </c>
       <c r="I35" s="171" t="n"/>
       <c r="J35" s="174" t="n"/>
       <c r="K35" s="169" t="n"/>
-      <c r="L35" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="182" t="n"/>
-      <c r="N35" s="183" t="n"/>
+      <c r="L35" s="186">
+        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="189" t="n"/>
+      <c r="N35" s="190" t="n"/>
       <c r="O35" s="102" t="n"/>
     </row>
     <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B36" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A36" s="177" t="n">
+        <v>45709</v>
+      </c>
+      <c r="B36" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C36" s="168" t="n"/>
       <c r="D36" s="169" t="n"/>
-      <c r="E36" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
+      <c r="E36" s="179">
+        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
         <v/>
       </c>
       <c r="F36" s="171" t="n"/>
-      <c r="G36" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
+      <c r="G36" s="180">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="181">
+        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
         <v/>
       </c>
       <c r="I36" s="171" t="n"/>
       <c r="J36" s="174" t="n"/>
       <c r="K36" s="169" t="n"/>
-      <c r="L36" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="175" t="n"/>
-      <c r="N36" s="176" t="n"/>
+      <c r="L36" s="179">
+        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
+        <v/>
+      </c>
+      <c r="M36" s="182" t="n"/>
+      <c r="N36" s="183" t="n"/>
       <c r="O36" s="102" t="n"/>
     </row>
     <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B37" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A37" s="166" t="n">
+        <v>45708</v>
+      </c>
+      <c r="B37" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C37" s="168" t="n"/>
       <c r="D37" s="169" t="n"/>
-      <c r="E37" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
+      <c r="E37" s="170">
+        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
         <v/>
       </c>
       <c r="F37" s="171" t="n"/>
-      <c r="G37" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
+      <c r="G37" s="172">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="173">
+        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
         <v/>
       </c>
       <c r="I37" s="171" t="n"/>
       <c r="J37" s="174" t="n"/>
       <c r="K37" s="169" t="n"/>
-      <c r="L37" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="182" t="n"/>
-      <c r="N37" s="183" t="n"/>
+      <c r="L37" s="170">
+        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="175" t="n"/>
+      <c r="N37" s="176" t="n"/>
       <c r="O37" s="102" t="n"/>
     </row>
     <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B38" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A38" s="177" t="n">
+        <v>45707</v>
+      </c>
+      <c r="B38" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C38" s="168" t="n"/>
       <c r="D38" s="169" t="n"/>
-      <c r="E38" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
+      <c r="E38" s="179">
+        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
         <v/>
       </c>
       <c r="F38" s="171" t="n"/>
-      <c r="G38" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
+      <c r="G38" s="180">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="181">
+        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
         <v/>
       </c>
       <c r="I38" s="171" t="n"/>
       <c r="J38" s="174" t="n"/>
       <c r="K38" s="169" t="n"/>
-      <c r="L38" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="175" t="n"/>
-      <c r="N38" s="176" t="n"/>
+      <c r="L38" s="179">
+        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
+        <v/>
+      </c>
+      <c r="M38" s="182" t="n"/>
+      <c r="N38" s="183" t="n"/>
       <c r="O38" s="102" t="n"/>
     </row>
     <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B39" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A39" s="166" t="n">
+        <v>45706</v>
+      </c>
+      <c r="B39" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C39" s="168" t="n"/>
       <c r="D39" s="169" t="n"/>
-      <c r="E39" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
+      <c r="E39" s="170">
+        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
         <v/>
       </c>
       <c r="F39" s="171" t="n"/>
-      <c r="G39" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
+      <c r="G39" s="172">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="173">
+        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
         <v/>
       </c>
       <c r="I39" s="171" t="n"/>
       <c r="J39" s="174" t="n"/>
       <c r="K39" s="169" t="n"/>
-      <c r="L39" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="182" t="n"/>
-      <c r="N39" s="183" t="n"/>
+      <c r="L39" s="170">
+        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
+        <v/>
+      </c>
+      <c r="M39" s="175" t="n"/>
+      <c r="N39" s="176" t="n"/>
       <c r="O39" s="102" t="n"/>
     </row>
     <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B40" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A40" s="177" t="n">
+        <v>45705</v>
+      </c>
+      <c r="B40" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C40" s="168" t="n"/>
       <c r="D40" s="169" t="n"/>
-      <c r="E40" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
+      <c r="E40" s="179">
+        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
         <v/>
       </c>
       <c r="F40" s="171" t="n"/>
-      <c r="G40" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
+      <c r="G40" s="180">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="181">
+        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
         <v/>
       </c>
       <c r="I40" s="171" t="n"/>
       <c r="J40" s="174" t="n"/>
       <c r="K40" s="169" t="n"/>
-      <c r="L40" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="189" t="n"/>
-      <c r="N40" s="190" t="n"/>
+      <c r="L40" s="179">
+        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
+        <v/>
+      </c>
+      <c r="M40" s="182" t="n"/>
+      <c r="N40" s="183" t="n"/>
       <c r="O40" s="102" t="n"/>
     </row>
     <row r="41" ht="21.75" customHeight="1" s="101">
       <c r="A41" s="184" t="n">
-        <v>45703</v>
+        <v>45704</v>
       </c>
       <c r="B41" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C41" s="168" t="n"/>
       <c r="D41" s="169" t="n"/>
       <c r="E41" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
+        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
         <v/>
       </c>
       <c r="F41" s="171" t="n"/>
       <c r="G41" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
         <v/>
       </c>
       <c r="H41" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
+        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
         <v/>
       </c>
       <c r="I41" s="171" t="n"/>
       <c r="J41" s="174" t="n"/>
       <c r="K41" s="169" t="n"/>
       <c r="L41" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
         <v/>
       </c>
       <c r="M41" s="189" t="n"/>
@@ -4909,244 +4918,244 @@
       <c r="O41" s="102" t="n"/>
     </row>
     <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B42" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A42" s="184" t="n">
+        <v>45703</v>
+      </c>
+      <c r="B42" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C42" s="168" t="n"/>
       <c r="D42" s="169" t="n"/>
-      <c r="E42" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
+      <c r="E42" s="186">
+        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
         <v/>
       </c>
       <c r="F42" s="171" t="n"/>
-      <c r="G42" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
+      <c r="G42" s="187">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="188">
+        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
         <v/>
       </c>
       <c r="I42" s="171" t="n"/>
       <c r="J42" s="174" t="n"/>
       <c r="K42" s="169" t="n"/>
-      <c r="L42" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="175" t="n"/>
-      <c r="N42" s="176" t="n"/>
+      <c r="L42" s="186">
+        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
+        <v/>
+      </c>
+      <c r="M42" s="189" t="n"/>
+      <c r="N42" s="190" t="n"/>
       <c r="O42" s="102" t="n"/>
     </row>
     <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B43" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A43" s="166" t="n">
+        <v>45702</v>
+      </c>
+      <c r="B43" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C43" s="168" t="n"/>
       <c r="D43" s="169" t="n"/>
-      <c r="E43" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
+      <c r="E43" s="170">
+        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
         <v/>
       </c>
       <c r="F43" s="171" t="n"/>
-      <c r="G43" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
+      <c r="G43" s="172">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="173">
+        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
         <v/>
       </c>
       <c r="I43" s="171" t="n"/>
       <c r="J43" s="174" t="n"/>
       <c r="K43" s="169" t="n"/>
-      <c r="L43" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="182" t="n"/>
-      <c r="N43" s="183" t="n"/>
+      <c r="L43" s="170">
+        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
+        <v/>
+      </c>
+      <c r="M43" s="175" t="n"/>
+      <c r="N43" s="176" t="n"/>
       <c r="O43" s="102" t="n"/>
     </row>
     <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B44" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A44" s="177" t="n">
+        <v>45701</v>
+      </c>
+      <c r="B44" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C44" s="168" t="n"/>
       <c r="D44" s="169" t="n"/>
-      <c r="E44" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
+      <c r="E44" s="179">
+        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
         <v/>
       </c>
       <c r="F44" s="171" t="n"/>
-      <c r="G44" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
+      <c r="G44" s="180">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="181">
+        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
         <v/>
       </c>
       <c r="I44" s="171" t="n"/>
       <c r="J44" s="174" t="n"/>
       <c r="K44" s="169" t="n"/>
-      <c r="L44" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="175" t="n"/>
-      <c r="N44" s="176" t="n"/>
+      <c r="L44" s="179">
+        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
+        <v/>
+      </c>
+      <c r="M44" s="182" t="n"/>
+      <c r="N44" s="183" t="n"/>
       <c r="O44" s="102" t="n"/>
     </row>
     <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B45" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A45" s="166" t="n">
+        <v>45700</v>
+      </c>
+      <c r="B45" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C45" s="168" t="n"/>
       <c r="D45" s="169" t="n"/>
-      <c r="E45" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
+      <c r="E45" s="170">
+        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
         <v/>
       </c>
       <c r="F45" s="171" t="n"/>
-      <c r="G45" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
+      <c r="G45" s="172">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="173">
+        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
         <v/>
       </c>
       <c r="I45" s="171" t="n"/>
       <c r="J45" s="174" t="n"/>
       <c r="K45" s="169" t="n"/>
-      <c r="L45" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="182" t="n"/>
-      <c r="N45" s="183" t="n"/>
+      <c r="L45" s="170">
+        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
+        <v/>
+      </c>
+      <c r="M45" s="175" t="n"/>
+      <c r="N45" s="176" t="n"/>
       <c r="O45" s="102" t="n"/>
     </row>
     <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B46" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A46" s="177" t="n">
+        <v>45699</v>
+      </c>
+      <c r="B46" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C46" s="168" t="n"/>
       <c r="D46" s="169" t="n"/>
-      <c r="E46" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
+      <c r="E46" s="179">
+        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
         <v/>
       </c>
       <c r="F46" s="171" t="n"/>
-      <c r="G46" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
+      <c r="G46" s="180">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="181">
+        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
         <v/>
       </c>
       <c r="I46" s="171" t="n"/>
       <c r="J46" s="174" t="n"/>
       <c r="K46" s="169" t="n"/>
-      <c r="L46" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="175" t="n"/>
-      <c r="N46" s="176" t="n"/>
+      <c r="L46" s="179">
+        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
+        <v/>
+      </c>
+      <c r="M46" s="182" t="n"/>
+      <c r="N46" s="183" t="n"/>
       <c r="O46" s="102" t="n"/>
     </row>
     <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B47" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A47" s="166" t="n">
+        <v>45698</v>
+      </c>
+      <c r="B47" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C47" s="168" t="n"/>
       <c r="D47" s="169" t="n"/>
-      <c r="E47" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
+      <c r="E47" s="170">
+        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
         <v/>
       </c>
       <c r="F47" s="171" t="n"/>
-      <c r="G47" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
+      <c r="G47" s="172">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="173">
+        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
         <v/>
       </c>
       <c r="I47" s="171" t="n"/>
       <c r="J47" s="174" t="n"/>
       <c r="K47" s="169" t="n"/>
-      <c r="L47" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="189" t="n"/>
-      <c r="N47" s="190" t="n"/>
+      <c r="L47" s="170">
+        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
+        <v/>
+      </c>
+      <c r="M47" s="175" t="n"/>
+      <c r="N47" s="176" t="n"/>
       <c r="O47" s="102" t="n"/>
     </row>
     <row r="48" ht="21.75" customHeight="1" s="101">
       <c r="A48" s="184" t="n">
-        <v>45696</v>
+        <v>45697</v>
       </c>
       <c r="B48" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C48" s="168" t="n"/>
       <c r="D48" s="169" t="n"/>
       <c r="E48" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
+        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
         <v/>
       </c>
       <c r="F48" s="171" t="n"/>
       <c r="G48" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
         <v/>
       </c>
       <c r="H48" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
+        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
         <v/>
       </c>
       <c r="I48" s="171" t="n"/>
       <c r="J48" s="174" t="n"/>
       <c r="K48" s="169" t="n"/>
       <c r="L48" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
         <v/>
       </c>
       <c r="M48" s="189" t="n"/>
@@ -5154,244 +5163,244 @@
       <c r="O48" s="102" t="n"/>
     </row>
     <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B49" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A49" s="184" t="n">
+        <v>45696</v>
+      </c>
+      <c r="B49" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C49" s="168" t="n"/>
       <c r="D49" s="169" t="n"/>
-      <c r="E49" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
+      <c r="E49" s="186">
+        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
         <v/>
       </c>
       <c r="F49" s="171" t="n"/>
-      <c r="G49" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
+      <c r="G49" s="187">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="188">
+        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
         <v/>
       </c>
       <c r="I49" s="171" t="n"/>
       <c r="J49" s="174" t="n"/>
       <c r="K49" s="169" t="n"/>
-      <c r="L49" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="182" t="n"/>
-      <c r="N49" s="183" t="n"/>
+      <c r="L49" s="186">
+        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
+        <v/>
+      </c>
+      <c r="M49" s="189" t="n"/>
+      <c r="N49" s="190" t="n"/>
       <c r="O49" s="102" t="n"/>
     </row>
     <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B50" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A50" s="177" t="n">
+        <v>45695</v>
+      </c>
+      <c r="B50" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C50" s="168" t="n"/>
       <c r="D50" s="169" t="n"/>
-      <c r="E50" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
+      <c r="E50" s="179">
+        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
         <v/>
       </c>
       <c r="F50" s="171" t="n"/>
-      <c r="G50" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
+      <c r="G50" s="180">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="181">
+        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
         <v/>
       </c>
       <c r="I50" s="171" t="n"/>
       <c r="J50" s="174" t="n"/>
       <c r="K50" s="169" t="n"/>
-      <c r="L50" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="175" t="n"/>
-      <c r="N50" s="176" t="n"/>
+      <c r="L50" s="179">
+        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
+        <v/>
+      </c>
+      <c r="M50" s="182" t="n"/>
+      <c r="N50" s="183" t="n"/>
       <c r="O50" s="102" t="n"/>
     </row>
     <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B51" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A51" s="166" t="n">
+        <v>45694</v>
+      </c>
+      <c r="B51" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C51" s="168" t="n"/>
       <c r="D51" s="169" t="n"/>
-      <c r="E51" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
+      <c r="E51" s="170">
+        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
         <v/>
       </c>
       <c r="F51" s="171" t="n"/>
-      <c r="G51" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
+      <c r="G51" s="172">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="173">
+        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
         <v/>
       </c>
       <c r="I51" s="171" t="n"/>
       <c r="J51" s="174" t="n"/>
       <c r="K51" s="169" t="n"/>
-      <c r="L51" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="182" t="n"/>
-      <c r="N51" s="183" t="n"/>
+      <c r="L51" s="170">
+        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
+        <v/>
+      </c>
+      <c r="M51" s="175" t="n"/>
+      <c r="N51" s="176" t="n"/>
       <c r="O51" s="102" t="n"/>
     </row>
     <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B52" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A52" s="177" t="n">
+        <v>45693</v>
+      </c>
+      <c r="B52" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C52" s="168" t="n"/>
       <c r="D52" s="169" t="n"/>
-      <c r="E52" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
+      <c r="E52" s="179">
+        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
         <v/>
       </c>
       <c r="F52" s="171" t="n"/>
-      <c r="G52" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
+      <c r="G52" s="180">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="181">
+        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
         <v/>
       </c>
       <c r="I52" s="171" t="n"/>
       <c r="J52" s="174" t="n"/>
       <c r="K52" s="169" t="n"/>
-      <c r="L52" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="175" t="n"/>
-      <c r="N52" s="176" t="n"/>
+      <c r="L52" s="179">
+        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
+        <v/>
+      </c>
+      <c r="M52" s="182" t="n"/>
+      <c r="N52" s="183" t="n"/>
       <c r="O52" s="102" t="n"/>
     </row>
     <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B53" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A53" s="166" t="n">
+        <v>45692</v>
+      </c>
+      <c r="B53" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C53" s="168" t="n"/>
       <c r="D53" s="169" t="n"/>
-      <c r="E53" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
+      <c r="E53" s="170">
+        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
         <v/>
       </c>
       <c r="F53" s="171" t="n"/>
-      <c r="G53" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
+      <c r="G53" s="172">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="173">
+        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
         <v/>
       </c>
       <c r="I53" s="171" t="n"/>
       <c r="J53" s="174" t="n"/>
       <c r="K53" s="169" t="n"/>
-      <c r="L53" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="182" t="n"/>
-      <c r="N53" s="183" t="n"/>
+      <c r="L53" s="170">
+        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
+        <v/>
+      </c>
+      <c r="M53" s="175" t="n"/>
+      <c r="N53" s="176" t="n"/>
       <c r="O53" s="102" t="n"/>
     </row>
     <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B54" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A54" s="177" t="n">
+        <v>45691</v>
+      </c>
+      <c r="B54" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C54" s="168" t="n"/>
       <c r="D54" s="169" t="n"/>
-      <c r="E54" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
+      <c r="E54" s="179">
+        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
         <v/>
       </c>
       <c r="F54" s="171" t="n"/>
-      <c r="G54" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
+      <c r="G54" s="180">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="181">
+        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
         <v/>
       </c>
       <c r="I54" s="171" t="n"/>
       <c r="J54" s="174" t="n"/>
       <c r="K54" s="169" t="n"/>
-      <c r="L54" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="189" t="n"/>
-      <c r="N54" s="190" t="n"/>
+      <c r="L54" s="179">
+        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
+        <v/>
+      </c>
+      <c r="M54" s="182" t="n"/>
+      <c r="N54" s="183" t="n"/>
       <c r="O54" s="102" t="n"/>
     </row>
     <row r="55" ht="21.75" customHeight="1" s="101">
       <c r="A55" s="184" t="n">
-        <v>45689</v>
+        <v>45690</v>
       </c>
       <c r="B55" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C55" s="168" t="n"/>
       <c r="D55" s="169" t="n"/>
       <c r="E55" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
+        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
         <v/>
       </c>
       <c r="F55" s="171" t="n"/>
       <c r="G55" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
         <v/>
       </c>
       <c r="H55" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
+        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
         <v/>
       </c>
       <c r="I55" s="171" t="n"/>
       <c r="J55" s="174" t="n"/>
       <c r="K55" s="169" t="n"/>
       <c r="L55" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
         <v/>
       </c>
       <c r="M55" s="189" t="n"/>
@@ -5399,244 +5408,244 @@
       <c r="O55" s="102" t="n"/>
     </row>
     <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B56" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A56" s="184" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B56" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C56" s="168" t="n"/>
       <c r="D56" s="169" t="n"/>
-      <c r="E56" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
+      <c r="E56" s="186">
+        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
         <v/>
       </c>
       <c r="F56" s="171" t="n"/>
-      <c r="G56" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
+      <c r="G56" s="187">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="188">
+        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
         <v/>
       </c>
       <c r="I56" s="171" t="n"/>
       <c r="J56" s="174" t="n"/>
       <c r="K56" s="169" t="n"/>
-      <c r="L56" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="175" t="n"/>
-      <c r="N56" s="176" t="n"/>
+      <c r="L56" s="186">
+        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
+        <v/>
+      </c>
+      <c r="M56" s="189" t="n"/>
+      <c r="N56" s="190" t="n"/>
       <c r="O56" s="102" t="n"/>
     </row>
     <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B57" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A57" s="166" t="n">
+        <v>45688</v>
+      </c>
+      <c r="B57" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C57" s="168" t="n"/>
       <c r="D57" s="169" t="n"/>
-      <c r="E57" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
+      <c r="E57" s="170">
+        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
         <v/>
       </c>
       <c r="F57" s="171" t="n"/>
-      <c r="G57" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
+      <c r="G57" s="172">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="173">
+        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
         <v/>
       </c>
       <c r="I57" s="171" t="n"/>
       <c r="J57" s="174" t="n"/>
       <c r="K57" s="169" t="n"/>
-      <c r="L57" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="182" t="n"/>
-      <c r="N57" s="183" t="n"/>
+      <c r="L57" s="170">
+        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
+        <v/>
+      </c>
+      <c r="M57" s="175" t="n"/>
+      <c r="N57" s="176" t="n"/>
       <c r="O57" s="102" t="n"/>
     </row>
     <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B58" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A58" s="177" t="n">
+        <v>45687</v>
+      </c>
+      <c r="B58" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C58" s="168" t="n"/>
       <c r="D58" s="169" t="n"/>
-      <c r="E58" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
+      <c r="E58" s="179">
+        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
         <v/>
       </c>
       <c r="F58" s="171" t="n"/>
-      <c r="G58" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
+      <c r="G58" s="180">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="181">
+        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
         <v/>
       </c>
       <c r="I58" s="171" t="n"/>
       <c r="J58" s="174" t="n"/>
       <c r="K58" s="169" t="n"/>
-      <c r="L58" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="175" t="n"/>
-      <c r="N58" s="176" t="n"/>
+      <c r="L58" s="179">
+        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
+        <v/>
+      </c>
+      <c r="M58" s="182" t="n"/>
+      <c r="N58" s="183" t="n"/>
       <c r="O58" s="102" t="n"/>
     </row>
     <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B59" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A59" s="166" t="n">
+        <v>45686</v>
+      </c>
+      <c r="B59" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C59" s="168" t="n"/>
       <c r="D59" s="169" t="n"/>
-      <c r="E59" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
+      <c r="E59" s="170">
+        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
         <v/>
       </c>
       <c r="F59" s="171" t="n"/>
-      <c r="G59" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
+      <c r="G59" s="172">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="173">
+        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
         <v/>
       </c>
       <c r="I59" s="171" t="n"/>
       <c r="J59" s="174" t="n"/>
       <c r="K59" s="169" t="n"/>
-      <c r="L59" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="182" t="n"/>
-      <c r="N59" s="183" t="n"/>
+      <c r="L59" s="170">
+        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
+        <v/>
+      </c>
+      <c r="M59" s="175" t="n"/>
+      <c r="N59" s="176" t="n"/>
       <c r="O59" s="102" t="n"/>
     </row>
     <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B60" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A60" s="177" t="n">
+        <v>45685</v>
+      </c>
+      <c r="B60" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C60" s="168" t="n"/>
       <c r="D60" s="169" t="n"/>
-      <c r="E60" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
+      <c r="E60" s="179">
+        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
         <v/>
       </c>
       <c r="F60" s="171" t="n"/>
-      <c r="G60" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
+      <c r="G60" s="180">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="181">
+        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
         <v/>
       </c>
       <c r="I60" s="171" t="n"/>
       <c r="J60" s="174" t="n"/>
       <c r="K60" s="169" t="n"/>
-      <c r="L60" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="175" t="n"/>
-      <c r="N60" s="176" t="n"/>
+      <c r="L60" s="179">
+        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
+        <v/>
+      </c>
+      <c r="M60" s="182" t="n"/>
+      <c r="N60" s="183" t="n"/>
       <c r="O60" s="102" t="n"/>
     </row>
     <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B61" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A61" s="166" t="n">
+        <v>45684</v>
+      </c>
+      <c r="B61" s="167" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C61" s="168" t="n"/>
       <c r="D61" s="169" t="n"/>
-      <c r="E61" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
+      <c r="E61" s="170">
+        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
         <v/>
       </c>
       <c r="F61" s="171" t="n"/>
-      <c r="G61" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
+      <c r="G61" s="172">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="173">
+        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
         <v/>
       </c>
       <c r="I61" s="171" t="n"/>
       <c r="J61" s="174" t="n"/>
       <c r="K61" s="169" t="n"/>
-      <c r="L61" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="189" t="n"/>
-      <c r="N61" s="190" t="n"/>
+      <c r="L61" s="170">
+        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
+        <v/>
+      </c>
+      <c r="M61" s="175" t="n"/>
+      <c r="N61" s="176" t="n"/>
       <c r="O61" s="102" t="n"/>
     </row>
     <row r="62" ht="21.75" customHeight="1" s="101">
       <c r="A62" s="184" t="n">
-        <v>45682</v>
+        <v>45683</v>
       </c>
       <c r="B62" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C62" s="168" t="n"/>
       <c r="D62" s="169" t="n"/>
       <c r="E62" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
+        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
         <v/>
       </c>
       <c r="F62" s="171" t="n"/>
       <c r="G62" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
         <v/>
       </c>
       <c r="H62" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
+        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
         <v/>
       </c>
       <c r="I62" s="171" t="n"/>
       <c r="J62" s="174" t="n"/>
       <c r="K62" s="169" t="n"/>
       <c r="L62" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
         <v/>
       </c>
       <c r="M62" s="189" t="n"/>
@@ -5644,244 +5653,244 @@
       <c r="O62" s="102" t="n"/>
     </row>
     <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B63" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A63" s="184" t="n">
+        <v>45682</v>
+      </c>
+      <c r="B63" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C63" s="168" t="n"/>
       <c r="D63" s="169" t="n"/>
-      <c r="E63" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
+      <c r="E63" s="186">
+        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
         <v/>
       </c>
       <c r="F63" s="171" t="n"/>
-      <c r="G63" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
+      <c r="G63" s="187">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="188">
+        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
         <v/>
       </c>
       <c r="I63" s="171" t="n"/>
       <c r="J63" s="174" t="n"/>
       <c r="K63" s="169" t="n"/>
-      <c r="L63" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="182" t="n"/>
-      <c r="N63" s="183" t="n"/>
+      <c r="L63" s="186">
+        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
+        <v/>
+      </c>
+      <c r="M63" s="189" t="n"/>
+      <c r="N63" s="190" t="n"/>
       <c r="O63" s="102" t="n"/>
     </row>
     <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B64" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A64" s="177" t="n">
+        <v>45681</v>
+      </c>
+      <c r="B64" s="178" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C64" s="168" t="n"/>
       <c r="D64" s="169" t="n"/>
-      <c r="E64" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
+      <c r="E64" s="179">
+        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
         <v/>
       </c>
       <c r="F64" s="171" t="n"/>
-      <c r="G64" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
+      <c r="G64" s="180">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="181">
+        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
         <v/>
       </c>
       <c r="I64" s="171" t="n"/>
       <c r="J64" s="174" t="n"/>
       <c r="K64" s="169" t="n"/>
-      <c r="L64" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="175" t="n"/>
-      <c r="N64" s="176" t="n"/>
+      <c r="L64" s="179">
+        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="182" t="n"/>
+      <c r="N64" s="183" t="n"/>
       <c r="O64" s="102" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B65" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A65" s="166" t="n">
+        <v>45680</v>
+      </c>
+      <c r="B65" s="167" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C65" s="168" t="n"/>
       <c r="D65" s="169" t="n"/>
-      <c r="E65" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
+      <c r="E65" s="170">
+        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
         <v/>
       </c>
       <c r="F65" s="171" t="n"/>
-      <c r="G65" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
+      <c r="G65" s="172">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="173">
+        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
         <v/>
       </c>
       <c r="I65" s="171" t="n"/>
       <c r="J65" s="174" t="n"/>
       <c r="K65" s="169" t="n"/>
-      <c r="L65" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="182" t="n"/>
-      <c r="N65" s="183" t="n"/>
+      <c r="L65" s="170">
+        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
+        <v/>
+      </c>
+      <c r="M65" s="175" t="n"/>
+      <c r="N65" s="176" t="n"/>
       <c r="O65" s="102" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B66" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A66" s="177" t="n">
+        <v>45679</v>
+      </c>
+      <c r="B66" s="178" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C66" s="168" t="n"/>
       <c r="D66" s="169" t="n"/>
-      <c r="E66" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
+      <c r="E66" s="179">
+        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
         <v/>
       </c>
       <c r="F66" s="171" t="n"/>
-      <c r="G66" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
+      <c r="G66" s="180">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="181">
+        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
         <v/>
       </c>
       <c r="I66" s="171" t="n"/>
       <c r="J66" s="174" t="n"/>
       <c r="K66" s="169" t="n"/>
-      <c r="L66" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="175" t="n"/>
-      <c r="N66" s="176" t="n"/>
+      <c r="L66" s="179">
+        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
+        <v/>
+      </c>
+      <c r="M66" s="182" t="n"/>
+      <c r="N66" s="183" t="n"/>
       <c r="O66" s="102" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B67" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
+      <c r="A67" s="166" t="n">
+        <v>45678</v>
+      </c>
+      <c r="B67" s="167" t="inlineStr">
+        <is>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C67" s="168" t="n"/>
       <c r="D67" s="169" t="n"/>
-      <c r="E67" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
+      <c r="E67" s="170">
+        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
         <v/>
       </c>
       <c r="F67" s="171" t="n"/>
-      <c r="G67" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
+      <c r="G67" s="172">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="173">
+        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
         <v/>
       </c>
       <c r="I67" s="171" t="n"/>
       <c r="J67" s="174" t="n"/>
       <c r="K67" s="169" t="n"/>
-      <c r="L67" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="182" t="n"/>
-      <c r="N67" s="183" t="n"/>
+      <c r="L67" s="170">
+        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
+        <v/>
+      </c>
+      <c r="M67" s="175" t="n"/>
+      <c r="N67" s="176" t="n"/>
       <c r="O67" s="102" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B68" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
+      <c r="A68" s="177" t="n">
+        <v>45677</v>
+      </c>
+      <c r="B68" s="178" t="inlineStr">
+        <is>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C68" s="168" t="n"/>
       <c r="D68" s="169" t="n"/>
-      <c r="E68" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
+      <c r="E68" s="179">
+        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
         <v/>
       </c>
       <c r="F68" s="171" t="n"/>
-      <c r="G68" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
+      <c r="G68" s="180">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="181">
+        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
         <v/>
       </c>
       <c r="I68" s="171" t="n"/>
       <c r="J68" s="174" t="n"/>
       <c r="K68" s="169" t="n"/>
-      <c r="L68" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M68" s="189" t="n"/>
-      <c r="N68" s="190" t="n"/>
+      <c r="L68" s="179">
+        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
+        <v/>
+      </c>
+      <c r="M68" s="182" t="n"/>
+      <c r="N68" s="183" t="n"/>
       <c r="O68" s="102" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1" s="101">
       <c r="A69" s="184" t="n">
-        <v>45675</v>
+        <v>45676</v>
       </c>
       <c r="B69" s="185" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C69" s="168" t="n"/>
       <c r="D69" s="169" t="n"/>
       <c r="E69" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
+        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
         <v/>
       </c>
       <c r="F69" s="171" t="n"/>
       <c r="G69" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
         <v/>
       </c>
       <c r="H69" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
+        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
         <v/>
       </c>
       <c r="I69" s="171" t="n"/>
       <c r="J69" s="174" t="n"/>
       <c r="K69" s="169" t="n"/>
       <c r="L69" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
         <v/>
       </c>
       <c r="M69" s="189" t="n"/>
@@ -5889,184 +5898,202 @@
       <c r="O69" s="102" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B70" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
+      <c r="A70" s="184" t="n">
+        <v>45675</v>
+      </c>
+      <c r="B70" s="185" t="inlineStr">
+        <is>
+          <t>Sat</t>
         </is>
       </c>
       <c r="C70" s="168" t="n"/>
       <c r="D70" s="169" t="n"/>
-      <c r="E70" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
+      <c r="E70" s="186">
+        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
         <v/>
       </c>
       <c r="F70" s="171" t="n"/>
-      <c r="G70" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
+      <c r="G70" s="187">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="188">
+        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
         <v/>
       </c>
       <c r="I70" s="171" t="n"/>
       <c r="J70" s="174" t="n"/>
       <c r="K70" s="169" t="n"/>
-      <c r="L70" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M70" s="175" t="n"/>
-      <c r="N70" s="176" t="n"/>
+      <c r="L70" s="186">
+        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
+        <v/>
+      </c>
+      <c r="M70" s="189" t="n"/>
+      <c r="N70" s="190" t="n"/>
       <c r="O70" s="102" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B71" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
+      <c r="A71" s="166" t="n">
+        <v>45674</v>
+      </c>
+      <c r="B71" s="167" t="inlineStr">
+        <is>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C71" s="168" t="n"/>
       <c r="D71" s="169" t="n"/>
-      <c r="E71" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
+      <c r="E71" s="170">
+        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
         <v/>
       </c>
       <c r="F71" s="171" t="n"/>
-      <c r="G71" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
+      <c r="G71" s="172">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="173">
+        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
         <v/>
       </c>
       <c r="I71" s="171" t="n"/>
       <c r="J71" s="174" t="n"/>
       <c r="K71" s="169" t="n"/>
-      <c r="L71" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M71" s="182" t="n"/>
-      <c r="N71" s="183" t="n"/>
+      <c r="L71" s="170">
+        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
+        <v/>
+      </c>
+      <c r="M71" s="175" t="n"/>
+      <c r="N71" s="176" t="n"/>
       <c r="O71" s="102" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B72" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
+      <c r="A72" s="177" t="n">
+        <v>45673</v>
+      </c>
+      <c r="B72" s="178" t="inlineStr">
+        <is>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C72" s="168" t="n"/>
       <c r="D72" s="169" t="n"/>
-      <c r="E72" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
+      <c r="E72" s="179">
+        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
         <v/>
       </c>
       <c r="F72" s="171" t="n"/>
-      <c r="G72" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H72" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
+      <c r="G72" s="180">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
+        <v/>
+      </c>
+      <c r="H72" s="181">
+        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
         <v/>
       </c>
       <c r="I72" s="171" t="n"/>
       <c r="J72" s="174" t="n"/>
       <c r="K72" s="169" t="n"/>
-      <c r="L72" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M72" s="175" t="n"/>
-      <c r="N72" s="176" t="n"/>
+      <c r="L72" s="179">
+        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
+        <v/>
+      </c>
+      <c r="M72" s="182" t="n"/>
+      <c r="N72" s="183" t="n"/>
       <c r="O72" s="102" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B73" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
+      <c r="A73" s="166" t="n">
+        <v>45672</v>
+      </c>
+      <c r="B73" s="167" t="inlineStr">
+        <is>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C73" s="168" t="n"/>
       <c r="D73" s="169" t="n"/>
-      <c r="E73" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+      <c r="E73" s="170">
+        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
         <v/>
       </c>
       <c r="F73" s="171" t="n"/>
-      <c r="G73" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H73" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+      <c r="G73" s="172">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H73" s="173">
+        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
         <v/>
       </c>
       <c r="I73" s="171" t="n"/>
       <c r="J73" s="174" t="n"/>
       <c r="K73" s="169" t="n"/>
-      <c r="L73" s="179">
+      <c r="L73" s="170">
+        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
+        <v/>
+      </c>
+      <c r="M73" s="175" t="n"/>
+      <c r="N73" s="176" t="n"/>
+      <c r="O73" s="102" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="177" t="n">
+        <v>45671</v>
+      </c>
+      <c r="B74" s="178" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C74" s="168" t="n"/>
+      <c r="D74" s="169" t="n"/>
+      <c r="E74" s="179">
+        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
+        <v/>
+      </c>
+      <c r="F74" s="171" t="n"/>
+      <c r="G74" s="180">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H74" s="181">
+        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
+        <v/>
+      </c>
+      <c r="I74" s="171" t="n"/>
+      <c r="J74" s="174" t="n"/>
+      <c r="K74" s="169" t="n"/>
+      <c r="L74" s="179">
         <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
         <v/>
       </c>
-      <c r="M73" s="182" t="n"/>
-      <c r="N73" s="183" t="n"/>
-      <c r="O73" s="102" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="191" t="n">
+      <c r="M74" s="182" t="n"/>
+      <c r="N74" s="183" t="n"/>
+      <c r="O74" s="102" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="191" t="n">
         <v>46093</v>
       </c>
-      <c r="B74" s="102" t="n"/>
-      <c r="C74" s="102" t="n"/>
-      <c r="D74" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E74" s="102" t="n"/>
-      <c r="F74" s="102" t="n"/>
-      <c r="G74" s="102" t="n"/>
-      <c r="H74" s="102" t="n"/>
-      <c r="I74" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J74" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K74" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L74" s="102" t="n"/>
-      <c r="M74" s="102" t="n"/>
-      <c r="N74" s="102" t="n"/>
-      <c r="O74" s="102" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="102" t="n"/>
       <c r="B75" s="102" t="n"/>
       <c r="C75" s="102" t="n"/>
-      <c r="D75" s="102" t="n"/>
+      <c r="D75" s="102" t="n">
+        <v>4.2523</v>
+      </c>
       <c r="E75" s="102" t="n"/>
       <c r="F75" s="102" t="n"/>
       <c r="G75" s="102" t="n"/>
       <c r="H75" s="102" t="n"/>
-      <c r="I75" s="102" t="n"/>
-      <c r="J75" s="102" t="n"/>
-      <c r="K75" s="102" t="n"/>
+      <c r="I75" s="102" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="J75" s="102" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="K75" s="102" t="n">
+        <v>10.6543</v>
+      </c>
       <c r="L75" s="102" t="n"/>
       <c r="M75" s="102" t="n"/>
       <c r="N75" s="102" t="n"/>
@@ -6122,6 +6149,23 @@
       <c r="M78" s="102" t="n"/>
       <c r="N78" s="102" t="n"/>
       <c r="O78" s="102" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="102" t="n"/>
+      <c r="B79" s="102" t="n"/>
+      <c r="C79" s="102" t="n"/>
+      <c r="D79" s="102" t="n"/>
+      <c r="E79" s="102" t="n"/>
+      <c r="F79" s="102" t="n"/>
+      <c r="G79" s="102" t="n"/>
+      <c r="H79" s="102" t="n"/>
+      <c r="I79" s="102" t="n"/>
+      <c r="J79" s="102" t="n"/>
+      <c r="K79" s="102" t="n"/>
+      <c r="L79" s="102" t="n"/>
+      <c r="M79" s="102" t="n"/>
+      <c r="N79" s="102" t="n"/>
+      <c r="O79" s="102" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3388,7 +3388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="100" min="1" max="1"/>
@@ -3526,40 +3526,46 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46093.86089493575</v>
+        <v>46094.2966857986</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C5" s="224" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D5" s="225" t="n">
         <v>4.2578</v>
       </c>
       <c r="E5" s="226" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F5" s="227" t="n"/>
-      <c r="G5" s="228" t="n"/>
-      <c r="H5" s="229" t="n"/>
+        <v>1.5029</v>
+      </c>
+      <c r="F5" s="227" t="n">
+        <v>1.1651</v>
+      </c>
+      <c r="G5" s="228" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="H5" s="229" t="n">
+        <v>0.2899</v>
+      </c>
       <c r="I5" s="227" t="n">
         <v>2.163</v>
       </c>
       <c r="J5" s="230" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K5" s="225" t="n">
         <v>10.7108</v>
       </c>
       <c r="L5" s="226" t="n">
-        <v>1.913</v>
+        <v>1.9644</v>
       </c>
       <c r="M5" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N5" s="232" t="inlineStr">
@@ -3570,7 +3576,7 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.84974697917</v>
+        <v>46093.29668083334</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3578,13 +3584,13 @@
         </is>
       </c>
       <c r="C6" s="224" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D6" s="225" t="n">
         <v>4.2578</v>
       </c>
       <c r="E6" s="226" t="n">
-        <v>1.4543</v>
+        <v>1.5029</v>
       </c>
       <c r="F6" s="227" t="n"/>
       <c r="G6" s="228" t="n"/>
@@ -3593,13 +3599,13 @@
         <v>2.163</v>
       </c>
       <c r="J6" s="230" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K6" s="225" t="n">
         <v>10.7108</v>
       </c>
       <c r="L6" s="226" t="n">
-        <v>1.913</v>
+        <v>1.9644</v>
       </c>
       <c r="M6" s="231" t="inlineStr">
         <is>
@@ -3608,2565 +3614,1021 @@
       </c>
       <c r="N6" s="232" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="236" t="n">
-        <v>46093.84472162037</v>
-      </c>
-      <c r="B7" s="237" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D7" s="238" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="I7" s="239" t="n">
-        <v>1.266</v>
-      </c>
-      <c r="J7" s="240" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K7" s="238" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L7" s="241" t="n">
-        <v>1.913022369944355</v>
-      </c>
-      <c r="M7" s="237" t="inlineStr">
-        <is>
-          <t>Auto: FX, DE, SE</t>
+      <c r="A7" s="222" t="n">
+        <v>46092.29668083334</v>
+      </c>
+      <c r="B7" s="223" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C7" s="224" t="n">
+        <v>6399</v>
+      </c>
+      <c r="D7" s="225" t="n">
+        <v>4.2523</v>
+      </c>
+      <c r="E7" s="226" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="F7" s="227" t="n"/>
+      <c r="G7" s="228" t="n"/>
+      <c r="H7" s="229" t="n"/>
+      <c r="I7" s="227" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J7" s="230" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="K7" s="225" t="n">
+        <v>10.6543</v>
+      </c>
+      <c r="L7" s="226" t="n">
+        <v>1.9748</v>
+      </c>
+      <c r="M7" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N7" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46093.82998255787</v>
+        <v>46091.29668083334</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C8" s="224" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D8" s="225" t="n">
-        <v>4.2578</v>
+        <v>4.2548</v>
       </c>
       <c r="E8" s="226" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F8" s="227" t="n">
-        <v>6.5536</v>
-      </c>
-      <c r="G8" s="228" t="n">
-        <v>-5.0993</v>
-      </c>
-      <c r="H8" s="229" t="n">
-        <v>-0.7781</v>
-      </c>
+        <v>1.5039</v>
+      </c>
+      <c r="F8" s="227" t="n"/>
+      <c r="G8" s="228" t="n"/>
+      <c r="H8" s="229" t="n"/>
       <c r="I8" s="227" t="n">
         <v>2.163</v>
       </c>
       <c r="J8" s="230" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K8" s="225" t="n">
-        <v>10.7108</v>
+        <v>10.606</v>
       </c>
       <c r="L8" s="226" t="n">
-        <v>1.913</v>
+        <v>1.9838</v>
       </c>
       <c r="M8" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
       <c r="N8" s="232" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
       <c r="A9" s="222" t="n">
-        <v>46093.82653238426</v>
+        <v>46090.29668083334</v>
       </c>
       <c r="B9" s="223" t="inlineStr">
         <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C9" s="224" t="n">
-        <v>6192</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C9" s="224" t="n"/>
       <c r="D9" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E9" s="226" t="n">
-        <v>1.4543</v>
-      </c>
+        <v>4.2785</v>
+      </c>
+      <c r="E9" s="226" t="n"/>
       <c r="F9" s="227" t="n"/>
       <c r="G9" s="228" t="n"/>
       <c r="H9" s="229" t="n"/>
-      <c r="I9" s="227" t="n"/>
+      <c r="I9" s="227" t="n">
+        <v>2.163</v>
+      </c>
       <c r="J9" s="230" t="n"/>
       <c r="K9" s="225" t="n">
-        <v>10.7108</v>
+        <v>10.6945</v>
       </c>
       <c r="L9" s="226" t="n"/>
       <c r="M9" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL</t>
+          <t>Auto: FX,DE</t>
         </is>
       </c>
       <c r="N9" s="232" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
       <c r="A10" s="222" t="n">
-        <v>46093.82300822917</v>
+        <v>46087.29668083334</v>
       </c>
       <c r="B10" s="223" t="inlineStr">
         <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C10" s="224" t="n">
-        <v>6192</v>
-      </c>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C10" s="224" t="n"/>
       <c r="D10" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E10" s="226" t="n">
-        <v>1.4543</v>
-      </c>
+        <v>4.2875</v>
+      </c>
+      <c r="E10" s="226" t="n"/>
       <c r="F10" s="227" t="n"/>
       <c r="G10" s="228" t="n"/>
       <c r="H10" s="229" t="n"/>
       <c r="I10" s="227" t="n">
         <v>2.163</v>
       </c>
-      <c r="J10" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="J10" s="230" t="n"/>
       <c r="K10" s="225" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L10" s="226" t="n">
-        <v>1.913</v>
-      </c>
+        <v>10.693</v>
+      </c>
+      <c r="L10" s="226" t="n"/>
       <c r="M10" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,DE</t>
         </is>
       </c>
       <c r="N10" s="232" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
       <c r="A11" s="222" t="n">
-        <v>46093.80209268518</v>
+        <v>46086.29668083334</v>
       </c>
       <c r="B11" s="223" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C11" s="224" t="n">
-        <v>6192</v>
-      </c>
+      <c r="C11" s="224" t="n"/>
       <c r="D11" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E11" s="226" t="n">
-        <v>1.4543</v>
-      </c>
+        <v>4.2725</v>
+      </c>
+      <c r="E11" s="226" t="n"/>
       <c r="F11" s="227" t="n"/>
       <c r="G11" s="228" t="n"/>
       <c r="H11" s="229" t="n"/>
-      <c r="I11" s="227" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J11" s="230" t="n">
-        <v>20.49</v>
-      </c>
+      <c r="I11" s="227" t="n"/>
+      <c r="J11" s="230" t="n"/>
       <c r="K11" s="225" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L11" s="226" t="n">
-        <v>1.913</v>
-      </c>
+        <v>10.6885</v>
+      </c>
+      <c r="L11" s="226" t="n"/>
       <c r="M11" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX</t>
         </is>
       </c>
       <c r="N11" s="232" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
       <c r="A12" s="222" t="n">
-        <v>46093.79037730324</v>
+        <v>46085.29668083334</v>
       </c>
       <c r="B12" s="223" t="inlineStr">
         <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C12" s="224" t="n">
-        <v>6192</v>
-      </c>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C12" s="224" t="n"/>
       <c r="D12" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E12" s="226" t="n">
-        <v>1.45427215933111</v>
-      </c>
-      <c r="F12" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G12" s="228" t="n">
-        <v>0.3414721593311101</v>
-      </c>
-      <c r="H12" s="229" t="n">
-        <v>0.3068585184499552</v>
-      </c>
-      <c r="I12" s="227" t="n">
-        <v>2.086</v>
-      </c>
-      <c r="J12" s="230" t="n">
-        <v>20.49</v>
-      </c>
+        <v>4.2588</v>
+      </c>
+      <c r="E12" s="226" t="n"/>
+      <c r="F12" s="227" t="n"/>
+      <c r="G12" s="228" t="n"/>
+      <c r="H12" s="229" t="n"/>
+      <c r="I12" s="227" t="n"/>
+      <c r="J12" s="230" t="n"/>
       <c r="K12" s="225" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L12" s="226" t="n">
-        <v>1.913022369944355</v>
-      </c>
+        <v>10.6785</v>
+      </c>
+      <c r="L12" s="226" t="n"/>
       <c r="M12" s="231" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX</t>
         </is>
       </c>
       <c r="N12" s="232" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
       <c r="A13" s="222" t="n">
-        <v>46093.78404206019</v>
+        <v>46084.29668083334</v>
       </c>
       <c r="B13" s="223" t="inlineStr">
         <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C13" s="224" t="n"/>
+      <c r="D13" s="225" t="n">
+        <v>4.2865</v>
+      </c>
+      <c r="E13" s="226" t="n"/>
+      <c r="F13" s="227" t="n"/>
+      <c r="G13" s="228" t="n"/>
+      <c r="H13" s="229" t="n"/>
+      <c r="I13" s="227" t="n"/>
+      <c r="J13" s="230" t="n"/>
+      <c r="K13" s="225" t="n">
+        <v>10.7265</v>
+      </c>
+      <c r="L13" s="226" t="n"/>
+      <c r="M13" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N13" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21.75" customHeight="1" s="101">
+      <c r="A14" s="222" t="n">
+        <v>46083.29668083334</v>
+      </c>
+      <c r="B14" s="223" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C14" s="224" t="n"/>
+      <c r="D14" s="225" t="n">
+        <v>4.244</v>
+      </c>
+      <c r="E14" s="226" t="n"/>
+      <c r="F14" s="227" t="n"/>
+      <c r="G14" s="228" t="n"/>
+      <c r="H14" s="229" t="n"/>
+      <c r="I14" s="227" t="n"/>
+      <c r="J14" s="230" t="n"/>
+      <c r="K14" s="225" t="n">
+        <v>10.708</v>
+      </c>
+      <c r="L14" s="226" t="n"/>
+      <c r="M14" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N14" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21.75" customHeight="1" s="101">
+      <c r="A15" s="222" t="n">
+        <v>46080.29668083334</v>
+      </c>
+      <c r="B15" s="223" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C15" s="224" t="n"/>
+      <c r="D15" s="225" t="n">
+        <v>4.2243</v>
+      </c>
+      <c r="E15" s="226" t="n"/>
+      <c r="F15" s="227" t="n"/>
+      <c r="G15" s="228" t="n"/>
+      <c r="H15" s="229" t="n"/>
+      <c r="I15" s="227" t="n"/>
+      <c r="J15" s="230" t="n"/>
+      <c r="K15" s="225" t="n">
+        <v>10.6643</v>
+      </c>
+      <c r="L15" s="226" t="n"/>
+      <c r="M15" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N15" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21.75" customHeight="1" s="101">
+      <c r="A16" s="222" t="n">
+        <v>46079.29668083334</v>
+      </c>
+      <c r="B16" s="223" t="inlineStr">
+        <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C13" s="224" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D13" s="225" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E13" s="226">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="227" t="n">
-        <v>1.1128</v>
-      </c>
-      <c r="G13" s="228">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="229">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I13" s="227" t="n">
-        <v>2.086</v>
-      </c>
-      <c r="J13" s="230" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K13" s="225" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L13" s="226">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M13" s="231" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
-        </is>
-      </c>
-      <c r="N13" s="232" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="211" t="n">
-        <v>46093.77185422453</v>
-      </c>
-      <c r="B14" s="212" t="inlineStr">
+      <c r="C16" s="224" t="n"/>
+      <c r="D16" s="225" t="n">
+        <v>4.2225</v>
+      </c>
+      <c r="E16" s="226" t="n"/>
+      <c r="F16" s="227" t="n"/>
+      <c r="G16" s="228" t="n"/>
+      <c r="H16" s="229" t="n"/>
+      <c r="I16" s="227" t="n"/>
+      <c r="J16" s="230" t="n"/>
+      <c r="K16" s="225" t="n">
+        <v>10.673</v>
+      </c>
+      <c r="L16" s="226" t="n"/>
+      <c r="M16" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N16" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21.75" customHeight="1" s="101">
+      <c r="A17" s="222" t="n">
+        <v>46078.29668083334</v>
+      </c>
+      <c r="B17" s="223" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C17" s="224" t="n"/>
+      <c r="D17" s="225" t="n">
+        <v>4.2233</v>
+      </c>
+      <c r="E17" s="226" t="n"/>
+      <c r="F17" s="227" t="n"/>
+      <c r="G17" s="228" t="n"/>
+      <c r="H17" s="229" t="n"/>
+      <c r="I17" s="227" t="n"/>
+      <c r="J17" s="230" t="n"/>
+      <c r="K17" s="225" t="n">
+        <v>10.6765</v>
+      </c>
+      <c r="L17" s="226" t="n"/>
+      <c r="M17" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N17" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21.75" customHeight="1" s="101">
+      <c r="A18" s="222" t="n">
+        <v>46077.29668083334</v>
+      </c>
+      <c r="B18" s="223" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C18" s="224" t="n"/>
+      <c r="D18" s="225" t="n">
+        <v>4.2203</v>
+      </c>
+      <c r="E18" s="226" t="n"/>
+      <c r="F18" s="227" t="n"/>
+      <c r="G18" s="228" t="n"/>
+      <c r="H18" s="229" t="n"/>
+      <c r="I18" s="227" t="n"/>
+      <c r="J18" s="230" t="n"/>
+      <c r="K18" s="225" t="n">
+        <v>10.688</v>
+      </c>
+      <c r="L18" s="226" t="n"/>
+      <c r="M18" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N18" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21.75" customHeight="1" s="101">
+      <c r="A19" s="222" t="n">
+        <v>46076.29668083334</v>
+      </c>
+      <c r="B19" s="223" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C19" s="224" t="n"/>
+      <c r="D19" s="225" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E19" s="226" t="n"/>
+      <c r="F19" s="227" t="n"/>
+      <c r="G19" s="228" t="n"/>
+      <c r="H19" s="229" t="n"/>
+      <c r="I19" s="227" t="n"/>
+      <c r="J19" s="230" t="n"/>
+      <c r="K19" s="225" t="n">
+        <v>10.6955</v>
+      </c>
+      <c r="L19" s="226" t="n"/>
+      <c r="M19" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N19" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="21.75" customHeight="1" s="101">
+      <c r="A20" s="222" t="n">
+        <v>46073.29668083334</v>
+      </c>
+      <c r="B20" s="223" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C20" s="224" t="n"/>
+      <c r="D20" s="225" t="n">
+        <v>4.2238</v>
+      </c>
+      <c r="E20" s="226" t="n"/>
+      <c r="F20" s="227" t="n"/>
+      <c r="G20" s="228" t="n"/>
+      <c r="H20" s="229" t="n"/>
+      <c r="I20" s="227" t="n"/>
+      <c r="J20" s="230" t="n"/>
+      <c r="K20" s="225" t="n">
+        <v>10.6745</v>
+      </c>
+      <c r="L20" s="226" t="n"/>
+      <c r="M20" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N20" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21.75" customHeight="1" s="101">
+      <c r="A21" s="222" t="n">
+        <v>46072.29668083334</v>
+      </c>
+      <c r="B21" s="223" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C14" s="213" t="n"/>
-      <c r="D14" s="214" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E14" s="215">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="216" t="n"/>
-      <c r="G14" s="217">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="218">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I14" s="216" t="n">
-        <v>2.086</v>
-      </c>
-      <c r="J14" s="219" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K14" s="214" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L14" s="215">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M14" s="220" t="inlineStr">
-        <is>
-          <t>Auto: FX,DE,SE</t>
-        </is>
-      </c>
-      <c r="N14" s="221" t="inlineStr">
-        <is>
-          <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="166" t="n">
-        <v>45730</v>
-      </c>
-      <c r="B15" s="167" t="inlineStr">
+      <c r="C21" s="224" t="n"/>
+      <c r="D21" s="225" t="n">
+        <v>4.2215</v>
+      </c>
+      <c r="E21" s="226" t="n"/>
+      <c r="F21" s="227" t="n"/>
+      <c r="G21" s="228" t="n"/>
+      <c r="H21" s="229" t="n"/>
+      <c r="I21" s="227" t="n"/>
+      <c r="J21" s="230" t="n"/>
+      <c r="K21" s="225" t="n">
+        <v>10.6915</v>
+      </c>
+      <c r="L21" s="226" t="n"/>
+      <c r="M21" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N21" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21.75" customHeight="1" s="101">
+      <c r="A22" s="222" t="n">
+        <v>46071.29668083334</v>
+      </c>
+      <c r="B22" s="223" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C22" s="224" t="n"/>
+      <c r="D22" s="225" t="n">
+        <v>4.2165</v>
+      </c>
+      <c r="E22" s="226" t="n"/>
+      <c r="F22" s="227" t="n"/>
+      <c r="G22" s="228" t="n"/>
+      <c r="H22" s="229" t="n"/>
+      <c r="I22" s="227" t="n"/>
+      <c r="J22" s="230" t="n"/>
+      <c r="K22" s="225" t="n">
+        <v>10.616</v>
+      </c>
+      <c r="L22" s="226" t="n"/>
+      <c r="M22" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N22" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21.75" customHeight="1" s="101">
+      <c r="A23" s="222" t="n">
+        <v>46070.29668083334</v>
+      </c>
+      <c r="B23" s="223" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C23" s="224" t="n"/>
+      <c r="D23" s="225" t="n">
+        <v>4.2138</v>
+      </c>
+      <c r="E23" s="226" t="n"/>
+      <c r="F23" s="227" t="n"/>
+      <c r="G23" s="228" t="n"/>
+      <c r="H23" s="229" t="n"/>
+      <c r="I23" s="227" t="n"/>
+      <c r="J23" s="230" t="n"/>
+      <c r="K23" s="225" t="n">
+        <v>10.648</v>
+      </c>
+      <c r="L23" s="226" t="n"/>
+      <c r="M23" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N23" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21.75" customHeight="1" s="101">
+      <c r="A24" s="222" t="n">
+        <v>46069.29668083334</v>
+      </c>
+      <c r="B24" s="223" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C24" s="224" t="n"/>
+      <c r="D24" s="225" t="n">
+        <v>4.2105</v>
+      </c>
+      <c r="E24" s="226" t="n"/>
+      <c r="F24" s="227" t="n"/>
+      <c r="G24" s="228" t="n"/>
+      <c r="H24" s="229" t="n"/>
+      <c r="I24" s="227" t="n"/>
+      <c r="J24" s="230" t="n"/>
+      <c r="K24" s="225" t="n">
+        <v>10.6205</v>
+      </c>
+      <c r="L24" s="226" t="n"/>
+      <c r="M24" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N24" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="21.75" customHeight="1" s="101">
+      <c r="A25" s="222" t="n">
+        <v>46066.29668083334</v>
+      </c>
+      <c r="B25" s="223" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C15" s="168" t="n"/>
-      <c r="D15" s="169" t="n"/>
-      <c r="E15" s="170">
-        <f>IF(AND(C5&lt;&gt;"",D5&lt;&gt;"",D5&lt;&gt;0),C5/D5/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="171" t="n"/>
-      <c r="G15" s="172">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;""),E5-F5,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="173">
-        <f>IF(AND(E5&lt;&gt;"",F5&lt;&gt;"",F5&lt;&gt;0),(E5-F5)/F5,"")</f>
-        <v/>
-      </c>
-      <c r="I15" s="171" t="n"/>
-      <c r="J15" s="174" t="n"/>
-      <c r="K15" s="169" t="n"/>
-      <c r="L15" s="170">
-        <f>IF(AND(J5&lt;&gt;"",K5&lt;&gt;"",K5&lt;&gt;0),J5/K5,"")</f>
-        <v/>
-      </c>
-      <c r="M15" s="175" t="n"/>
-      <c r="N15" s="176" t="n"/>
-      <c r="O15" s="102" t="n"/>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="177" t="n">
-        <v>45729</v>
-      </c>
-      <c r="B16" s="178" t="inlineStr">
+      <c r="C25" s="224" t="n"/>
+      <c r="D25" s="225" t="n">
+        <v>4.215</v>
+      </c>
+      <c r="E25" s="226" t="n"/>
+      <c r="F25" s="227" t="n"/>
+      <c r="G25" s="228" t="n"/>
+      <c r="H25" s="229" t="n"/>
+      <c r="I25" s="227" t="n"/>
+      <c r="J25" s="230" t="n"/>
+      <c r="K25" s="225" t="n">
+        <v>10.6254</v>
+      </c>
+      <c r="L25" s="226" t="n"/>
+      <c r="M25" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N25" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21.75" customHeight="1" s="101">
+      <c r="A26" s="222" t="n">
+        <v>46065.29668083334</v>
+      </c>
+      <c r="B26" s="223" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C16" s="168" t="n"/>
-      <c r="D16" s="169" t="n"/>
-      <c r="E16" s="179">
-        <f>IF(AND(C6&lt;&gt;"",D6&lt;&gt;"",D6&lt;&gt;0),C6/D6/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="171" t="n"/>
-      <c r="G16" s="180">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;""),E6-F6,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="181">
-        <f>IF(AND(E6&lt;&gt;"",F6&lt;&gt;"",F6&lt;&gt;0),(E6-F6)/F6,"")</f>
-        <v/>
-      </c>
-      <c r="I16" s="171" t="n"/>
-      <c r="J16" s="174" t="n"/>
-      <c r="K16" s="169" t="n"/>
-      <c r="L16" s="179">
-        <f>IF(AND(J6&lt;&gt;"",K6&lt;&gt;"",K6&lt;&gt;0),J6/K6,"")</f>
-        <v/>
-      </c>
-      <c r="M16" s="182" t="n"/>
-      <c r="N16" s="183" t="n"/>
-      <c r="O16" s="102" t="n"/>
-    </row>
-    <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="166" t="n">
-        <v>45728</v>
-      </c>
-      <c r="B17" s="167" t="inlineStr">
+      <c r="C26" s="224" t="n"/>
+      <c r="D26" s="225" t="n">
+        <v>4.2158</v>
+      </c>
+      <c r="E26" s="226" t="n"/>
+      <c r="F26" s="227" t="n"/>
+      <c r="G26" s="228" t="n"/>
+      <c r="H26" s="229" t="n"/>
+      <c r="I26" s="227" t="n"/>
+      <c r="J26" s="230" t="n"/>
+      <c r="K26" s="225" t="n">
+        <v>10.567</v>
+      </c>
+      <c r="L26" s="226" t="n"/>
+      <c r="M26" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N26" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="21.75" customHeight="1" s="101">
+      <c r="A27" s="222" t="n">
+        <v>46064.29668083334</v>
+      </c>
+      <c r="B27" s="223" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C17" s="168" t="n"/>
-      <c r="D17" s="169" t="n"/>
-      <c r="E17" s="170">
-        <f>IF(AND(C7&lt;&gt;"",D7&lt;&gt;"",D7&lt;&gt;0),C7/D7/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="171" t="n"/>
-      <c r="G17" s="172">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;""),E7-F7,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="173">
-        <f>IF(AND(E7&lt;&gt;"",F7&lt;&gt;"",F7&lt;&gt;0),(E7-F7)/F7,"")</f>
-        <v/>
-      </c>
-      <c r="I17" s="171" t="n"/>
-      <c r="J17" s="174" t="n"/>
-      <c r="K17" s="169" t="n"/>
-      <c r="L17" s="170">
-        <f>IF(AND(J7&lt;&gt;"",K7&lt;&gt;"",K7&lt;&gt;0),J7/K7,"")</f>
-        <v/>
-      </c>
-      <c r="M17" s="175" t="n"/>
-      <c r="N17" s="176" t="n"/>
-      <c r="O17" s="102" t="n"/>
-    </row>
-    <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="177" t="n">
-        <v>45727</v>
-      </c>
-      <c r="B18" s="178" t="inlineStr">
+      <c r="C27" s="224" t="n"/>
+      <c r="D27" s="225" t="n">
+        <v>4.2135</v>
+      </c>
+      <c r="E27" s="226" t="n"/>
+      <c r="F27" s="227" t="n"/>
+      <c r="G27" s="228" t="n"/>
+      <c r="H27" s="229" t="n"/>
+      <c r="I27" s="227" t="n"/>
+      <c r="J27" s="230" t="n"/>
+      <c r="K27" s="225" t="n">
+        <v>10.564</v>
+      </c>
+      <c r="L27" s="226" t="n"/>
+      <c r="M27" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N27" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21.75" customHeight="1" s="101">
+      <c r="A28" s="222" t="n">
+        <v>46063.29668083334</v>
+      </c>
+      <c r="B28" s="223" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C18" s="168" t="n"/>
-      <c r="D18" s="169" t="n"/>
-      <c r="E18" s="179">
-        <f>IF(AND(C8&lt;&gt;"",D8&lt;&gt;"",D8&lt;&gt;0),C8/D8/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="171" t="n"/>
-      <c r="G18" s="180">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;""),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H18" s="181">
-        <f>IF(AND(E8&lt;&gt;"",F8&lt;&gt;"",F8&lt;&gt;0),(E8-F8)/F8,"")</f>
-        <v/>
-      </c>
-      <c r="I18" s="171" t="n"/>
-      <c r="J18" s="174" t="n"/>
-      <c r="K18" s="169" t="n"/>
-      <c r="L18" s="179">
-        <f>IF(AND(J8&lt;&gt;"",K8&lt;&gt;"",K8&lt;&gt;0),J8/K8,"")</f>
-        <v/>
-      </c>
-      <c r="M18" s="182" t="n"/>
-      <c r="N18" s="183" t="n"/>
-      <c r="O18" s="102" t="n"/>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B19" s="167" t="inlineStr">
+      <c r="C28" s="224" t="n"/>
+      <c r="D28" s="225" t="n">
+        <v>4.217</v>
+      </c>
+      <c r="E28" s="226" t="n"/>
+      <c r="F28" s="227" t="n"/>
+      <c r="G28" s="228" t="n"/>
+      <c r="H28" s="229" t="n"/>
+      <c r="I28" s="227" t="n"/>
+      <c r="J28" s="230" t="n"/>
+      <c r="K28" s="225" t="n">
+        <v>10.6135</v>
+      </c>
+      <c r="L28" s="226" t="n"/>
+      <c r="M28" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N28" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21.75" customHeight="1" s="101">
+      <c r="A29" s="222" t="n">
+        <v>46062.29668083334</v>
+      </c>
+      <c r="B29" s="223" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C19" s="168" t="n"/>
-      <c r="D19" s="169" t="n"/>
-      <c r="E19" s="170">
-        <f>IF(AND(C9&lt;&gt;"",D9&lt;&gt;"",D9&lt;&gt;0),C9/D9/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="171" t="n"/>
-      <c r="G19" s="172">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;""),E9-F9,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="173">
-        <f>IF(AND(E9&lt;&gt;"",F9&lt;&gt;"",F9&lt;&gt;0),(E9-F9)/F9,"")</f>
-        <v/>
-      </c>
-      <c r="I19" s="171" t="n"/>
-      <c r="J19" s="174" t="n"/>
-      <c r="K19" s="169" t="n"/>
-      <c r="L19" s="170">
-        <f>IF(AND(J9&lt;&gt;"",K9&lt;&gt;"",K9&lt;&gt;0),J9/K9,"")</f>
-        <v/>
-      </c>
-      <c r="M19" s="175" t="n"/>
-      <c r="N19" s="176" t="n"/>
-      <c r="O19" s="102" t="n"/>
-    </row>
-    <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="184" t="n">
-        <v>45725</v>
-      </c>
-      <c r="B20" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C20" s="168" t="n"/>
-      <c r="D20" s="169" t="n"/>
-      <c r="E20" s="186">
-        <f>IF(AND(C10&lt;&gt;"",D10&lt;&gt;"",D10&lt;&gt;0),C10/D10/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="171" t="n"/>
-      <c r="G20" s="187">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;""),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H20" s="188">
-        <f>IF(AND(E10&lt;&gt;"",F10&lt;&gt;"",F10&lt;&gt;0),(E10-F10)/F10,"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="171" t="n"/>
-      <c r="J20" s="174" t="n"/>
-      <c r="K20" s="169" t="n"/>
-      <c r="L20" s="186">
-        <f>IF(AND(J10&lt;&gt;"",K10&lt;&gt;"",K10&lt;&gt;0),J10/K10,"")</f>
-        <v/>
-      </c>
-      <c r="M20" s="189" t="n"/>
-      <c r="N20" s="190" t="n"/>
-      <c r="O20" s="102" t="n"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="184" t="n">
-        <v>45724</v>
-      </c>
-      <c r="B21" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C21" s="168" t="n"/>
-      <c r="D21" s="169" t="n"/>
-      <c r="E21" s="186">
-        <f>IF(AND(C11&lt;&gt;"",D11&lt;&gt;"",D11&lt;&gt;0),C11/D11/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="171" t="n"/>
-      <c r="G21" s="187">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;""),E11-F11,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="188">
-        <f>IF(AND(E11&lt;&gt;"",F11&lt;&gt;"",F11&lt;&gt;0),(E11-F11)/F11,"")</f>
-        <v/>
-      </c>
-      <c r="I21" s="171" t="n"/>
-      <c r="J21" s="174" t="n"/>
-      <c r="K21" s="169" t="n"/>
-      <c r="L21" s="186">
-        <f>IF(AND(J11&lt;&gt;"",K11&lt;&gt;"",K11&lt;&gt;0),J11/K11,"")</f>
-        <v/>
-      </c>
-      <c r="M21" s="189" t="n"/>
-      <c r="N21" s="190" t="n"/>
-      <c r="O21" s="102" t="n"/>
-    </row>
-    <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="177" t="n">
-        <v>45723</v>
-      </c>
-      <c r="B22" s="178" t="inlineStr">
+      <c r="C29" s="224" t="n"/>
+      <c r="D29" s="225" t="n">
+        <v>4.2118</v>
+      </c>
+      <c r="E29" s="226" t="n"/>
+      <c r="F29" s="227" t="n"/>
+      <c r="G29" s="228" t="n"/>
+      <c r="H29" s="229" t="n"/>
+      <c r="I29" s="227" t="n"/>
+      <c r="J29" s="230" t="n"/>
+      <c r="K29" s="225" t="n">
+        <v>10.6505</v>
+      </c>
+      <c r="L29" s="226" t="n"/>
+      <c r="M29" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N29" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="21.75" customHeight="1" s="101">
+      <c r="A30" s="222" t="n">
+        <v>46059.29668083334</v>
+      </c>
+      <c r="B30" s="223" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C22" s="168" t="n"/>
-      <c r="D22" s="169" t="n"/>
-      <c r="E22" s="179">
-        <f>IF(AND(C12&lt;&gt;"",D12&lt;&gt;"",D12&lt;&gt;0),C12/D12/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="171" t="n"/>
-      <c r="G22" s="180">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;""),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H22" s="181">
-        <f>IF(AND(E12&lt;&gt;"",F12&lt;&gt;"",F12&lt;&gt;0),(E12-F12)/F12,"")</f>
-        <v/>
-      </c>
-      <c r="I22" s="171" t="n"/>
-      <c r="J22" s="174" t="n"/>
-      <c r="K22" s="169" t="n"/>
-      <c r="L22" s="179">
-        <f>IF(AND(J12&lt;&gt;"",K12&lt;&gt;"",K12&lt;&gt;0),J12/K12,"")</f>
-        <v/>
-      </c>
-      <c r="M22" s="182" t="n"/>
-      <c r="N22" s="183" t="n"/>
-      <c r="O22" s="102" t="n"/>
-    </row>
-    <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="166" t="n">
-        <v>45722</v>
-      </c>
-      <c r="B23" s="167" t="inlineStr">
+      <c r="C30" s="224" t="n"/>
+      <c r="D30" s="225" t="n">
+        <v>4.2185</v>
+      </c>
+      <c r="E30" s="226" t="n"/>
+      <c r="F30" s="227" t="n"/>
+      <c r="G30" s="228" t="n"/>
+      <c r="H30" s="229" t="n"/>
+      <c r="I30" s="227" t="n"/>
+      <c r="J30" s="230" t="n"/>
+      <c r="K30" s="225" t="n">
+        <v>10.6735</v>
+      </c>
+      <c r="L30" s="226" t="n"/>
+      <c r="M30" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N30" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="21.75" customHeight="1" s="101">
+      <c r="A31" s="222" t="n">
+        <v>46058.29668083334</v>
+      </c>
+      <c r="B31" s="223" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C23" s="168" t="n"/>
-      <c r="D23" s="169" t="n"/>
-      <c r="E23" s="170">
-        <f>IF(AND(C13&lt;&gt;"",D13&lt;&gt;"",D13&lt;&gt;0),C13/D13/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="171" t="n"/>
-      <c r="G23" s="172">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;""),E13-F13,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="173">
-        <f>IF(AND(E13&lt;&gt;"",F13&lt;&gt;"",F13&lt;&gt;0),(E13-F13)/F13,"")</f>
-        <v/>
-      </c>
-      <c r="I23" s="171" t="n"/>
-      <c r="J23" s="174" t="n"/>
-      <c r="K23" s="169" t="n"/>
-      <c r="L23" s="170">
-        <f>IF(AND(J13&lt;&gt;"",K13&lt;&gt;"",K13&lt;&gt;0),J13/K13,"")</f>
-        <v/>
-      </c>
-      <c r="M23" s="175" t="n"/>
-      <c r="N23" s="176" t="n"/>
-      <c r="O23" s="102" t="n"/>
-    </row>
-    <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="177" t="n">
-        <v>45721</v>
-      </c>
-      <c r="B24" s="178" t="inlineStr">
+      <c r="C31" s="224" t="n"/>
+      <c r="D31" s="225" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="E31" s="226" t="n"/>
+      <c r="F31" s="227" t="n"/>
+      <c r="G31" s="228" t="n"/>
+      <c r="H31" s="229" t="n"/>
+      <c r="I31" s="227" t="n"/>
+      <c r="J31" s="230" t="n"/>
+      <c r="K31" s="225" t="n">
+        <v>10.641</v>
+      </c>
+      <c r="L31" s="226" t="n"/>
+      <c r="M31" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N31" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21.75" customHeight="1" s="101">
+      <c r="A32" s="222" t="n">
+        <v>46057.29668083334</v>
+      </c>
+      <c r="B32" s="223" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C24" s="168" t="n"/>
-      <c r="D24" s="169" t="n"/>
-      <c r="E24" s="179">
-        <f>IF(AND(C14&lt;&gt;"",D14&lt;&gt;"",D14&lt;&gt;0),C14/D14/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="171" t="n"/>
-      <c r="G24" s="180">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;""),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H24" s="181">
-        <f>IF(AND(E14&lt;&gt;"",F14&lt;&gt;"",F14&lt;&gt;0),(E14-F14)/F14,"")</f>
-        <v/>
-      </c>
-      <c r="I24" s="171" t="n"/>
-      <c r="J24" s="174" t="n"/>
-      <c r="K24" s="169" t="n"/>
-      <c r="L24" s="179">
-        <f>IF(AND(J14&lt;&gt;"",K14&lt;&gt;"",K14&lt;&gt;0),J14/K14,"")</f>
-        <v/>
-      </c>
-      <c r="M24" s="182" t="n"/>
-      <c r="N24" s="183" t="n"/>
-      <c r="O24" s="102" t="n"/>
-    </row>
-    <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="166" t="n">
-        <v>45720</v>
-      </c>
-      <c r="B25" s="167" t="inlineStr">
+      <c r="C32" s="224" t="n"/>
+      <c r="D32" s="225" t="n">
+        <v>4.2235</v>
+      </c>
+      <c r="E32" s="226" t="n"/>
+      <c r="F32" s="227" t="n"/>
+      <c r="G32" s="228" t="n"/>
+      <c r="H32" s="229" t="n"/>
+      <c r="I32" s="227" t="n"/>
+      <c r="J32" s="230" t="n"/>
+      <c r="K32" s="225" t="n">
+        <v>10.577</v>
+      </c>
+      <c r="L32" s="226" t="n"/>
+      <c r="M32" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N32" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="21.75" customHeight="1" s="101">
+      <c r="A33" s="222" t="n">
+        <v>46056.29668083334</v>
+      </c>
+      <c r="B33" s="223" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C25" s="168" t="n"/>
-      <c r="D25" s="169" t="n"/>
-      <c r="E25" s="170">
-        <f>IF(AND(C15&lt;&gt;"",D15&lt;&gt;"",D15&lt;&gt;0),C15/D15/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="171" t="n"/>
-      <c r="G25" s="172">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;""),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="173">
-        <f>IF(AND(E15&lt;&gt;"",F15&lt;&gt;"",F15&lt;&gt;0),(E15-F15)/F15,"")</f>
-        <v/>
-      </c>
-      <c r="I25" s="171" t="n"/>
-      <c r="J25" s="174" t="n"/>
-      <c r="K25" s="169" t="n"/>
-      <c r="L25" s="170">
-        <f>IF(AND(J15&lt;&gt;"",K15&lt;&gt;"",K15&lt;&gt;0),J15/K15,"")</f>
-        <v/>
-      </c>
-      <c r="M25" s="175" t="n"/>
-      <c r="N25" s="176" t="n"/>
-      <c r="O25" s="102" t="n"/>
-    </row>
-    <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B26" s="178" t="inlineStr">
+      <c r="C33" s="224" t="n"/>
+      <c r="D33" s="225" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="E33" s="226" t="n"/>
+      <c r="F33" s="227" t="n"/>
+      <c r="G33" s="228" t="n"/>
+      <c r="H33" s="229" t="n"/>
+      <c r="I33" s="227" t="n"/>
+      <c r="J33" s="230" t="n"/>
+      <c r="K33" s="225" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L33" s="226" t="n"/>
+      <c r="M33" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N33" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="21.75" customHeight="1" s="101">
+      <c r="A34" s="222" t="n">
+        <v>46055.29668083334</v>
+      </c>
+      <c r="B34" s="223" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="C26" s="168" t="n"/>
-      <c r="D26" s="169" t="n"/>
-      <c r="E26" s="179">
-        <f>IF(AND(C16&lt;&gt;"",D16&lt;&gt;"",D16&lt;&gt;0),C16/D16/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="171" t="n"/>
-      <c r="G26" s="180">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;""),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H26" s="181">
-        <f>IF(AND(E16&lt;&gt;"",F16&lt;&gt;"",F16&lt;&gt;0),(E16-F16)/F16,"")</f>
-        <v/>
-      </c>
-      <c r="I26" s="171" t="n"/>
-      <c r="J26" s="174" t="n"/>
-      <c r="K26" s="169" t="n"/>
-      <c r="L26" s="179">
-        <f>IF(AND(J16&lt;&gt;"",K16&lt;&gt;"",K16&lt;&gt;0),J16/K16,"")</f>
-        <v/>
-      </c>
-      <c r="M26" s="182" t="n"/>
-      <c r="N26" s="183" t="n"/>
-      <c r="O26" s="102" t="n"/>
-    </row>
-    <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="184" t="n">
-        <v>45718</v>
-      </c>
-      <c r="B27" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C27" s="168" t="n"/>
-      <c r="D27" s="169" t="n"/>
-      <c r="E27" s="186">
-        <f>IF(AND(C17&lt;&gt;"",D17&lt;&gt;"",D17&lt;&gt;0),C17/D17/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="171" t="n"/>
-      <c r="G27" s="187">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;""),E17-F17,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="188">
-        <f>IF(AND(E17&lt;&gt;"",F17&lt;&gt;"",F17&lt;&gt;0),(E17-F17)/F17,"")</f>
-        <v/>
-      </c>
-      <c r="I27" s="171" t="n"/>
-      <c r="J27" s="174" t="n"/>
-      <c r="K27" s="169" t="n"/>
-      <c r="L27" s="186">
-        <f>IF(AND(J17&lt;&gt;"",K17&lt;&gt;"",K17&lt;&gt;0),J17/K17,"")</f>
-        <v/>
-      </c>
-      <c r="M27" s="189" t="n"/>
-      <c r="N27" s="190" t="n"/>
-      <c r="O27" s="102" t="n"/>
-    </row>
-    <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="184" t="n">
-        <v>45717</v>
-      </c>
-      <c r="B28" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C28" s="168" t="n"/>
-      <c r="D28" s="169" t="n"/>
-      <c r="E28" s="186">
-        <f>IF(AND(C18&lt;&gt;"",D18&lt;&gt;"",D18&lt;&gt;0),C18/D18/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="171" t="n"/>
-      <c r="G28" s="187">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;""),E18-F18,"")</f>
-        <v/>
-      </c>
-      <c r="H28" s="188">
-        <f>IF(AND(E18&lt;&gt;"",F18&lt;&gt;"",F18&lt;&gt;0),(E18-F18)/F18,"")</f>
-        <v/>
-      </c>
-      <c r="I28" s="171" t="n"/>
-      <c r="J28" s="174" t="n"/>
-      <c r="K28" s="169" t="n"/>
-      <c r="L28" s="186">
-        <f>IF(AND(J18&lt;&gt;"",K18&lt;&gt;"",K18&lt;&gt;0),J18/K18,"")</f>
-        <v/>
-      </c>
-      <c r="M28" s="189" t="n"/>
-      <c r="N28" s="190" t="n"/>
-      <c r="O28" s="102" t="n"/>
-    </row>
-    <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="166" t="n">
-        <v>45716</v>
-      </c>
-      <c r="B29" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C29" s="168" t="n"/>
-      <c r="D29" s="169" t="n"/>
-      <c r="E29" s="170">
-        <f>IF(AND(C19&lt;&gt;"",D19&lt;&gt;"",D19&lt;&gt;0),C19/D19/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="171" t="n"/>
-      <c r="G29" s="172">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;""),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="173">
-        <f>IF(AND(E19&lt;&gt;"",F19&lt;&gt;"",F19&lt;&gt;0),(E19-F19)/F19,"")</f>
-        <v/>
-      </c>
-      <c r="I29" s="171" t="n"/>
-      <c r="J29" s="174" t="n"/>
-      <c r="K29" s="169" t="n"/>
-      <c r="L29" s="170">
-        <f>IF(AND(J19&lt;&gt;"",K19&lt;&gt;"",K19&lt;&gt;0),J19/K19,"")</f>
-        <v/>
-      </c>
-      <c r="M29" s="175" t="n"/>
-      <c r="N29" s="176" t="n"/>
-      <c r="O29" s="102" t="n"/>
-    </row>
-    <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="177" t="n">
-        <v>45715</v>
-      </c>
-      <c r="B30" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C30" s="168" t="n"/>
-      <c r="D30" s="169" t="n"/>
-      <c r="E30" s="179">
-        <f>IF(AND(C20&lt;&gt;"",D20&lt;&gt;"",D20&lt;&gt;0),C20/D20/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="171" t="n"/>
-      <c r="G30" s="180">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;""),E20-F20,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="181">
-        <f>IF(AND(E20&lt;&gt;"",F20&lt;&gt;"",F20&lt;&gt;0),(E20-F20)/F20,"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="171" t="n"/>
-      <c r="J30" s="174" t="n"/>
-      <c r="K30" s="169" t="n"/>
-      <c r="L30" s="179">
-        <f>IF(AND(J20&lt;&gt;"",K20&lt;&gt;"",K20&lt;&gt;0),J20/K20,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="182" t="n"/>
-      <c r="N30" s="183" t="n"/>
-      <c r="O30" s="102" t="n"/>
-    </row>
-    <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="166" t="n">
-        <v>45714</v>
-      </c>
-      <c r="B31" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C31" s="168" t="n"/>
-      <c r="D31" s="169" t="n"/>
-      <c r="E31" s="170">
-        <f>IF(AND(C21&lt;&gt;"",D21&lt;&gt;"",D21&lt;&gt;0),C21/D21/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="171" t="n"/>
-      <c r="G31" s="172">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;""),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="173">
-        <f>IF(AND(E21&lt;&gt;"",F21&lt;&gt;"",F21&lt;&gt;0),(E21-F21)/F21,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="171" t="n"/>
-      <c r="J31" s="174" t="n"/>
-      <c r="K31" s="169" t="n"/>
-      <c r="L31" s="170">
-        <f>IF(AND(J21&lt;&gt;"",K21&lt;&gt;"",K21&lt;&gt;0),J21/K21,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="175" t="n"/>
-      <c r="N31" s="176" t="n"/>
-      <c r="O31" s="102" t="n"/>
-    </row>
-    <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="177" t="n">
-        <v>45713</v>
-      </c>
-      <c r="B32" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C32" s="168" t="n"/>
-      <c r="D32" s="169" t="n"/>
-      <c r="E32" s="179">
-        <f>IF(AND(C22&lt;&gt;"",D22&lt;&gt;"",D22&lt;&gt;0),C22/D22/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="171" t="n"/>
-      <c r="G32" s="180">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;""),E22-F22,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="181">
-        <f>IF(AND(E22&lt;&gt;"",F22&lt;&gt;"",F22&lt;&gt;0),(E22-F22)/F22,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="171" t="n"/>
-      <c r="J32" s="174" t="n"/>
-      <c r="K32" s="169" t="n"/>
-      <c r="L32" s="179">
-        <f>IF(AND(J22&lt;&gt;"",K22&lt;&gt;"",K22&lt;&gt;0),J22/K22,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="182" t="n"/>
-      <c r="N32" s="183" t="n"/>
-      <c r="O32" s="102" t="n"/>
-    </row>
-    <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B33" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C33" s="168" t="n"/>
-      <c r="D33" s="169" t="n"/>
-      <c r="E33" s="170">
-        <f>IF(AND(C23&lt;&gt;"",D23&lt;&gt;"",D23&lt;&gt;0),C23/D23/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="171" t="n"/>
-      <c r="G33" s="172">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;""),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="173">
-        <f>IF(AND(E23&lt;&gt;"",F23&lt;&gt;"",F23&lt;&gt;0),(E23-F23)/F23,"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="171" t="n"/>
-      <c r="J33" s="174" t="n"/>
-      <c r="K33" s="169" t="n"/>
-      <c r="L33" s="170">
-        <f>IF(AND(J23&lt;&gt;"",K23&lt;&gt;"",K23&lt;&gt;0),J23/K23,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="175" t="n"/>
-      <c r="N33" s="176" t="n"/>
-      <c r="O33" s="102" t="n"/>
-    </row>
-    <row r="34" ht="21.75" customHeight="1" s="101">
-      <c r="A34" s="184" t="n">
-        <v>45711</v>
-      </c>
-      <c r="B34" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C34" s="168" t="n"/>
-      <c r="D34" s="169" t="n"/>
-      <c r="E34" s="186">
-        <f>IF(AND(C24&lt;&gt;"",D24&lt;&gt;"",D24&lt;&gt;0),C24/D24/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="171" t="n"/>
-      <c r="G34" s="187">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;""),E24-F24,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="188">
-        <f>IF(AND(E24&lt;&gt;"",F24&lt;&gt;"",F24&lt;&gt;0),(E24-F24)/F24,"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="171" t="n"/>
-      <c r="J34" s="174" t="n"/>
-      <c r="K34" s="169" t="n"/>
-      <c r="L34" s="186">
-        <f>IF(AND(J24&lt;&gt;"",K24&lt;&gt;"",K24&lt;&gt;0),J24/K24,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="189" t="n"/>
-      <c r="N34" s="190" t="n"/>
-      <c r="O34" s="102" t="n"/>
-    </row>
-    <row r="35" ht="21.75" customHeight="1" s="101">
-      <c r="A35" s="184" t="n">
-        <v>45710</v>
-      </c>
-      <c r="B35" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C35" s="168" t="n"/>
-      <c r="D35" s="169" t="n"/>
-      <c r="E35" s="186">
-        <f>IF(AND(C25&lt;&gt;"",D25&lt;&gt;"",D25&lt;&gt;0),C25/D25/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="171" t="n"/>
-      <c r="G35" s="187">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;""),E25-F25,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="188">
-        <f>IF(AND(E25&lt;&gt;"",F25&lt;&gt;"",F25&lt;&gt;0),(E25-F25)/F25,"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="171" t="n"/>
-      <c r="J35" s="174" t="n"/>
-      <c r="K35" s="169" t="n"/>
-      <c r="L35" s="186">
-        <f>IF(AND(J25&lt;&gt;"",K25&lt;&gt;"",K25&lt;&gt;0),J25/K25,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="189" t="n"/>
-      <c r="N35" s="190" t="n"/>
-      <c r="O35" s="102" t="n"/>
-    </row>
-    <row r="36" ht="21.75" customHeight="1" s="101">
-      <c r="A36" s="177" t="n">
-        <v>45709</v>
-      </c>
-      <c r="B36" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C36" s="168" t="n"/>
-      <c r="D36" s="169" t="n"/>
-      <c r="E36" s="179">
-        <f>IF(AND(C26&lt;&gt;"",D26&lt;&gt;"",D26&lt;&gt;0),C26/D26/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="171" t="n"/>
-      <c r="G36" s="180">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;""),E26-F26,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="181">
-        <f>IF(AND(E26&lt;&gt;"",F26&lt;&gt;"",F26&lt;&gt;0),(E26-F26)/F26,"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="171" t="n"/>
-      <c r="J36" s="174" t="n"/>
-      <c r="K36" s="169" t="n"/>
-      <c r="L36" s="179">
-        <f>IF(AND(J26&lt;&gt;"",K26&lt;&gt;"",K26&lt;&gt;0),J26/K26,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="182" t="n"/>
-      <c r="N36" s="183" t="n"/>
-      <c r="O36" s="102" t="n"/>
-    </row>
-    <row r="37" ht="21.75" customHeight="1" s="101">
-      <c r="A37" s="166" t="n">
-        <v>45708</v>
-      </c>
-      <c r="B37" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C37" s="168" t="n"/>
-      <c r="D37" s="169" t="n"/>
-      <c r="E37" s="170">
-        <f>IF(AND(C27&lt;&gt;"",D27&lt;&gt;"",D27&lt;&gt;0),C27/D27/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="171" t="n"/>
-      <c r="G37" s="172">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;""),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="173">
-        <f>IF(AND(E27&lt;&gt;"",F27&lt;&gt;"",F27&lt;&gt;0),(E27-F27)/F27,"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="171" t="n"/>
-      <c r="J37" s="174" t="n"/>
-      <c r="K37" s="169" t="n"/>
-      <c r="L37" s="170">
-        <f>IF(AND(J27&lt;&gt;"",K27&lt;&gt;"",K27&lt;&gt;0),J27/K27,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="175" t="n"/>
-      <c r="N37" s="176" t="n"/>
-      <c r="O37" s="102" t="n"/>
-    </row>
-    <row r="38" ht="21.75" customHeight="1" s="101">
-      <c r="A38" s="177" t="n">
-        <v>45707</v>
-      </c>
-      <c r="B38" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C38" s="168" t="n"/>
-      <c r="D38" s="169" t="n"/>
-      <c r="E38" s="179">
-        <f>IF(AND(C28&lt;&gt;"",D28&lt;&gt;"",D28&lt;&gt;0),C28/D28/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="171" t="n"/>
-      <c r="G38" s="180">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;""),E28-F28,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="181">
-        <f>IF(AND(E28&lt;&gt;"",F28&lt;&gt;"",F28&lt;&gt;0),(E28-F28)/F28,"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="171" t="n"/>
-      <c r="J38" s="174" t="n"/>
-      <c r="K38" s="169" t="n"/>
-      <c r="L38" s="179">
-        <f>IF(AND(J28&lt;&gt;"",K28&lt;&gt;"",K28&lt;&gt;0),J28/K28,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="182" t="n"/>
-      <c r="N38" s="183" t="n"/>
-      <c r="O38" s="102" t="n"/>
-    </row>
-    <row r="39" ht="21.75" customHeight="1" s="101">
-      <c r="A39" s="166" t="n">
-        <v>45706</v>
-      </c>
-      <c r="B39" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C39" s="168" t="n"/>
-      <c r="D39" s="169" t="n"/>
-      <c r="E39" s="170">
-        <f>IF(AND(C29&lt;&gt;"",D29&lt;&gt;"",D29&lt;&gt;0),C29/D29/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="171" t="n"/>
-      <c r="G39" s="172">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;""),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="173">
-        <f>IF(AND(E29&lt;&gt;"",F29&lt;&gt;"",F29&lt;&gt;0),(E29-F29)/F29,"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="171" t="n"/>
-      <c r="J39" s="174" t="n"/>
-      <c r="K39" s="169" t="n"/>
-      <c r="L39" s="170">
-        <f>IF(AND(J29&lt;&gt;"",K29&lt;&gt;"",K29&lt;&gt;0),J29/K29,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="175" t="n"/>
-      <c r="N39" s="176" t="n"/>
-      <c r="O39" s="102" t="n"/>
-    </row>
-    <row r="40" ht="21.75" customHeight="1" s="101">
-      <c r="A40" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B40" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C40" s="168" t="n"/>
-      <c r="D40" s="169" t="n"/>
-      <c r="E40" s="179">
-        <f>IF(AND(C30&lt;&gt;"",D30&lt;&gt;"",D30&lt;&gt;0),C30/D30/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="171" t="n"/>
-      <c r="G40" s="180">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;""),E30-F30,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="181">
-        <f>IF(AND(E30&lt;&gt;"",F30&lt;&gt;"",F30&lt;&gt;0),(E30-F30)/F30,"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="171" t="n"/>
-      <c r="J40" s="174" t="n"/>
-      <c r="K40" s="169" t="n"/>
-      <c r="L40" s="179">
-        <f>IF(AND(J30&lt;&gt;"",K30&lt;&gt;"",K30&lt;&gt;0),J30/K30,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="182" t="n"/>
-      <c r="N40" s="183" t="n"/>
-      <c r="O40" s="102" t="n"/>
-    </row>
-    <row r="41" ht="21.75" customHeight="1" s="101">
-      <c r="A41" s="184" t="n">
-        <v>45704</v>
-      </c>
-      <c r="B41" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C41" s="168" t="n"/>
-      <c r="D41" s="169" t="n"/>
-      <c r="E41" s="186">
-        <f>IF(AND(C31&lt;&gt;"",D31&lt;&gt;"",D31&lt;&gt;0),C31/D31/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="171" t="n"/>
-      <c r="G41" s="187">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;""),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="188">
-        <f>IF(AND(E31&lt;&gt;"",F31&lt;&gt;"",F31&lt;&gt;0),(E31-F31)/F31,"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="171" t="n"/>
-      <c r="J41" s="174" t="n"/>
-      <c r="K41" s="169" t="n"/>
-      <c r="L41" s="186">
-        <f>IF(AND(J31&lt;&gt;"",K31&lt;&gt;"",K31&lt;&gt;0),J31/K31,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="189" t="n"/>
-      <c r="N41" s="190" t="n"/>
-      <c r="O41" s="102" t="n"/>
-    </row>
-    <row r="42" ht="21.75" customHeight="1" s="101">
-      <c r="A42" s="184" t="n">
-        <v>45703</v>
-      </c>
-      <c r="B42" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C42" s="168" t="n"/>
-      <c r="D42" s="169" t="n"/>
-      <c r="E42" s="186">
-        <f>IF(AND(C32&lt;&gt;"",D32&lt;&gt;"",D32&lt;&gt;0),C32/D32/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="171" t="n"/>
-      <c r="G42" s="187">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;""),E32-F32,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="188">
-        <f>IF(AND(E32&lt;&gt;"",F32&lt;&gt;"",F32&lt;&gt;0),(E32-F32)/F32,"")</f>
-        <v/>
-      </c>
-      <c r="I42" s="171" t="n"/>
-      <c r="J42" s="174" t="n"/>
-      <c r="K42" s="169" t="n"/>
-      <c r="L42" s="186">
-        <f>IF(AND(J32&lt;&gt;"",K32&lt;&gt;"",K32&lt;&gt;0),J32/K32,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="189" t="n"/>
-      <c r="N42" s="190" t="n"/>
-      <c r="O42" s="102" t="n"/>
-    </row>
-    <row r="43" ht="21.75" customHeight="1" s="101">
-      <c r="A43" s="166" t="n">
-        <v>45702</v>
-      </c>
-      <c r="B43" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C43" s="168" t="n"/>
-      <c r="D43" s="169" t="n"/>
-      <c r="E43" s="170">
-        <f>IF(AND(C33&lt;&gt;"",D33&lt;&gt;"",D33&lt;&gt;0),C33/D33/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="171" t="n"/>
-      <c r="G43" s="172">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;""),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="173">
-        <f>IF(AND(E33&lt;&gt;"",F33&lt;&gt;"",F33&lt;&gt;0),(E33-F33)/F33,"")</f>
-        <v/>
-      </c>
-      <c r="I43" s="171" t="n"/>
-      <c r="J43" s="174" t="n"/>
-      <c r="K43" s="169" t="n"/>
-      <c r="L43" s="170">
-        <f>IF(AND(J33&lt;&gt;"",K33&lt;&gt;"",K33&lt;&gt;0),J33/K33,"")</f>
-        <v/>
-      </c>
-      <c r="M43" s="175" t="n"/>
-      <c r="N43" s="176" t="n"/>
-      <c r="O43" s="102" t="n"/>
-    </row>
-    <row r="44" ht="21.75" customHeight="1" s="101">
-      <c r="A44" s="177" t="n">
-        <v>45701</v>
-      </c>
-      <c r="B44" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C44" s="168" t="n"/>
-      <c r="D44" s="169" t="n"/>
-      <c r="E44" s="179">
-        <f>IF(AND(C34&lt;&gt;"",D34&lt;&gt;"",D34&lt;&gt;0),C34/D34/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="171" t="n"/>
-      <c r="G44" s="180">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;""),E34-F34,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="181">
-        <f>IF(AND(E34&lt;&gt;"",F34&lt;&gt;"",F34&lt;&gt;0),(E34-F34)/F34,"")</f>
-        <v/>
-      </c>
-      <c r="I44" s="171" t="n"/>
-      <c r="J44" s="174" t="n"/>
-      <c r="K44" s="169" t="n"/>
-      <c r="L44" s="179">
-        <f>IF(AND(J34&lt;&gt;"",K34&lt;&gt;"",K34&lt;&gt;0),J34/K34,"")</f>
-        <v/>
-      </c>
-      <c r="M44" s="182" t="n"/>
-      <c r="N44" s="183" t="n"/>
-      <c r="O44" s="102" t="n"/>
-    </row>
-    <row r="45" ht="21.75" customHeight="1" s="101">
-      <c r="A45" s="166" t="n">
-        <v>45700</v>
-      </c>
-      <c r="B45" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C45" s="168" t="n"/>
-      <c r="D45" s="169" t="n"/>
-      <c r="E45" s="170">
-        <f>IF(AND(C35&lt;&gt;"",D35&lt;&gt;"",D35&lt;&gt;0),C35/D35/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="171" t="n"/>
-      <c r="G45" s="172">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;""),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="173">
-        <f>IF(AND(E35&lt;&gt;"",F35&lt;&gt;"",F35&lt;&gt;0),(E35-F35)/F35,"")</f>
-        <v/>
-      </c>
-      <c r="I45" s="171" t="n"/>
-      <c r="J45" s="174" t="n"/>
-      <c r="K45" s="169" t="n"/>
-      <c r="L45" s="170">
-        <f>IF(AND(J35&lt;&gt;"",K35&lt;&gt;"",K35&lt;&gt;0),J35/K35,"")</f>
-        <v/>
-      </c>
-      <c r="M45" s="175" t="n"/>
-      <c r="N45" s="176" t="n"/>
-      <c r="O45" s="102" t="n"/>
-    </row>
-    <row r="46" ht="21.75" customHeight="1" s="101">
-      <c r="A46" s="177" t="n">
-        <v>45699</v>
-      </c>
-      <c r="B46" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C46" s="168" t="n"/>
-      <c r="D46" s="169" t="n"/>
-      <c r="E46" s="179">
-        <f>IF(AND(C36&lt;&gt;"",D36&lt;&gt;"",D36&lt;&gt;0),C36/D36/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="171" t="n"/>
-      <c r="G46" s="180">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;""),E36-F36,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="181">
-        <f>IF(AND(E36&lt;&gt;"",F36&lt;&gt;"",F36&lt;&gt;0),(E36-F36)/F36,"")</f>
-        <v/>
-      </c>
-      <c r="I46" s="171" t="n"/>
-      <c r="J46" s="174" t="n"/>
-      <c r="K46" s="169" t="n"/>
-      <c r="L46" s="179">
-        <f>IF(AND(J36&lt;&gt;"",K36&lt;&gt;"",K36&lt;&gt;0),J36/K36,"")</f>
-        <v/>
-      </c>
-      <c r="M46" s="182" t="n"/>
-      <c r="N46" s="183" t="n"/>
-      <c r="O46" s="102" t="n"/>
-    </row>
-    <row r="47" ht="21.75" customHeight="1" s="101">
-      <c r="A47" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B47" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C47" s="168" t="n"/>
-      <c r="D47" s="169" t="n"/>
-      <c r="E47" s="170">
-        <f>IF(AND(C37&lt;&gt;"",D37&lt;&gt;"",D37&lt;&gt;0),C37/D37/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="171" t="n"/>
-      <c r="G47" s="172">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;""),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="173">
-        <f>IF(AND(E37&lt;&gt;"",F37&lt;&gt;"",F37&lt;&gt;0),(E37-F37)/F37,"")</f>
-        <v/>
-      </c>
-      <c r="I47" s="171" t="n"/>
-      <c r="J47" s="174" t="n"/>
-      <c r="K47" s="169" t="n"/>
-      <c r="L47" s="170">
-        <f>IF(AND(J37&lt;&gt;"",K37&lt;&gt;"",K37&lt;&gt;0),J37/K37,"")</f>
-        <v/>
-      </c>
-      <c r="M47" s="175" t="n"/>
-      <c r="N47" s="176" t="n"/>
-      <c r="O47" s="102" t="n"/>
-    </row>
-    <row r="48" ht="21.75" customHeight="1" s="101">
-      <c r="A48" s="184" t="n">
-        <v>45697</v>
-      </c>
-      <c r="B48" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C48" s="168" t="n"/>
-      <c r="D48" s="169" t="n"/>
-      <c r="E48" s="186">
-        <f>IF(AND(C38&lt;&gt;"",D38&lt;&gt;"",D38&lt;&gt;0),C38/D38/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="171" t="n"/>
-      <c r="G48" s="187">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;""),E38-F38,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="188">
-        <f>IF(AND(E38&lt;&gt;"",F38&lt;&gt;"",F38&lt;&gt;0),(E38-F38)/F38,"")</f>
-        <v/>
-      </c>
-      <c r="I48" s="171" t="n"/>
-      <c r="J48" s="174" t="n"/>
-      <c r="K48" s="169" t="n"/>
-      <c r="L48" s="186">
-        <f>IF(AND(J38&lt;&gt;"",K38&lt;&gt;"",K38&lt;&gt;0),J38/K38,"")</f>
-        <v/>
-      </c>
-      <c r="M48" s="189" t="n"/>
-      <c r="N48" s="190" t="n"/>
-      <c r="O48" s="102" t="n"/>
-    </row>
-    <row r="49" ht="21.75" customHeight="1" s="101">
-      <c r="A49" s="184" t="n">
-        <v>45696</v>
-      </c>
-      <c r="B49" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C49" s="168" t="n"/>
-      <c r="D49" s="169" t="n"/>
-      <c r="E49" s="186">
-        <f>IF(AND(C39&lt;&gt;"",D39&lt;&gt;"",D39&lt;&gt;0),C39/D39/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="171" t="n"/>
-      <c r="G49" s="187">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;""),E39-F39,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="188">
-        <f>IF(AND(E39&lt;&gt;"",F39&lt;&gt;"",F39&lt;&gt;0),(E39-F39)/F39,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="171" t="n"/>
-      <c r="J49" s="174" t="n"/>
-      <c r="K49" s="169" t="n"/>
-      <c r="L49" s="186">
-        <f>IF(AND(J39&lt;&gt;"",K39&lt;&gt;"",K39&lt;&gt;0),J39/K39,"")</f>
-        <v/>
-      </c>
-      <c r="M49" s="189" t="n"/>
-      <c r="N49" s="190" t="n"/>
-      <c r="O49" s="102" t="n"/>
-    </row>
-    <row r="50" ht="21.75" customHeight="1" s="101">
-      <c r="A50" s="177" t="n">
-        <v>45695</v>
-      </c>
-      <c r="B50" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C50" s="168" t="n"/>
-      <c r="D50" s="169" t="n"/>
-      <c r="E50" s="179">
-        <f>IF(AND(C40&lt;&gt;"",D40&lt;&gt;"",D40&lt;&gt;0),C40/D40/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="171" t="n"/>
-      <c r="G50" s="180">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;""),E40-F40,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="181">
-        <f>IF(AND(E40&lt;&gt;"",F40&lt;&gt;"",F40&lt;&gt;0),(E40-F40)/F40,"")</f>
-        <v/>
-      </c>
-      <c r="I50" s="171" t="n"/>
-      <c r="J50" s="174" t="n"/>
-      <c r="K50" s="169" t="n"/>
-      <c r="L50" s="179">
-        <f>IF(AND(J40&lt;&gt;"",K40&lt;&gt;"",K40&lt;&gt;0),J40/K40,"")</f>
-        <v/>
-      </c>
-      <c r="M50" s="182" t="n"/>
-      <c r="N50" s="183" t="n"/>
-      <c r="O50" s="102" t="n"/>
-    </row>
-    <row r="51" ht="21.75" customHeight="1" s="101">
-      <c r="A51" s="166" t="n">
-        <v>45694</v>
-      </c>
-      <c r="B51" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C51" s="168" t="n"/>
-      <c r="D51" s="169" t="n"/>
-      <c r="E51" s="170">
-        <f>IF(AND(C41&lt;&gt;"",D41&lt;&gt;"",D41&lt;&gt;0),C41/D41/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="171" t="n"/>
-      <c r="G51" s="172">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;""),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="173">
-        <f>IF(AND(E41&lt;&gt;"",F41&lt;&gt;"",F41&lt;&gt;0),(E41-F41)/F41,"")</f>
-        <v/>
-      </c>
-      <c r="I51" s="171" t="n"/>
-      <c r="J51" s="174" t="n"/>
-      <c r="K51" s="169" t="n"/>
-      <c r="L51" s="170">
-        <f>IF(AND(J41&lt;&gt;"",K41&lt;&gt;"",K41&lt;&gt;0),J41/K41,"")</f>
-        <v/>
-      </c>
-      <c r="M51" s="175" t="n"/>
-      <c r="N51" s="176" t="n"/>
-      <c r="O51" s="102" t="n"/>
-    </row>
-    <row r="52" ht="21.75" customHeight="1" s="101">
-      <c r="A52" s="177" t="n">
-        <v>45693</v>
-      </c>
-      <c r="B52" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C52" s="168" t="n"/>
-      <c r="D52" s="169" t="n"/>
-      <c r="E52" s="179">
-        <f>IF(AND(C42&lt;&gt;"",D42&lt;&gt;"",D42&lt;&gt;0),C42/D42/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="171" t="n"/>
-      <c r="G52" s="180">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;""),E42-F42,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="181">
-        <f>IF(AND(E42&lt;&gt;"",F42&lt;&gt;"",F42&lt;&gt;0),(E42-F42)/F42,"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="171" t="n"/>
-      <c r="J52" s="174" t="n"/>
-      <c r="K52" s="169" t="n"/>
-      <c r="L52" s="179">
-        <f>IF(AND(J42&lt;&gt;"",K42&lt;&gt;"",K42&lt;&gt;0),J42/K42,"")</f>
-        <v/>
-      </c>
-      <c r="M52" s="182" t="n"/>
-      <c r="N52" s="183" t="n"/>
-      <c r="O52" s="102" t="n"/>
-    </row>
-    <row r="53" ht="21.75" customHeight="1" s="101">
-      <c r="A53" s="166" t="n">
-        <v>45692</v>
-      </c>
-      <c r="B53" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C53" s="168" t="n"/>
-      <c r="D53" s="169" t="n"/>
-      <c r="E53" s="170">
-        <f>IF(AND(C43&lt;&gt;"",D43&lt;&gt;"",D43&lt;&gt;0),C43/D43/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="171" t="n"/>
-      <c r="G53" s="172">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;""),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="173">
-        <f>IF(AND(E43&lt;&gt;"",F43&lt;&gt;"",F43&lt;&gt;0),(E43-F43)/F43,"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="171" t="n"/>
-      <c r="J53" s="174" t="n"/>
-      <c r="K53" s="169" t="n"/>
-      <c r="L53" s="170">
-        <f>IF(AND(J43&lt;&gt;"",K43&lt;&gt;"",K43&lt;&gt;0),J43/K43,"")</f>
-        <v/>
-      </c>
-      <c r="M53" s="175" t="n"/>
-      <c r="N53" s="176" t="n"/>
-      <c r="O53" s="102" t="n"/>
-    </row>
-    <row r="54" ht="21.75" customHeight="1" s="101">
-      <c r="A54" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B54" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C54" s="168" t="n"/>
-      <c r="D54" s="169" t="n"/>
-      <c r="E54" s="179">
-        <f>IF(AND(C44&lt;&gt;"",D44&lt;&gt;"",D44&lt;&gt;0),C44/D44/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="171" t="n"/>
-      <c r="G54" s="180">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;""),E44-F44,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="181">
-        <f>IF(AND(E44&lt;&gt;"",F44&lt;&gt;"",F44&lt;&gt;0),(E44-F44)/F44,"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="171" t="n"/>
-      <c r="J54" s="174" t="n"/>
-      <c r="K54" s="169" t="n"/>
-      <c r="L54" s="179">
-        <f>IF(AND(J44&lt;&gt;"",K44&lt;&gt;"",K44&lt;&gt;0),J44/K44,"")</f>
-        <v/>
-      </c>
-      <c r="M54" s="182" t="n"/>
-      <c r="N54" s="183" t="n"/>
-      <c r="O54" s="102" t="n"/>
-    </row>
-    <row r="55" ht="21.75" customHeight="1" s="101">
-      <c r="A55" s="184" t="n">
-        <v>45690</v>
-      </c>
-      <c r="B55" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C55" s="168" t="n"/>
-      <c r="D55" s="169" t="n"/>
-      <c r="E55" s="186">
-        <f>IF(AND(C45&lt;&gt;"",D45&lt;&gt;"",D45&lt;&gt;0),C45/D45/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="171" t="n"/>
-      <c r="G55" s="187">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;""),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="188">
-        <f>IF(AND(E45&lt;&gt;"",F45&lt;&gt;"",F45&lt;&gt;0),(E45-F45)/F45,"")</f>
-        <v/>
-      </c>
-      <c r="I55" s="171" t="n"/>
-      <c r="J55" s="174" t="n"/>
-      <c r="K55" s="169" t="n"/>
-      <c r="L55" s="186">
-        <f>IF(AND(J45&lt;&gt;"",K45&lt;&gt;"",K45&lt;&gt;0),J45/K45,"")</f>
-        <v/>
-      </c>
-      <c r="M55" s="189" t="n"/>
-      <c r="N55" s="190" t="n"/>
-      <c r="O55" s="102" t="n"/>
-    </row>
-    <row r="56" ht="21.75" customHeight="1" s="101">
-      <c r="A56" s="184" t="n">
-        <v>45689</v>
-      </c>
-      <c r="B56" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C56" s="168" t="n"/>
-      <c r="D56" s="169" t="n"/>
-      <c r="E56" s="186">
-        <f>IF(AND(C46&lt;&gt;"",D46&lt;&gt;"",D46&lt;&gt;0),C46/D46/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F56" s="171" t="n"/>
-      <c r="G56" s="187">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;""),E46-F46,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="188">
-        <f>IF(AND(E46&lt;&gt;"",F46&lt;&gt;"",F46&lt;&gt;0),(E46-F46)/F46,"")</f>
-        <v/>
-      </c>
-      <c r="I56" s="171" t="n"/>
-      <c r="J56" s="174" t="n"/>
-      <c r="K56" s="169" t="n"/>
-      <c r="L56" s="186">
-        <f>IF(AND(J46&lt;&gt;"",K46&lt;&gt;"",K46&lt;&gt;0),J46/K46,"")</f>
-        <v/>
-      </c>
-      <c r="M56" s="189" t="n"/>
-      <c r="N56" s="190" t="n"/>
-      <c r="O56" s="102" t="n"/>
-    </row>
-    <row r="57" ht="21.75" customHeight="1" s="101">
-      <c r="A57" s="166" t="n">
-        <v>45688</v>
-      </c>
-      <c r="B57" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C57" s="168" t="n"/>
-      <c r="D57" s="169" t="n"/>
-      <c r="E57" s="170">
-        <f>IF(AND(C47&lt;&gt;"",D47&lt;&gt;"",D47&lt;&gt;0),C47/D47/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F57" s="171" t="n"/>
-      <c r="G57" s="172">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;""),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="173">
-        <f>IF(AND(E47&lt;&gt;"",F47&lt;&gt;"",F47&lt;&gt;0),(E47-F47)/F47,"")</f>
-        <v/>
-      </c>
-      <c r="I57" s="171" t="n"/>
-      <c r="J57" s="174" t="n"/>
-      <c r="K57" s="169" t="n"/>
-      <c r="L57" s="170">
-        <f>IF(AND(J47&lt;&gt;"",K47&lt;&gt;"",K47&lt;&gt;0),J47/K47,"")</f>
-        <v/>
-      </c>
-      <c r="M57" s="175" t="n"/>
-      <c r="N57" s="176" t="n"/>
-      <c r="O57" s="102" t="n"/>
-    </row>
-    <row r="58" ht="21.75" customHeight="1" s="101">
-      <c r="A58" s="177" t="n">
-        <v>45687</v>
-      </c>
-      <c r="B58" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C58" s="168" t="n"/>
-      <c r="D58" s="169" t="n"/>
-      <c r="E58" s="179">
-        <f>IF(AND(C48&lt;&gt;"",D48&lt;&gt;"",D48&lt;&gt;0),C48/D48/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="171" t="n"/>
-      <c r="G58" s="180">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;""),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="181">
-        <f>IF(AND(E48&lt;&gt;"",F48&lt;&gt;"",F48&lt;&gt;0),(E48-F48)/F48,"")</f>
-        <v/>
-      </c>
-      <c r="I58" s="171" t="n"/>
-      <c r="J58" s="174" t="n"/>
-      <c r="K58" s="169" t="n"/>
-      <c r="L58" s="179">
-        <f>IF(AND(J48&lt;&gt;"",K48&lt;&gt;"",K48&lt;&gt;0),J48/K48,"")</f>
-        <v/>
-      </c>
-      <c r="M58" s="182" t="n"/>
-      <c r="N58" s="183" t="n"/>
-      <c r="O58" s="102" t="n"/>
-    </row>
-    <row r="59" ht="21.75" customHeight="1" s="101">
-      <c r="A59" s="166" t="n">
-        <v>45686</v>
-      </c>
-      <c r="B59" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C59" s="168" t="n"/>
-      <c r="D59" s="169" t="n"/>
-      <c r="E59" s="170">
-        <f>IF(AND(C49&lt;&gt;"",D49&lt;&gt;"",D49&lt;&gt;0),C49/D49/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F59" s="171" t="n"/>
-      <c r="G59" s="172">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;""),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="173">
-        <f>IF(AND(E49&lt;&gt;"",F49&lt;&gt;"",F49&lt;&gt;0),(E49-F49)/F49,"")</f>
-        <v/>
-      </c>
-      <c r="I59" s="171" t="n"/>
-      <c r="J59" s="174" t="n"/>
-      <c r="K59" s="169" t="n"/>
-      <c r="L59" s="170">
-        <f>IF(AND(J49&lt;&gt;"",K49&lt;&gt;"",K49&lt;&gt;0),J49/K49,"")</f>
-        <v/>
-      </c>
-      <c r="M59" s="175" t="n"/>
-      <c r="N59" s="176" t="n"/>
-      <c r="O59" s="102" t="n"/>
-    </row>
-    <row r="60" ht="21.75" customHeight="1" s="101">
-      <c r="A60" s="177" t="n">
-        <v>45685</v>
-      </c>
-      <c r="B60" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C60" s="168" t="n"/>
-      <c r="D60" s="169" t="n"/>
-      <c r="E60" s="179">
-        <f>IF(AND(C50&lt;&gt;"",D50&lt;&gt;"",D50&lt;&gt;0),C50/D50/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="171" t="n"/>
-      <c r="G60" s="180">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;""),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="181">
-        <f>IF(AND(E50&lt;&gt;"",F50&lt;&gt;"",F50&lt;&gt;0),(E50-F50)/F50,"")</f>
-        <v/>
-      </c>
-      <c r="I60" s="171" t="n"/>
-      <c r="J60" s="174" t="n"/>
-      <c r="K60" s="169" t="n"/>
-      <c r="L60" s="179">
-        <f>IF(AND(J50&lt;&gt;"",K50&lt;&gt;"",K50&lt;&gt;0),J50/K50,"")</f>
-        <v/>
-      </c>
-      <c r="M60" s="182" t="n"/>
-      <c r="N60" s="183" t="n"/>
-      <c r="O60" s="102" t="n"/>
-    </row>
-    <row r="61" ht="21.75" customHeight="1" s="101">
-      <c r="A61" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B61" s="167" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C61" s="168" t="n"/>
-      <c r="D61" s="169" t="n"/>
-      <c r="E61" s="170">
-        <f>IF(AND(C51&lt;&gt;"",D51&lt;&gt;"",D51&lt;&gt;0),C51/D51/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F61" s="171" t="n"/>
-      <c r="G61" s="172">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;""),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="173">
-        <f>IF(AND(E51&lt;&gt;"",F51&lt;&gt;"",F51&lt;&gt;0),(E51-F51)/F51,"")</f>
-        <v/>
-      </c>
-      <c r="I61" s="171" t="n"/>
-      <c r="J61" s="174" t="n"/>
-      <c r="K61" s="169" t="n"/>
-      <c r="L61" s="170">
-        <f>IF(AND(J51&lt;&gt;"",K51&lt;&gt;"",K51&lt;&gt;0),J51/K51,"")</f>
-        <v/>
-      </c>
-      <c r="M61" s="175" t="n"/>
-      <c r="N61" s="176" t="n"/>
-      <c r="O61" s="102" t="n"/>
-    </row>
-    <row r="62" ht="21.75" customHeight="1" s="101">
-      <c r="A62" s="184" t="n">
-        <v>45683</v>
-      </c>
-      <c r="B62" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C62" s="168" t="n"/>
-      <c r="D62" s="169" t="n"/>
-      <c r="E62" s="186">
-        <f>IF(AND(C52&lt;&gt;"",D52&lt;&gt;"",D52&lt;&gt;0),C52/D52/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F62" s="171" t="n"/>
-      <c r="G62" s="187">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;""),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="188">
-        <f>IF(AND(E52&lt;&gt;"",F52&lt;&gt;"",F52&lt;&gt;0),(E52-F52)/F52,"")</f>
-        <v/>
-      </c>
-      <c r="I62" s="171" t="n"/>
-      <c r="J62" s="174" t="n"/>
-      <c r="K62" s="169" t="n"/>
-      <c r="L62" s="186">
-        <f>IF(AND(J52&lt;&gt;"",K52&lt;&gt;"",K52&lt;&gt;0),J52/K52,"")</f>
-        <v/>
-      </c>
-      <c r="M62" s="189" t="n"/>
-      <c r="N62" s="190" t="n"/>
-      <c r="O62" s="102" t="n"/>
-    </row>
-    <row r="63" ht="21.75" customHeight="1" s="101">
-      <c r="A63" s="184" t="n">
-        <v>45682</v>
-      </c>
-      <c r="B63" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C63" s="168" t="n"/>
-      <c r="D63" s="169" t="n"/>
-      <c r="E63" s="186">
-        <f>IF(AND(C53&lt;&gt;"",D53&lt;&gt;"",D53&lt;&gt;0),C53/D53/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F63" s="171" t="n"/>
-      <c r="G63" s="187">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;""),E53-F53,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="188">
-        <f>IF(AND(E53&lt;&gt;"",F53&lt;&gt;"",F53&lt;&gt;0),(E53-F53)/F53,"")</f>
-        <v/>
-      </c>
-      <c r="I63" s="171" t="n"/>
-      <c r="J63" s="174" t="n"/>
-      <c r="K63" s="169" t="n"/>
-      <c r="L63" s="186">
-        <f>IF(AND(J53&lt;&gt;"",K53&lt;&gt;"",K53&lt;&gt;0),J53/K53,"")</f>
-        <v/>
-      </c>
-      <c r="M63" s="189" t="n"/>
-      <c r="N63" s="190" t="n"/>
-      <c r="O63" s="102" t="n"/>
-    </row>
-    <row r="64" ht="21.75" customHeight="1" s="101">
-      <c r="A64" s="177" t="n">
-        <v>45681</v>
-      </c>
-      <c r="B64" s="178" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C64" s="168" t="n"/>
-      <c r="D64" s="169" t="n"/>
-      <c r="E64" s="179">
-        <f>IF(AND(C54&lt;&gt;"",D54&lt;&gt;"",D54&lt;&gt;0),C54/D54/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F64" s="171" t="n"/>
-      <c r="G64" s="180">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;""),E54-F54,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="181">
-        <f>IF(AND(E54&lt;&gt;"",F54&lt;&gt;"",F54&lt;&gt;0),(E54-F54)/F54,"")</f>
-        <v/>
-      </c>
-      <c r="I64" s="171" t="n"/>
-      <c r="J64" s="174" t="n"/>
-      <c r="K64" s="169" t="n"/>
-      <c r="L64" s="179">
-        <f>IF(AND(J54&lt;&gt;"",K54&lt;&gt;"",K54&lt;&gt;0),J54/K54,"")</f>
-        <v/>
-      </c>
-      <c r="M64" s="182" t="n"/>
-      <c r="N64" s="183" t="n"/>
-      <c r="O64" s="102" t="n"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="101">
-      <c r="A65" s="166" t="n">
-        <v>45680</v>
-      </c>
-      <c r="B65" s="167" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C65" s="168" t="n"/>
-      <c r="D65" s="169" t="n"/>
-      <c r="E65" s="170">
-        <f>IF(AND(C55&lt;&gt;"",D55&lt;&gt;"",D55&lt;&gt;0),C55/D55/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F65" s="171" t="n"/>
-      <c r="G65" s="172">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;""),E55-F55,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="173">
-        <f>IF(AND(E55&lt;&gt;"",F55&lt;&gt;"",F55&lt;&gt;0),(E55-F55)/F55,"")</f>
-        <v/>
-      </c>
-      <c r="I65" s="171" t="n"/>
-      <c r="J65" s="174" t="n"/>
-      <c r="K65" s="169" t="n"/>
-      <c r="L65" s="170">
-        <f>IF(AND(J55&lt;&gt;"",K55&lt;&gt;"",K55&lt;&gt;0),J55/K55,"")</f>
-        <v/>
-      </c>
-      <c r="M65" s="175" t="n"/>
-      <c r="N65" s="176" t="n"/>
-      <c r="O65" s="102" t="n"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="101">
-      <c r="A66" s="177" t="n">
-        <v>45679</v>
-      </c>
-      <c r="B66" s="178" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C66" s="168" t="n"/>
-      <c r="D66" s="169" t="n"/>
-      <c r="E66" s="179">
-        <f>IF(AND(C56&lt;&gt;"",D56&lt;&gt;"",D56&lt;&gt;0),C56/D56/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F66" s="171" t="n"/>
-      <c r="G66" s="180">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;""),E56-F56,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="181">
-        <f>IF(AND(E56&lt;&gt;"",F56&lt;&gt;"",F56&lt;&gt;0),(E56-F56)/F56,"")</f>
-        <v/>
-      </c>
-      <c r="I66" s="171" t="n"/>
-      <c r="J66" s="174" t="n"/>
-      <c r="K66" s="169" t="n"/>
-      <c r="L66" s="179">
-        <f>IF(AND(J56&lt;&gt;"",K56&lt;&gt;"",K56&lt;&gt;0),J56/K56,"")</f>
-        <v/>
-      </c>
-      <c r="M66" s="182" t="n"/>
-      <c r="N66" s="183" t="n"/>
-      <c r="O66" s="102" t="n"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="101">
-      <c r="A67" s="166" t="n">
-        <v>45678</v>
-      </c>
-      <c r="B67" s="167" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C67" s="168" t="n"/>
-      <c r="D67" s="169" t="n"/>
-      <c r="E67" s="170">
-        <f>IF(AND(C57&lt;&gt;"",D57&lt;&gt;"",D57&lt;&gt;0),C57/D57/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="171" t="n"/>
-      <c r="G67" s="172">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;""),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="173">
-        <f>IF(AND(E57&lt;&gt;"",F57&lt;&gt;"",F57&lt;&gt;0),(E57-F57)/F57,"")</f>
-        <v/>
-      </c>
-      <c r="I67" s="171" t="n"/>
-      <c r="J67" s="174" t="n"/>
-      <c r="K67" s="169" t="n"/>
-      <c r="L67" s="170">
-        <f>IF(AND(J57&lt;&gt;"",K57&lt;&gt;"",K57&lt;&gt;0),J57/K57,"")</f>
-        <v/>
-      </c>
-      <c r="M67" s="175" t="n"/>
-      <c r="N67" s="176" t="n"/>
-      <c r="O67" s="102" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" s="101">
-      <c r="A68" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B68" s="178" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C68" s="168" t="n"/>
-      <c r="D68" s="169" t="n"/>
-      <c r="E68" s="179">
-        <f>IF(AND(C58&lt;&gt;"",D58&lt;&gt;"",D58&lt;&gt;0),C58/D58/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F68" s="171" t="n"/>
-      <c r="G68" s="180">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;""),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="181">
-        <f>IF(AND(E58&lt;&gt;"",F58&lt;&gt;"",F58&lt;&gt;0),(E58-F58)/F58,"")</f>
-        <v/>
-      </c>
-      <c r="I68" s="171" t="n"/>
-      <c r="J68" s="174" t="n"/>
-      <c r="K68" s="169" t="n"/>
-      <c r="L68" s="179">
-        <f>IF(AND(J58&lt;&gt;"",K58&lt;&gt;"",K58&lt;&gt;0),J58/K58,"")</f>
-        <v/>
-      </c>
-      <c r="M68" s="182" t="n"/>
-      <c r="N68" s="183" t="n"/>
-      <c r="O68" s="102" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" s="101">
-      <c r="A69" s="184" t="n">
-        <v>45676</v>
-      </c>
-      <c r="B69" s="185" t="inlineStr">
-        <is>
-          <t>Sun</t>
-        </is>
-      </c>
-      <c r="C69" s="168" t="n"/>
-      <c r="D69" s="169" t="n"/>
-      <c r="E69" s="186">
-        <f>IF(AND(C59&lt;&gt;"",D59&lt;&gt;"",D59&lt;&gt;0),C59/D59/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F69" s="171" t="n"/>
-      <c r="G69" s="187">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;""),E59-F59,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="188">
-        <f>IF(AND(E59&lt;&gt;"",F59&lt;&gt;"",F59&lt;&gt;0),(E59-F59)/F59,"")</f>
-        <v/>
-      </c>
-      <c r="I69" s="171" t="n"/>
-      <c r="J69" s="174" t="n"/>
-      <c r="K69" s="169" t="n"/>
-      <c r="L69" s="186">
-        <f>IF(AND(J59&lt;&gt;"",K59&lt;&gt;"",K59&lt;&gt;0),J59/K59,"")</f>
-        <v/>
-      </c>
-      <c r="M69" s="189" t="n"/>
-      <c r="N69" s="190" t="n"/>
-      <c r="O69" s="102" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="184" t="n">
-        <v>45675</v>
-      </c>
-      <c r="B70" s="185" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="C70" s="168" t="n"/>
-      <c r="D70" s="169" t="n"/>
-      <c r="E70" s="186">
-        <f>IF(AND(C60&lt;&gt;"",D60&lt;&gt;"",D60&lt;&gt;0),C60/D60/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F70" s="171" t="n"/>
-      <c r="G70" s="187">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;""),E60-F60,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="188">
-        <f>IF(AND(E60&lt;&gt;"",F60&lt;&gt;"",F60&lt;&gt;0),(E60-F60)/F60,"")</f>
-        <v/>
-      </c>
-      <c r="I70" s="171" t="n"/>
-      <c r="J70" s="174" t="n"/>
-      <c r="K70" s="169" t="n"/>
-      <c r="L70" s="186">
-        <f>IF(AND(J60&lt;&gt;"",K60&lt;&gt;"",K60&lt;&gt;0),J60/K60,"")</f>
-        <v/>
-      </c>
-      <c r="M70" s="189" t="n"/>
-      <c r="N70" s="190" t="n"/>
-      <c r="O70" s="102" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="166" t="n">
-        <v>45674</v>
-      </c>
-      <c r="B71" s="167" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C71" s="168" t="n"/>
-      <c r="D71" s="169" t="n"/>
-      <c r="E71" s="170">
-        <f>IF(AND(C61&lt;&gt;"",D61&lt;&gt;"",D61&lt;&gt;0),C61/D61/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F71" s="171" t="n"/>
-      <c r="G71" s="172">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;""),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="173">
-        <f>IF(AND(E61&lt;&gt;"",F61&lt;&gt;"",F61&lt;&gt;0),(E61-F61)/F61,"")</f>
-        <v/>
-      </c>
-      <c r="I71" s="171" t="n"/>
-      <c r="J71" s="174" t="n"/>
-      <c r="K71" s="169" t="n"/>
-      <c r="L71" s="170">
-        <f>IF(AND(J61&lt;&gt;"",K61&lt;&gt;"",K61&lt;&gt;0),J61/K61,"")</f>
-        <v/>
-      </c>
-      <c r="M71" s="175" t="n"/>
-      <c r="N71" s="176" t="n"/>
-      <c r="O71" s="102" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="177" t="n">
-        <v>45673</v>
-      </c>
-      <c r="B72" s="178" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C72" s="168" t="n"/>
-      <c r="D72" s="169" t="n"/>
-      <c r="E72" s="179">
-        <f>IF(AND(C62&lt;&gt;"",D62&lt;&gt;"",D62&lt;&gt;0),C62/D62/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F72" s="171" t="n"/>
-      <c r="G72" s="180">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;""),E62-F62,"")</f>
-        <v/>
-      </c>
-      <c r="H72" s="181">
-        <f>IF(AND(E62&lt;&gt;"",F62&lt;&gt;"",F62&lt;&gt;0),(E62-F62)/F62,"")</f>
-        <v/>
-      </c>
-      <c r="I72" s="171" t="n"/>
-      <c r="J72" s="174" t="n"/>
-      <c r="K72" s="169" t="n"/>
-      <c r="L72" s="179">
-        <f>IF(AND(J62&lt;&gt;"",K62&lt;&gt;"",K62&lt;&gt;0),J62/K62,"")</f>
-        <v/>
-      </c>
-      <c r="M72" s="182" t="n"/>
-      <c r="N72" s="183" t="n"/>
-      <c r="O72" s="102" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="166" t="n">
-        <v>45672</v>
-      </c>
-      <c r="B73" s="167" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C73" s="168" t="n"/>
-      <c r="D73" s="169" t="n"/>
-      <c r="E73" s="170">
-        <f>IF(AND(C63&lt;&gt;"",D63&lt;&gt;"",D63&lt;&gt;0),C63/D63/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F73" s="171" t="n"/>
-      <c r="G73" s="172">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;""),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H73" s="173">
-        <f>IF(AND(E63&lt;&gt;"",F63&lt;&gt;"",F63&lt;&gt;0),(E63-F63)/F63,"")</f>
-        <v/>
-      </c>
-      <c r="I73" s="171" t="n"/>
-      <c r="J73" s="174" t="n"/>
-      <c r="K73" s="169" t="n"/>
-      <c r="L73" s="170">
-        <f>IF(AND(J63&lt;&gt;"",K63&lt;&gt;"",K63&lt;&gt;0),J63/K63,"")</f>
-        <v/>
-      </c>
-      <c r="M73" s="175" t="n"/>
-      <c r="N73" s="176" t="n"/>
-      <c r="O73" s="102" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="177" t="n">
-        <v>45671</v>
-      </c>
-      <c r="B74" s="178" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="C74" s="168" t="n"/>
-      <c r="D74" s="169" t="n"/>
-      <c r="E74" s="179">
-        <f>IF(AND(C64&lt;&gt;"",D64&lt;&gt;"",D64&lt;&gt;0),C64/D64/1000,"")</f>
-        <v/>
-      </c>
-      <c r="F74" s="171" t="n"/>
-      <c r="G74" s="180">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;""),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H74" s="181">
-        <f>IF(AND(E64&lt;&gt;"",F64&lt;&gt;"",F64&lt;&gt;0),(E64-F64)/F64,"")</f>
-        <v/>
-      </c>
-      <c r="I74" s="171" t="n"/>
-      <c r="J74" s="174" t="n"/>
-      <c r="K74" s="169" t="n"/>
-      <c r="L74" s="179">
-        <f>IF(AND(J64&lt;&gt;"",K64&lt;&gt;"",K64&lt;&gt;0),J64/K64,"")</f>
-        <v/>
-      </c>
-      <c r="M74" s="182" t="n"/>
-      <c r="N74" s="183" t="n"/>
-      <c r="O74" s="102" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="191" t="n">
-        <v>46093</v>
-      </c>
-      <c r="B75" s="102" t="n"/>
-      <c r="C75" s="102" t="n"/>
-      <c r="D75" s="102" t="n">
-        <v>4.2523</v>
-      </c>
-      <c r="E75" s="102" t="n"/>
-      <c r="F75" s="102" t="n"/>
-      <c r="G75" s="102" t="n"/>
-      <c r="H75" s="102" t="n"/>
-      <c r="I75" s="102" t="n">
-        <v>2.104</v>
-      </c>
-      <c r="J75" s="102" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K75" s="102" t="n">
-        <v>10.6543</v>
-      </c>
-      <c r="L75" s="102" t="n"/>
-      <c r="M75" s="102" t="n"/>
-      <c r="N75" s="102" t="n"/>
-      <c r="O75" s="102" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="102" t="n"/>
-      <c r="B76" s="102" t="n"/>
-      <c r="C76" s="102" t="n"/>
-      <c r="D76" s="102" t="n"/>
-      <c r="E76" s="102" t="n"/>
-      <c r="F76" s="102" t="n"/>
-      <c r="G76" s="102" t="n"/>
-      <c r="H76" s="102" t="n"/>
-      <c r="I76" s="102" t="n"/>
-      <c r="J76" s="102" t="n"/>
-      <c r="K76" s="102" t="n"/>
-      <c r="L76" s="102" t="n"/>
-      <c r="M76" s="102" t="n"/>
-      <c r="N76" s="102" t="n"/>
-      <c r="O76" s="102" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="102" t="n"/>
-      <c r="B77" s="102" t="n"/>
-      <c r="C77" s="102" t="n"/>
-      <c r="D77" s="102" t="n"/>
-      <c r="E77" s="102" t="n"/>
-      <c r="F77" s="102" t="n"/>
-      <c r="G77" s="102" t="n"/>
-      <c r="H77" s="102" t="n"/>
-      <c r="I77" s="102" t="n"/>
-      <c r="J77" s="102" t="n"/>
-      <c r="K77" s="102" t="n"/>
-      <c r="L77" s="102" t="n"/>
-      <c r="M77" s="102" t="n"/>
-      <c r="N77" s="102" t="n"/>
-      <c r="O77" s="102" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="102" t="n"/>
-      <c r="B78" s="102" t="n"/>
-      <c r="C78" s="102" t="n"/>
-      <c r="D78" s="102" t="n"/>
-      <c r="E78" s="102" t="n"/>
-      <c r="F78" s="102" t="n"/>
-      <c r="G78" s="102" t="n"/>
-      <c r="H78" s="102" t="n"/>
-      <c r="I78" s="102" t="n"/>
-      <c r="J78" s="102" t="n"/>
-      <c r="K78" s="102" t="n"/>
-      <c r="L78" s="102" t="n"/>
-      <c r="M78" s="102" t="n"/>
-      <c r="N78" s="102" t="n"/>
-      <c r="O78" s="102" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="102" t="n"/>
-      <c r="B79" s="102" t="n"/>
-      <c r="C79" s="102" t="n"/>
-      <c r="D79" s="102" t="n"/>
-      <c r="E79" s="102" t="n"/>
-      <c r="F79" s="102" t="n"/>
-      <c r="G79" s="102" t="n"/>
-      <c r="H79" s="102" t="n"/>
-      <c r="I79" s="102" t="n"/>
-      <c r="J79" s="102" t="n"/>
-      <c r="K79" s="102" t="n"/>
-      <c r="L79" s="102" t="n"/>
-      <c r="M79" s="102" t="n"/>
-      <c r="N79" s="102" t="n"/>
-      <c r="O79" s="102" t="n"/>
-    </row>
+      <c r="C34" s="224" t="n"/>
+      <c r="D34" s="225" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E34" s="226" t="n"/>
+      <c r="F34" s="227" t="n"/>
+      <c r="G34" s="228" t="n"/>
+      <c r="H34" s="229" t="n"/>
+      <c r="I34" s="227" t="n"/>
+      <c r="J34" s="230" t="n"/>
+      <c r="K34" s="225" t="n">
+        <v>10.5935</v>
+      </c>
+      <c r="L34" s="226" t="n"/>
+      <c r="M34" s="231" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N34" s="232" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21.75" customHeight="1" s="101"/>
+    <row r="36" ht="21.75" customHeight="1" s="101"/>
+    <row r="37" ht="21.75" customHeight="1" s="101"/>
+    <row r="38" ht="21.75" customHeight="1" s="101"/>
+    <row r="39" ht="21.75" customHeight="1" s="101"/>
+    <row r="40" ht="21.75" customHeight="1" s="101"/>
+    <row r="41" ht="21.75" customHeight="1" s="101"/>
+    <row r="42" ht="21.75" customHeight="1" s="101"/>
+    <row r="43" ht="21.75" customHeight="1" s="101"/>
+    <row r="44" ht="21.75" customHeight="1" s="101"/>
+    <row r="45" ht="21.75" customHeight="1" s="101"/>
+    <row r="46" ht="21.75" customHeight="1" s="101"/>
+    <row r="47" ht="21.75" customHeight="1" s="101"/>
+    <row r="48" ht="21.75" customHeight="1" s="101"/>
+    <row r="49" ht="21.75" customHeight="1" s="101"/>
+    <row r="50" ht="21.75" customHeight="1" s="101"/>
+    <row r="51" ht="21.75" customHeight="1" s="101"/>
+    <row r="52" ht="21.75" customHeight="1" s="101"/>
+    <row r="53" ht="21.75" customHeight="1" s="101"/>
+    <row r="54" ht="21.75" customHeight="1" s="101"/>
+    <row r="55" ht="21.75" customHeight="1" s="101"/>
+    <row r="56" ht="21.75" customHeight="1" s="101"/>
+    <row r="57" ht="21.75" customHeight="1" s="101"/>
+    <row r="58" ht="21.75" customHeight="1" s="101"/>
+    <row r="59" ht="21.75" customHeight="1" s="101"/>
+    <row r="60" ht="21.75" customHeight="1" s="101"/>
+    <row r="61" ht="21.75" customHeight="1" s="101"/>
+    <row r="62" ht="21.75" customHeight="1" s="101"/>
+    <row r="63" ht="21.75" customHeight="1" s="101"/>
+    <row r="64" ht="21.75" customHeight="1" s="101"/>
+    <row r="65" ht="15" customHeight="1" s="101"/>
+    <row r="66" ht="15" customHeight="1" s="101"/>
+    <row r="67" ht="15" customHeight="1" s="101"/>
+    <row r="68" ht="15" customHeight="1" s="101"/>
+    <row r="69" ht="15" customHeight="1" s="101"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="J3:L3"/>
@@ -6242,7 +4704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="100" min="1" max="1"/>
@@ -6321,7 +4783,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="101">
       <c r="A4" s="233" t="n">
-        <v>46090.80209268518</v>
+        <v>46090.2966857986</v>
       </c>
       <c r="B4" s="234" t="n">
         <v>1.901</v>
@@ -6348,624 +4810,41 @@
         <v>0.08749999999999999</v>
       </c>
     </row>
-    <row r="5" ht="21.75" customHeight="1" s="101">
-      <c r="A5" s="166" t="n">
-        <v>45726</v>
-      </c>
-      <c r="B5" s="171" t="n"/>
-      <c r="C5" s="171" t="n"/>
-      <c r="D5" s="171" t="n"/>
-      <c r="E5" s="171" t="n"/>
-      <c r="F5" s="171" t="n"/>
-      <c r="G5" s="171" t="n"/>
-      <c r="H5" s="171" t="n"/>
-      <c r="I5" s="173">
-        <f>IF(AND(B4&lt;&gt;"",H4&lt;&gt;"",H4&lt;&gt;0),(B4-H4)/H4,"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="175" t="n"/>
-      <c r="K5" s="102" t="n"/>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="101">
-      <c r="A6" s="177" t="n">
-        <v>45719</v>
-      </c>
-      <c r="B6" s="171" t="n"/>
-      <c r="C6" s="171" t="n"/>
-      <c r="D6" s="171" t="n"/>
-      <c r="E6" s="171" t="n"/>
-      <c r="F6" s="171" t="n"/>
-      <c r="G6" s="171" t="n"/>
-      <c r="H6" s="171" t="n"/>
-      <c r="I6" s="181">
-        <f>IF(AND(B5&lt;&gt;"",H5&lt;&gt;"",H5&lt;&gt;0),(B5-H5)/H5,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="182" t="n"/>
-      <c r="K6" s="102" t="n"/>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="101">
-      <c r="A7" s="166" t="n">
-        <v>45712</v>
-      </c>
-      <c r="B7" s="171" t="n"/>
-      <c r="C7" s="171" t="n"/>
-      <c r="D7" s="171" t="n"/>
-      <c r="E7" s="171" t="n"/>
-      <c r="F7" s="171" t="n"/>
-      <c r="G7" s="171" t="n"/>
-      <c r="H7" s="171" t="n"/>
-      <c r="I7" s="173">
-        <f>IF(AND(B6&lt;&gt;"",H6&lt;&gt;"",H6&lt;&gt;0),(B6-H6)/H6,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="175" t="n"/>
-      <c r="K7" s="102" t="n"/>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="101">
-      <c r="A8" s="177" t="n">
-        <v>45705</v>
-      </c>
-      <c r="B8" s="171" t="n"/>
-      <c r="C8" s="171" t="n"/>
-      <c r="D8" s="171" t="n"/>
-      <c r="E8" s="171" t="n"/>
-      <c r="F8" s="171" t="n"/>
-      <c r="G8" s="171" t="n"/>
-      <c r="H8" s="171" t="n"/>
-      <c r="I8" s="181">
-        <f>IF(AND(B7&lt;&gt;"",H7&lt;&gt;"",H7&lt;&gt;0),(B7-H7)/H7,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="182" t="n"/>
-      <c r="K8" s="102" t="n"/>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="101">
-      <c r="A9" s="166" t="n">
-        <v>45698</v>
-      </c>
-      <c r="B9" s="171" t="n"/>
-      <c r="C9" s="171" t="n"/>
-      <c r="D9" s="171" t="n"/>
-      <c r="E9" s="171" t="n"/>
-      <c r="F9" s="171" t="n"/>
-      <c r="G9" s="171" t="n"/>
-      <c r="H9" s="171" t="n"/>
-      <c r="I9" s="173">
-        <f>IF(AND(B8&lt;&gt;"",H8&lt;&gt;"",H8&lt;&gt;0),(B8-H8)/H8,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="175" t="n"/>
-      <c r="K9" s="102" t="n"/>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="101">
-      <c r="A10" s="177" t="n">
-        <v>45691</v>
-      </c>
-      <c r="B10" s="171" t="n"/>
-      <c r="C10" s="171" t="n"/>
-      <c r="D10" s="171" t="n"/>
-      <c r="E10" s="171" t="n"/>
-      <c r="F10" s="171" t="n"/>
-      <c r="G10" s="171" t="n"/>
-      <c r="H10" s="171" t="n"/>
-      <c r="I10" s="181">
-        <f>IF(AND(B9&lt;&gt;"",H9&lt;&gt;"",H9&lt;&gt;0),(B9-H9)/H9,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="182" t="n"/>
-      <c r="K10" s="102" t="n"/>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" s="101">
-      <c r="A11" s="166" t="n">
-        <v>45684</v>
-      </c>
-      <c r="B11" s="171" t="n"/>
-      <c r="C11" s="171" t="n"/>
-      <c r="D11" s="171" t="n"/>
-      <c r="E11" s="171" t="n"/>
-      <c r="F11" s="171" t="n"/>
-      <c r="G11" s="171" t="n"/>
-      <c r="H11" s="171" t="n"/>
-      <c r="I11" s="173">
-        <f>IF(AND(B10&lt;&gt;"",H10&lt;&gt;"",H10&lt;&gt;0),(B10-H10)/H10,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="175" t="n"/>
-      <c r="K11" s="102" t="n"/>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" s="101">
-      <c r="A12" s="177" t="n">
-        <v>45677</v>
-      </c>
-      <c r="B12" s="171" t="n"/>
-      <c r="C12" s="171" t="n"/>
-      <c r="D12" s="171" t="n"/>
-      <c r="E12" s="171" t="n"/>
-      <c r="F12" s="171" t="n"/>
-      <c r="G12" s="171" t="n"/>
-      <c r="H12" s="171" t="n"/>
-      <c r="I12" s="181">
-        <f>IF(AND(B11&lt;&gt;"",H11&lt;&gt;"",H11&lt;&gt;0),(B11-H11)/H11,"")</f>
-        <v/>
-      </c>
-      <c r="J12" s="182" t="n"/>
-      <c r="K12" s="102" t="n"/>
-    </row>
-    <row r="13" ht="21.75" customHeight="1" s="101">
-      <c r="A13" s="166" t="n">
-        <v>45670</v>
-      </c>
-      <c r="B13" s="171" t="n"/>
-      <c r="C13" s="171" t="n"/>
-      <c r="D13" s="171" t="n"/>
-      <c r="E13" s="171" t="n"/>
-      <c r="F13" s="171" t="n"/>
-      <c r="G13" s="171" t="n"/>
-      <c r="H13" s="171" t="n"/>
-      <c r="I13" s="173">
-        <f>IF(AND(B12&lt;&gt;"",H12&lt;&gt;"",H12&lt;&gt;0),(B12-H12)/H12,"")</f>
-        <v/>
-      </c>
-      <c r="J13" s="175" t="n"/>
-      <c r="K13" s="102" t="n"/>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" s="101">
-      <c r="A14" s="177" t="n">
-        <v>45663</v>
-      </c>
-      <c r="B14" s="171" t="n"/>
-      <c r="C14" s="171" t="n"/>
-      <c r="D14" s="171" t="n"/>
-      <c r="E14" s="171" t="n"/>
-      <c r="F14" s="171" t="n"/>
-      <c r="G14" s="171" t="n"/>
-      <c r="H14" s="171" t="n"/>
-      <c r="I14" s="181">
-        <f>IF(AND(B13&lt;&gt;"",H13&lt;&gt;"",H13&lt;&gt;0),(B13-H13)/H13,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="182" t="n"/>
-      <c r="K14" s="102" t="n"/>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" s="101">
-      <c r="A15" s="166" t="n">
-        <v>45656</v>
-      </c>
-      <c r="B15" s="171" t="n"/>
-      <c r="C15" s="171" t="n"/>
-      <c r="D15" s="171" t="n"/>
-      <c r="E15" s="171" t="n"/>
-      <c r="F15" s="171" t="n"/>
-      <c r="G15" s="171" t="n"/>
-      <c r="H15" s="171" t="n"/>
-      <c r="I15" s="173">
-        <f>IF(AND(B14&lt;&gt;"",H14&lt;&gt;"",H14&lt;&gt;0),(B14-H14)/H14,"")</f>
-        <v/>
-      </c>
-      <c r="J15" s="175" t="n"/>
-      <c r="K15" s="102" t="n"/>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" s="101">
-      <c r="A16" s="177" t="n">
-        <v>45649</v>
-      </c>
-      <c r="B16" s="171" t="n"/>
-      <c r="C16" s="171" t="n"/>
-      <c r="D16" s="171" t="n"/>
-      <c r="E16" s="171" t="n"/>
-      <c r="F16" s="171" t="n"/>
-      <c r="G16" s="171" t="n"/>
-      <c r="H16" s="171" t="n"/>
-      <c r="I16" s="181">
-        <f>IF(AND(B15&lt;&gt;"",H15&lt;&gt;"",H15&lt;&gt;0),(B15-H15)/H15,"")</f>
-        <v/>
-      </c>
-      <c r="J16" s="182" t="n"/>
-      <c r="K16" s="102" t="n"/>
-    </row>
-    <row r="17" ht="21.75" customHeight="1" s="101">
-      <c r="A17" s="166" t="n">
-        <v>45642</v>
-      </c>
-      <c r="B17" s="171" t="n"/>
-      <c r="C17" s="171" t="n"/>
-      <c r="D17" s="171" t="n"/>
-      <c r="E17" s="171" t="n"/>
-      <c r="F17" s="171" t="n"/>
-      <c r="G17" s="171" t="n"/>
-      <c r="H17" s="171" t="n"/>
-      <c r="I17" s="173">
-        <f>IF(AND(B16&lt;&gt;"",H16&lt;&gt;"",H16&lt;&gt;0),(B16-H16)/H16,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="175" t="n"/>
-      <c r="K17" s="102" t="n"/>
-    </row>
-    <row r="18" ht="21.75" customHeight="1" s="101">
-      <c r="A18" s="177" t="n">
-        <v>45635</v>
-      </c>
-      <c r="B18" s="171" t="n"/>
-      <c r="C18" s="171" t="n"/>
-      <c r="D18" s="171" t="n"/>
-      <c r="E18" s="171" t="n"/>
-      <c r="F18" s="171" t="n"/>
-      <c r="G18" s="171" t="n"/>
-      <c r="H18" s="171" t="n"/>
-      <c r="I18" s="181">
-        <f>IF(AND(B17&lt;&gt;"",H17&lt;&gt;"",H17&lt;&gt;0),(B17-H17)/H17,"")</f>
-        <v/>
-      </c>
-      <c r="J18" s="182" t="n"/>
-      <c r="K18" s="102" t="n"/>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" s="101">
-      <c r="A19" s="166" t="n">
-        <v>45628</v>
-      </c>
-      <c r="B19" s="171" t="n"/>
-      <c r="C19" s="171" t="n"/>
-      <c r="D19" s="171" t="n"/>
-      <c r="E19" s="171" t="n"/>
-      <c r="F19" s="171" t="n"/>
-      <c r="G19" s="171" t="n"/>
-      <c r="H19" s="171" t="n"/>
-      <c r="I19" s="173">
-        <f>IF(AND(B18&lt;&gt;"",H18&lt;&gt;"",H18&lt;&gt;0),(B18-H18)/H18,"")</f>
-        <v/>
-      </c>
-      <c r="J19" s="175" t="n"/>
-      <c r="K19" s="102" t="n"/>
-    </row>
-    <row r="20" ht="21.75" customHeight="1" s="101">
-      <c r="A20" s="177" t="n">
-        <v>45621</v>
-      </c>
-      <c r="B20" s="171" t="n"/>
-      <c r="C20" s="171" t="n"/>
-      <c r="D20" s="171" t="n"/>
-      <c r="E20" s="171" t="n"/>
-      <c r="F20" s="171" t="n"/>
-      <c r="G20" s="171" t="n"/>
-      <c r="H20" s="171" t="n"/>
-      <c r="I20" s="181">
-        <f>IF(AND(B19&lt;&gt;"",H19&lt;&gt;"",H19&lt;&gt;0),(B19-H19)/H19,"")</f>
-        <v/>
-      </c>
-      <c r="J20" s="182" t="n"/>
-      <c r="K20" s="102" t="n"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="101">
-      <c r="A21" s="166" t="n">
-        <v>45614</v>
-      </c>
-      <c r="B21" s="171" t="n"/>
-      <c r="C21" s="171" t="n"/>
-      <c r="D21" s="171" t="n"/>
-      <c r="E21" s="171" t="n"/>
-      <c r="F21" s="171" t="n"/>
-      <c r="G21" s="171" t="n"/>
-      <c r="H21" s="171" t="n"/>
-      <c r="I21" s="173">
-        <f>IF(AND(B20&lt;&gt;"",H20&lt;&gt;"",H20&lt;&gt;0),(B20-H20)/H20,"")</f>
-        <v/>
-      </c>
-      <c r="J21" s="175" t="n"/>
-      <c r="K21" s="102" t="n"/>
-    </row>
-    <row r="22" ht="21.75" customHeight="1" s="101">
-      <c r="A22" s="177" t="n">
-        <v>45607</v>
-      </c>
-      <c r="B22" s="171" t="n"/>
-      <c r="C22" s="171" t="n"/>
-      <c r="D22" s="171" t="n"/>
-      <c r="E22" s="171" t="n"/>
-      <c r="F22" s="171" t="n"/>
-      <c r="G22" s="171" t="n"/>
-      <c r="H22" s="171" t="n"/>
-      <c r="I22" s="181">
-        <f>IF(AND(B21&lt;&gt;"",H21&lt;&gt;"",H21&lt;&gt;0),(B21-H21)/H21,"")</f>
-        <v/>
-      </c>
-      <c r="J22" s="182" t="n"/>
-      <c r="K22" s="102" t="n"/>
-    </row>
-    <row r="23" ht="21.75" customHeight="1" s="101">
-      <c r="A23" s="166" t="n">
-        <v>45600</v>
-      </c>
-      <c r="B23" s="171" t="n"/>
-      <c r="C23" s="171" t="n"/>
-      <c r="D23" s="171" t="n"/>
-      <c r="E23" s="171" t="n"/>
-      <c r="F23" s="171" t="n"/>
-      <c r="G23" s="171" t="n"/>
-      <c r="H23" s="171" t="n"/>
-      <c r="I23" s="173">
-        <f>IF(AND(B22&lt;&gt;"",H22&lt;&gt;"",H22&lt;&gt;0),(B22-H22)/H22,"")</f>
-        <v/>
-      </c>
-      <c r="J23" s="175" t="n"/>
-      <c r="K23" s="102" t="n"/>
-    </row>
-    <row r="24" ht="21.75" customHeight="1" s="101">
-      <c r="A24" s="177" t="n">
-        <v>45593</v>
-      </c>
-      <c r="B24" s="171" t="n"/>
-      <c r="C24" s="171" t="n"/>
-      <c r="D24" s="171" t="n"/>
-      <c r="E24" s="171" t="n"/>
-      <c r="F24" s="171" t="n"/>
-      <c r="G24" s="171" t="n"/>
-      <c r="H24" s="171" t="n"/>
-      <c r="I24" s="181">
-        <f>IF(AND(B23&lt;&gt;"",H23&lt;&gt;"",H23&lt;&gt;0),(B23-H23)/H23,"")</f>
-        <v/>
-      </c>
-      <c r="J24" s="182" t="n"/>
-      <c r="K24" s="102" t="n"/>
-    </row>
-    <row r="25" ht="21.75" customHeight="1" s="101">
-      <c r="A25" s="166" t="n">
-        <v>45586</v>
-      </c>
-      <c r="B25" s="171" t="n"/>
-      <c r="C25" s="171" t="n"/>
-      <c r="D25" s="171" t="n"/>
-      <c r="E25" s="171" t="n"/>
-      <c r="F25" s="171" t="n"/>
-      <c r="G25" s="171" t="n"/>
-      <c r="H25" s="171" t="n"/>
-      <c r="I25" s="173">
-        <f>IF(AND(B24&lt;&gt;"",H24&lt;&gt;"",H24&lt;&gt;0),(B24-H24)/H24,"")</f>
-        <v/>
-      </c>
-      <c r="J25" s="175" t="n"/>
-      <c r="K25" s="102" t="n"/>
-    </row>
-    <row r="26" ht="21.75" customHeight="1" s="101">
-      <c r="A26" s="177" t="n">
-        <v>45579</v>
-      </c>
-      <c r="B26" s="171" t="n"/>
-      <c r="C26" s="171" t="n"/>
-      <c r="D26" s="171" t="n"/>
-      <c r="E26" s="171" t="n"/>
-      <c r="F26" s="171" t="n"/>
-      <c r="G26" s="171" t="n"/>
-      <c r="H26" s="171" t="n"/>
-      <c r="I26" s="181">
-        <f>IF(AND(B25&lt;&gt;"",H25&lt;&gt;"",H25&lt;&gt;0),(B25-H25)/H25,"")</f>
-        <v/>
-      </c>
-      <c r="J26" s="182" t="n"/>
-      <c r="K26" s="102" t="n"/>
-    </row>
-    <row r="27" ht="21.75" customHeight="1" s="101">
-      <c r="A27" s="166" t="n">
-        <v>45572</v>
-      </c>
-      <c r="B27" s="171" t="n"/>
-      <c r="C27" s="171" t="n"/>
-      <c r="D27" s="171" t="n"/>
-      <c r="E27" s="171" t="n"/>
-      <c r="F27" s="171" t="n"/>
-      <c r="G27" s="171" t="n"/>
-      <c r="H27" s="171" t="n"/>
-      <c r="I27" s="173">
-        <f>IF(AND(B26&lt;&gt;"",H26&lt;&gt;"",H26&lt;&gt;0),(B26-H26)/H26,"")</f>
-        <v/>
-      </c>
-      <c r="J27" s="175" t="n"/>
-      <c r="K27" s="102" t="n"/>
-    </row>
-    <row r="28" ht="21.75" customHeight="1" s="101">
-      <c r="A28" s="177" t="n">
-        <v>45565</v>
-      </c>
-      <c r="B28" s="171" t="n"/>
-      <c r="C28" s="171" t="n"/>
-      <c r="D28" s="171" t="n"/>
-      <c r="E28" s="171" t="n"/>
-      <c r="F28" s="171" t="n"/>
-      <c r="G28" s="171" t="n"/>
-      <c r="H28" s="171" t="n"/>
-      <c r="I28" s="181">
-        <f>IF(AND(B27&lt;&gt;"",H27&lt;&gt;"",H27&lt;&gt;0),(B27-H27)/H27,"")</f>
-        <v/>
-      </c>
-      <c r="J28" s="182" t="n"/>
-      <c r="K28" s="102" t="n"/>
-    </row>
-    <row r="29" ht="21.75" customHeight="1" s="101">
-      <c r="A29" s="166" t="n">
-        <v>45558</v>
-      </c>
-      <c r="B29" s="171" t="n"/>
-      <c r="C29" s="171" t="n"/>
-      <c r="D29" s="171" t="n"/>
-      <c r="E29" s="171" t="n"/>
-      <c r="F29" s="171" t="n"/>
-      <c r="G29" s="171" t="n"/>
-      <c r="H29" s="171" t="n"/>
-      <c r="I29" s="173">
-        <f>IF(AND(B28&lt;&gt;"",H28&lt;&gt;"",H28&lt;&gt;0),(B28-H28)/H28,"")</f>
-        <v/>
-      </c>
-      <c r="J29" s="175" t="n"/>
-      <c r="K29" s="102" t="n"/>
-    </row>
-    <row r="30" ht="21.75" customHeight="1" s="101">
-      <c r="A30" s="177" t="n">
-        <v>45551</v>
-      </c>
-      <c r="B30" s="171" t="n"/>
-      <c r="C30" s="171" t="n"/>
-      <c r="D30" s="171" t="n"/>
-      <c r="E30" s="171" t="n"/>
-      <c r="F30" s="171" t="n"/>
-      <c r="G30" s="171" t="n"/>
-      <c r="H30" s="171" t="n"/>
-      <c r="I30" s="181">
-        <f>IF(AND(B29&lt;&gt;"",H29&lt;&gt;"",H29&lt;&gt;0),(B29-H29)/H29,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="182" t="n"/>
-      <c r="K30" s="102" t="n"/>
-    </row>
-    <row r="31" ht="21.75" customHeight="1" s="101">
-      <c r="A31" s="166" t="n">
-        <v>45544</v>
-      </c>
-      <c r="B31" s="171" t="n"/>
-      <c r="C31" s="171" t="n"/>
-      <c r="D31" s="171" t="n"/>
-      <c r="E31" s="171" t="n"/>
-      <c r="F31" s="171" t="n"/>
-      <c r="G31" s="171" t="n"/>
-      <c r="H31" s="171" t="n"/>
-      <c r="I31" s="173">
-        <f>IF(AND(B30&lt;&gt;"",H30&lt;&gt;"",H30&lt;&gt;0),(B30-H30)/H30,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="175" t="n"/>
-      <c r="K31" s="102" t="n"/>
-    </row>
-    <row r="32" ht="21.75" customHeight="1" s="101">
-      <c r="A32" s="177" t="n">
-        <v>45537</v>
-      </c>
-      <c r="B32" s="171" t="n"/>
-      <c r="C32" s="171" t="n"/>
-      <c r="D32" s="171" t="n"/>
-      <c r="E32" s="171" t="n"/>
-      <c r="F32" s="171" t="n"/>
-      <c r="G32" s="171" t="n"/>
-      <c r="H32" s="171" t="n"/>
-      <c r="I32" s="181">
-        <f>IF(AND(B31&lt;&gt;"",H31&lt;&gt;"",H31&lt;&gt;0),(B31-H31)/H31,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="182" t="n"/>
-      <c r="K32" s="102" t="n"/>
-    </row>
-    <row r="33" ht="21.75" customHeight="1" s="101">
-      <c r="A33" s="166" t="n">
-        <v>45530</v>
-      </c>
-      <c r="B33" s="171" t="n"/>
-      <c r="C33" s="171" t="n"/>
-      <c r="D33" s="171" t="n"/>
-      <c r="E33" s="171" t="n"/>
-      <c r="F33" s="171" t="n"/>
-      <c r="G33" s="171" t="n"/>
-      <c r="H33" s="171" t="n"/>
-      <c r="I33" s="173">
-        <f>IF(AND(B32&lt;&gt;"",H32&lt;&gt;"",H32&lt;&gt;0),(B32-H32)/H32,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="175" t="n"/>
-      <c r="K33" s="102" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="101">
-      <c r="A34" s="177" t="n">
-        <v>45523</v>
-      </c>
-      <c r="B34" s="171" t="n"/>
-      <c r="C34" s="171" t="n"/>
-      <c r="D34" s="171" t="n"/>
-      <c r="E34" s="171" t="n"/>
-      <c r="F34" s="171" t="n"/>
-      <c r="G34" s="171" t="n"/>
-      <c r="H34" s="171" t="n"/>
-      <c r="I34" s="181">
-        <f>IF(AND(B33&lt;&gt;"",H33&lt;&gt;"",H33&lt;&gt;0),(B33-H33)/H33,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="182" t="n"/>
-      <c r="K34" s="102" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="101">
-      <c r="A35" s="102" t="n"/>
-      <c r="B35" s="102" t="n"/>
-      <c r="C35" s="102" t="n"/>
-      <c r="D35" s="102" t="n"/>
-      <c r="E35" s="102" t="n"/>
-      <c r="F35" s="102" t="n"/>
-      <c r="G35" s="102" t="n"/>
-      <c r="H35" s="102" t="n"/>
-      <c r="I35" s="102" t="n"/>
-      <c r="J35" s="102" t="n"/>
-      <c r="K35" s="102" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="101">
-      <c r="A36" s="102" t="n"/>
-      <c r="B36" s="102" t="n"/>
-      <c r="C36" s="102" t="n"/>
-      <c r="D36" s="102" t="n"/>
-      <c r="E36" s="102" t="n"/>
-      <c r="F36" s="102" t="n"/>
-      <c r="G36" s="102" t="n"/>
-      <c r="H36" s="102" t="n"/>
-      <c r="I36" s="102" t="n"/>
-      <c r="J36" s="102" t="n"/>
-      <c r="K36" s="102" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="101">
-      <c r="A37" s="102" t="n"/>
-      <c r="B37" s="102" t="n"/>
-      <c r="C37" s="102" t="n"/>
-      <c r="D37" s="102" t="n"/>
-      <c r="E37" s="102" t="n"/>
-      <c r="F37" s="102" t="n"/>
-      <c r="G37" s="102" t="n"/>
-      <c r="H37" s="102" t="n"/>
-      <c r="I37" s="102" t="n"/>
-      <c r="J37" s="102" t="n"/>
-      <c r="K37" s="102" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="101">
-      <c r="A38" s="102" t="n"/>
-      <c r="B38" s="102" t="n"/>
-      <c r="C38" s="102" t="n"/>
-      <c r="D38" s="102" t="n"/>
-      <c r="E38" s="102" t="n"/>
-      <c r="F38" s="102" t="n"/>
-      <c r="G38" s="102" t="n"/>
-      <c r="H38" s="102" t="n"/>
-      <c r="I38" s="102" t="n"/>
-      <c r="J38" s="102" t="n"/>
-      <c r="K38" s="102" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="101">
-      <c r="A39" s="102" t="n"/>
-      <c r="B39" s="102" t="n"/>
-      <c r="C39" s="102" t="n"/>
-      <c r="D39" s="102" t="n"/>
-      <c r="E39" s="102" t="n"/>
-      <c r="F39" s="102" t="n"/>
-      <c r="G39" s="102" t="n"/>
-      <c r="H39" s="102" t="n"/>
-      <c r="I39" s="102" t="n"/>
-      <c r="J39" s="102" t="n"/>
-      <c r="K39" s="102" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="102" t="n"/>
-      <c r="B40" s="102" t="n"/>
-      <c r="C40" s="102" t="n"/>
-      <c r="D40" s="102" t="n"/>
-      <c r="E40" s="102" t="n"/>
-      <c r="F40" s="102" t="n"/>
-      <c r="G40" s="102" t="n"/>
-      <c r="H40" s="102" t="n"/>
-      <c r="I40" s="102" t="n"/>
-      <c r="J40" s="102" t="n"/>
-      <c r="K40" s="102" t="n"/>
-    </row>
+    <row r="5" ht="21.75" customHeight="1" s="101"/>
+    <row r="6" ht="21.75" customHeight="1" s="101"/>
+    <row r="7" ht="21.75" customHeight="1" s="101"/>
+    <row r="8" ht="21.75" customHeight="1" s="101"/>
+    <row r="9" ht="21.75" customHeight="1" s="101"/>
+    <row r="10" ht="21.75" customHeight="1" s="101"/>
+    <row r="11" ht="21.75" customHeight="1" s="101"/>
+    <row r="12" ht="21.75" customHeight="1" s="101"/>
+    <row r="13" ht="21.75" customHeight="1" s="101"/>
+    <row r="14" ht="21.75" customHeight="1" s="101"/>
+    <row r="15" ht="21.75" customHeight="1" s="101"/>
+    <row r="16" ht="21.75" customHeight="1" s="101"/>
+    <row r="17" ht="21.75" customHeight="1" s="101"/>
+    <row r="18" ht="21.75" customHeight="1" s="101"/>
+    <row r="19" ht="21.75" customHeight="1" s="101"/>
+    <row r="20" ht="21.75" customHeight="1" s="101"/>
+    <row r="21" ht="21.75" customHeight="1" s="101"/>
+    <row r="22" ht="21.75" customHeight="1" s="101"/>
+    <row r="23" ht="21.75" customHeight="1" s="101"/>
+    <row r="24" ht="21.75" customHeight="1" s="101"/>
+    <row r="25" ht="21.75" customHeight="1" s="101"/>
+    <row r="26" ht="21.75" customHeight="1" s="101"/>
+    <row r="27" ht="21.75" customHeight="1" s="101"/>
+    <row r="28" ht="21.75" customHeight="1" s="101"/>
+    <row r="29" ht="21.75" customHeight="1" s="101"/>
+    <row r="30" ht="21.75" customHeight="1" s="101"/>
+    <row r="31" ht="21.75" customHeight="1" s="101"/>
+    <row r="32" ht="21.75" customHeight="1" s="101"/>
+    <row r="33" ht="21.75" customHeight="1" s="101"/>
+    <row r="34" ht="15" customHeight="1" s="101"/>
+    <row r="35" ht="15" customHeight="1" s="101"/>
+    <row r="36" ht="15" customHeight="1" s="101"/>
+    <row r="37" ht="15" customHeight="1" s="101"/>
+    <row r="38" ht="15" customHeight="1" s="101"/>
+    <row r="39" ht="15" customHeight="1" s="101"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3526,7 +3526,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46094.2966857986</v>
+        <v>46094.30280758087</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3543,13 +3543,13 @@
         <v>1.5029</v>
       </c>
       <c r="F5" s="227" t="n">
-        <v>1.1651</v>
+        <v>1.7561</v>
       </c>
       <c r="G5" s="228" t="n">
-        <v>0.3378</v>
+        <v>-0.2532</v>
       </c>
       <c r="H5" s="229" t="n">
-        <v>0.2899</v>
+        <v>-0.1442</v>
       </c>
       <c r="I5" s="227" t="n">
         <v>2.163</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="101">
       <c r="A4" s="233" t="n">
-        <v>46090.2966857986</v>
+        <v>46090.30280758087</v>
       </c>
       <c r="B4" s="234" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3526,7 +3526,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="101">
       <c r="A5" s="222" t="n">
-        <v>46094.30280758087</v>
+        <v>46094.30497180892</v>
       </c>
       <c r="B5" s="223" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="101">
       <c r="A6" s="222" t="n">
-        <v>46093.29668083334</v>
+        <v>46093.30496681713</v>
       </c>
       <c r="B6" s="223" t="inlineStr">
         <is>
@@ -3620,7 +3620,7 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="101">
       <c r="A7" s="222" t="n">
-        <v>46092.29668083334</v>
+        <v>46092.30496681713</v>
       </c>
       <c r="B7" s="223" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="101">
       <c r="A8" s="222" t="n">
-        <v>46091.29668083334</v>
+        <v>46091.30496681713</v>
       </c>
       <c r="B8" s="223" t="inlineStr">
         <is>
@@ -3708,7 +3708,7 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="101">
       <c r="A9" s="222" t="n">
-        <v>46090.29668083334</v>
+        <v>46090.30496681713</v>
       </c>
       <c r="B9" s="223" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" s="101">
       <c r="A10" s="222" t="n">
-        <v>46087.29668083334</v>
+        <v>46087.30496681713</v>
       </c>
       <c r="B10" s="223" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" s="101">
       <c r="A11" s="222" t="n">
-        <v>46086.29668083334</v>
+        <v>46086.30496681713</v>
       </c>
       <c r="B11" s="223" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="12" ht="21.75" customHeight="1" s="101">
       <c r="A12" s="222" t="n">
-        <v>46085.29668083334</v>
+        <v>46085.30496681713</v>
       </c>
       <c r="B12" s="223" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
     </row>
     <row r="13" ht="21.75" customHeight="1" s="101">
       <c r="A13" s="222" t="n">
-        <v>46084.29668083334</v>
+        <v>46084.30496681713</v>
       </c>
       <c r="B13" s="223" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
     </row>
     <row r="14" ht="21.75" customHeight="1" s="101">
       <c r="A14" s="222" t="n">
-        <v>46083.29668083334</v>
+        <v>46083.30496681713</v>
       </c>
       <c r="B14" s="223" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="15" ht="21.75" customHeight="1" s="101">
       <c r="A15" s="222" t="n">
-        <v>46080.29668083334</v>
+        <v>46080.30496681713</v>
       </c>
       <c r="B15" s="223" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="16" ht="21.75" customHeight="1" s="101">
       <c r="A16" s="222" t="n">
-        <v>46079.29668083334</v>
+        <v>46079.30496681713</v>
       </c>
       <c r="B16" s="223" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="17" ht="21.75" customHeight="1" s="101">
       <c r="A17" s="222" t="n">
-        <v>46078.29668083334</v>
+        <v>46078.30496681713</v>
       </c>
       <c r="B17" s="223" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="18" ht="21.75" customHeight="1" s="101">
       <c r="A18" s="222" t="n">
-        <v>46077.29668083334</v>
+        <v>46077.30496681713</v>
       </c>
       <c r="B18" s="223" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="19" ht="21.75" customHeight="1" s="101">
       <c r="A19" s="222" t="n">
-        <v>46076.29668083334</v>
+        <v>46076.30496681713</v>
       </c>
       <c r="B19" s="223" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="20" ht="21.75" customHeight="1" s="101">
       <c r="A20" s="222" t="n">
-        <v>46073.29668083334</v>
+        <v>46073.30496681713</v>
       </c>
       <c r="B20" s="223" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
     </row>
     <row r="21" ht="21.75" customHeight="1" s="101">
       <c r="A21" s="222" t="n">
-        <v>46072.29668083334</v>
+        <v>46072.30496681713</v>
       </c>
       <c r="B21" s="223" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="22" ht="21.75" customHeight="1" s="101">
       <c r="A22" s="222" t="n">
-        <v>46071.29668083334</v>
+        <v>46071.30496681713</v>
       </c>
       <c r="B22" s="223" t="inlineStr">
         <is>
@@ -4188,7 +4188,7 @@
     </row>
     <row r="23" ht="21.75" customHeight="1" s="101">
       <c r="A23" s="222" t="n">
-        <v>46070.29668083334</v>
+        <v>46070.30496681713</v>
       </c>
       <c r="B23" s="223" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
     </row>
     <row r="24" ht="21.75" customHeight="1" s="101">
       <c r="A24" s="222" t="n">
-        <v>46069.29668083334</v>
+        <v>46069.30496681713</v>
       </c>
       <c r="B24" s="223" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
     </row>
     <row r="25" ht="21.75" customHeight="1" s="101">
       <c r="A25" s="222" t="n">
-        <v>46066.29668083334</v>
+        <v>46066.30496681713</v>
       </c>
       <c r="B25" s="223" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
     </row>
     <row r="26" ht="21.75" customHeight="1" s="101">
       <c r="A26" s="222" t="n">
-        <v>46065.29668083334</v>
+        <v>46065.30496681713</v>
       </c>
       <c r="B26" s="223" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
     </row>
     <row r="27" ht="21.75" customHeight="1" s="101">
       <c r="A27" s="222" t="n">
-        <v>46064.29668083334</v>
+        <v>46064.30496681713</v>
       </c>
       <c r="B27" s="223" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="28" ht="21.75" customHeight="1" s="101">
       <c r="A28" s="222" t="n">
-        <v>46063.29668083334</v>
+        <v>46063.30496681713</v>
       </c>
       <c r="B28" s="223" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="29" ht="21.75" customHeight="1" s="101">
       <c r="A29" s="222" t="n">
-        <v>46062.29668083334</v>
+        <v>46062.30496681713</v>
       </c>
       <c r="B29" s="223" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
     </row>
     <row r="30" ht="21.75" customHeight="1" s="101">
       <c r="A30" s="222" t="n">
-        <v>46059.29668083334</v>
+        <v>46059.30496681713</v>
       </c>
       <c r="B30" s="223" t="inlineStr">
         <is>
@@ -4460,7 +4460,7 @@
     </row>
     <row r="31" ht="21.75" customHeight="1" s="101">
       <c r="A31" s="222" t="n">
-        <v>46058.29668083334</v>
+        <v>46058.30496681713</v>
       </c>
       <c r="B31" s="223" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
     </row>
     <row r="32" ht="21.75" customHeight="1" s="101">
       <c r="A32" s="222" t="n">
-        <v>46057.29668083334</v>
+        <v>46057.30496681713</v>
       </c>
       <c r="B32" s="223" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
     </row>
     <row r="33" ht="21.75" customHeight="1" s="101">
       <c r="A33" s="222" t="n">
-        <v>46056.29668083334</v>
+        <v>46056.30496681713</v>
       </c>
       <c r="B33" s="223" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="34" ht="21.75" customHeight="1" s="101">
       <c r="A34" s="222" t="n">
-        <v>46055.29668083334</v>
+        <v>46055.30496681713</v>
       </c>
       <c r="B34" s="223" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="101">
       <c r="A4" s="233" t="n">
-        <v>46090.30280758087</v>
+        <v>46090.30497180892</v>
       </c>
       <c r="B4" s="234" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domantas.skupeika\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C94BE61F-B16C-4C1F-8E7D-11886A13A059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{757444FB-8534-44F6-8237-976DC05A92FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3723,8 +3723,13 @@
       <c r="F8" s="41">
         <v>1.8080000000000001</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
+      <c r="G8" s="42">
+        <f>E8-F8</f>
+        <v>-0.31345266522515747</v>
+      </c>
+      <c r="H8" s="43">
+        <v>-0.17336983696081718</v>
+      </c>
       <c r="I8" s="41">
         <v>2.198</v>
       </c>
@@ -3799,8 +3804,13 @@
       <c r="F10" s="41">
         <v>1.845</v>
       </c>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
+      <c r="G10" s="42">
+        <f t="shared" ref="G9:G34" si="0">E10-F10</f>
+        <v>-0.41059766763848393</v>
+      </c>
+      <c r="H10" s="43">
+        <v>-0.22254616132167152</v>
+      </c>
       <c r="I10" s="41">
         <v>2.089</v>
       </c>
@@ -3839,8 +3849,13 @@
       <c r="F11" s="41">
         <v>1.734</v>
       </c>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
+      <c r="G11" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.38584318314803978</v>
+      </c>
+      <c r="H11" s="43">
+        <v>-0.22251625325723171</v>
+      </c>
       <c r="I11" s="41">
         <v>2.0550000000000002</v>
       </c>
@@ -3879,8 +3894,13 @@
       <c r="F12" s="41">
         <v>1.738</v>
       </c>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
+      <c r="G12" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.4040561660561659</v>
+      </c>
+      <c r="H12" s="43">
+        <v>-0.23248340969859949</v>
+      </c>
       <c r="I12" s="41">
         <v>2.0110000000000001</v>
       </c>
@@ -3919,8 +3939,13 @@
       <c r="F13" s="41">
         <v>1.619</v>
       </c>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
+      <c r="G13" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.39725731949142662</v>
+      </c>
+      <c r="H13" s="43">
+        <v>-0.24537203180446363</v>
+      </c>
       <c r="I13" s="41">
         <v>1.9159999999999999</v>
       </c>
@@ -3995,8 +4020,13 @@
       <c r="F15" s="41">
         <v>1.506</v>
       </c>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
+      <c r="G15" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.37516175461023127</v>
+      </c>
+      <c r="H15" s="43">
+        <v>-0.24911139084344705</v>
+      </c>
       <c r="I15" s="41">
         <v>1.748</v>
       </c>
@@ -4035,8 +4065,13 @@
       <c r="F16" s="41">
         <v>1.492</v>
       </c>
-      <c r="G16" s="42"/>
-      <c r="H16" s="43"/>
+      <c r="G16" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.3684949674363529</v>
+      </c>
+      <c r="H16" s="43">
+        <v>-0.24698054117718024</v>
+      </c>
       <c r="I16" s="41">
         <v>1.726</v>
       </c>
@@ -4075,8 +4110,13 @@
       <c r="F17" s="41">
         <v>1.4950000000000001</v>
       </c>
-      <c r="G17" s="42"/>
-      <c r="H17" s="43"/>
+      <c r="G17" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.36673537281272939</v>
+      </c>
+      <c r="H17" s="43">
+        <v>-0.24530794168075543</v>
+      </c>
       <c r="I17" s="41">
         <v>1.74</v>
       </c>
@@ -4115,8 +4155,13 @@
       <c r="F18" s="41">
         <v>1.5049999999999999</v>
       </c>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
+      <c r="G18" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.37498554605122836</v>
+      </c>
+      <c r="H18" s="43">
+        <v>-0.24915983126327468</v>
+      </c>
       <c r="I18" s="41">
         <v>1.7450000000000001</v>
       </c>
@@ -4191,8 +4236,13 @@
       <c r="F20" s="41">
         <v>1.4870000000000001</v>
       </c>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
+      <c r="G20" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.36407751313982661</v>
+      </c>
+      <c r="H20" s="43">
+        <v>-0.24484029128434875</v>
+      </c>
       <c r="I20" s="41">
         <v>1.7270000000000001</v>
       </c>
@@ -4231,8 +4281,13 @@
       <c r="F21" s="41">
         <v>1.46</v>
       </c>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
+      <c r="G21" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.37105057444036471</v>
+      </c>
+      <c r="H21" s="43">
+        <v>-0.25414422906874296</v>
+      </c>
       <c r="I21" s="41">
         <v>1.7130000000000001</v>
       </c>
@@ -4271,8 +4326,13 @@
       <c r="F22" s="41">
         <v>1.4430000000000001</v>
       </c>
-      <c r="G22" s="42"/>
-      <c r="H22" s="43"/>
+      <c r="G22" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.35939985770188532</v>
+      </c>
+      <c r="H22" s="43">
+        <v>-0.24906435045175696</v>
+      </c>
       <c r="I22" s="41">
         <v>1.6970000000000001</v>
       </c>
@@ -4311,8 +4371,13 @@
       <c r="F23" s="41">
         <v>1.448</v>
       </c>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
+      <c r="G23" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.36180701504580171</v>
+      </c>
+      <c r="H23" s="43">
+        <v>-0.24986672309792937</v>
+      </c>
       <c r="I23" s="41">
         <v>1.7150000000000001</v>
       </c>
@@ -4387,8 +4452,13 @@
       <c r="F25" s="41">
         <v>1.4430000000000001</v>
       </c>
-      <c r="G25" s="42"/>
-      <c r="H25" s="43"/>
+      <c r="G25" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.35332028469750898</v>
+      </c>
+      <c r="H25" s="43">
+        <v>-0.24485120214657585</v>
+      </c>
       <c r="I25" s="41">
         <v>1.72</v>
       </c>
@@ -4427,8 +4497,13 @@
       <c r="F26" s="41">
         <v>1.4550000000000001</v>
       </c>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+      <c r="G26" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.36078300678400299</v>
+      </c>
+      <c r="H26" s="43">
+        <v>-0.24796082940481304</v>
+      </c>
       <c r="I26" s="41"/>
       <c r="J26" s="44">
         <v>16.64</v>
@@ -4465,8 +4540,13 @@
       <c r="F27" s="41">
         <v>1.4530000000000001</v>
       </c>
-      <c r="G27" s="42"/>
-      <c r="H27" s="43"/>
+      <c r="G27" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.35913504212649827</v>
+      </c>
+      <c r="H27" s="43">
+        <v>-0.24716795741672282</v>
+      </c>
       <c r="I27" s="41"/>
       <c r="J27" s="44">
         <v>16.79</v>
@@ -4503,8 +4583,13 @@
       <c r="F28" s="41">
         <v>1.456</v>
       </c>
-      <c r="G28" s="42"/>
-      <c r="H28" s="43"/>
+      <c r="G28" s="42">
+        <f t="shared" si="0"/>
+        <v>-0.36043443206070647</v>
+      </c>
+      <c r="H28" s="43">
+        <v>-0.24755112092081488</v>
+      </c>
       <c r="I28" s="41"/>
       <c r="J28" s="44">
         <v>16.940000000000001</v>
@@ -4796,10 +4881,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:H64">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4904,7 +4989,7 @@
     </row>
     <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="47">
-        <v>46090.304971808917</v>
+        <v>46090</v>
       </c>
       <c r="B4" s="48">
         <v>1.901</v>
@@ -4928,14 +5013,154 @@
         <v>1.748</v>
       </c>
       <c r="I4" s="49">
-        <v>8.7499999999999994E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="47">
+        <v>46083</v>
+      </c>
+      <c r="B5" s="48">
+        <v>1.641</v>
+      </c>
+      <c r="C5" s="48">
+        <v>1.548</v>
+      </c>
+      <c r="D5" s="48">
+        <v>1.4279999999999999</v>
+      </c>
+      <c r="E5" s="48">
+        <v>1.794</v>
+      </c>
+      <c r="F5" s="48">
+        <v>1.579</v>
+      </c>
+      <c r="G5" s="48">
+        <v>1.9510000000000001</v>
+      </c>
+      <c r="H5" s="48">
+        <v>1.5720000000000001</v>
+      </c>
+      <c r="I5" s="49">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="47">
+        <v>46076</v>
+      </c>
+      <c r="B6" s="48">
+        <v>1.637</v>
+      </c>
+      <c r="C6" s="48">
+        <v>1.544</v>
+      </c>
+      <c r="D6" s="48">
+        <v>1.423</v>
+      </c>
+      <c r="E6" s="48">
+        <v>1.79</v>
+      </c>
+      <c r="F6" s="48">
+        <v>1.575</v>
+      </c>
+      <c r="G6" s="48">
+        <v>1.9450000000000001</v>
+      </c>
+      <c r="H6" s="48">
+        <v>1.5680000000000001</v>
+      </c>
+      <c r="I6" s="49">
+        <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="47">
+        <v>46069</v>
+      </c>
+      <c r="B7" s="48">
+        <v>1.6319999999999999</v>
+      </c>
+      <c r="C7" s="48">
+        <v>1.538</v>
+      </c>
+      <c r="D7" s="48">
+        <v>1.417</v>
+      </c>
+      <c r="E7" s="48">
+        <v>1.786</v>
+      </c>
+      <c r="F7" s="48">
+        <v>1.571</v>
+      </c>
+      <c r="G7" s="48">
+        <v>1.9390000000000001</v>
+      </c>
+      <c r="H7" s="48">
+        <v>1.5640000000000001</v>
+      </c>
+      <c r="I7" s="49">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="47">
+        <v>46062</v>
+      </c>
+      <c r="B8" s="48">
+        <v>1.625</v>
+      </c>
+      <c r="C8" s="48">
+        <v>1.532</v>
+      </c>
+      <c r="D8" s="48">
+        <v>1.41</v>
+      </c>
+      <c r="E8" s="48">
+        <v>1.78</v>
+      </c>
+      <c r="F8" s="48">
+        <v>1.5680000000000001</v>
+      </c>
+      <c r="G8" s="48">
+        <v>1.9319999999999999</v>
+      </c>
+      <c r="H8" s="48">
+        <v>1.5580000000000001</v>
+      </c>
+      <c r="I8" s="49">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="47">
+        <v>46055</v>
+      </c>
+      <c r="B9" s="48">
+        <v>1.6180000000000001</v>
+      </c>
+      <c r="C9" s="48">
+        <v>1.5249999999999999</v>
+      </c>
+      <c r="D9" s="48">
+        <v>1.4019999999999999</v>
+      </c>
+      <c r="E9" s="48">
+        <v>1.772</v>
+      </c>
+      <c r="F9" s="48">
+        <v>1.5620000000000001</v>
+      </c>
+      <c r="G9" s="48">
+        <v>1.925</v>
+      </c>
+      <c r="H9" s="48">
+        <v>1.5529999999999999</v>
+      </c>
+      <c r="I9" s="49">
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
     <row r="10" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5035,10 +5260,10 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I4:I33">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -28,6 +28,7 @@
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -1168,7 +1169,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1197,7 +1198,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1226,7 +1227,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1255,7 +1256,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1284,7 +1285,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1313,7 +1314,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1342,7 +1343,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                   <a:endParaRPr lang="lt-LT"/>
                 </a:p>
@@ -1371,7 +1372,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="lt-LT"/>
               </a:p>
@@ -1465,7 +1466,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="lt-LT"/>
           </a:p>
@@ -1545,7 +1546,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="lt-LT"/>
           </a:p>
@@ -3046,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="51" min="1" max="1"/>
@@ -3184,128 +3185,134 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46094.3788481689</v>
+        <v>46097.32398920194</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C5" s="102" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D5" s="103" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E5" s="104" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F5" s="105" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G5" s="106" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H5" s="107" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I5" s="105" t="n">
         <v>2.163</v>
       </c>
       <c r="J5" s="108" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="K5" s="103" t="n">
+        <v>10.7545</v>
+      </c>
+      <c r="L5" s="104" t="n">
+        <v>2.0308</v>
+      </c>
+      <c r="M5" s="109" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N5" s="110" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.75" customHeight="1" s="51">
+      <c r="A6" s="100" t="n">
+        <v>46094.3788481713</v>
+      </c>
+      <c r="B6" s="101" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C6" s="102" t="n">
+        <v>6399</v>
+      </c>
+      <c r="D6" s="103" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E6" s="104" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F6" s="105" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G6" s="106" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H6" s="107" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I6" s="105" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J6" s="108" t="n">
         <v>21.04</v>
       </c>
-      <c r="K5" s="103" t="n">
+      <c r="K6" s="103" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L5" s="104" t="n">
+      <c r="L6" s="104" t="n">
         <v>1.9644</v>
       </c>
-      <c r="M5" s="109" t="inlineStr">
+      <c r="M6" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N5" s="110" t="inlineStr">
+      <c r="N6" s="110" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" s="51">
-      <c r="A6" s="36" t="n">
-        <v>46093.30496681713</v>
-      </c>
-      <c r="B6" s="37" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C6" s="38" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D6" s="39" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <v>1.5029</v>
-      </c>
-      <c r="F6" s="41" t="n"/>
-      <c r="G6" s="111" t="n"/>
-      <c r="H6" s="112" t="n"/>
-      <c r="I6" s="41" t="n"/>
-      <c r="J6" s="44" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K6" s="39" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L6" s="40" t="n">
-        <v>1.9644</v>
-      </c>
-      <c r="M6" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N6" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21.75" customHeight="1" s="51">
       <c r="A7" s="36" t="n">
-        <v>46092.30496681713</v>
+        <v>46093.30496681713</v>
       </c>
       <c r="B7" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C7" s="38" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D7" s="39" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>1.5048</v>
+        <v>1.5029</v>
       </c>
       <c r="F7" s="41" t="n"/>
       <c r="G7" s="111" t="n"/>
       <c r="H7" s="112" t="n"/>
-      <c r="I7" s="41" t="n">
-        <v>2.137</v>
-      </c>
+      <c r="I7" s="41" t="n"/>
       <c r="J7" s="44" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K7" s="39" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M7" s="45" t="inlineStr">
         <is>
@@ -3320,89 +3327,91 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="51">
       <c r="A8" s="36" t="n">
+        <v>46092.30496681713</v>
+      </c>
+      <c r="B8" s="37" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C8" s="38" t="n">
+        <v>6195</v>
+      </c>
+      <c r="D8" s="39" t="n">
+        <v>4.2523</v>
+      </c>
+      <c r="E8" s="40" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="F8" s="41" t="n"/>
+      <c r="G8" s="111" t="n"/>
+      <c r="H8" s="112" t="n"/>
+      <c r="I8" s="41" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="J8" s="44" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="K8" s="39" t="n">
+        <v>10.6543</v>
+      </c>
+      <c r="L8" s="40" t="n">
+        <v>1.9748</v>
+      </c>
+      <c r="M8" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N8" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="51">
+      <c r="A9" s="36" t="n">
         <v>46091.30496681713</v>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C9" s="38" t="n">
         <v>6359</v>
       </c>
-      <c r="D8" s="39" t="n">
+      <c r="D9" s="39" t="n">
         <v>4.2548</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E9" s="40" t="n">
         <v>1.494547334774843</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F9" s="41" t="n">
         <v>1.808</v>
       </c>
-      <c r="G8" s="111">
+      <c r="G9" s="111">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H8" s="112" t="n">
+      <c r="H9" s="112" t="n">
         <v>-0.1733698369608172</v>
       </c>
-      <c r="I8" s="41" t="n">
+      <c r="I9" s="41" t="n">
         <v>2.198</v>
       </c>
-      <c r="J8" s="44" t="n">
+      <c r="J9" s="44" t="n">
         <v>21.59</v>
       </c>
-      <c r="K8" s="39" t="n">
+      <c r="K9" s="39" t="n">
         <v>10.606</v>
       </c>
-      <c r="L8" s="40" t="n">
+      <c r="L9" s="40" t="n">
         <v>1.9838</v>
       </c>
-      <c r="M8" s="45" t="inlineStr">
+      <c r="M9" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N8" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="51">
-      <c r="A9" s="36" t="n">
-        <v>46090.30496681713</v>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="n"/>
-      <c r="D9" s="39" t="n">
-        <v>4.2785</v>
-      </c>
-      <c r="E9" s="40" t="n"/>
-      <c r="F9" s="41" t="n">
-        <v>1.792</v>
-      </c>
-      <c r="G9" s="111" t="n"/>
-      <c r="H9" s="112" t="n"/>
-      <c r="I9" s="41" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="J9" s="44" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K9" s="39" t="n">
-        <v>10.6945</v>
-      </c>
-      <c r="L9" s="40" t="n">
-        <v>1.962691102903361</v>
-      </c>
-      <c r="M9" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,DE</t>
         </is>
       </c>
       <c r="N9" s="46" t="inlineStr">
@@ -3413,238 +3422,238 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" s="51">
       <c r="A10" s="36" t="n">
+        <v>46090.30496681713</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n">
+        <v>4.2785</v>
+      </c>
+      <c r="E10" s="40" t="n"/>
+      <c r="F10" s="41" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="G10" s="111" t="n"/>
+      <c r="H10" s="112" t="n"/>
+      <c r="I10" s="41" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K10" s="39" t="n">
+        <v>10.6945</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>1.962691102903361</v>
+      </c>
+      <c r="M10" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE</t>
+        </is>
+      </c>
+      <c r="N10" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1" s="51">
+      <c r="A11" s="36" t="n">
         <v>46087.30496681713</v>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n">
+      <c r="C11" s="38" t="n">
         <v>6150</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D11" s="39" t="n">
         <v>4.2875</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E11" s="40" t="n">
         <v>1.434402332361516</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F11" s="41" t="n">
         <v>1.845</v>
       </c>
-      <c r="G10" s="111">
+      <c r="G11" s="111">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H10" s="112" t="n">
+      <c r="H11" s="112" t="n">
         <v>-0.2225461613216715</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I11" s="41" t="n">
         <v>2.089</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J11" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K10" s="39" t="n">
+      <c r="K11" s="39" t="n">
         <v>10.693</v>
       </c>
-      <c r="L10" s="40" t="n">
+      <c r="L11" s="40" t="n">
         <v>1.864771345740204</v>
       </c>
-      <c r="M10" s="45" t="inlineStr">
+      <c r="M11" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,DE</t>
         </is>
       </c>
-      <c r="N10" s="46" t="inlineStr">
+      <c r="N11" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="21.75" customHeight="1" s="51">
-      <c r="A11" s="36" t="n">
+    <row r="12" ht="21.75" customHeight="1" s="51">
+      <c r="A12" s="36" t="n">
         <v>46086.30496681713</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C11" s="38" t="n">
+      <c r="C12" s="38" t="n">
         <v>5760</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D12" s="39" t="n">
         <v>4.2725</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E12" s="40" t="n">
         <v>1.34815681685196</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F12" s="41" t="n">
         <v>1.734</v>
       </c>
-      <c r="G11" s="111">
+      <c r="G12" s="111">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H11" s="112" t="n">
+      <c r="H12" s="112" t="n">
         <v>-0.2225162532572317</v>
       </c>
-      <c r="I11" s="41" t="n">
+      <c r="I12" s="41" t="n">
         <v>2.055</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J12" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K11" s="39" t="n">
+      <c r="K12" s="39" t="n">
         <v>10.6885</v>
       </c>
-      <c r="L11" s="40" t="n">
+      <c r="L12" s="40" t="n">
         <v>1.865556439163587</v>
       </c>
-      <c r="M11" s="45" t="inlineStr">
+      <c r="M12" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N11" s="46" t="inlineStr">
+      <c r="N12" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21.75" customHeight="1" s="51">
-      <c r="A12" s="36" t="n">
+    <row r="13" ht="21.75" customHeight="1" s="51">
+      <c r="A13" s="36" t="n">
         <v>46085.30496681713</v>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n">
+      <c r="C13" s="38" t="n">
         <v>5681</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D13" s="39" t="n">
         <v>4.2588</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E13" s="40" t="n">
         <v>1.333943833943834</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F13" s="41" t="n">
         <v>1.738</v>
       </c>
-      <c r="G12" s="111">
+      <c r="G13" s="111">
         <f>E12-F12</f>
         <v/>
       </c>
-      <c r="H12" s="112" t="n">
+      <c r="H13" s="112" t="n">
         <v>-0.2324834096985995</v>
       </c>
-      <c r="I12" s="41" t="n">
+      <c r="I13" s="41" t="n">
         <v>2.011</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J13" s="44" t="n">
         <v>18.64</v>
       </c>
-      <c r="K12" s="39" t="n">
+      <c r="K13" s="39" t="n">
         <v>10.6785</v>
       </c>
-      <c r="L12" s="40" t="n">
+      <c r="L13" s="40" t="n">
         <v>1.74556351547502</v>
       </c>
-      <c r="M12" s="45" t="inlineStr">
+      <c r="M13" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N12" s="46" t="inlineStr">
+      <c r="N13" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="51">
-      <c r="A13" s="36" t="n">
+    <row r="14" ht="21.75" customHeight="1" s="51">
+      <c r="A14" s="36" t="n">
         <v>46084.30496681713</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C14" s="38" t="n">
         <v>5237</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D14" s="39" t="n">
         <v>4.2865</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E14" s="40" t="n">
         <v>1.221742680508573</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F14" s="41" t="n">
         <v>1.619</v>
       </c>
-      <c r="G13" s="111">
+      <c r="G14" s="111">
         <f>E13-F13</f>
         <v/>
       </c>
-      <c r="H13" s="112" t="n">
+      <c r="H14" s="112" t="n">
         <v>-0.2453720318044636</v>
       </c>
-      <c r="I13" s="41" t="n">
+      <c r="I14" s="41" t="n">
         <v>1.916</v>
-      </c>
-      <c r="J13" s="44" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="K13" s="39" t="n">
-        <v>10.7265</v>
-      </c>
-      <c r="L13" s="40" t="n">
-        <v>1.61655712487764</v>
-      </c>
-      <c r="M13" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N13" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21.75" customHeight="1" s="51">
-      <c r="A14" s="36" t="n">
-        <v>46083.30496681713</v>
-      </c>
-      <c r="B14" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="39" t="n">
-        <v>4.244</v>
-      </c>
-      <c r="E14" s="40" t="n"/>
-      <c r="F14" s="41" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="G14" s="111" t="n"/>
-      <c r="H14" s="112" t="n"/>
-      <c r="I14" s="41" t="n">
-        <v>1.815</v>
       </c>
       <c r="J14" s="44" t="n">
         <v>17.34</v>
       </c>
       <c r="K14" s="39" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M14" s="45" t="inlineStr">
         <is>
@@ -3659,238 +3668,238 @@
     </row>
     <row r="15" ht="21.75" customHeight="1" s="51">
       <c r="A15" s="36" t="n">
-        <v>46080.30496681713</v>
+        <v>46083.30496681713</v>
       </c>
       <c r="B15" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="n">
-        <v>4777</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E15" s="40" t="n">
-        <v>1.130838245389769</v>
-      </c>
+        <v>4.244</v>
+      </c>
+      <c r="E15" s="40" t="n"/>
       <c r="F15" s="41" t="n">
         <v>1.506</v>
       </c>
-      <c r="G15" s="111">
+      <c r="G15" s="111" t="n"/>
+      <c r="H15" s="112" t="n"/>
+      <c r="I15" s="41" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="J15" s="44" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="K15" s="39" t="n">
+        <v>10.708</v>
+      </c>
+      <c r="L15" s="40" t="n">
+        <v>1.619350018677624</v>
+      </c>
+      <c r="M15" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N15" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="21.75" customHeight="1" s="51">
+      <c r="A16" s="36" t="n">
+        <v>46080.30496681713</v>
+      </c>
+      <c r="B16" s="37" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>4.2243</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <v>1.130838245389769</v>
+      </c>
+      <c r="F16" s="41" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="G16" s="111">
         <f>E15-F15</f>
         <v/>
       </c>
-      <c r="H15" s="112" t="n">
+      <c r="H16" s="112" t="n">
         <v>-0.2491113908434471</v>
       </c>
-      <c r="I15" s="41" t="n">
+      <c r="I16" s="41" t="n">
         <v>1.748</v>
       </c>
-      <c r="J15" s="44" t="n">
+      <c r="J16" s="44" t="n">
         <v>17.19</v>
       </c>
-      <c r="K15" s="39" t="n">
+      <c r="K16" s="39" t="n">
         <v>10.6643</v>
       </c>
-      <c r="L15" s="40" t="n">
+      <c r="L16" s="40" t="n">
         <v>1.611920144782124</v>
       </c>
-      <c r="M15" s="45" t="inlineStr">
+      <c r="M16" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N15" s="46" t="inlineStr">
+      <c r="N16" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21.75" customHeight="1" s="51">
-      <c r="A16" s="36" t="n">
+    <row r="17" ht="21.75" customHeight="1" s="51">
+      <c r="A17" s="36" t="n">
         <v>46079.30496681713</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C17" s="38" t="n">
         <v>4744</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D17" s="39" t="n">
         <v>4.2225</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E17" s="40" t="n">
         <v>1.123505032563647</v>
       </c>
-      <c r="F16" s="41" t="n">
+      <c r="F17" s="41" t="n">
         <v>1.492</v>
       </c>
-      <c r="G16" s="111">
+      <c r="G17" s="111">
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H16" s="112" t="n">
+      <c r="H17" s="112" t="n">
         <v>-0.2469805411771802</v>
       </c>
-      <c r="I16" s="41" t="n">
+      <c r="I17" s="41" t="n">
         <v>1.726</v>
       </c>
-      <c r="J16" s="44" t="n">
+      <c r="J17" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K16" s="39" t="n">
+      <c r="K17" s="39" t="n">
         <v>10.673</v>
       </c>
-      <c r="L16" s="40" t="n">
+      <c r="L17" s="40" t="n">
         <v>1.624660357912489</v>
       </c>
-      <c r="M16" s="45" t="inlineStr">
+      <c r="M17" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N16" s="46" t="inlineStr">
+      <c r="N17" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="21.75" customHeight="1" s="51">
-      <c r="A17" s="36" t="n">
+    <row r="18" ht="21.75" customHeight="1" s="51">
+      <c r="A18" s="36" t="n">
         <v>46078.30496681713</v>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n">
+      <c r="C18" s="38" t="n">
         <v>4765</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D18" s="39" t="n">
         <v>4.2233</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E18" s="40" t="n">
         <v>1.128264627187271</v>
       </c>
-      <c r="F17" s="41" t="n">
+      <c r="F18" s="41" t="n">
         <v>1.495</v>
       </c>
-      <c r="G17" s="111">
+      <c r="G18" s="111">
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H17" s="112" t="n">
+      <c r="H18" s="112" t="n">
         <v>-0.2453079416807554</v>
       </c>
-      <c r="I17" s="41" t="n">
+      <c r="I18" s="41" t="n">
         <v>1.74</v>
       </c>
-      <c r="J17" s="44" t="n">
+      <c r="J18" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K17" s="39" t="n">
+      <c r="K18" s="39" t="n">
         <v>10.6765</v>
       </c>
-      <c r="L17" s="40" t="n">
+      <c r="L18" s="40" t="n">
         <v>1.624127757223809</v>
       </c>
-      <c r="M17" s="45" t="inlineStr">
+      <c r="M18" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N17" s="46" t="inlineStr">
+      <c r="N18" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="51">
-      <c r="A18" s="36" t="n">
+    <row r="19" ht="21.75" customHeight="1" s="51">
+      <c r="A19" s="36" t="n">
         <v>46077.30496681713</v>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C19" s="38" t="n">
         <v>4769</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D19" s="39" t="n">
         <v>4.2203</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E19" s="40" t="n">
         <v>1.130014453948772</v>
       </c>
-      <c r="F18" s="41" t="n">
+      <c r="F19" s="41" t="n">
         <v>1.505</v>
       </c>
-      <c r="G18" s="111">
+      <c r="G19" s="111">
         <f>E18-F18</f>
         <v/>
       </c>
-      <c r="H18" s="112" t="n">
+      <c r="H19" s="112" t="n">
         <v>-0.2491598312632747</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I19" s="41" t="n">
         <v>1.745</v>
-      </c>
-      <c r="J18" s="44" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="K18" s="39" t="n">
-        <v>10.688</v>
-      </c>
-      <c r="L18" s="40" t="n">
-        <v>1.613023952095808</v>
-      </c>
-      <c r="M18" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N18" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="21.75" customHeight="1" s="51">
-      <c r="A19" s="36" t="n">
-        <v>46076.30496681713</v>
-      </c>
-      <c r="B19" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E19" s="40" t="n"/>
-      <c r="F19" s="41" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="G19" s="111" t="n"/>
-      <c r="H19" s="112" t="n"/>
-      <c r="I19" s="41" t="n">
-        <v>1.742</v>
       </c>
       <c r="J19" s="44" t="n">
         <v>17.24</v>
       </c>
       <c r="K19" s="39" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M19" s="45" t="inlineStr">
         <is>
@@ -3905,238 +3914,238 @@
     </row>
     <row r="20" ht="21.75" customHeight="1" s="51">
       <c r="A20" s="36" t="n">
+        <v>46076.30496681713</v>
+      </c>
+      <c r="B20" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E20" s="40" t="n"/>
+      <c r="F20" s="41" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G20" s="111" t="n"/>
+      <c r="H20" s="112" t="n"/>
+      <c r="I20" s="41" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="J20" s="44" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="K20" s="39" t="n">
+        <v>10.6955</v>
+      </c>
+      <c r="L20" s="40" t="n">
+        <v>1.611892852134075</v>
+      </c>
+      <c r="M20" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N20" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21.75" customHeight="1" s="51">
+      <c r="A21" s="36" t="n">
         <v>46073.30496681713</v>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n">
+      <c r="C21" s="38" t="n">
         <v>4743</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D21" s="39" t="n">
         <v>4.2238</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E21" s="40" t="n">
         <v>1.122922486860173</v>
       </c>
-      <c r="F20" s="41" t="n">
+      <c r="F21" s="41" t="n">
         <v>1.487</v>
       </c>
-      <c r="G20" s="111">
+      <c r="G21" s="111">
         <f>E20-F20</f>
         <v/>
       </c>
-      <c r="H20" s="112" t="n">
+      <c r="H21" s="112" t="n">
         <v>-0.2448402912843488</v>
       </c>
-      <c r="I20" s="41" t="n">
+      <c r="I21" s="41" t="n">
         <v>1.727</v>
       </c>
-      <c r="J20" s="44" t="n">
+      <c r="J21" s="44" t="n">
         <v>16.89</v>
       </c>
-      <c r="K20" s="39" t="n">
+      <c r="K21" s="39" t="n">
         <v>10.6745</v>
       </c>
-      <c r="L20" s="40" t="n">
+      <c r="L21" s="40" t="n">
         <v>1.582275516417631</v>
       </c>
-      <c r="M20" s="45" t="inlineStr">
+      <c r="M21" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N20" s="46" t="inlineStr">
+      <c r="N21" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="21.75" customHeight="1" s="51">
-      <c r="A21" s="36" t="n">
+    <row r="22" ht="21.75" customHeight="1" s="51">
+      <c r="A22" s="36" t="n">
         <v>46072.30496681713</v>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n">
+      <c r="C22" s="38" t="n">
         <v>4597</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D22" s="39" t="n">
         <v>4.2215</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E22" s="40" t="n">
         <v>1.088949425559635</v>
       </c>
-      <c r="F21" s="41" t="n">
+      <c r="F22" s="41" t="n">
         <v>1.46</v>
       </c>
-      <c r="G21" s="111">
+      <c r="G22" s="111">
         <f>E21-F21</f>
         <v/>
       </c>
-      <c r="H21" s="112" t="n">
+      <c r="H22" s="112" t="n">
         <v>-0.254144229068743</v>
       </c>
-      <c r="I21" s="41" t="n">
+      <c r="I22" s="41" t="n">
         <v>1.713</v>
       </c>
-      <c r="J21" s="44" t="n">
+      <c r="J22" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K21" s="39" t="n">
+      <c r="K22" s="39" t="n">
         <v>10.6915</v>
       </c>
-      <c r="L21" s="40" t="n">
+      <c r="L22" s="40" t="n">
         <v>1.556376560819343</v>
       </c>
-      <c r="M21" s="45" t="inlineStr">
+      <c r="M22" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N21" s="46" t="inlineStr">
+      <c r="N22" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="21.75" customHeight="1" s="51">
-      <c r="A22" s="36" t="n">
+    <row r="23" ht="21.75" customHeight="1" s="51">
+      <c r="A23" s="36" t="n">
         <v>46071.30496681713</v>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C23" s="38" t="n">
         <v>4569</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D23" s="39" t="n">
         <v>4.2165</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E23" s="40" t="n">
         <v>1.083600142298115</v>
       </c>
-      <c r="F22" s="41" t="n">
+      <c r="F23" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G22" s="111">
+      <c r="G23" s="111">
         <f>E22-F22</f>
         <v/>
       </c>
-      <c r="H22" s="112" t="n">
+      <c r="H23" s="112" t="n">
         <v>-0.249064350451757</v>
       </c>
-      <c r="I22" s="41" t="n">
+      <c r="I23" s="41" t="n">
         <v>1.697</v>
       </c>
-      <c r="J22" s="44" t="n">
+      <c r="J23" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K22" s="39" t="n">
+      <c r="K23" s="39" t="n">
         <v>10.616</v>
       </c>
-      <c r="L22" s="40" t="n">
+      <c r="L23" s="40" t="n">
         <v>1.567445365486059</v>
       </c>
-      <c r="M22" s="45" t="inlineStr">
+      <c r="M23" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N22" s="46" t="inlineStr">
+      <c r="N23" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="51">
-      <c r="A23" s="36" t="n">
+    <row r="24" ht="21.75" customHeight="1" s="51">
+      <c r="A24" s="36" t="n">
         <v>46070.30496681713</v>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n">
+      <c r="C24" s="38" t="n">
         <v>4577</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D24" s="39" t="n">
         <v>4.2138</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E24" s="40" t="n">
         <v>1.086192984954198</v>
       </c>
-      <c r="F23" s="41" t="n">
+      <c r="F24" s="41" t="n">
         <v>1.448</v>
       </c>
-      <c r="G23" s="111">
+      <c r="G24" s="111">
         <f>E23-F23</f>
         <v/>
       </c>
-      <c r="H23" s="112" t="n">
+      <c r="H24" s="112" t="n">
         <v>-0.2498667230979294</v>
       </c>
-      <c r="I23" s="41" t="n">
+      <c r="I24" s="41" t="n">
         <v>1.715</v>
-      </c>
-      <c r="J23" s="44" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="K23" s="39" t="n">
-        <v>10.648</v>
-      </c>
-      <c r="L23" s="40" t="n">
-        <v>1.562734785875282</v>
-      </c>
-      <c r="M23" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N23" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="21.75" customHeight="1" s="51">
-      <c r="A24" s="36" t="n">
-        <v>46069.30496681713</v>
-      </c>
-      <c r="B24" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C24" s="38" t="n"/>
-      <c r="D24" s="39" t="n">
-        <v>4.2105</v>
-      </c>
-      <c r="E24" s="40" t="n"/>
-      <c r="F24" s="41" t="n">
-        <v>1.448</v>
-      </c>
-      <c r="G24" s="111" t="n"/>
-      <c r="H24" s="112" t="n"/>
-      <c r="I24" s="41" t="n">
-        <v>1.724</v>
       </c>
       <c r="J24" s="44" t="n">
         <v>16.64</v>
       </c>
       <c r="K24" s="39" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L24" s="40" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M24" s="45" t="inlineStr">
         <is>
@@ -4151,230 +4160,232 @@
     </row>
     <row r="25" ht="21.75" customHeight="1" s="51">
       <c r="A25" s="36" t="n">
+        <v>46069.30496681713</v>
+      </c>
+      <c r="B25" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n">
+        <v>4.2105</v>
+      </c>
+      <c r="E25" s="40" t="n"/>
+      <c r="F25" s="41" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="G25" s="111" t="n"/>
+      <c r="H25" s="112" t="n"/>
+      <c r="I25" s="41" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="J25" s="44" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="K25" s="39" t="n">
+        <v>10.6205</v>
+      </c>
+      <c r="L25" s="40" t="n">
+        <v>1.566781224989407</v>
+      </c>
+      <c r="M25" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N25" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="21.75" customHeight="1" s="51">
+      <c r="A26" s="36" t="n">
         <v>46066.30496681713</v>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n">
+      <c r="C26" s="38" t="n">
         <v>4593</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D26" s="39" t="n">
         <v>4.215</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E26" s="40" t="n">
         <v>1.089679715302491</v>
       </c>
-      <c r="F25" s="41" t="n">
+      <c r="F26" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G25" s="111">
+      <c r="G26" s="111">
         <f>E25-F25</f>
         <v/>
       </c>
-      <c r="H25" s="112" t="n">
+      <c r="H26" s="112" t="n">
         <v>-0.2448512021465759</v>
       </c>
-      <c r="I25" s="41" t="n">
+      <c r="I26" s="41" t="n">
         <v>1.72</v>
       </c>
-      <c r="J25" s="44" t="n">
+      <c r="J26" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K25" s="39" t="n">
+      <c r="K26" s="39" t="n">
         <v>10.6254</v>
       </c>
-      <c r="L25" s="40" t="n">
+      <c r="L26" s="40" t="n">
         <v>1.566058689555217</v>
       </c>
-      <c r="M25" s="45" t="inlineStr">
+      <c r="M26" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N25" s="46" t="inlineStr">
+      <c r="N26" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="21.75" customHeight="1" s="51">
-      <c r="A26" s="36" t="n">
+    <row r="27" ht="21.75" customHeight="1" s="51">
+      <c r="A27" s="36" t="n">
         <v>46065.30496681713</v>
       </c>
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C26" s="38" t="n">
+      <c r="C27" s="38" t="n">
         <v>4613</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D27" s="39" t="n">
         <v>4.2158</v>
       </c>
-      <c r="E26" s="40" t="n">
+      <c r="E27" s="40" t="n">
         <v>1.094216993215997</v>
       </c>
-      <c r="F26" s="41" t="n">
+      <c r="F27" s="41" t="n">
         <v>1.455</v>
       </c>
-      <c r="G26" s="111">
+      <c r="G27" s="111">
         <f>E26-F26</f>
         <v/>
       </c>
-      <c r="H26" s="112" t="n">
+      <c r="H27" s="112" t="n">
         <v>-0.247960829404813</v>
       </c>
-      <c r="I26" s="41" t="n"/>
-      <c r="J26" s="44" t="n">
+      <c r="I27" s="41" t="n"/>
+      <c r="J27" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K26" s="39" t="n">
+      <c r="K27" s="39" t="n">
         <v>10.567</v>
       </c>
-      <c r="L26" s="40" t="n">
+      <c r="L27" s="40" t="n">
         <v>1.574713731428031</v>
       </c>
-      <c r="M26" s="45" t="inlineStr">
+      <c r="M27" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N26" s="46" t="inlineStr">
+      <c r="N27" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="21.75" customHeight="1" s="51">
-      <c r="A27" s="36" t="n">
+    <row r="28" ht="21.75" customHeight="1" s="51">
+      <c r="A28" s="36" t="n">
         <v>46064.30496681713</v>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n">
+      <c r="C28" s="38" t="n">
         <v>4609</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D28" s="39" t="n">
         <v>4.2135</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E28" s="40" t="n">
         <v>1.093864957873502</v>
       </c>
-      <c r="F27" s="41" t="n">
+      <c r="F28" s="41" t="n">
         <v>1.453</v>
       </c>
-      <c r="G27" s="111">
+      <c r="G28" s="111">
         <f>E27-F27</f>
         <v/>
       </c>
-      <c r="H27" s="112" t="n">
+      <c r="H28" s="112" t="n">
         <v>-0.2471679574167228</v>
       </c>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="44" t="n">
+      <c r="I28" s="41" t="n"/>
+      <c r="J28" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K27" s="39" t="n">
+      <c r="K28" s="39" t="n">
         <v>10.564</v>
       </c>
-      <c r="L27" s="40" t="n">
+      <c r="L28" s="40" t="n">
         <v>1.589360090874669</v>
       </c>
-      <c r="M27" s="45" t="inlineStr">
+      <c r="M28" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N27" s="46" t="inlineStr">
+      <c r="N28" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="21.75" customHeight="1" s="51">
-      <c r="A28" s="36" t="n">
+    <row r="29" ht="21.75" customHeight="1" s="51">
+      <c r="A29" s="36" t="n">
         <v>46063.30496681713</v>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C29" s="38" t="n">
         <v>4620</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D29" s="39" t="n">
         <v>4.217</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E29" s="40" t="n">
         <v>1.095565567939293</v>
       </c>
-      <c r="F28" s="41" t="n">
+      <c r="F29" s="41" t="n">
         <v>1.456</v>
       </c>
-      <c r="G28" s="111">
+      <c r="G29" s="111">
         <f>E28-F28</f>
         <v/>
       </c>
-      <c r="H28" s="112" t="n">
+      <c r="H29" s="112" t="n">
         <v>-0.2475511209208149</v>
       </c>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="44" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="K28" s="39" t="n">
-        <v>10.6135</v>
-      </c>
-      <c r="L28" s="40" t="n">
-        <v>1.59608046356056</v>
-      </c>
-      <c r="M28" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N28" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="21.75" customHeight="1" s="51">
-      <c r="A29" s="36" t="n">
-        <v>46062.30496681713</v>
-      </c>
-      <c r="B29" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C29" s="38" t="n"/>
-      <c r="D29" s="39" t="n">
-        <v>4.2118</v>
-      </c>
-      <c r="E29" s="40" t="n"/>
-      <c r="F29" s="41" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="G29" s="111" t="n"/>
-      <c r="H29" s="112" t="n"/>
       <c r="I29" s="41" t="n"/>
       <c r="J29" s="44" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K29" s="39" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L29" s="40" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M29" s="45" t="inlineStr">
         <is>
@@ -4389,34 +4400,32 @@
     </row>
     <row r="30" ht="21.75" customHeight="1" s="51">
       <c r="A30" s="36" t="n">
-        <v>46059.30496681713</v>
+        <v>46062.30496681713</v>
       </c>
       <c r="B30" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C30" s="38" t="n">
-        <v>4608</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C30" s="38" t="n"/>
       <c r="D30" s="39" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E30" s="40" t="n">
-        <v>1.092331397416143</v>
-      </c>
-      <c r="F30" s="41" t="n"/>
+        <v>4.2118</v>
+      </c>
+      <c r="E30" s="40" t="n"/>
+      <c r="F30" s="41" t="n">
+        <v>1.462</v>
+      </c>
       <c r="G30" s="111" t="n"/>
       <c r="H30" s="112" t="n"/>
       <c r="I30" s="41" t="n"/>
       <c r="J30" s="44" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K30" s="39" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L30" s="40" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M30" s="45" t="inlineStr">
         <is>
@@ -4431,21 +4440,21 @@
     </row>
     <row r="31" ht="21.75" customHeight="1" s="51">
       <c r="A31" s="36" t="n">
-        <v>46058.30496681713</v>
+        <v>46059.30496681713</v>
       </c>
       <c r="B31" s="37" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C31" s="38" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D31" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E31" s="40" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="F31" s="41" t="n"/>
       <c r="G31" s="111" t="n"/>
@@ -4455,10 +4464,10 @@
         <v>16.69</v>
       </c>
       <c r="K31" s="39" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M31" s="45" t="inlineStr">
         <is>
@@ -4473,21 +4482,21 @@
     </row>
     <row r="32" ht="21.75" customHeight="1" s="51">
       <c r="A32" s="36" t="n">
-        <v>46057.30496681713</v>
+        <v>46058.30496681713</v>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C32" s="38" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D32" s="39" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E32" s="40" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="F32" s="41" t="n"/>
       <c r="G32" s="111" t="n"/>
@@ -4497,10 +4506,10 @@
         <v>16.69</v>
       </c>
       <c r="K32" s="39" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M32" s="45" t="inlineStr">
         <is>
@@ -4515,34 +4524,34 @@
     </row>
     <row r="33" ht="21.75" customHeight="1" s="51">
       <c r="A33" s="36" t="n">
-        <v>46056.30496681713</v>
+        <v>46057.30496681713</v>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C33" s="38" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="F33" s="41" t="n"/>
       <c r="G33" s="111" t="n"/>
       <c r="H33" s="112" t="n"/>
       <c r="I33" s="41" t="n"/>
       <c r="J33" s="44" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M33" s="45" t="inlineStr">
         <is>
@@ -4557,43 +4566,84 @@
     </row>
     <row r="34" ht="21.75" customHeight="1" s="51">
       <c r="A34" s="36" t="n">
-        <v>46055.30496681713</v>
+        <v>46056.30496681713</v>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C34" s="38" t="n"/>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C34" s="38" t="n">
+        <v>4622</v>
+      </c>
       <c r="D34" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E34" s="40" t="n"/>
+        <v>4.2205</v>
+      </c>
+      <c r="E34" s="40" t="n">
+        <v>1.095130908660111</v>
+      </c>
       <c r="F34" s="41" t="n"/>
       <c r="G34" s="111" t="n"/>
       <c r="H34" s="112" t="n"/>
       <c r="I34" s="41" t="n"/>
       <c r="J34" s="44" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K34" s="39" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L34" s="40" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M34" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N34" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="21.75" customHeight="1" s="51">
+      <c r="A35" s="36" t="n">
+        <v>46055.30496681713</v>
+      </c>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E35" s="40" t="n"/>
+      <c r="F35" s="41" t="n"/>
+      <c r="G35" s="111" t="n"/>
+      <c r="H35" s="112" t="n"/>
+      <c r="I35" s="41" t="n"/>
+      <c r="J35" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K34" s="39" t="n">
+      <c r="K35" s="39" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L34" s="40" t="n">
+      <c r="L35" s="40" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M34" s="45" t="inlineStr">
+      <c r="M35" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N34" s="46" t="inlineStr">
+      <c r="N35" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="21.75" customHeight="1" s="51"/>
     <row r="36" ht="21.75" customHeight="1" s="51"/>
     <row r="37" ht="21.75" customHeight="1" s="51"/>
     <row r="38" ht="21.75" customHeight="1" s="51"/>
@@ -4694,7 +4744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="14" customWidth="1" style="51" min="1" max="1"/>
@@ -4773,7 +4823,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46090.3788481689</v>
+        <v>46097.32398920194</v>
       </c>
       <c r="B4" s="114" t="n">
         <v>1.901</v>
@@ -4801,58 +4851,58 @@
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
-      <c r="A5" s="47" t="n">
-        <v>46083</v>
-      </c>
-      <c r="B5" s="48" t="n">
-        <v>1.641</v>
-      </c>
-      <c r="C5" s="48" t="n">
-        <v>1.548</v>
-      </c>
-      <c r="D5" s="48" t="n">
-        <v>1.428</v>
-      </c>
-      <c r="E5" s="48" t="n">
-        <v>1.794</v>
-      </c>
-      <c r="F5" s="48" t="n">
-        <v>1.579</v>
-      </c>
-      <c r="G5" s="48" t="n">
-        <v>1.951</v>
-      </c>
-      <c r="H5" s="48" t="n">
-        <v>1.572</v>
-      </c>
-      <c r="I5" s="116" t="n">
-        <v>0.044</v>
+      <c r="A5" s="113" t="n">
+        <v>46090.3788481713</v>
+      </c>
+      <c r="B5" s="114" t="n">
+        <v>1.901</v>
+      </c>
+      <c r="C5" s="114" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="D5" s="114" t="n">
+        <v>1.688</v>
+      </c>
+      <c r="E5" s="114" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="F5" s="114" t="n">
+        <v>1.783</v>
+      </c>
+      <c r="G5" s="114" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="H5" s="114" t="n">
+        <v>1.748</v>
+      </c>
+      <c r="I5" s="115" t="n">
+        <v>0.08749999999999999</v>
       </c>
     </row>
     <row r="6" ht="21.75" customHeight="1" s="51">
       <c r="A6" s="47" t="n">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="B6" s="48" t="n">
-        <v>1.637</v>
+        <v>1.641</v>
       </c>
       <c r="C6" s="48" t="n">
-        <v>1.544</v>
+        <v>1.548</v>
       </c>
       <c r="D6" s="48" t="n">
-        <v>1.423</v>
+        <v>1.428</v>
       </c>
       <c r="E6" s="48" t="n">
-        <v>1.79</v>
+        <v>1.794</v>
       </c>
       <c r="F6" s="48" t="n">
-        <v>1.575</v>
+        <v>1.579</v>
       </c>
       <c r="G6" s="48" t="n">
-        <v>1.945</v>
+        <v>1.951</v>
       </c>
       <c r="H6" s="48" t="n">
-        <v>1.568</v>
+        <v>1.572</v>
       </c>
       <c r="I6" s="116" t="n">
         <v>0.044</v>
@@ -4860,57 +4910,57 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="51">
       <c r="A7" s="47" t="n">
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="B7" s="48" t="n">
-        <v>1.632</v>
+        <v>1.637</v>
       </c>
       <c r="C7" s="48" t="n">
-        <v>1.538</v>
+        <v>1.544</v>
       </c>
       <c r="D7" s="48" t="n">
-        <v>1.417</v>
+        <v>1.423</v>
       </c>
       <c r="E7" s="48" t="n">
-        <v>1.786</v>
+        <v>1.79</v>
       </c>
       <c r="F7" s="48" t="n">
-        <v>1.571</v>
+        <v>1.575</v>
       </c>
       <c r="G7" s="48" t="n">
-        <v>1.939</v>
+        <v>1.945</v>
       </c>
       <c r="H7" s="48" t="n">
-        <v>1.564</v>
+        <v>1.568</v>
       </c>
       <c r="I7" s="116" t="n">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="51">
       <c r="A8" s="47" t="n">
-        <v>46062</v>
+        <v>46069</v>
       </c>
       <c r="B8" s="48" t="n">
-        <v>1.625</v>
+        <v>1.632</v>
       </c>
       <c r="C8" s="48" t="n">
-        <v>1.532</v>
+        <v>1.538</v>
       </c>
       <c r="D8" s="48" t="n">
-        <v>1.41</v>
+        <v>1.417</v>
       </c>
       <c r="E8" s="48" t="n">
-        <v>1.78</v>
+        <v>1.786</v>
       </c>
       <c r="F8" s="48" t="n">
-        <v>1.568</v>
+        <v>1.571</v>
       </c>
       <c r="G8" s="48" t="n">
-        <v>1.932</v>
+        <v>1.939</v>
       </c>
       <c r="H8" s="48" t="n">
-        <v>1.558</v>
+        <v>1.564</v>
       </c>
       <c r="I8" s="116" t="n">
         <v>0.043</v>
@@ -4918,34 +4968,62 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="51">
       <c r="A9" s="47" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B9" s="48" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="C9" s="48" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="D9" s="48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E9" s="48" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F9" s="48" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="G9" s="48" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="H9" s="48" t="n">
+        <v>1.558</v>
+      </c>
+      <c r="I9" s="116" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="51">
+      <c r="A10" s="47" t="n">
         <v>46055</v>
       </c>
-      <c r="B9" s="48" t="n">
+      <c r="B10" s="48" t="n">
         <v>1.618</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C10" s="48" t="n">
         <v>1.525</v>
       </c>
-      <c r="D9" s="48" t="n">
+      <c r="D10" s="48" t="n">
         <v>1.402</v>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E10" s="48" t="n">
         <v>1.772</v>
       </c>
-      <c r="F9" s="48" t="n">
+      <c r="F10" s="48" t="n">
         <v>1.562</v>
       </c>
-      <c r="G9" s="48" t="n">
+      <c r="G10" s="48" t="n">
         <v>1.925</v>
       </c>
-      <c r="H9" s="48" t="n">
+      <c r="H10" s="48" t="n">
         <v>1.553</v>
       </c>
-      <c r="I9" s="116" t="n">
+      <c r="I10" s="116" t="n">
         <v>0.042</v>
       </c>
     </row>
-    <row r="10" ht="21.75" customHeight="1" s="51"/>
     <row r="11" ht="21.75" customHeight="1" s="51"/>
     <row r="12" ht="21.75" customHeight="1" s="51"/>
     <row r="13" ht="21.75" customHeight="1" s="51"/>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -28,7 +28,6 @@
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -3185,7 +3184,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46097.32398920194</v>
+        <v>46097.40237722721</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
@@ -3224,7 +3223,7 @@
       </c>
       <c r="M5" s="109" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT</t>
         </is>
       </c>
       <c r="N5" s="110" t="inlineStr">
@@ -4823,7 +4822,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46097.32398920194</v>
+        <v>46097.32398920139</v>
       </c>
       <c r="B4" s="114" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -28,6 +28,7 @@
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -3046,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="51" min="1" max="1"/>
@@ -3184,43 +3185,37 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46097.40237722721</v>
+        <v>46098.39469012326</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C5" s="102" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D5" s="103" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E5" s="104" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F5" s="105" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G5" s="106" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H5" s="107" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I5" s="105" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J5" s="108" t="n">
-        <v>21.84</v>
-      </c>
+        <v>-0.1614</v>
+      </c>
+      <c r="I5" s="105" t="n"/>
+      <c r="J5" s="108" t="n"/>
       <c r="K5" s="103" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L5" s="104" t="n">
-        <v>2.0308</v>
-      </c>
+        <v>10.769</v>
+      </c>
+      <c r="L5" s="104" t="n"/>
       <c r="M5" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT</t>
@@ -3234,128 +3229,134 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="51">
       <c r="A6" s="100" t="n">
-        <v>46094.3788481713</v>
+        <v>46097.40237722222</v>
       </c>
       <c r="B6" s="101" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C6" s="102" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E6" s="104" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F6" s="105" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G6" s="106" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H6" s="107" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I6" s="105" t="n">
         <v>2.163</v>
       </c>
       <c r="J6" s="108" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="K6" s="103" t="n">
+        <v>10.7545</v>
+      </c>
+      <c r="L6" s="104" t="n">
+        <v>2.0308</v>
+      </c>
+      <c r="M6" s="109" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT</t>
+        </is>
+      </c>
+      <c r="N6" s="110" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="21.75" customHeight="1" s="51">
+      <c r="A7" s="100" t="n">
+        <v>46094.3788481713</v>
+      </c>
+      <c r="B7" s="101" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C7" s="102" t="n">
+        <v>6399</v>
+      </c>
+      <c r="D7" s="103" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E7" s="104" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F7" s="105" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G7" s="106" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H7" s="107" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I7" s="105" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J7" s="108" t="n">
         <v>21.04</v>
       </c>
-      <c r="K6" s="103" t="n">
+      <c r="K7" s="103" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L6" s="104" t="n">
+      <c r="L7" s="104" t="n">
         <v>1.9644</v>
       </c>
-      <c r="M6" s="109" t="inlineStr">
+      <c r="M7" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N6" s="110" t="inlineStr">
+      <c r="N7" s="110" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="21.75" customHeight="1" s="51">
-      <c r="A7" s="36" t="n">
-        <v>46093.30496681713</v>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C7" s="38" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D7" s="39" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E7" s="40" t="n">
-        <v>1.5029</v>
-      </c>
-      <c r="F7" s="41" t="n"/>
-      <c r="G7" s="111" t="n"/>
-      <c r="H7" s="112" t="n"/>
-      <c r="I7" s="41" t="n"/>
-      <c r="J7" s="44" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K7" s="39" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L7" s="40" t="n">
-        <v>1.9644</v>
-      </c>
-      <c r="M7" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N7" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="8" ht="21.75" customHeight="1" s="51">
       <c r="A8" s="36" t="n">
-        <v>46092.30496681713</v>
+        <v>46093.30496681713</v>
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C8" s="38" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D8" s="39" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>1.5048</v>
+        <v>1.5029</v>
       </c>
       <c r="F8" s="41" t="n"/>
       <c r="G8" s="111" t="n"/>
       <c r="H8" s="112" t="n"/>
-      <c r="I8" s="41" t="n">
-        <v>2.137</v>
-      </c>
+      <c r="I8" s="41" t="n"/>
       <c r="J8" s="44" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K8" s="39" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M8" s="45" t="inlineStr">
         <is>
@@ -3370,89 +3371,91 @@
     </row>
     <row r="9" ht="21.75" customHeight="1" s="51">
       <c r="A9" s="36" t="n">
+        <v>46092.30496681713</v>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C9" s="38" t="n">
+        <v>6195</v>
+      </c>
+      <c r="D9" s="39" t="n">
+        <v>4.2523</v>
+      </c>
+      <c r="E9" s="40" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="111" t="n"/>
+      <c r="H9" s="112" t="n"/>
+      <c r="I9" s="41" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="J9" s="44" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="K9" s="39" t="n">
+        <v>10.6543</v>
+      </c>
+      <c r="L9" s="40" t="n">
+        <v>1.9748</v>
+      </c>
+      <c r="M9" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N9" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="21.75" customHeight="1" s="51">
+      <c r="A10" s="36" t="n">
         <v>46091.30496681713</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B10" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C9" s="38" t="n">
+      <c r="C10" s="38" t="n">
         <v>6359</v>
       </c>
-      <c r="D9" s="39" t="n">
+      <c r="D10" s="39" t="n">
         <v>4.2548</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E10" s="40" t="n">
         <v>1.494547334774843</v>
       </c>
-      <c r="F9" s="41" t="n">
+      <c r="F10" s="41" t="n">
         <v>1.808</v>
       </c>
-      <c r="G9" s="111">
+      <c r="G10" s="111">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H9" s="112" t="n">
+      <c r="H10" s="112" t="n">
         <v>-0.1733698369608172</v>
       </c>
-      <c r="I9" s="41" t="n">
+      <c r="I10" s="41" t="n">
         <v>2.198</v>
       </c>
-      <c r="J9" s="44" t="n">
+      <c r="J10" s="44" t="n">
         <v>21.59</v>
       </c>
-      <c r="K9" s="39" t="n">
+      <c r="K10" s="39" t="n">
         <v>10.606</v>
       </c>
-      <c r="L9" s="40" t="n">
+      <c r="L10" s="40" t="n">
         <v>1.9838</v>
       </c>
-      <c r="M9" s="45" t="inlineStr">
+      <c r="M10" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N9" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="21.75" customHeight="1" s="51">
-      <c r="A10" s="36" t="n">
-        <v>46090.30496681713</v>
-      </c>
-      <c r="B10" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C10" s="38" t="n"/>
-      <c r="D10" s="39" t="n">
-        <v>4.2785</v>
-      </c>
-      <c r="E10" s="40" t="n"/>
-      <c r="F10" s="41" t="n">
-        <v>1.792</v>
-      </c>
-      <c r="G10" s="111" t="n"/>
-      <c r="H10" s="112" t="n"/>
-      <c r="I10" s="41" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="J10" s="44" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K10" s="39" t="n">
-        <v>10.6945</v>
-      </c>
-      <c r="L10" s="40" t="n">
-        <v>1.962691102903361</v>
-      </c>
-      <c r="M10" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,DE</t>
         </is>
       </c>
       <c r="N10" s="46" t="inlineStr">
@@ -3463,238 +3466,238 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" s="51">
       <c r="A11" s="36" t="n">
+        <v>46090.30496681713</v>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="n">
+        <v>4.2785</v>
+      </c>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="41" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="G11" s="111" t="n"/>
+      <c r="H11" s="112" t="n"/>
+      <c r="I11" s="41" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K11" s="39" t="n">
+        <v>10.6945</v>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>1.962691102903361</v>
+      </c>
+      <c r="M11" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE</t>
+        </is>
+      </c>
+      <c r="N11" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.75" customHeight="1" s="51">
+      <c r="A12" s="36" t="n">
         <v>46087.30496681713</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C11" s="38" t="n">
+      <c r="C12" s="38" t="n">
         <v>6150</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D12" s="39" t="n">
         <v>4.2875</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E12" s="40" t="n">
         <v>1.434402332361516</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F12" s="41" t="n">
         <v>1.845</v>
       </c>
-      <c r="G11" s="111">
+      <c r="G12" s="111">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H11" s="112" t="n">
+      <c r="H12" s="112" t="n">
         <v>-0.2225461613216715</v>
       </c>
-      <c r="I11" s="41" t="n">
+      <c r="I12" s="41" t="n">
         <v>2.089</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J12" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K11" s="39" t="n">
+      <c r="K12" s="39" t="n">
         <v>10.693</v>
       </c>
-      <c r="L11" s="40" t="n">
+      <c r="L12" s="40" t="n">
         <v>1.864771345740204</v>
       </c>
-      <c r="M11" s="45" t="inlineStr">
+      <c r="M12" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,DE</t>
         </is>
       </c>
-      <c r="N11" s="46" t="inlineStr">
+      <c r="N12" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="21.75" customHeight="1" s="51">
-      <c r="A12" s="36" t="n">
+    <row r="13" ht="21.75" customHeight="1" s="51">
+      <c r="A13" s="36" t="n">
         <v>46086.30496681713</v>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n">
+      <c r="C13" s="38" t="n">
         <v>5760</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D13" s="39" t="n">
         <v>4.2725</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E13" s="40" t="n">
         <v>1.34815681685196</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F13" s="41" t="n">
         <v>1.734</v>
       </c>
-      <c r="G12" s="111">
+      <c r="G13" s="111">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H12" s="112" t="n">
+      <c r="H13" s="112" t="n">
         <v>-0.2225162532572317</v>
       </c>
-      <c r="I12" s="41" t="n">
+      <c r="I13" s="41" t="n">
         <v>2.055</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J13" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K12" s="39" t="n">
+      <c r="K13" s="39" t="n">
         <v>10.6885</v>
       </c>
-      <c r="L12" s="40" t="n">
+      <c r="L13" s="40" t="n">
         <v>1.865556439163587</v>
       </c>
-      <c r="M12" s="45" t="inlineStr">
+      <c r="M13" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N12" s="46" t="inlineStr">
+      <c r="N13" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="51">
-      <c r="A13" s="36" t="n">
+    <row r="14" ht="21.75" customHeight="1" s="51">
+      <c r="A14" s="36" t="n">
         <v>46085.30496681713</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C14" s="38" t="n">
         <v>5681</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D14" s="39" t="n">
         <v>4.2588</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E14" s="40" t="n">
         <v>1.333943833943834</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F14" s="41" t="n">
         <v>1.738</v>
       </c>
-      <c r="G13" s="111">
+      <c r="G14" s="111">
         <f>E12-F12</f>
         <v/>
       </c>
-      <c r="H13" s="112" t="n">
+      <c r="H14" s="112" t="n">
         <v>-0.2324834096985995</v>
       </c>
-      <c r="I13" s="41" t="n">
+      <c r="I14" s="41" t="n">
         <v>2.011</v>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J14" s="44" t="n">
         <v>18.64</v>
       </c>
-      <c r="K13" s="39" t="n">
+      <c r="K14" s="39" t="n">
         <v>10.6785</v>
       </c>
-      <c r="L13" s="40" t="n">
+      <c r="L14" s="40" t="n">
         <v>1.74556351547502</v>
       </c>
-      <c r="M13" s="45" t="inlineStr">
+      <c r="M14" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N13" s="46" t="inlineStr">
+      <c r="N14" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21.75" customHeight="1" s="51">
-      <c r="A14" s="36" t="n">
+    <row r="15" ht="21.75" customHeight="1" s="51">
+      <c r="A15" s="36" t="n">
         <v>46084.30496681713</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C14" s="38" t="n">
+      <c r="C15" s="38" t="n">
         <v>5237</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D15" s="39" t="n">
         <v>4.2865</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E15" s="40" t="n">
         <v>1.221742680508573</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F15" s="41" t="n">
         <v>1.619</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G15" s="111">
         <f>E13-F13</f>
         <v/>
       </c>
-      <c r="H14" s="112" t="n">
+      <c r="H15" s="112" t="n">
         <v>-0.2453720318044636</v>
       </c>
-      <c r="I14" s="41" t="n">
+      <c r="I15" s="41" t="n">
         <v>1.916</v>
-      </c>
-      <c r="J14" s="44" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="K14" s="39" t="n">
-        <v>10.7265</v>
-      </c>
-      <c r="L14" s="40" t="n">
-        <v>1.61655712487764</v>
-      </c>
-      <c r="M14" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N14" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="21.75" customHeight="1" s="51">
-      <c r="A15" s="36" t="n">
-        <v>46083.30496681713</v>
-      </c>
-      <c r="B15" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C15" s="38" t="n"/>
-      <c r="D15" s="39" t="n">
-        <v>4.244</v>
-      </c>
-      <c r="E15" s="40" t="n"/>
-      <c r="F15" s="41" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="G15" s="111" t="n"/>
-      <c r="H15" s="112" t="n"/>
-      <c r="I15" s="41" t="n">
-        <v>1.815</v>
       </c>
       <c r="J15" s="44" t="n">
         <v>17.34</v>
       </c>
       <c r="K15" s="39" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M15" s="45" t="inlineStr">
         <is>
@@ -3709,238 +3712,238 @@
     </row>
     <row r="16" ht="21.75" customHeight="1" s="51">
       <c r="A16" s="36" t="n">
-        <v>46080.30496681713</v>
+        <v>46083.30496681713</v>
       </c>
       <c r="B16" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="n">
-        <v>4777</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E16" s="40" t="n">
-        <v>1.130838245389769</v>
-      </c>
+        <v>4.244</v>
+      </c>
+      <c r="E16" s="40" t="n"/>
       <c r="F16" s="41" t="n">
         <v>1.506</v>
       </c>
-      <c r="G16" s="111">
+      <c r="G16" s="111" t="n"/>
+      <c r="H16" s="112" t="n"/>
+      <c r="I16" s="41" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="J16" s="44" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="K16" s="39" t="n">
+        <v>10.708</v>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>1.619350018677624</v>
+      </c>
+      <c r="M16" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N16" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="21.75" customHeight="1" s="51">
+      <c r="A17" s="36" t="n">
+        <v>46080.30496681713</v>
+      </c>
+      <c r="B17" s="37" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D17" s="39" t="n">
+        <v>4.2243</v>
+      </c>
+      <c r="E17" s="40" t="n">
+        <v>1.130838245389769</v>
+      </c>
+      <c r="F17" s="41" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="G17" s="111">
         <f>E15-F15</f>
         <v/>
       </c>
-      <c r="H16" s="112" t="n">
+      <c r="H17" s="112" t="n">
         <v>-0.2491113908434471</v>
       </c>
-      <c r="I16" s="41" t="n">
+      <c r="I17" s="41" t="n">
         <v>1.748</v>
       </c>
-      <c r="J16" s="44" t="n">
+      <c r="J17" s="44" t="n">
         <v>17.19</v>
       </c>
-      <c r="K16" s="39" t="n">
+      <c r="K17" s="39" t="n">
         <v>10.6643</v>
       </c>
-      <c r="L16" s="40" t="n">
+      <c r="L17" s="40" t="n">
         <v>1.611920144782124</v>
       </c>
-      <c r="M16" s="45" t="inlineStr">
+      <c r="M17" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N16" s="46" t="inlineStr">
+      <c r="N17" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="21.75" customHeight="1" s="51">
-      <c r="A17" s="36" t="n">
+    <row r="18" ht="21.75" customHeight="1" s="51">
+      <c r="A18" s="36" t="n">
         <v>46079.30496681713</v>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B18" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C17" s="38" t="n">
+      <c r="C18" s="38" t="n">
         <v>4744</v>
       </c>
-      <c r="D17" s="39" t="n">
+      <c r="D18" s="39" t="n">
         <v>4.2225</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E18" s="40" t="n">
         <v>1.123505032563647</v>
       </c>
-      <c r="F17" s="41" t="n">
+      <c r="F18" s="41" t="n">
         <v>1.492</v>
       </c>
-      <c r="G17" s="111">
+      <c r="G18" s="111">
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H17" s="112" t="n">
+      <c r="H18" s="112" t="n">
         <v>-0.2469805411771802</v>
       </c>
-      <c r="I17" s="41" t="n">
+      <c r="I18" s="41" t="n">
         <v>1.726</v>
       </c>
-      <c r="J17" s="44" t="n">
+      <c r="J18" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K17" s="39" t="n">
+      <c r="K18" s="39" t="n">
         <v>10.673</v>
       </c>
-      <c r="L17" s="40" t="n">
+      <c r="L18" s="40" t="n">
         <v>1.624660357912489</v>
       </c>
-      <c r="M17" s="45" t="inlineStr">
+      <c r="M18" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N17" s="46" t="inlineStr">
+      <c r="N18" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="51">
-      <c r="A18" s="36" t="n">
+    <row r="19" ht="21.75" customHeight="1" s="51">
+      <c r="A19" s="36" t="n">
         <v>46078.30496681713</v>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C19" s="38" t="n">
         <v>4765</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D19" s="39" t="n">
         <v>4.2233</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E19" s="40" t="n">
         <v>1.128264627187271</v>
       </c>
-      <c r="F18" s="41" t="n">
+      <c r="F19" s="41" t="n">
         <v>1.495</v>
       </c>
-      <c r="G18" s="111">
+      <c r="G19" s="111">
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H18" s="112" t="n">
+      <c r="H19" s="112" t="n">
         <v>-0.2453079416807554</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I19" s="41" t="n">
         <v>1.74</v>
       </c>
-      <c r="J18" s="44" t="n">
+      <c r="J19" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K18" s="39" t="n">
+      <c r="K19" s="39" t="n">
         <v>10.6765</v>
       </c>
-      <c r="L18" s="40" t="n">
+      <c r="L19" s="40" t="n">
         <v>1.624127757223809</v>
       </c>
-      <c r="M18" s="45" t="inlineStr">
+      <c r="M19" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N18" s="46" t="inlineStr">
+      <c r="N19" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="21.75" customHeight="1" s="51">
-      <c r="A19" s="36" t="n">
+    <row r="20" ht="21.75" customHeight="1" s="51">
+      <c r="A20" s="36" t="n">
         <v>46077.30496681713</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C20" s="38" t="n">
         <v>4769</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D20" s="39" t="n">
         <v>4.2203</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E20" s="40" t="n">
         <v>1.130014453948772</v>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F20" s="41" t="n">
         <v>1.505</v>
       </c>
-      <c r="G19" s="111">
+      <c r="G20" s="111">
         <f>E18-F18</f>
         <v/>
       </c>
-      <c r="H19" s="112" t="n">
+      <c r="H20" s="112" t="n">
         <v>-0.2491598312632747</v>
       </c>
-      <c r="I19" s="41" t="n">
+      <c r="I20" s="41" t="n">
         <v>1.745</v>
-      </c>
-      <c r="J19" s="44" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="K19" s="39" t="n">
-        <v>10.688</v>
-      </c>
-      <c r="L19" s="40" t="n">
-        <v>1.613023952095808</v>
-      </c>
-      <c r="M19" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N19" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="21.75" customHeight="1" s="51">
-      <c r="A20" s="36" t="n">
-        <v>46076.30496681713</v>
-      </c>
-      <c r="B20" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C20" s="38" t="n"/>
-      <c r="D20" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E20" s="40" t="n"/>
-      <c r="F20" s="41" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="G20" s="111" t="n"/>
-      <c r="H20" s="112" t="n"/>
-      <c r="I20" s="41" t="n">
-        <v>1.742</v>
       </c>
       <c r="J20" s="44" t="n">
         <v>17.24</v>
       </c>
       <c r="K20" s="39" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M20" s="45" t="inlineStr">
         <is>
@@ -3955,238 +3958,238 @@
     </row>
     <row r="21" ht="21.75" customHeight="1" s="51">
       <c r="A21" s="36" t="n">
+        <v>46076.30496681713</v>
+      </c>
+      <c r="B21" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E21" s="40" t="n"/>
+      <c r="F21" s="41" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G21" s="111" t="n"/>
+      <c r="H21" s="112" t="n"/>
+      <c r="I21" s="41" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="J21" s="44" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="K21" s="39" t="n">
+        <v>10.6955</v>
+      </c>
+      <c r="L21" s="40" t="n">
+        <v>1.611892852134075</v>
+      </c>
+      <c r="M21" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N21" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="21.75" customHeight="1" s="51">
+      <c r="A22" s="36" t="n">
         <v>46073.30496681713</v>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n">
+      <c r="C22" s="38" t="n">
         <v>4743</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D22" s="39" t="n">
         <v>4.2238</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E22" s="40" t="n">
         <v>1.122922486860173</v>
       </c>
-      <c r="F21" s="41" t="n">
+      <c r="F22" s="41" t="n">
         <v>1.487</v>
       </c>
-      <c r="G21" s="111">
+      <c r="G22" s="111">
         <f>E20-F20</f>
         <v/>
       </c>
-      <c r="H21" s="112" t="n">
+      <c r="H22" s="112" t="n">
         <v>-0.2448402912843488</v>
       </c>
-      <c r="I21" s="41" t="n">
+      <c r="I22" s="41" t="n">
         <v>1.727</v>
       </c>
-      <c r="J21" s="44" t="n">
+      <c r="J22" s="44" t="n">
         <v>16.89</v>
       </c>
-      <c r="K21" s="39" t="n">
+      <c r="K22" s="39" t="n">
         <v>10.6745</v>
       </c>
-      <c r="L21" s="40" t="n">
+      <c r="L22" s="40" t="n">
         <v>1.582275516417631</v>
       </c>
-      <c r="M21" s="45" t="inlineStr">
+      <c r="M22" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N21" s="46" t="inlineStr">
+      <c r="N22" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="21.75" customHeight="1" s="51">
-      <c r="A22" s="36" t="n">
+    <row r="23" ht="21.75" customHeight="1" s="51">
+      <c r="A23" s="36" t="n">
         <v>46072.30496681713</v>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C23" s="38" t="n">
         <v>4597</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D23" s="39" t="n">
         <v>4.2215</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E23" s="40" t="n">
         <v>1.088949425559635</v>
       </c>
-      <c r="F22" s="41" t="n">
+      <c r="F23" s="41" t="n">
         <v>1.46</v>
       </c>
-      <c r="G22" s="111">
+      <c r="G23" s="111">
         <f>E21-F21</f>
         <v/>
       </c>
-      <c r="H22" s="112" t="n">
+      <c r="H23" s="112" t="n">
         <v>-0.254144229068743</v>
       </c>
-      <c r="I22" s="41" t="n">
+      <c r="I23" s="41" t="n">
         <v>1.713</v>
       </c>
-      <c r="J22" s="44" t="n">
+      <c r="J23" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K22" s="39" t="n">
+      <c r="K23" s="39" t="n">
         <v>10.6915</v>
       </c>
-      <c r="L22" s="40" t="n">
+      <c r="L23" s="40" t="n">
         <v>1.556376560819343</v>
       </c>
-      <c r="M22" s="45" t="inlineStr">
+      <c r="M23" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N22" s="46" t="inlineStr">
+      <c r="N23" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="51">
-      <c r="A23" s="36" t="n">
+    <row r="24" ht="21.75" customHeight="1" s="51">
+      <c r="A24" s="36" t="n">
         <v>46071.30496681713</v>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n">
+      <c r="C24" s="38" t="n">
         <v>4569</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D24" s="39" t="n">
         <v>4.2165</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E24" s="40" t="n">
         <v>1.083600142298115</v>
       </c>
-      <c r="F23" s="41" t="n">
+      <c r="F24" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G23" s="111">
+      <c r="G24" s="111">
         <f>E22-F22</f>
         <v/>
       </c>
-      <c r="H23" s="112" t="n">
+      <c r="H24" s="112" t="n">
         <v>-0.249064350451757</v>
       </c>
-      <c r="I23" s="41" t="n">
+      <c r="I24" s="41" t="n">
         <v>1.697</v>
       </c>
-      <c r="J23" s="44" t="n">
+      <c r="J24" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K23" s="39" t="n">
+      <c r="K24" s="39" t="n">
         <v>10.616</v>
       </c>
-      <c r="L23" s="40" t="n">
+      <c r="L24" s="40" t="n">
         <v>1.567445365486059</v>
       </c>
-      <c r="M23" s="45" t="inlineStr">
+      <c r="M24" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N23" s="46" t="inlineStr">
+      <c r="N24" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="21.75" customHeight="1" s="51">
-      <c r="A24" s="36" t="n">
+    <row r="25" ht="21.75" customHeight="1" s="51">
+      <c r="A25" s="36" t="n">
         <v>46070.30496681713</v>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n">
+      <c r="C25" s="38" t="n">
         <v>4577</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D25" s="39" t="n">
         <v>4.2138</v>
       </c>
-      <c r="E24" s="40" t="n">
+      <c r="E25" s="40" t="n">
         <v>1.086192984954198</v>
       </c>
-      <c r="F24" s="41" t="n">
+      <c r="F25" s="41" t="n">
         <v>1.448</v>
       </c>
-      <c r="G24" s="111">
+      <c r="G25" s="111">
         <f>E23-F23</f>
         <v/>
       </c>
-      <c r="H24" s="112" t="n">
+      <c r="H25" s="112" t="n">
         <v>-0.2498667230979294</v>
       </c>
-      <c r="I24" s="41" t="n">
+      <c r="I25" s="41" t="n">
         <v>1.715</v>
-      </c>
-      <c r="J24" s="44" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="K24" s="39" t="n">
-        <v>10.648</v>
-      </c>
-      <c r="L24" s="40" t="n">
-        <v>1.562734785875282</v>
-      </c>
-      <c r="M24" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N24" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="21.75" customHeight="1" s="51">
-      <c r="A25" s="36" t="n">
-        <v>46069.30496681713</v>
-      </c>
-      <c r="B25" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C25" s="38" t="n"/>
-      <c r="D25" s="39" t="n">
-        <v>4.2105</v>
-      </c>
-      <c r="E25" s="40" t="n"/>
-      <c r="F25" s="41" t="n">
-        <v>1.448</v>
-      </c>
-      <c r="G25" s="111" t="n"/>
-      <c r="H25" s="112" t="n"/>
-      <c r="I25" s="41" t="n">
-        <v>1.724</v>
       </c>
       <c r="J25" s="44" t="n">
         <v>16.64</v>
       </c>
       <c r="K25" s="39" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L25" s="40" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M25" s="45" t="inlineStr">
         <is>
@@ -4201,230 +4204,232 @@
     </row>
     <row r="26" ht="21.75" customHeight="1" s="51">
       <c r="A26" s="36" t="n">
+        <v>46069.30496681713</v>
+      </c>
+      <c r="B26" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n">
+        <v>4.2105</v>
+      </c>
+      <c r="E26" s="40" t="n"/>
+      <c r="F26" s="41" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="G26" s="111" t="n"/>
+      <c r="H26" s="112" t="n"/>
+      <c r="I26" s="41" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="J26" s="44" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="K26" s="39" t="n">
+        <v>10.6205</v>
+      </c>
+      <c r="L26" s="40" t="n">
+        <v>1.566781224989407</v>
+      </c>
+      <c r="M26" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N26" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="21.75" customHeight="1" s="51">
+      <c r="A27" s="36" t="n">
         <v>46066.30496681713</v>
       </c>
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C26" s="38" t="n">
+      <c r="C27" s="38" t="n">
         <v>4593</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D27" s="39" t="n">
         <v>4.215</v>
       </c>
-      <c r="E26" s="40" t="n">
+      <c r="E27" s="40" t="n">
         <v>1.089679715302491</v>
       </c>
-      <c r="F26" s="41" t="n">
+      <c r="F27" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G26" s="111">
+      <c r="G27" s="111">
         <f>E25-F25</f>
         <v/>
       </c>
-      <c r="H26" s="112" t="n">
+      <c r="H27" s="112" t="n">
         <v>-0.2448512021465759</v>
       </c>
-      <c r="I26" s="41" t="n">
+      <c r="I27" s="41" t="n">
         <v>1.72</v>
       </c>
-      <c r="J26" s="44" t="n">
+      <c r="J27" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K26" s="39" t="n">
+      <c r="K27" s="39" t="n">
         <v>10.6254</v>
       </c>
-      <c r="L26" s="40" t="n">
+      <c r="L27" s="40" t="n">
         <v>1.566058689555217</v>
       </c>
-      <c r="M26" s="45" t="inlineStr">
+      <c r="M27" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N26" s="46" t="inlineStr">
+      <c r="N27" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="21.75" customHeight="1" s="51">
-      <c r="A27" s="36" t="n">
+    <row r="28" ht="21.75" customHeight="1" s="51">
+      <c r="A28" s="36" t="n">
         <v>46065.30496681713</v>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n">
+      <c r="C28" s="38" t="n">
         <v>4613</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D28" s="39" t="n">
         <v>4.2158</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E28" s="40" t="n">
         <v>1.094216993215997</v>
       </c>
-      <c r="F27" s="41" t="n">
+      <c r="F28" s="41" t="n">
         <v>1.455</v>
       </c>
-      <c r="G27" s="111">
+      <c r="G28" s="111">
         <f>E26-F26</f>
         <v/>
       </c>
-      <c r="H27" s="112" t="n">
+      <c r="H28" s="112" t="n">
         <v>-0.247960829404813</v>
       </c>
-      <c r="I27" s="41" t="n"/>
-      <c r="J27" s="44" t="n">
+      <c r="I28" s="41" t="n"/>
+      <c r="J28" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K27" s="39" t="n">
+      <c r="K28" s="39" t="n">
         <v>10.567</v>
       </c>
-      <c r="L27" s="40" t="n">
+      <c r="L28" s="40" t="n">
         <v>1.574713731428031</v>
       </c>
-      <c r="M27" s="45" t="inlineStr">
+      <c r="M28" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N27" s="46" t="inlineStr">
+      <c r="N28" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="21.75" customHeight="1" s="51">
-      <c r="A28" s="36" t="n">
+    <row r="29" ht="21.75" customHeight="1" s="51">
+      <c r="A29" s="36" t="n">
         <v>46064.30496681713</v>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C29" s="38" t="n">
         <v>4609</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D29" s="39" t="n">
         <v>4.2135</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E29" s="40" t="n">
         <v>1.093864957873502</v>
       </c>
-      <c r="F28" s="41" t="n">
+      <c r="F29" s="41" t="n">
         <v>1.453</v>
       </c>
-      <c r="G28" s="111">
+      <c r="G29" s="111">
         <f>E27-F27</f>
         <v/>
       </c>
-      <c r="H28" s="112" t="n">
+      <c r="H29" s="112" t="n">
         <v>-0.2471679574167228</v>
       </c>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="44" t="n">
+      <c r="I29" s="41" t="n"/>
+      <c r="J29" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K28" s="39" t="n">
+      <c r="K29" s="39" t="n">
         <v>10.564</v>
       </c>
-      <c r="L28" s="40" t="n">
+      <c r="L29" s="40" t="n">
         <v>1.589360090874669</v>
       </c>
-      <c r="M28" s="45" t="inlineStr">
+      <c r="M29" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N28" s="46" t="inlineStr">
+      <c r="N29" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="21.75" customHeight="1" s="51">
-      <c r="A29" s="36" t="n">
+    <row r="30" ht="21.75" customHeight="1" s="51">
+      <c r="A30" s="36" t="n">
         <v>46063.30496681713</v>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C30" s="38" t="n">
         <v>4620</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D30" s="39" t="n">
         <v>4.217</v>
       </c>
-      <c r="E29" s="40" t="n">
+      <c r="E30" s="40" t="n">
         <v>1.095565567939293</v>
       </c>
-      <c r="F29" s="41" t="n">
+      <c r="F30" s="41" t="n">
         <v>1.456</v>
       </c>
-      <c r="G29" s="111">
+      <c r="G30" s="111">
         <f>E28-F28</f>
         <v/>
       </c>
-      <c r="H29" s="112" t="n">
+      <c r="H30" s="112" t="n">
         <v>-0.2475511209208149</v>
       </c>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="44" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="K29" s="39" t="n">
-        <v>10.6135</v>
-      </c>
-      <c r="L29" s="40" t="n">
-        <v>1.59608046356056</v>
-      </c>
-      <c r="M29" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N29" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="21.75" customHeight="1" s="51">
-      <c r="A30" s="36" t="n">
-        <v>46062.30496681713</v>
-      </c>
-      <c r="B30" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C30" s="38" t="n"/>
-      <c r="D30" s="39" t="n">
-        <v>4.2118</v>
-      </c>
-      <c r="E30" s="40" t="n"/>
-      <c r="F30" s="41" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="G30" s="111" t="n"/>
-      <c r="H30" s="112" t="n"/>
       <c r="I30" s="41" t="n"/>
       <c r="J30" s="44" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K30" s="39" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L30" s="40" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M30" s="45" t="inlineStr">
         <is>
@@ -4439,34 +4444,32 @@
     </row>
     <row r="31" ht="21.75" customHeight="1" s="51">
       <c r="A31" s="36" t="n">
-        <v>46059.30496681713</v>
+        <v>46062.30496681713</v>
       </c>
       <c r="B31" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C31" s="38" t="n">
-        <v>4608</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C31" s="38" t="n"/>
       <c r="D31" s="39" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E31" s="40" t="n">
-        <v>1.092331397416143</v>
-      </c>
-      <c r="F31" s="41" t="n"/>
+        <v>4.2118</v>
+      </c>
+      <c r="E31" s="40" t="n"/>
+      <c r="F31" s="41" t="n">
+        <v>1.462</v>
+      </c>
       <c r="G31" s="111" t="n"/>
       <c r="H31" s="112" t="n"/>
       <c r="I31" s="41" t="n"/>
       <c r="J31" s="44" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K31" s="39" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M31" s="45" t="inlineStr">
         <is>
@@ -4481,21 +4484,21 @@
     </row>
     <row r="32" ht="21.75" customHeight="1" s="51">
       <c r="A32" s="36" t="n">
-        <v>46058.30496681713</v>
+        <v>46059.30496681713</v>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C32" s="38" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D32" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E32" s="40" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="F32" s="41" t="n"/>
       <c r="G32" s="111" t="n"/>
@@ -4505,10 +4508,10 @@
         <v>16.69</v>
       </c>
       <c r="K32" s="39" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M32" s="45" t="inlineStr">
         <is>
@@ -4523,21 +4526,21 @@
     </row>
     <row r="33" ht="21.75" customHeight="1" s="51">
       <c r="A33" s="36" t="n">
-        <v>46057.30496681713</v>
+        <v>46058.30496681713</v>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C33" s="38" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="F33" s="41" t="n"/>
       <c r="G33" s="111" t="n"/>
@@ -4547,10 +4550,10 @@
         <v>16.69</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M33" s="45" t="inlineStr">
         <is>
@@ -4565,34 +4568,34 @@
     </row>
     <row r="34" ht="21.75" customHeight="1" s="51">
       <c r="A34" s="36" t="n">
-        <v>46056.30496681713</v>
+        <v>46057.30496681713</v>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C34" s="38" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E34" s="40" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="F34" s="41" t="n"/>
       <c r="G34" s="111" t="n"/>
       <c r="H34" s="112" t="n"/>
       <c r="I34" s="41" t="n"/>
       <c r="J34" s="44" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K34" s="39" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L34" s="40" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M34" s="45" t="inlineStr">
         <is>
@@ -4607,43 +4610,84 @@
     </row>
     <row r="35" ht="21.75" customHeight="1" s="51">
       <c r="A35" s="36" t="n">
-        <v>46055.30496681713</v>
+        <v>46056.30496681713</v>
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C35" s="38" t="n"/>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C35" s="38" t="n">
+        <v>4622</v>
+      </c>
       <c r="D35" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E35" s="40" t="n"/>
+        <v>4.2205</v>
+      </c>
+      <c r="E35" s="40" t="n">
+        <v>1.095130908660111</v>
+      </c>
       <c r="F35" s="41" t="n"/>
       <c r="G35" s="111" t="n"/>
       <c r="H35" s="112" t="n"/>
       <c r="I35" s="41" t="n"/>
       <c r="J35" s="44" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K35" s="39" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L35" s="40" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M35" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N35" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="21.75" customHeight="1" s="51">
+      <c r="A36" s="36" t="n">
+        <v>46055.30496681713</v>
+      </c>
+      <c r="B36" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E36" s="40" t="n"/>
+      <c r="F36" s="41" t="n"/>
+      <c r="G36" s="111" t="n"/>
+      <c r="H36" s="112" t="n"/>
+      <c r="I36" s="41" t="n"/>
+      <c r="J36" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K35" s="39" t="n">
+      <c r="K36" s="39" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L35" s="40" t="n">
+      <c r="L36" s="40" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M35" s="45" t="inlineStr">
+      <c r="M36" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N35" s="46" t="inlineStr">
+      <c r="N36" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="21.75" customHeight="1" s="51"/>
     <row r="37" ht="21.75" customHeight="1" s="51"/>
     <row r="38" ht="21.75" customHeight="1" s="51"/>
     <row r="39" ht="21.75" customHeight="1" s="51"/>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3047,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="51" min="1" max="1"/>
@@ -3185,40 +3185,46 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46098.39469012326</v>
+        <v>46099.30180732688</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C5" s="102" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D5" s="103" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E5" s="104" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F5" s="105" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G5" s="106" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H5" s="107" t="n">
-        <v>-0.1614</v>
-      </c>
-      <c r="I5" s="105" t="n"/>
-      <c r="J5" s="108" t="n"/>
+        <v>-0.1731</v>
+      </c>
+      <c r="I5" s="105" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J5" s="108" t="n">
+        <v>22.44</v>
+      </c>
       <c r="K5" s="103" t="n">
-        <v>10.769</v>
-      </c>
-      <c r="L5" s="104" t="n"/>
+        <v>10.7055</v>
+      </c>
+      <c r="L5" s="104" t="n">
+        <v>2.0961</v>
+      </c>
       <c r="M5" s="109" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N5" s="110" t="inlineStr">
@@ -3229,43 +3235,37 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="51">
       <c r="A6" s="100" t="n">
-        <v>46097.40237722222</v>
+        <v>46098.39469012732</v>
       </c>
       <c r="B6" s="101" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C6" s="102" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E6" s="104" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F6" s="105" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G6" s="106" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H6" s="107" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I6" s="105" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J6" s="108" t="n">
-        <v>21.84</v>
-      </c>
+        <v>-0.1614</v>
+      </c>
+      <c r="I6" s="105" t="n"/>
+      <c r="J6" s="108" t="n"/>
       <c r="K6" s="103" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L6" s="104" t="n">
-        <v>2.0308</v>
-      </c>
+        <v>10.769</v>
+      </c>
+      <c r="L6" s="104" t="n"/>
       <c r="M6" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT</t>
@@ -3279,128 +3279,134 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="51">
       <c r="A7" s="100" t="n">
-        <v>46094.3788481713</v>
+        <v>46097.40237722222</v>
       </c>
       <c r="B7" s="101" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C7" s="102" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E7" s="104" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F7" s="105" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G7" s="106" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H7" s="107" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I7" s="105" t="n">
         <v>2.163</v>
       </c>
       <c r="J7" s="108" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="K7" s="103" t="n">
+        <v>10.7545</v>
+      </c>
+      <c r="L7" s="104" t="n">
+        <v>2.0308</v>
+      </c>
+      <c r="M7" s="109" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT</t>
+        </is>
+      </c>
+      <c r="N7" s="110" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21.75" customHeight="1" s="51">
+      <c r="A8" s="100" t="n">
+        <v>46094.3788481713</v>
+      </c>
+      <c r="B8" s="101" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C8" s="102" t="n">
+        <v>6399</v>
+      </c>
+      <c r="D8" s="103" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E8" s="104" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F8" s="105" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G8" s="106" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H8" s="107" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I8" s="105" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J8" s="108" t="n">
         <v>21.04</v>
       </c>
-      <c r="K7" s="103" t="n">
+      <c r="K8" s="103" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L7" s="104" t="n">
+      <c r="L8" s="104" t="n">
         <v>1.9644</v>
       </c>
-      <c r="M7" s="109" t="inlineStr">
+      <c r="M8" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N7" s="110" t="inlineStr">
+      <c r="N8" s="110" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="21.75" customHeight="1" s="51">
-      <c r="A8" s="36" t="n">
-        <v>46093.30496681713</v>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C8" s="38" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D8" s="39" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E8" s="40" t="n">
-        <v>1.5029</v>
-      </c>
-      <c r="F8" s="41" t="n"/>
-      <c r="G8" s="111" t="n"/>
-      <c r="H8" s="112" t="n"/>
-      <c r="I8" s="41" t="n"/>
-      <c r="J8" s="44" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K8" s="39" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L8" s="40" t="n">
-        <v>1.9644</v>
-      </c>
-      <c r="M8" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N8" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21.75" customHeight="1" s="51">
       <c r="A9" s="36" t="n">
-        <v>46092.30496681713</v>
+        <v>46093.30496681713</v>
       </c>
       <c r="B9" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C9" s="38" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D9" s="39" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>1.5048</v>
+        <v>1.5029</v>
       </c>
       <c r="F9" s="41" t="n"/>
       <c r="G9" s="111" t="n"/>
       <c r="H9" s="112" t="n"/>
-      <c r="I9" s="41" t="n">
-        <v>2.137</v>
-      </c>
+      <c r="I9" s="41" t="n"/>
       <c r="J9" s="44" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K9" s="39" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M9" s="45" t="inlineStr">
         <is>
@@ -3415,89 +3421,91 @@
     </row>
     <row r="10" ht="21.75" customHeight="1" s="51">
       <c r="A10" s="36" t="n">
+        <v>46092.30496681713</v>
+      </c>
+      <c r="B10" s="37" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C10" s="38" t="n">
+        <v>6195</v>
+      </c>
+      <c r="D10" s="39" t="n">
+        <v>4.2523</v>
+      </c>
+      <c r="E10" s="40" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="F10" s="41" t="n"/>
+      <c r="G10" s="111" t="n"/>
+      <c r="H10" s="112" t="n"/>
+      <c r="I10" s="41" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="J10" s="44" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="K10" s="39" t="n">
+        <v>10.6543</v>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>1.9748</v>
+      </c>
+      <c r="M10" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N10" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.75" customHeight="1" s="51">
+      <c r="A11" s="36" t="n">
         <v>46091.30496681713</v>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B11" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C10" s="38" t="n">
+      <c r="C11" s="38" t="n">
         <v>6359</v>
       </c>
-      <c r="D10" s="39" t="n">
+      <c r="D11" s="39" t="n">
         <v>4.2548</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E11" s="40" t="n">
         <v>1.494547334774843</v>
       </c>
-      <c r="F10" s="41" t="n">
+      <c r="F11" s="41" t="n">
         <v>1.808</v>
       </c>
-      <c r="G10" s="111">
+      <c r="G11" s="111">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H10" s="112" t="n">
+      <c r="H11" s="112" t="n">
         <v>-0.1733698369608172</v>
       </c>
-      <c r="I10" s="41" t="n">
+      <c r="I11" s="41" t="n">
         <v>2.198</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J11" s="44" t="n">
         <v>21.59</v>
       </c>
-      <c r="K10" s="39" t="n">
+      <c r="K11" s="39" t="n">
         <v>10.606</v>
       </c>
-      <c r="L10" s="40" t="n">
+      <c r="L11" s="40" t="n">
         <v>1.9838</v>
       </c>
-      <c r="M10" s="45" t="inlineStr">
+      <c r="M11" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N10" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="21.75" customHeight="1" s="51">
-      <c r="A11" s="36" t="n">
-        <v>46090.30496681713</v>
-      </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="39" t="n">
-        <v>4.2785</v>
-      </c>
-      <c r="E11" s="40" t="n"/>
-      <c r="F11" s="41" t="n">
-        <v>1.792</v>
-      </c>
-      <c r="G11" s="111" t="n"/>
-      <c r="H11" s="112" t="n"/>
-      <c r="I11" s="41" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="J11" s="44" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K11" s="39" t="n">
-        <v>10.6945</v>
-      </c>
-      <c r="L11" s="40" t="n">
-        <v>1.962691102903361</v>
-      </c>
-      <c r="M11" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,DE</t>
         </is>
       </c>
       <c r="N11" s="46" t="inlineStr">
@@ -3508,238 +3516,238 @@
     </row>
     <row r="12" ht="21.75" customHeight="1" s="51">
       <c r="A12" s="36" t="n">
+        <v>46090.30496681713</v>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n">
+        <v>4.2785</v>
+      </c>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="41" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="G12" s="111" t="n"/>
+      <c r="H12" s="112" t="n"/>
+      <c r="I12" s="41" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="J12" s="44" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K12" s="39" t="n">
+        <v>10.6945</v>
+      </c>
+      <c r="L12" s="40" t="n">
+        <v>1.962691102903361</v>
+      </c>
+      <c r="M12" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE</t>
+        </is>
+      </c>
+      <c r="N12" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21.75" customHeight="1" s="51">
+      <c r="A13" s="36" t="n">
         <v>46087.30496681713</v>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C12" s="38" t="n">
+      <c r="C13" s="38" t="n">
         <v>6150</v>
       </c>
-      <c r="D12" s="39" t="n">
+      <c r="D13" s="39" t="n">
         <v>4.2875</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E13" s="40" t="n">
         <v>1.434402332361516</v>
       </c>
-      <c r="F12" s="41" t="n">
+      <c r="F13" s="41" t="n">
         <v>1.845</v>
       </c>
-      <c r="G12" s="111">
+      <c r="G13" s="111">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H12" s="112" t="n">
+      <c r="H13" s="112" t="n">
         <v>-0.2225461613216715</v>
       </c>
-      <c r="I12" s="41" t="n">
+      <c r="I13" s="41" t="n">
         <v>2.089</v>
       </c>
-      <c r="J12" s="44" t="n">
+      <c r="J13" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K12" s="39" t="n">
+      <c r="K13" s="39" t="n">
         <v>10.693</v>
       </c>
-      <c r="L12" s="40" t="n">
+      <c r="L13" s="40" t="n">
         <v>1.864771345740204</v>
       </c>
-      <c r="M12" s="45" t="inlineStr">
+      <c r="M13" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,DE</t>
         </is>
       </c>
-      <c r="N12" s="46" t="inlineStr">
+      <c r="N13" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="21.75" customHeight="1" s="51">
-      <c r="A13" s="36" t="n">
+    <row r="14" ht="21.75" customHeight="1" s="51">
+      <c r="A14" s="36" t="n">
         <v>46086.30496681713</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C14" s="38" t="n">
         <v>5760</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D14" s="39" t="n">
         <v>4.2725</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E14" s="40" t="n">
         <v>1.34815681685196</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F14" s="41" t="n">
         <v>1.734</v>
       </c>
-      <c r="G13" s="111">
+      <c r="G14" s="111">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H13" s="112" t="n">
+      <c r="H14" s="112" t="n">
         <v>-0.2225162532572317</v>
       </c>
-      <c r="I13" s="41" t="n">
+      <c r="I14" s="41" t="n">
         <v>2.055</v>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J14" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K13" s="39" t="n">
+      <c r="K14" s="39" t="n">
         <v>10.6885</v>
       </c>
-      <c r="L13" s="40" t="n">
+      <c r="L14" s="40" t="n">
         <v>1.865556439163587</v>
       </c>
-      <c r="M13" s="45" t="inlineStr">
+      <c r="M14" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N13" s="46" t="inlineStr">
+      <c r="N14" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21.75" customHeight="1" s="51">
-      <c r="A14" s="36" t="n">
+    <row r="15" ht="21.75" customHeight="1" s="51">
+      <c r="A15" s="36" t="n">
         <v>46085.30496681713</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C14" s="38" t="n">
+      <c r="C15" s="38" t="n">
         <v>5681</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D15" s="39" t="n">
         <v>4.2588</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E15" s="40" t="n">
         <v>1.333943833943834</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F15" s="41" t="n">
         <v>1.738</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G15" s="111">
         <f>E12-F12</f>
         <v/>
       </c>
-      <c r="H14" s="112" t="n">
+      <c r="H15" s="112" t="n">
         <v>-0.2324834096985995</v>
       </c>
-      <c r="I14" s="41" t="n">
+      <c r="I15" s="41" t="n">
         <v>2.011</v>
       </c>
-      <c r="J14" s="44" t="n">
+      <c r="J15" s="44" t="n">
         <v>18.64</v>
       </c>
-      <c r="K14" s="39" t="n">
+      <c r="K15" s="39" t="n">
         <v>10.6785</v>
       </c>
-      <c r="L14" s="40" t="n">
+      <c r="L15" s="40" t="n">
         <v>1.74556351547502</v>
       </c>
-      <c r="M14" s="45" t="inlineStr">
+      <c r="M15" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N14" s="46" t="inlineStr">
+      <c r="N15" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="21.75" customHeight="1" s="51">
-      <c r="A15" s="36" t="n">
+    <row r="16" ht="21.75" customHeight="1" s="51">
+      <c r="A16" s="36" t="n">
         <v>46084.30496681713</v>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C15" s="38" t="n">
+      <c r="C16" s="38" t="n">
         <v>5237</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D16" s="39" t="n">
         <v>4.2865</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E16" s="40" t="n">
         <v>1.221742680508573</v>
       </c>
-      <c r="F15" s="41" t="n">
+      <c r="F16" s="41" t="n">
         <v>1.619</v>
       </c>
-      <c r="G15" s="111">
+      <c r="G16" s="111">
         <f>E13-F13</f>
         <v/>
       </c>
-      <c r="H15" s="112" t="n">
+      <c r="H16" s="112" t="n">
         <v>-0.2453720318044636</v>
       </c>
-      <c r="I15" s="41" t="n">
+      <c r="I16" s="41" t="n">
         <v>1.916</v>
-      </c>
-      <c r="J15" s="44" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="K15" s="39" t="n">
-        <v>10.7265</v>
-      </c>
-      <c r="L15" s="40" t="n">
-        <v>1.61655712487764</v>
-      </c>
-      <c r="M15" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N15" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="21.75" customHeight="1" s="51">
-      <c r="A16" s="36" t="n">
-        <v>46083.30496681713</v>
-      </c>
-      <c r="B16" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C16" s="38" t="n"/>
-      <c r="D16" s="39" t="n">
-        <v>4.244</v>
-      </c>
-      <c r="E16" s="40" t="n"/>
-      <c r="F16" s="41" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="G16" s="111" t="n"/>
-      <c r="H16" s="112" t="n"/>
-      <c r="I16" s="41" t="n">
-        <v>1.815</v>
       </c>
       <c r="J16" s="44" t="n">
         <v>17.34</v>
       </c>
       <c r="K16" s="39" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M16" s="45" t="inlineStr">
         <is>
@@ -3754,238 +3762,238 @@
     </row>
     <row r="17" ht="21.75" customHeight="1" s="51">
       <c r="A17" s="36" t="n">
-        <v>46080.30496681713</v>
+        <v>46083.30496681713</v>
       </c>
       <c r="B17" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="n">
-        <v>4777</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E17" s="40" t="n">
-        <v>1.130838245389769</v>
-      </c>
+        <v>4.244</v>
+      </c>
+      <c r="E17" s="40" t="n"/>
       <c r="F17" s="41" t="n">
         <v>1.506</v>
       </c>
-      <c r="G17" s="111">
+      <c r="G17" s="111" t="n"/>
+      <c r="H17" s="112" t="n"/>
+      <c r="I17" s="41" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="J17" s="44" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="K17" s="39" t="n">
+        <v>10.708</v>
+      </c>
+      <c r="L17" s="40" t="n">
+        <v>1.619350018677624</v>
+      </c>
+      <c r="M17" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N17" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="21.75" customHeight="1" s="51">
+      <c r="A18" s="36" t="n">
+        <v>46080.30496681713</v>
+      </c>
+      <c r="B18" s="37" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D18" s="39" t="n">
+        <v>4.2243</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>1.130838245389769</v>
+      </c>
+      <c r="F18" s="41" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="G18" s="111">
         <f>E15-F15</f>
         <v/>
       </c>
-      <c r="H17" s="112" t="n">
+      <c r="H18" s="112" t="n">
         <v>-0.2491113908434471</v>
       </c>
-      <c r="I17" s="41" t="n">
+      <c r="I18" s="41" t="n">
         <v>1.748</v>
       </c>
-      <c r="J17" s="44" t="n">
+      <c r="J18" s="44" t="n">
         <v>17.19</v>
       </c>
-      <c r="K17" s="39" t="n">
+      <c r="K18" s="39" t="n">
         <v>10.6643</v>
       </c>
-      <c r="L17" s="40" t="n">
+      <c r="L18" s="40" t="n">
         <v>1.611920144782124</v>
       </c>
-      <c r="M17" s="45" t="inlineStr">
+      <c r="M18" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N17" s="46" t="inlineStr">
+      <c r="N18" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="21.75" customHeight="1" s="51">
-      <c r="A18" s="36" t="n">
+    <row r="19" ht="21.75" customHeight="1" s="51">
+      <c r="A19" s="36" t="n">
         <v>46079.30496681713</v>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B19" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C18" s="38" t="n">
+      <c r="C19" s="38" t="n">
         <v>4744</v>
       </c>
-      <c r="D18" s="39" t="n">
+      <c r="D19" s="39" t="n">
         <v>4.2225</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E19" s="40" t="n">
         <v>1.123505032563647</v>
       </c>
-      <c r="F18" s="41" t="n">
+      <c r="F19" s="41" t="n">
         <v>1.492</v>
       </c>
-      <c r="G18" s="111">
+      <c r="G19" s="111">
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H18" s="112" t="n">
+      <c r="H19" s="112" t="n">
         <v>-0.2469805411771802</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I19" s="41" t="n">
         <v>1.726</v>
       </c>
-      <c r="J18" s="44" t="n">
+      <c r="J19" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K18" s="39" t="n">
+      <c r="K19" s="39" t="n">
         <v>10.673</v>
       </c>
-      <c r="L18" s="40" t="n">
+      <c r="L19" s="40" t="n">
         <v>1.624660357912489</v>
       </c>
-      <c r="M18" s="45" t="inlineStr">
+      <c r="M19" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N18" s="46" t="inlineStr">
+      <c r="N19" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="21.75" customHeight="1" s="51">
-      <c r="A19" s="36" t="n">
+    <row r="20" ht="21.75" customHeight="1" s="51">
+      <c r="A20" s="36" t="n">
         <v>46078.30496681713</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C20" s="38" t="n">
         <v>4765</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D20" s="39" t="n">
         <v>4.2233</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E20" s="40" t="n">
         <v>1.128264627187271</v>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F20" s="41" t="n">
         <v>1.495</v>
       </c>
-      <c r="G19" s="111">
+      <c r="G20" s="111">
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H19" s="112" t="n">
+      <c r="H20" s="112" t="n">
         <v>-0.2453079416807554</v>
       </c>
-      <c r="I19" s="41" t="n">
+      <c r="I20" s="41" t="n">
         <v>1.74</v>
       </c>
-      <c r="J19" s="44" t="n">
+      <c r="J20" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K19" s="39" t="n">
+      <c r="K20" s="39" t="n">
         <v>10.6765</v>
       </c>
-      <c r="L19" s="40" t="n">
+      <c r="L20" s="40" t="n">
         <v>1.624127757223809</v>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M20" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N19" s="46" t="inlineStr">
+      <c r="N20" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="21.75" customHeight="1" s="51">
-      <c r="A20" s="36" t="n">
+    <row r="21" ht="21.75" customHeight="1" s="51">
+      <c r="A21" s="36" t="n">
         <v>46077.30496681713</v>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n">
+      <c r="C21" s="38" t="n">
         <v>4769</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D21" s="39" t="n">
         <v>4.2203</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E21" s="40" t="n">
         <v>1.130014453948772</v>
       </c>
-      <c r="F20" s="41" t="n">
+      <c r="F21" s="41" t="n">
         <v>1.505</v>
       </c>
-      <c r="G20" s="111">
+      <c r="G21" s="111">
         <f>E18-F18</f>
         <v/>
       </c>
-      <c r="H20" s="112" t="n">
+      <c r="H21" s="112" t="n">
         <v>-0.2491598312632747</v>
       </c>
-      <c r="I20" s="41" t="n">
+      <c r="I21" s="41" t="n">
         <v>1.745</v>
-      </c>
-      <c r="J20" s="44" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="K20" s="39" t="n">
-        <v>10.688</v>
-      </c>
-      <c r="L20" s="40" t="n">
-        <v>1.613023952095808</v>
-      </c>
-      <c r="M20" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N20" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" s="51">
-      <c r="A21" s="36" t="n">
-        <v>46076.30496681713</v>
-      </c>
-      <c r="B21" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C21" s="38" t="n"/>
-      <c r="D21" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E21" s="40" t="n"/>
-      <c r="F21" s="41" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="G21" s="111" t="n"/>
-      <c r="H21" s="112" t="n"/>
-      <c r="I21" s="41" t="n">
-        <v>1.742</v>
       </c>
       <c r="J21" s="44" t="n">
         <v>17.24</v>
       </c>
       <c r="K21" s="39" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M21" s="45" t="inlineStr">
         <is>
@@ -4000,238 +4008,238 @@
     </row>
     <row r="22" ht="21.75" customHeight="1" s="51">
       <c r="A22" s="36" t="n">
+        <v>46076.30496681713</v>
+      </c>
+      <c r="B22" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E22" s="40" t="n"/>
+      <c r="F22" s="41" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G22" s="111" t="n"/>
+      <c r="H22" s="112" t="n"/>
+      <c r="I22" s="41" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="J22" s="44" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="K22" s="39" t="n">
+        <v>10.6955</v>
+      </c>
+      <c r="L22" s="40" t="n">
+        <v>1.611892852134075</v>
+      </c>
+      <c r="M22" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N22" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="21.75" customHeight="1" s="51">
+      <c r="A23" s="36" t="n">
         <v>46073.30496681713</v>
       </c>
-      <c r="B22" s="37" t="inlineStr">
+      <c r="B23" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C22" s="38" t="n">
+      <c r="C23" s="38" t="n">
         <v>4743</v>
       </c>
-      <c r="D22" s="39" t="n">
+      <c r="D23" s="39" t="n">
         <v>4.2238</v>
       </c>
-      <c r="E22" s="40" t="n">
+      <c r="E23" s="40" t="n">
         <v>1.122922486860173</v>
       </c>
-      <c r="F22" s="41" t="n">
+      <c r="F23" s="41" t="n">
         <v>1.487</v>
       </c>
-      <c r="G22" s="111">
+      <c r="G23" s="111">
         <f>E20-F20</f>
         <v/>
       </c>
-      <c r="H22" s="112" t="n">
+      <c r="H23" s="112" t="n">
         <v>-0.2448402912843488</v>
       </c>
-      <c r="I22" s="41" t="n">
+      <c r="I23" s="41" t="n">
         <v>1.727</v>
       </c>
-      <c r="J22" s="44" t="n">
+      <c r="J23" s="44" t="n">
         <v>16.89</v>
       </c>
-      <c r="K22" s="39" t="n">
+      <c r="K23" s="39" t="n">
         <v>10.6745</v>
       </c>
-      <c r="L22" s="40" t="n">
+      <c r="L23" s="40" t="n">
         <v>1.582275516417631</v>
       </c>
-      <c r="M22" s="45" t="inlineStr">
+      <c r="M23" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N22" s="46" t="inlineStr">
+      <c r="N23" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="21.75" customHeight="1" s="51">
-      <c r="A23" s="36" t="n">
+    <row r="24" ht="21.75" customHeight="1" s="51">
+      <c r="A24" s="36" t="n">
         <v>46072.30496681713</v>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n">
+      <c r="C24" s="38" t="n">
         <v>4597</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D24" s="39" t="n">
         <v>4.2215</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E24" s="40" t="n">
         <v>1.088949425559635</v>
       </c>
-      <c r="F23" s="41" t="n">
+      <c r="F24" s="41" t="n">
         <v>1.46</v>
       </c>
-      <c r="G23" s="111">
+      <c r="G24" s="111">
         <f>E21-F21</f>
         <v/>
       </c>
-      <c r="H23" s="112" t="n">
+      <c r="H24" s="112" t="n">
         <v>-0.254144229068743</v>
       </c>
-      <c r="I23" s="41" t="n">
+      <c r="I24" s="41" t="n">
         <v>1.713</v>
       </c>
-      <c r="J23" s="44" t="n">
+      <c r="J24" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K23" s="39" t="n">
+      <c r="K24" s="39" t="n">
         <v>10.6915</v>
       </c>
-      <c r="L23" s="40" t="n">
+      <c r="L24" s="40" t="n">
         <v>1.556376560819343</v>
       </c>
-      <c r="M23" s="45" t="inlineStr">
+      <c r="M24" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N23" s="46" t="inlineStr">
+      <c r="N24" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="21.75" customHeight="1" s="51">
-      <c r="A24" s="36" t="n">
+    <row r="25" ht="21.75" customHeight="1" s="51">
+      <c r="A25" s="36" t="n">
         <v>46071.30496681713</v>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n">
+      <c r="C25" s="38" t="n">
         <v>4569</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D25" s="39" t="n">
         <v>4.2165</v>
       </c>
-      <c r="E24" s="40" t="n">
+      <c r="E25" s="40" t="n">
         <v>1.083600142298115</v>
       </c>
-      <c r="F24" s="41" t="n">
+      <c r="F25" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G24" s="111">
+      <c r="G25" s="111">
         <f>E22-F22</f>
         <v/>
       </c>
-      <c r="H24" s="112" t="n">
+      <c r="H25" s="112" t="n">
         <v>-0.249064350451757</v>
       </c>
-      <c r="I24" s="41" t="n">
+      <c r="I25" s="41" t="n">
         <v>1.697</v>
       </c>
-      <c r="J24" s="44" t="n">
+      <c r="J25" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K24" s="39" t="n">
+      <c r="K25" s="39" t="n">
         <v>10.616</v>
       </c>
-      <c r="L24" s="40" t="n">
+      <c r="L25" s="40" t="n">
         <v>1.567445365486059</v>
       </c>
-      <c r="M24" s="45" t="inlineStr">
+      <c r="M25" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N24" s="46" t="inlineStr">
+      <c r="N25" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="21.75" customHeight="1" s="51">
-      <c r="A25" s="36" t="n">
+    <row r="26" ht="21.75" customHeight="1" s="51">
+      <c r="A26" s="36" t="n">
         <v>46070.30496681713</v>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n">
+      <c r="C26" s="38" t="n">
         <v>4577</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D26" s="39" t="n">
         <v>4.2138</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E26" s="40" t="n">
         <v>1.086192984954198</v>
       </c>
-      <c r="F25" s="41" t="n">
+      <c r="F26" s="41" t="n">
         <v>1.448</v>
       </c>
-      <c r="G25" s="111">
+      <c r="G26" s="111">
         <f>E23-F23</f>
         <v/>
       </c>
-      <c r="H25" s="112" t="n">
+      <c r="H26" s="112" t="n">
         <v>-0.2498667230979294</v>
       </c>
-      <c r="I25" s="41" t="n">
+      <c r="I26" s="41" t="n">
         <v>1.715</v>
-      </c>
-      <c r="J25" s="44" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="K25" s="39" t="n">
-        <v>10.648</v>
-      </c>
-      <c r="L25" s="40" t="n">
-        <v>1.562734785875282</v>
-      </c>
-      <c r="M25" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N25" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="21.75" customHeight="1" s="51">
-      <c r="A26" s="36" t="n">
-        <v>46069.30496681713</v>
-      </c>
-      <c r="B26" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C26" s="38" t="n"/>
-      <c r="D26" s="39" t="n">
-        <v>4.2105</v>
-      </c>
-      <c r="E26" s="40" t="n"/>
-      <c r="F26" s="41" t="n">
-        <v>1.448</v>
-      </c>
-      <c r="G26" s="111" t="n"/>
-      <c r="H26" s="112" t="n"/>
-      <c r="I26" s="41" t="n">
-        <v>1.724</v>
       </c>
       <c r="J26" s="44" t="n">
         <v>16.64</v>
       </c>
       <c r="K26" s="39" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L26" s="40" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M26" s="45" t="inlineStr">
         <is>
@@ -4246,230 +4254,232 @@
     </row>
     <row r="27" ht="21.75" customHeight="1" s="51">
       <c r="A27" s="36" t="n">
+        <v>46069.30496681713</v>
+      </c>
+      <c r="B27" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n">
+        <v>4.2105</v>
+      </c>
+      <c r="E27" s="40" t="n"/>
+      <c r="F27" s="41" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="G27" s="111" t="n"/>
+      <c r="H27" s="112" t="n"/>
+      <c r="I27" s="41" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="J27" s="44" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="K27" s="39" t="n">
+        <v>10.6205</v>
+      </c>
+      <c r="L27" s="40" t="n">
+        <v>1.566781224989407</v>
+      </c>
+      <c r="M27" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N27" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="21.75" customHeight="1" s="51">
+      <c r="A28" s="36" t="n">
         <v>46066.30496681713</v>
       </c>
-      <c r="B27" s="37" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n">
+      <c r="C28" s="38" t="n">
         <v>4593</v>
       </c>
-      <c r="D27" s="39" t="n">
+      <c r="D28" s="39" t="n">
         <v>4.215</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E28" s="40" t="n">
         <v>1.089679715302491</v>
       </c>
-      <c r="F27" s="41" t="n">
+      <c r="F28" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G27" s="111">
+      <c r="G28" s="111">
         <f>E25-F25</f>
         <v/>
       </c>
-      <c r="H27" s="112" t="n">
+      <c r="H28" s="112" t="n">
         <v>-0.2448512021465759</v>
       </c>
-      <c r="I27" s="41" t="n">
+      <c r="I28" s="41" t="n">
         <v>1.72</v>
       </c>
-      <c r="J27" s="44" t="n">
+      <c r="J28" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K27" s="39" t="n">
+      <c r="K28" s="39" t="n">
         <v>10.6254</v>
       </c>
-      <c r="L27" s="40" t="n">
+      <c r="L28" s="40" t="n">
         <v>1.566058689555217</v>
       </c>
-      <c r="M27" s="45" t="inlineStr">
+      <c r="M28" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N27" s="46" t="inlineStr">
+      <c r="N28" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="21.75" customHeight="1" s="51">
-      <c r="A28" s="36" t="n">
+    <row r="29" ht="21.75" customHeight="1" s="51">
+      <c r="A29" s="36" t="n">
         <v>46065.30496681713</v>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C29" s="38" t="n">
         <v>4613</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D29" s="39" t="n">
         <v>4.2158</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E29" s="40" t="n">
         <v>1.094216993215997</v>
       </c>
-      <c r="F28" s="41" t="n">
+      <c r="F29" s="41" t="n">
         <v>1.455</v>
       </c>
-      <c r="G28" s="111">
+      <c r="G29" s="111">
         <f>E26-F26</f>
         <v/>
       </c>
-      <c r="H28" s="112" t="n">
+      <c r="H29" s="112" t="n">
         <v>-0.247960829404813</v>
       </c>
-      <c r="I28" s="41" t="n"/>
-      <c r="J28" s="44" t="n">
+      <c r="I29" s="41" t="n"/>
+      <c r="J29" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K28" s="39" t="n">
+      <c r="K29" s="39" t="n">
         <v>10.567</v>
       </c>
-      <c r="L28" s="40" t="n">
+      <c r="L29" s="40" t="n">
         <v>1.574713731428031</v>
       </c>
-      <c r="M28" s="45" t="inlineStr">
+      <c r="M29" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N28" s="46" t="inlineStr">
+      <c r="N29" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="21.75" customHeight="1" s="51">
-      <c r="A29" s="36" t="n">
+    <row r="30" ht="21.75" customHeight="1" s="51">
+      <c r="A30" s="36" t="n">
         <v>46064.30496681713</v>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C30" s="38" t="n">
         <v>4609</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D30" s="39" t="n">
         <v>4.2135</v>
       </c>
-      <c r="E29" s="40" t="n">
+      <c r="E30" s="40" t="n">
         <v>1.093864957873502</v>
       </c>
-      <c r="F29" s="41" t="n">
+      <c r="F30" s="41" t="n">
         <v>1.453</v>
       </c>
-      <c r="G29" s="111">
+      <c r="G30" s="111">
         <f>E27-F27</f>
         <v/>
       </c>
-      <c r="H29" s="112" t="n">
+      <c r="H30" s="112" t="n">
         <v>-0.2471679574167228</v>
       </c>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="44" t="n">
+      <c r="I30" s="41" t="n"/>
+      <c r="J30" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K29" s="39" t="n">
+      <c r="K30" s="39" t="n">
         <v>10.564</v>
       </c>
-      <c r="L29" s="40" t="n">
+      <c r="L30" s="40" t="n">
         <v>1.589360090874669</v>
       </c>
-      <c r="M29" s="45" t="inlineStr">
+      <c r="M30" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N29" s="46" t="inlineStr">
+      <c r="N30" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="21.75" customHeight="1" s="51">
-      <c r="A30" s="36" t="n">
+    <row r="31" ht="21.75" customHeight="1" s="51">
+      <c r="A31" s="36" t="n">
         <v>46063.30496681713</v>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C31" s="38" t="n">
         <v>4620</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D31" s="39" t="n">
         <v>4.217</v>
       </c>
-      <c r="E30" s="40" t="n">
+      <c r="E31" s="40" t="n">
         <v>1.095565567939293</v>
       </c>
-      <c r="F30" s="41" t="n">
+      <c r="F31" s="41" t="n">
         <v>1.456</v>
       </c>
-      <c r="G30" s="111">
+      <c r="G31" s="111">
         <f>E28-F28</f>
         <v/>
       </c>
-      <c r="H30" s="112" t="n">
+      <c r="H31" s="112" t="n">
         <v>-0.2475511209208149</v>
       </c>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="44" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="K30" s="39" t="n">
-        <v>10.6135</v>
-      </c>
-      <c r="L30" s="40" t="n">
-        <v>1.59608046356056</v>
-      </c>
-      <c r="M30" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N30" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="21.75" customHeight="1" s="51">
-      <c r="A31" s="36" t="n">
-        <v>46062.30496681713</v>
-      </c>
-      <c r="B31" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C31" s="38" t="n"/>
-      <c r="D31" s="39" t="n">
-        <v>4.2118</v>
-      </c>
-      <c r="E31" s="40" t="n"/>
-      <c r="F31" s="41" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="G31" s="111" t="n"/>
-      <c r="H31" s="112" t="n"/>
       <c r="I31" s="41" t="n"/>
       <c r="J31" s="44" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K31" s="39" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L31" s="40" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M31" s="45" t="inlineStr">
         <is>
@@ -4484,34 +4494,32 @@
     </row>
     <row r="32" ht="21.75" customHeight="1" s="51">
       <c r="A32" s="36" t="n">
-        <v>46059.30496681713</v>
+        <v>46062.30496681713</v>
       </c>
       <c r="B32" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C32" s="38" t="n">
-        <v>4608</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C32" s="38" t="n"/>
       <c r="D32" s="39" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E32" s="40" t="n">
-        <v>1.092331397416143</v>
-      </c>
-      <c r="F32" s="41" t="n"/>
+        <v>4.2118</v>
+      </c>
+      <c r="E32" s="40" t="n"/>
+      <c r="F32" s="41" t="n">
+        <v>1.462</v>
+      </c>
       <c r="G32" s="111" t="n"/>
       <c r="H32" s="112" t="n"/>
       <c r="I32" s="41" t="n"/>
       <c r="J32" s="44" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K32" s="39" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M32" s="45" t="inlineStr">
         <is>
@@ -4526,21 +4534,21 @@
     </row>
     <row r="33" ht="21.75" customHeight="1" s="51">
       <c r="A33" s="36" t="n">
-        <v>46058.30496681713</v>
+        <v>46059.30496681713</v>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C33" s="38" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D33" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E33" s="40" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="F33" s="41" t="n"/>
       <c r="G33" s="111" t="n"/>
@@ -4550,10 +4558,10 @@
         <v>16.69</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M33" s="45" t="inlineStr">
         <is>
@@ -4568,21 +4576,21 @@
     </row>
     <row r="34" ht="21.75" customHeight="1" s="51">
       <c r="A34" s="36" t="n">
-        <v>46057.30496681713</v>
+        <v>46058.30496681713</v>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C34" s="38" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E34" s="40" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="F34" s="41" t="n"/>
       <c r="G34" s="111" t="n"/>
@@ -4592,10 +4600,10 @@
         <v>16.69</v>
       </c>
       <c r="K34" s="39" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L34" s="40" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M34" s="45" t="inlineStr">
         <is>
@@ -4610,34 +4618,34 @@
     </row>
     <row r="35" ht="21.75" customHeight="1" s="51">
       <c r="A35" s="36" t="n">
-        <v>46056.30496681713</v>
+        <v>46057.30496681713</v>
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C35" s="38" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E35" s="40" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="F35" s="41" t="n"/>
       <c r="G35" s="111" t="n"/>
       <c r="H35" s="112" t="n"/>
       <c r="I35" s="41" t="n"/>
       <c r="J35" s="44" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K35" s="39" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L35" s="40" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M35" s="45" t="inlineStr">
         <is>
@@ -4652,43 +4660,84 @@
     </row>
     <row r="36" ht="21.75" customHeight="1" s="51">
       <c r="A36" s="36" t="n">
-        <v>46055.30496681713</v>
+        <v>46056.30496681713</v>
       </c>
       <c r="B36" s="37" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C36" s="38" t="n"/>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C36" s="38" t="n">
+        <v>4622</v>
+      </c>
       <c r="D36" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E36" s="40" t="n"/>
+        <v>4.2205</v>
+      </c>
+      <c r="E36" s="40" t="n">
+        <v>1.095130908660111</v>
+      </c>
       <c r="F36" s="41" t="n"/>
       <c r="G36" s="111" t="n"/>
       <c r="H36" s="112" t="n"/>
       <c r="I36" s="41" t="n"/>
       <c r="J36" s="44" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K36" s="39" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L36" s="40" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M36" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N36" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="21.75" customHeight="1" s="51">
+      <c r="A37" s="36" t="n">
+        <v>46055.30496681713</v>
+      </c>
+      <c r="B37" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E37" s="40" t="n"/>
+      <c r="F37" s="41" t="n"/>
+      <c r="G37" s="111" t="n"/>
+      <c r="H37" s="112" t="n"/>
+      <c r="I37" s="41" t="n"/>
+      <c r="J37" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K36" s="39" t="n">
+      <c r="K37" s="39" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L36" s="40" t="n">
+      <c r="L37" s="40" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M36" s="45" t="inlineStr">
+      <c r="M37" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N36" s="46" t="inlineStr">
+      <c r="N37" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="21.75" customHeight="1" s="51"/>
     <row r="38" ht="21.75" customHeight="1" s="51"/>
     <row r="39" ht="21.75" customHeight="1" s="51"/>
     <row r="40" ht="21.75" customHeight="1" s="51"/>
@@ -4866,7 +4915,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46097.32398920139</v>
+        <v>46097.30180732688</v>
       </c>
       <c r="B4" s="114" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -28,7 +28,6 @@
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -3185,7 +3184,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46099.30180732688</v>
+        <v>46099.39440692261</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
@@ -4915,7 +4914,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46097.30180732688</v>
+        <v>46097.39440692261</v>
       </c>
       <c r="B4" s="114" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3184,7 +3184,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46099.39440692261</v>
+        <v>46099.57810183834</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46097.39440692261</v>
+        <v>46097.57810183834</v>
       </c>
       <c r="B4" s="114" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -28,6 +28,7 @@
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -3046,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="51" min="1" max="1"/>
@@ -3184,42 +3185,42 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46099.57810183834</v>
+        <v>46100.31114975031</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C5" s="102" t="n">
-        <v>6565</v>
+        <v>6620</v>
       </c>
       <c r="D5" s="103" t="n">
-        <v>4.2593</v>
+        <v>4.2713</v>
       </c>
       <c r="E5" s="104" t="n">
-        <v>1.5413</v>
+        <v>1.5499</v>
       </c>
       <c r="F5" s="105" t="n">
-        <v>1.864</v>
+        <v>1.8547</v>
       </c>
       <c r="G5" s="106" t="n">
-        <v>-0.3227</v>
+        <v>-0.3048</v>
       </c>
       <c r="H5" s="107" t="n">
-        <v>-0.1731</v>
+        <v>-0.1643</v>
       </c>
       <c r="I5" s="105" t="n">
         <v>2.163</v>
       </c>
       <c r="J5" s="108" t="n">
-        <v>22.44</v>
+        <v>22.29</v>
       </c>
       <c r="K5" s="103" t="n">
-        <v>10.7055</v>
+        <v>10.7778</v>
       </c>
       <c r="L5" s="104" t="n">
-        <v>2.0961</v>
+        <v>2.0681</v>
       </c>
       <c r="M5" s="109" t="inlineStr">
         <is>
@@ -3234,40 +3235,46 @@
     </row>
     <row r="6" ht="21.75" customHeight="1" s="51">
       <c r="A6" s="100" t="n">
-        <v>46098.39469012732</v>
+        <v>46099.57810184028</v>
       </c>
       <c r="B6" s="101" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C6" s="102" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D6" s="103" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E6" s="104" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F6" s="105" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G6" s="106" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H6" s="107" t="n">
-        <v>-0.1614</v>
-      </c>
-      <c r="I6" s="105" t="n"/>
-      <c r="J6" s="108" t="n"/>
+        <v>-0.1731</v>
+      </c>
+      <c r="I6" s="105" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J6" s="108" t="n">
+        <v>22.44</v>
+      </c>
       <c r="K6" s="103" t="n">
-        <v>10.769</v>
-      </c>
-      <c r="L6" s="104" t="n"/>
+        <v>10.7055</v>
+      </c>
+      <c r="L6" s="104" t="n">
+        <v>2.0961</v>
+      </c>
       <c r="M6" s="109" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N6" s="110" t="inlineStr">
@@ -3278,43 +3285,37 @@
     </row>
     <row r="7" ht="21.75" customHeight="1" s="51">
       <c r="A7" s="100" t="n">
-        <v>46097.40237722222</v>
+        <v>46098.39469012732</v>
       </c>
       <c r="B7" s="101" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C7" s="102" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D7" s="103" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E7" s="104" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F7" s="105" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G7" s="106" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H7" s="107" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I7" s="105" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J7" s="108" t="n">
-        <v>21.84</v>
-      </c>
+        <v>-0.1614</v>
+      </c>
+      <c r="I7" s="105" t="n"/>
+      <c r="J7" s="108" t="n"/>
       <c r="K7" s="103" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L7" s="104" t="n">
-        <v>2.0308</v>
-      </c>
+        <v>10.769</v>
+      </c>
+      <c r="L7" s="104" t="n"/>
       <c r="M7" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT</t>
@@ -3328,128 +3329,134 @@
     </row>
     <row r="8" ht="21.75" customHeight="1" s="51">
       <c r="A8" s="100" t="n">
-        <v>46094.3788481713</v>
+        <v>46097.40237722222</v>
       </c>
       <c r="B8" s="101" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C8" s="102" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D8" s="103" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E8" s="104" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F8" s="105" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G8" s="106" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H8" s="107" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I8" s="105" t="n">
         <v>2.163</v>
       </c>
       <c r="J8" s="108" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="K8" s="103" t="n">
+        <v>10.7545</v>
+      </c>
+      <c r="L8" s="104" t="n">
+        <v>2.0308</v>
+      </c>
+      <c r="M8" s="109" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT</t>
+        </is>
+      </c>
+      <c r="N8" s="110" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="21.75" customHeight="1" s="51">
+      <c r="A9" s="100" t="n">
+        <v>46094.3788481713</v>
+      </c>
+      <c r="B9" s="101" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C9" s="102" t="n">
+        <v>6399</v>
+      </c>
+      <c r="D9" s="103" t="n">
+        <v>4.2578</v>
+      </c>
+      <c r="E9" s="104" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F9" s="105" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G9" s="106" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H9" s="107" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I9" s="105" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J9" s="108" t="n">
         <v>21.04</v>
       </c>
-      <c r="K8" s="103" t="n">
+      <c r="K9" s="103" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L8" s="104" t="n">
+      <c r="L9" s="104" t="n">
         <v>1.9644</v>
       </c>
-      <c r="M8" s="109" t="inlineStr">
+      <c r="M9" s="109" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N8" s="110" t="inlineStr">
+      <c r="N9" s="110" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="21.75" customHeight="1" s="51">
-      <c r="A9" s="36" t="n">
-        <v>46093.30496681713</v>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="C9" s="38" t="n">
-        <v>6192</v>
-      </c>
-      <c r="D9" s="39" t="n">
-        <v>4.2578</v>
-      </c>
-      <c r="E9" s="40" t="n">
-        <v>1.5029</v>
-      </c>
-      <c r="F9" s="41" t="n"/>
-      <c r="G9" s="111" t="n"/>
-      <c r="H9" s="112" t="n"/>
-      <c r="I9" s="41" t="n"/>
-      <c r="J9" s="44" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="K9" s="39" t="n">
-        <v>10.7108</v>
-      </c>
-      <c r="L9" s="40" t="n">
-        <v>1.9644</v>
-      </c>
-      <c r="M9" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N9" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
         </is>
       </c>
     </row>
     <row r="10" ht="21.75" customHeight="1" s="51">
       <c r="A10" s="36" t="n">
-        <v>46092.30496681713</v>
+        <v>46093.30496681713</v>
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C10" s="38" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D10" s="39" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>1.5048</v>
+        <v>1.5029</v>
       </c>
       <c r="F10" s="41" t="n"/>
       <c r="G10" s="111" t="n"/>
       <c r="H10" s="112" t="n"/>
-      <c r="I10" s="41" t="n">
-        <v>2.137</v>
-      </c>
+      <c r="I10" s="41" t="n"/>
       <c r="J10" s="44" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K10" s="39" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M10" s="45" t="inlineStr">
         <is>
@@ -3464,89 +3471,91 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" s="51">
       <c r="A11" s="36" t="n">
+        <v>46092.30496681713</v>
+      </c>
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C11" s="38" t="n">
+        <v>6195</v>
+      </c>
+      <c r="D11" s="39" t="n">
+        <v>4.2523</v>
+      </c>
+      <c r="E11" s="40" t="n">
+        <v>1.5048</v>
+      </c>
+      <c r="F11" s="41" t="n"/>
+      <c r="G11" s="111" t="n"/>
+      <c r="H11" s="112" t="n"/>
+      <c r="I11" s="41" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="J11" s="44" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="K11" s="39" t="n">
+        <v>10.6543</v>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>1.9748</v>
+      </c>
+      <c r="M11" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+      <c r="N11" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21.75" customHeight="1" s="51">
+      <c r="A12" s="36" t="n">
         <v>46091.30496681713</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B12" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C11" s="38" t="n">
+      <c r="C12" s="38" t="n">
         <v>6359</v>
       </c>
-      <c r="D11" s="39" t="n">
+      <c r="D12" s="39" t="n">
         <v>4.2548</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E12" s="40" t="n">
         <v>1.494547334774843</v>
       </c>
-      <c r="F11" s="41" t="n">
+      <c r="F12" s="41" t="n">
         <v>1.808</v>
       </c>
-      <c r="G11" s="111">
+      <c r="G12" s="111">
         <f>E8-F8</f>
         <v/>
       </c>
-      <c r="H11" s="112" t="n">
+      <c r="H12" s="112" t="n">
         <v>-0.1733698369608172</v>
       </c>
-      <c r="I11" s="41" t="n">
+      <c r="I12" s="41" t="n">
         <v>2.198</v>
       </c>
-      <c r="J11" s="44" t="n">
+      <c r="J12" s="44" t="n">
         <v>21.59</v>
       </c>
-      <c r="K11" s="39" t="n">
+      <c r="K12" s="39" t="n">
         <v>10.606</v>
       </c>
-      <c r="L11" s="40" t="n">
+      <c r="L12" s="40" t="n">
         <v>1.9838</v>
       </c>
-      <c r="M11" s="45" t="inlineStr">
+      <c r="M12" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,PL,DE,SE</t>
-        </is>
-      </c>
-      <c r="N11" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="21.75" customHeight="1" s="51">
-      <c r="A12" s="36" t="n">
-        <v>46090.30496681713</v>
-      </c>
-      <c r="B12" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="39" t="n">
-        <v>4.2785</v>
-      </c>
-      <c r="E12" s="40" t="n"/>
-      <c r="F12" s="41" t="n">
-        <v>1.792</v>
-      </c>
-      <c r="G12" s="111" t="n"/>
-      <c r="H12" s="112" t="n"/>
-      <c r="I12" s="41" t="n">
-        <v>2.175</v>
-      </c>
-      <c r="J12" s="44" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="K12" s="39" t="n">
-        <v>10.6945</v>
-      </c>
-      <c r="L12" s="40" t="n">
-        <v>1.962691102903361</v>
-      </c>
-      <c r="M12" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX,DE</t>
         </is>
       </c>
       <c r="N12" s="46" t="inlineStr">
@@ -3557,238 +3566,238 @@
     </row>
     <row r="13" ht="21.75" customHeight="1" s="51">
       <c r="A13" s="36" t="n">
+        <v>46090.30496681713</v>
+      </c>
+      <c r="B13" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n">
+        <v>4.2785</v>
+      </c>
+      <c r="E13" s="40" t="n"/>
+      <c r="F13" s="41" t="n">
+        <v>1.792</v>
+      </c>
+      <c r="G13" s="111" t="n"/>
+      <c r="H13" s="112" t="n"/>
+      <c r="I13" s="41" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="J13" s="44" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="K13" s="39" t="n">
+        <v>10.6945</v>
+      </c>
+      <c r="L13" s="40" t="n">
+        <v>1.962691102903361</v>
+      </c>
+      <c r="M13" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE</t>
+        </is>
+      </c>
+      <c r="N13" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21.75" customHeight="1" s="51">
+      <c r="A14" s="36" t="n">
         <v>46087.30496681713</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C13" s="38" t="n">
+      <c r="C14" s="38" t="n">
         <v>6150</v>
       </c>
-      <c r="D13" s="39" t="n">
+      <c r="D14" s="39" t="n">
         <v>4.2875</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E14" s="40" t="n">
         <v>1.434402332361516</v>
       </c>
-      <c r="F13" s="41" t="n">
+      <c r="F14" s="41" t="n">
         <v>1.845</v>
       </c>
-      <c r="G13" s="111">
+      <c r="G14" s="111">
         <f>E10-F10</f>
         <v/>
       </c>
-      <c r="H13" s="112" t="n">
+      <c r="H14" s="112" t="n">
         <v>-0.2225461613216715</v>
       </c>
-      <c r="I13" s="41" t="n">
+      <c r="I14" s="41" t="n">
         <v>2.089</v>
       </c>
-      <c r="J13" s="44" t="n">
+      <c r="J14" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K13" s="39" t="n">
+      <c r="K14" s="39" t="n">
         <v>10.693</v>
       </c>
-      <c r="L13" s="40" t="n">
+      <c r="L14" s="40" t="n">
         <v>1.864771345740204</v>
       </c>
-      <c r="M13" s="45" t="inlineStr">
+      <c r="M14" s="45" t="inlineStr">
         <is>
           <t>Auto: FX,DE</t>
         </is>
       </c>
-      <c r="N13" s="46" t="inlineStr">
+      <c r="N14" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="21.75" customHeight="1" s="51">
-      <c r="A14" s="36" t="n">
+    <row r="15" ht="21.75" customHeight="1" s="51">
+      <c r="A15" s="36" t="n">
         <v>46086.30496681713</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C14" s="38" t="n">
+      <c r="C15" s="38" t="n">
         <v>5760</v>
       </c>
-      <c r="D14" s="39" t="n">
+      <c r="D15" s="39" t="n">
         <v>4.2725</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E15" s="40" t="n">
         <v>1.34815681685196</v>
       </c>
-      <c r="F14" s="41" t="n">
+      <c r="F15" s="41" t="n">
         <v>1.734</v>
       </c>
-      <c r="G14" s="111">
+      <c r="G15" s="111">
         <f>E11-F11</f>
         <v/>
       </c>
-      <c r="H14" s="112" t="n">
+      <c r="H15" s="112" t="n">
         <v>-0.2225162532572317</v>
       </c>
-      <c r="I14" s="41" t="n">
+      <c r="I15" s="41" t="n">
         <v>2.055</v>
       </c>
-      <c r="J14" s="44" t="n">
+      <c r="J15" s="44" t="n">
         <v>19.94</v>
       </c>
-      <c r="K14" s="39" t="n">
+      <c r="K15" s="39" t="n">
         <v>10.6885</v>
       </c>
-      <c r="L14" s="40" t="n">
+      <c r="L15" s="40" t="n">
         <v>1.865556439163587</v>
       </c>
-      <c r="M14" s="45" t="inlineStr">
+      <c r="M15" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N14" s="46" t="inlineStr">
+      <c r="N15" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="21.75" customHeight="1" s="51">
-      <c r="A15" s="36" t="n">
+    <row r="16" ht="21.75" customHeight="1" s="51">
+      <c r="A16" s="36" t="n">
         <v>46085.30496681713</v>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C15" s="38" t="n">
+      <c r="C16" s="38" t="n">
         <v>5681</v>
       </c>
-      <c r="D15" s="39" t="n">
+      <c r="D16" s="39" t="n">
         <v>4.2588</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E16" s="40" t="n">
         <v>1.333943833943834</v>
       </c>
-      <c r="F15" s="41" t="n">
+      <c r="F16" s="41" t="n">
         <v>1.738</v>
       </c>
-      <c r="G15" s="111">
+      <c r="G16" s="111">
         <f>E12-F12</f>
         <v/>
       </c>
-      <c r="H15" s="112" t="n">
+      <c r="H16" s="112" t="n">
         <v>-0.2324834096985995</v>
       </c>
-      <c r="I15" s="41" t="n">
+      <c r="I16" s="41" t="n">
         <v>2.011</v>
       </c>
-      <c r="J15" s="44" t="n">
+      <c r="J16" s="44" t="n">
         <v>18.64</v>
       </c>
-      <c r="K15" s="39" t="n">
+      <c r="K16" s="39" t="n">
         <v>10.6785</v>
       </c>
-      <c r="L15" s="40" t="n">
+      <c r="L16" s="40" t="n">
         <v>1.74556351547502</v>
       </c>
-      <c r="M15" s="45" t="inlineStr">
+      <c r="M16" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N15" s="46" t="inlineStr">
+      <c r="N16" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="21.75" customHeight="1" s="51">
-      <c r="A16" s="36" t="n">
+    <row r="17" ht="21.75" customHeight="1" s="51">
+      <c r="A17" s="36" t="n">
         <v>46084.30496681713</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C16" s="38" t="n">
+      <c r="C17" s="38" t="n">
         <v>5237</v>
       </c>
-      <c r="D16" s="39" t="n">
+      <c r="D17" s="39" t="n">
         <v>4.2865</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E17" s="40" t="n">
         <v>1.221742680508573</v>
       </c>
-      <c r="F16" s="41" t="n">
+      <c r="F17" s="41" t="n">
         <v>1.619</v>
       </c>
-      <c r="G16" s="111">
+      <c r="G17" s="111">
         <f>E13-F13</f>
         <v/>
       </c>
-      <c r="H16" s="112" t="n">
+      <c r="H17" s="112" t="n">
         <v>-0.2453720318044636</v>
       </c>
-      <c r="I16" s="41" t="n">
+      <c r="I17" s="41" t="n">
         <v>1.916</v>
-      </c>
-      <c r="J16" s="44" t="n">
-        <v>17.34</v>
-      </c>
-      <c r="K16" s="39" t="n">
-        <v>10.7265</v>
-      </c>
-      <c r="L16" s="40" t="n">
-        <v>1.61655712487764</v>
-      </c>
-      <c r="M16" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N16" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21.75" customHeight="1" s="51">
-      <c r="A17" s="36" t="n">
-        <v>46083.30496681713</v>
-      </c>
-      <c r="B17" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C17" s="38" t="n"/>
-      <c r="D17" s="39" t="n">
-        <v>4.244</v>
-      </c>
-      <c r="E17" s="40" t="n"/>
-      <c r="F17" s="41" t="n">
-        <v>1.506</v>
-      </c>
-      <c r="G17" s="111" t="n"/>
-      <c r="H17" s="112" t="n"/>
-      <c r="I17" s="41" t="n">
-        <v>1.815</v>
       </c>
       <c r="J17" s="44" t="n">
         <v>17.34</v>
       </c>
       <c r="K17" s="39" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M17" s="45" t="inlineStr">
         <is>
@@ -3803,238 +3812,238 @@
     </row>
     <row r="18" ht="21.75" customHeight="1" s="51">
       <c r="A18" s="36" t="n">
-        <v>46080.30496681713</v>
+        <v>46083.30496681713</v>
       </c>
       <c r="B18" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C18" s="38" t="n">
-        <v>4777</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E18" s="40" t="n">
-        <v>1.130838245389769</v>
-      </c>
+        <v>4.244</v>
+      </c>
+      <c r="E18" s="40" t="n"/>
       <c r="F18" s="41" t="n">
         <v>1.506</v>
       </c>
-      <c r="G18" s="111">
+      <c r="G18" s="111" t="n"/>
+      <c r="H18" s="112" t="n"/>
+      <c r="I18" s="41" t="n">
+        <v>1.815</v>
+      </c>
+      <c r="J18" s="44" t="n">
+        <v>17.34</v>
+      </c>
+      <c r="K18" s="39" t="n">
+        <v>10.708</v>
+      </c>
+      <c r="L18" s="40" t="n">
+        <v>1.619350018677624</v>
+      </c>
+      <c r="M18" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N18" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="21.75" customHeight="1" s="51">
+      <c r="A19" s="36" t="n">
+        <v>46080.30496681713</v>
+      </c>
+      <c r="B19" s="37" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C19" s="38" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D19" s="39" t="n">
+        <v>4.2243</v>
+      </c>
+      <c r="E19" s="40" t="n">
+        <v>1.130838245389769</v>
+      </c>
+      <c r="F19" s="41" t="n">
+        <v>1.506</v>
+      </c>
+      <c r="G19" s="111">
         <f>E15-F15</f>
         <v/>
       </c>
-      <c r="H18" s="112" t="n">
+      <c r="H19" s="112" t="n">
         <v>-0.2491113908434471</v>
       </c>
-      <c r="I18" s="41" t="n">
+      <c r="I19" s="41" t="n">
         <v>1.748</v>
       </c>
-      <c r="J18" s="44" t="n">
+      <c r="J19" s="44" t="n">
         <v>17.19</v>
       </c>
-      <c r="K18" s="39" t="n">
+      <c r="K19" s="39" t="n">
         <v>10.6643</v>
       </c>
-      <c r="L18" s="40" t="n">
+      <c r="L19" s="40" t="n">
         <v>1.611920144782124</v>
       </c>
-      <c r="M18" s="45" t="inlineStr">
+      <c r="M19" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N18" s="46" t="inlineStr">
+      <c r="N19" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="21.75" customHeight="1" s="51">
-      <c r="A19" s="36" t="n">
+    <row r="20" ht="21.75" customHeight="1" s="51">
+      <c r="A20" s="36" t="n">
         <v>46079.30496681713</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B20" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C20" s="38" t="n">
         <v>4744</v>
       </c>
-      <c r="D19" s="39" t="n">
+      <c r="D20" s="39" t="n">
         <v>4.2225</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E20" s="40" t="n">
         <v>1.123505032563647</v>
       </c>
-      <c r="F19" s="41" t="n">
+      <c r="F20" s="41" t="n">
         <v>1.492</v>
       </c>
-      <c r="G19" s="111">
+      <c r="G20" s="111">
         <f>E16-F16</f>
         <v/>
       </c>
-      <c r="H19" s="112" t="n">
+      <c r="H20" s="112" t="n">
         <v>-0.2469805411771802</v>
       </c>
-      <c r="I19" s="41" t="n">
+      <c r="I20" s="41" t="n">
         <v>1.726</v>
       </c>
-      <c r="J19" s="44" t="n">
+      <c r="J20" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K19" s="39" t="n">
+      <c r="K20" s="39" t="n">
         <v>10.673</v>
       </c>
-      <c r="L19" s="40" t="n">
+      <c r="L20" s="40" t="n">
         <v>1.624660357912489</v>
       </c>
-      <c r="M19" s="45" t="inlineStr">
+      <c r="M20" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N19" s="46" t="inlineStr">
+      <c r="N20" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="21.75" customHeight="1" s="51">
-      <c r="A20" s="36" t="n">
+    <row r="21" ht="21.75" customHeight="1" s="51">
+      <c r="A21" s="36" t="n">
         <v>46078.30496681713</v>
       </c>
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B21" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C20" s="38" t="n">
+      <c r="C21" s="38" t="n">
         <v>4765</v>
       </c>
-      <c r="D20" s="39" t="n">
+      <c r="D21" s="39" t="n">
         <v>4.2233</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E21" s="40" t="n">
         <v>1.128264627187271</v>
       </c>
-      <c r="F20" s="41" t="n">
+      <c r="F21" s="41" t="n">
         <v>1.495</v>
       </c>
-      <c r="G20" s="111">
+      <c r="G21" s="111">
         <f>E17-F17</f>
         <v/>
       </c>
-      <c r="H20" s="112" t="n">
+      <c r="H21" s="112" t="n">
         <v>-0.2453079416807554</v>
       </c>
-      <c r="I20" s="41" t="n">
+      <c r="I21" s="41" t="n">
         <v>1.74</v>
       </c>
-      <c r="J20" s="44" t="n">
+      <c r="J21" s="44" t="n">
         <v>17.34</v>
       </c>
-      <c r="K20" s="39" t="n">
+      <c r="K21" s="39" t="n">
         <v>10.6765</v>
       </c>
-      <c r="L20" s="40" t="n">
+      <c r="L21" s="40" t="n">
         <v>1.624127757223809</v>
       </c>
-      <c r="M20" s="45" t="inlineStr">
+      <c r="M21" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N20" s="46" t="inlineStr">
+      <c r="N21" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="21.75" customHeight="1" s="51">
-      <c r="A21" s="36" t="n">
+    <row r="22" ht="21.75" customHeight="1" s="51">
+      <c r="A22" s="36" t="n">
         <v>46077.30496681713</v>
       </c>
-      <c r="B21" s="37" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n">
+      <c r="C22" s="38" t="n">
         <v>4769</v>
       </c>
-      <c r="D21" s="39" t="n">
+      <c r="D22" s="39" t="n">
         <v>4.2203</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E22" s="40" t="n">
         <v>1.130014453948772</v>
       </c>
-      <c r="F21" s="41" t="n">
+      <c r="F22" s="41" t="n">
         <v>1.505</v>
       </c>
-      <c r="G21" s="111">
+      <c r="G22" s="111">
         <f>E18-F18</f>
         <v/>
       </c>
-      <c r="H21" s="112" t="n">
+      <c r="H22" s="112" t="n">
         <v>-0.2491598312632747</v>
       </c>
-      <c r="I21" s="41" t="n">
+      <c r="I22" s="41" t="n">
         <v>1.745</v>
-      </c>
-      <c r="J21" s="44" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="K21" s="39" t="n">
-        <v>10.688</v>
-      </c>
-      <c r="L21" s="40" t="n">
-        <v>1.613023952095808</v>
-      </c>
-      <c r="M21" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N21" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="21.75" customHeight="1" s="51">
-      <c r="A22" s="36" t="n">
-        <v>46076.30496681713</v>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C22" s="38" t="n"/>
-      <c r="D22" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E22" s="40" t="n"/>
-      <c r="F22" s="41" t="n">
-        <v>1.492</v>
-      </c>
-      <c r="G22" s="111" t="n"/>
-      <c r="H22" s="112" t="n"/>
-      <c r="I22" s="41" t="n">
-        <v>1.742</v>
       </c>
       <c r="J22" s="44" t="n">
         <v>17.24</v>
       </c>
       <c r="K22" s="39" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M22" s="45" t="inlineStr">
         <is>
@@ -4049,238 +4058,238 @@
     </row>
     <row r="23" ht="21.75" customHeight="1" s="51">
       <c r="A23" s="36" t="n">
+        <v>46076.30496681713</v>
+      </c>
+      <c r="B23" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="41" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="G23" s="111" t="n"/>
+      <c r="H23" s="112" t="n"/>
+      <c r="I23" s="41" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="J23" s="44" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="K23" s="39" t="n">
+        <v>10.6955</v>
+      </c>
+      <c r="L23" s="40" t="n">
+        <v>1.611892852134075</v>
+      </c>
+      <c r="M23" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N23" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="21.75" customHeight="1" s="51">
+      <c r="A24" s="36" t="n">
         <v>46073.30496681713</v>
       </c>
-      <c r="B23" s="37" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C23" s="38" t="n">
+      <c r="C24" s="38" t="n">
         <v>4743</v>
       </c>
-      <c r="D23" s="39" t="n">
+      <c r="D24" s="39" t="n">
         <v>4.2238</v>
       </c>
-      <c r="E23" s="40" t="n">
+      <c r="E24" s="40" t="n">
         <v>1.122922486860173</v>
       </c>
-      <c r="F23" s="41" t="n">
+      <c r="F24" s="41" t="n">
         <v>1.487</v>
       </c>
-      <c r="G23" s="111">
+      <c r="G24" s="111">
         <f>E20-F20</f>
         <v/>
       </c>
-      <c r="H23" s="112" t="n">
+      <c r="H24" s="112" t="n">
         <v>-0.2448402912843488</v>
       </c>
-      <c r="I23" s="41" t="n">
+      <c r="I24" s="41" t="n">
         <v>1.727</v>
       </c>
-      <c r="J23" s="44" t="n">
+      <c r="J24" s="44" t="n">
         <v>16.89</v>
       </c>
-      <c r="K23" s="39" t="n">
+      <c r="K24" s="39" t="n">
         <v>10.6745</v>
       </c>
-      <c r="L23" s="40" t="n">
+      <c r="L24" s="40" t="n">
         <v>1.582275516417631</v>
       </c>
-      <c r="M23" s="45" t="inlineStr">
+      <c r="M24" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N23" s="46" t="inlineStr">
+      <c r="N24" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="21.75" customHeight="1" s="51">
-      <c r="A24" s="36" t="n">
+    <row r="25" ht="21.75" customHeight="1" s="51">
+      <c r="A25" s="36" t="n">
         <v>46072.30496681713</v>
       </c>
-      <c r="B24" s="37" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C24" s="38" t="n">
+      <c r="C25" s="38" t="n">
         <v>4597</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D25" s="39" t="n">
         <v>4.2215</v>
       </c>
-      <c r="E24" s="40" t="n">
+      <c r="E25" s="40" t="n">
         <v>1.088949425559635</v>
       </c>
-      <c r="F24" s="41" t="n">
+      <c r="F25" s="41" t="n">
         <v>1.46</v>
       </c>
-      <c r="G24" s="111">
+      <c r="G25" s="111">
         <f>E21-F21</f>
         <v/>
       </c>
-      <c r="H24" s="112" t="n">
+      <c r="H25" s="112" t="n">
         <v>-0.254144229068743</v>
       </c>
-      <c r="I24" s="41" t="n">
+      <c r="I25" s="41" t="n">
         <v>1.713</v>
       </c>
-      <c r="J24" s="44" t="n">
+      <c r="J25" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K24" s="39" t="n">
+      <c r="K25" s="39" t="n">
         <v>10.6915</v>
       </c>
-      <c r="L24" s="40" t="n">
+      <c r="L25" s="40" t="n">
         <v>1.556376560819343</v>
       </c>
-      <c r="M24" s="45" t="inlineStr">
+      <c r="M25" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N24" s="46" t="inlineStr">
+      <c r="N25" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="21.75" customHeight="1" s="51">
-      <c r="A25" s="36" t="n">
+    <row r="26" ht="21.75" customHeight="1" s="51">
+      <c r="A26" s="36" t="n">
         <v>46071.30496681713</v>
       </c>
-      <c r="B25" s="37" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C25" s="38" t="n">
+      <c r="C26" s="38" t="n">
         <v>4569</v>
       </c>
-      <c r="D25" s="39" t="n">
+      <c r="D26" s="39" t="n">
         <v>4.2165</v>
       </c>
-      <c r="E25" s="40" t="n">
+      <c r="E26" s="40" t="n">
         <v>1.083600142298115</v>
       </c>
-      <c r="F25" s="41" t="n">
+      <c r="F26" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G25" s="111">
+      <c r="G26" s="111">
         <f>E22-F22</f>
         <v/>
       </c>
-      <c r="H25" s="112" t="n">
+      <c r="H26" s="112" t="n">
         <v>-0.249064350451757</v>
       </c>
-      <c r="I25" s="41" t="n">
+      <c r="I26" s="41" t="n">
         <v>1.697</v>
       </c>
-      <c r="J25" s="44" t="n">
+      <c r="J26" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K25" s="39" t="n">
+      <c r="K26" s="39" t="n">
         <v>10.616</v>
       </c>
-      <c r="L25" s="40" t="n">
+      <c r="L26" s="40" t="n">
         <v>1.567445365486059</v>
       </c>
-      <c r="M25" s="45" t="inlineStr">
+      <c r="M26" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N25" s="46" t="inlineStr">
+      <c r="N26" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="21.75" customHeight="1" s="51">
-      <c r="A26" s="36" t="n">
+    <row r="27" ht="21.75" customHeight="1" s="51">
+      <c r="A27" s="36" t="n">
         <v>46070.30496681713</v>
       </c>
-      <c r="B26" s="37" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C26" s="38" t="n">
+      <c r="C27" s="38" t="n">
         <v>4577</v>
       </c>
-      <c r="D26" s="39" t="n">
+      <c r="D27" s="39" t="n">
         <v>4.2138</v>
       </c>
-      <c r="E26" s="40" t="n">
+      <c r="E27" s="40" t="n">
         <v>1.086192984954198</v>
       </c>
-      <c r="F26" s="41" t="n">
+      <c r="F27" s="41" t="n">
         <v>1.448</v>
       </c>
-      <c r="G26" s="111">
+      <c r="G27" s="111">
         <f>E23-F23</f>
         <v/>
       </c>
-      <c r="H26" s="112" t="n">
+      <c r="H27" s="112" t="n">
         <v>-0.2498667230979294</v>
       </c>
-      <c r="I26" s="41" t="n">
+      <c r="I27" s="41" t="n">
         <v>1.715</v>
-      </c>
-      <c r="J26" s="44" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="K26" s="39" t="n">
-        <v>10.648</v>
-      </c>
-      <c r="L26" s="40" t="n">
-        <v>1.562734785875282</v>
-      </c>
-      <c r="M26" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N26" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="21.75" customHeight="1" s="51">
-      <c r="A27" s="36" t="n">
-        <v>46069.30496681713</v>
-      </c>
-      <c r="B27" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="39" t="n">
-        <v>4.2105</v>
-      </c>
-      <c r="E27" s="40" t="n"/>
-      <c r="F27" s="41" t="n">
-        <v>1.448</v>
-      </c>
-      <c r="G27" s="111" t="n"/>
-      <c r="H27" s="112" t="n"/>
-      <c r="I27" s="41" t="n">
-        <v>1.724</v>
       </c>
       <c r="J27" s="44" t="n">
         <v>16.64</v>
       </c>
       <c r="K27" s="39" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L27" s="40" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M27" s="45" t="inlineStr">
         <is>
@@ -4295,230 +4304,232 @@
     </row>
     <row r="28" ht="21.75" customHeight="1" s="51">
       <c r="A28" s="36" t="n">
+        <v>46069.30496681713</v>
+      </c>
+      <c r="B28" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n">
+        <v>4.2105</v>
+      </c>
+      <c r="E28" s="40" t="n"/>
+      <c r="F28" s="41" t="n">
+        <v>1.448</v>
+      </c>
+      <c r="G28" s="111" t="n"/>
+      <c r="H28" s="112" t="n"/>
+      <c r="I28" s="41" t="n">
+        <v>1.724</v>
+      </c>
+      <c r="J28" s="44" t="n">
+        <v>16.64</v>
+      </c>
+      <c r="K28" s="39" t="n">
+        <v>10.6205</v>
+      </c>
+      <c r="L28" s="40" t="n">
+        <v>1.566781224989407</v>
+      </c>
+      <c r="M28" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N28" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="21.75" customHeight="1" s="51">
+      <c r="A29" s="36" t="n">
         <v>46066.30496681713</v>
       </c>
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B29" s="37" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C28" s="38" t="n">
+      <c r="C29" s="38" t="n">
         <v>4593</v>
       </c>
-      <c r="D28" s="39" t="n">
+      <c r="D29" s="39" t="n">
         <v>4.215</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E29" s="40" t="n">
         <v>1.089679715302491</v>
       </c>
-      <c r="F28" s="41" t="n">
+      <c r="F29" s="41" t="n">
         <v>1.443</v>
       </c>
-      <c r="G28" s="111">
+      <c r="G29" s="111">
         <f>E25-F25</f>
         <v/>
       </c>
-      <c r="H28" s="112" t="n">
+      <c r="H29" s="112" t="n">
         <v>-0.2448512021465759</v>
       </c>
-      <c r="I28" s="41" t="n">
+      <c r="I29" s="41" t="n">
         <v>1.72</v>
       </c>
-      <c r="J28" s="44" t="n">
+      <c r="J29" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K28" s="39" t="n">
+      <c r="K29" s="39" t="n">
         <v>10.6254</v>
       </c>
-      <c r="L28" s="40" t="n">
+      <c r="L29" s="40" t="n">
         <v>1.566058689555217</v>
       </c>
-      <c r="M28" s="45" t="inlineStr">
+      <c r="M29" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N28" s="46" t="inlineStr">
+      <c r="N29" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="21.75" customHeight="1" s="51">
-      <c r="A29" s="36" t="n">
+    <row r="30" ht="21.75" customHeight="1" s="51">
+      <c r="A30" s="36" t="n">
         <v>46065.30496681713</v>
       </c>
-      <c r="B29" s="37" t="inlineStr">
+      <c r="B30" s="37" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C29" s="38" t="n">
+      <c r="C30" s="38" t="n">
         <v>4613</v>
       </c>
-      <c r="D29" s="39" t="n">
+      <c r="D30" s="39" t="n">
         <v>4.2158</v>
       </c>
-      <c r="E29" s="40" t="n">
+      <c r="E30" s="40" t="n">
         <v>1.094216993215997</v>
       </c>
-      <c r="F29" s="41" t="n">
+      <c r="F30" s="41" t="n">
         <v>1.455</v>
       </c>
-      <c r="G29" s="111">
+      <c r="G30" s="111">
         <f>E26-F26</f>
         <v/>
       </c>
-      <c r="H29" s="112" t="n">
+      <c r="H30" s="112" t="n">
         <v>-0.247960829404813</v>
       </c>
-      <c r="I29" s="41" t="n"/>
-      <c r="J29" s="44" t="n">
+      <c r="I30" s="41" t="n"/>
+      <c r="J30" s="44" t="n">
         <v>16.64</v>
       </c>
-      <c r="K29" s="39" t="n">
+      <c r="K30" s="39" t="n">
         <v>10.567</v>
       </c>
-      <c r="L29" s="40" t="n">
+      <c r="L30" s="40" t="n">
         <v>1.574713731428031</v>
       </c>
-      <c r="M29" s="45" t="inlineStr">
+      <c r="M30" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N29" s="46" t="inlineStr">
+      <c r="N30" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="21.75" customHeight="1" s="51">
-      <c r="A30" s="36" t="n">
+    <row r="31" ht="21.75" customHeight="1" s="51">
+      <c r="A31" s="36" t="n">
         <v>46064.30496681713</v>
       </c>
-      <c r="B30" s="37" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="C30" s="38" t="n">
+      <c r="C31" s="38" t="n">
         <v>4609</v>
       </c>
-      <c r="D30" s="39" t="n">
+      <c r="D31" s="39" t="n">
         <v>4.2135</v>
       </c>
-      <c r="E30" s="40" t="n">
+      <c r="E31" s="40" t="n">
         <v>1.093864957873502</v>
       </c>
-      <c r="F30" s="41" t="n">
+      <c r="F31" s="41" t="n">
         <v>1.453</v>
       </c>
-      <c r="G30" s="111">
+      <c r="G31" s="111">
         <f>E27-F27</f>
         <v/>
       </c>
-      <c r="H30" s="112" t="n">
+      <c r="H31" s="112" t="n">
         <v>-0.2471679574167228</v>
       </c>
-      <c r="I30" s="41" t="n"/>
-      <c r="J30" s="44" t="n">
+      <c r="I31" s="41" t="n"/>
+      <c r="J31" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K30" s="39" t="n">
+      <c r="K31" s="39" t="n">
         <v>10.564</v>
       </c>
-      <c r="L30" s="40" t="n">
+      <c r="L31" s="40" t="n">
         <v>1.589360090874669</v>
       </c>
-      <c r="M30" s="45" t="inlineStr">
+      <c r="M31" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N30" s="46" t="inlineStr">
+      <c r="N31" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="21.75" customHeight="1" s="51">
-      <c r="A31" s="36" t="n">
+    <row r="32" ht="21.75" customHeight="1" s="51">
+      <c r="A32" s="36" t="n">
         <v>46063.30496681713</v>
       </c>
-      <c r="B31" s="37" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n">
+      <c r="C32" s="38" t="n">
         <v>4620</v>
       </c>
-      <c r="D31" s="39" t="n">
+      <c r="D32" s="39" t="n">
         <v>4.217</v>
       </c>
-      <c r="E31" s="40" t="n">
+      <c r="E32" s="40" t="n">
         <v>1.095565567939293</v>
       </c>
-      <c r="F31" s="41" t="n">
+      <c r="F32" s="41" t="n">
         <v>1.456</v>
       </c>
-      <c r="G31" s="111">
+      <c r="G32" s="111">
         <f>E28-F28</f>
         <v/>
       </c>
-      <c r="H31" s="112" t="n">
+      <c r="H32" s="112" t="n">
         <v>-0.2475511209208149</v>
       </c>
-      <c r="I31" s="41" t="n"/>
-      <c r="J31" s="44" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="K31" s="39" t="n">
-        <v>10.6135</v>
-      </c>
-      <c r="L31" s="40" t="n">
-        <v>1.59608046356056</v>
-      </c>
-      <c r="M31" s="45" t="inlineStr">
-        <is>
-          <t>Auto: FX</t>
-        </is>
-      </c>
-      <c r="N31" s="46" t="inlineStr">
-        <is>
-          <t>Backfill</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="21.75" customHeight="1" s="51">
-      <c r="A32" s="36" t="n">
-        <v>46062.30496681713</v>
-      </c>
-      <c r="B32" s="37" t="inlineStr">
-        <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n">
-        <v>4.2118</v>
-      </c>
-      <c r="E32" s="40" t="n"/>
-      <c r="F32" s="41" t="n">
-        <v>1.462</v>
-      </c>
-      <c r="G32" s="111" t="n"/>
-      <c r="H32" s="112" t="n"/>
       <c r="I32" s="41" t="n"/>
       <c r="J32" s="44" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K32" s="39" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L32" s="40" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M32" s="45" t="inlineStr">
         <is>
@@ -4533,34 +4544,32 @@
     </row>
     <row r="33" ht="21.75" customHeight="1" s="51">
       <c r="A33" s="36" t="n">
-        <v>46059.30496681713</v>
+        <v>46062.30496681713</v>
       </c>
       <c r="B33" s="37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C33" s="38" t="n">
-        <v>4608</v>
-      </c>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C33" s="38" t="n"/>
       <c r="D33" s="39" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E33" s="40" t="n">
-        <v>1.092331397416143</v>
-      </c>
-      <c r="F33" s="41" t="n"/>
+        <v>4.2118</v>
+      </c>
+      <c r="E33" s="40" t="n"/>
+      <c r="F33" s="41" t="n">
+        <v>1.462</v>
+      </c>
       <c r="G33" s="111" t="n"/>
       <c r="H33" s="112" t="n"/>
       <c r="I33" s="41" t="n"/>
       <c r="J33" s="44" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K33" s="39" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L33" s="40" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M33" s="45" t="inlineStr">
         <is>
@@ -4575,21 +4584,21 @@
     </row>
     <row r="34" ht="21.75" customHeight="1" s="51">
       <c r="A34" s="36" t="n">
-        <v>46058.30496681713</v>
+        <v>46059.30496681713</v>
       </c>
       <c r="B34" s="37" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C34" s="38" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E34" s="40" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="F34" s="41" t="n"/>
       <c r="G34" s="111" t="n"/>
@@ -4599,10 +4608,10 @@
         <v>16.69</v>
       </c>
       <c r="K34" s="39" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L34" s="40" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M34" s="45" t="inlineStr">
         <is>
@@ -4617,21 +4626,21 @@
     </row>
     <row r="35" ht="21.75" customHeight="1" s="51">
       <c r="A35" s="36" t="n">
-        <v>46057.30496681713</v>
+        <v>46058.30496681713</v>
       </c>
       <c r="B35" s="37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C35" s="38" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E35" s="40" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="F35" s="41" t="n"/>
       <c r="G35" s="111" t="n"/>
@@ -4641,10 +4650,10 @@
         <v>16.69</v>
       </c>
       <c r="K35" s="39" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L35" s="40" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M35" s="45" t="inlineStr">
         <is>
@@ -4659,34 +4668,34 @@
     </row>
     <row r="36" ht="21.75" customHeight="1" s="51">
       <c r="A36" s="36" t="n">
-        <v>46056.30496681713</v>
+        <v>46057.30496681713</v>
       </c>
       <c r="B36" s="37" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C36" s="38" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D36" s="39" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E36" s="40" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="F36" s="41" t="n"/>
       <c r="G36" s="111" t="n"/>
       <c r="H36" s="112" t="n"/>
       <c r="I36" s="41" t="n"/>
       <c r="J36" s="44" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K36" s="39" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L36" s="40" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M36" s="45" t="inlineStr">
         <is>
@@ -4701,43 +4710,84 @@
     </row>
     <row r="37" ht="21.75" customHeight="1" s="51">
       <c r="A37" s="36" t="n">
-        <v>46055.30496681713</v>
+        <v>46056.30496681713</v>
       </c>
       <c r="B37" s="37" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
-      </c>
-      <c r="C37" s="38" t="n"/>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C37" s="38" t="n">
+        <v>4622</v>
+      </c>
       <c r="D37" s="39" t="n">
-        <v>4.2173</v>
-      </c>
-      <c r="E37" s="40" t="n"/>
+        <v>4.2205</v>
+      </c>
+      <c r="E37" s="40" t="n">
+        <v>1.095130908660111</v>
+      </c>
       <c r="F37" s="41" t="n"/>
       <c r="G37" s="111" t="n"/>
       <c r="H37" s="112" t="n"/>
       <c r="I37" s="41" t="n"/>
       <c r="J37" s="44" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K37" s="39" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L37" s="40" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M37" s="45" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+      <c r="N37" s="46" t="inlineStr">
+        <is>
+          <t>Backfill</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="21.75" customHeight="1" s="51">
+      <c r="A38" s="36" t="n">
+        <v>46055.30496681713</v>
+      </c>
+      <c r="B38" s="37" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="E38" s="40" t="n"/>
+      <c r="F38" s="41" t="n"/>
+      <c r="G38" s="111" t="n"/>
+      <c r="H38" s="112" t="n"/>
+      <c r="I38" s="41" t="n"/>
+      <c r="J38" s="44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K37" s="39" t="n">
+      <c r="K38" s="39" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L37" s="40" t="n">
+      <c r="L38" s="40" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M37" s="45" t="inlineStr">
+      <c r="M38" s="45" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
       </c>
-      <c r="N37" s="46" t="inlineStr">
+      <c r="N38" s="46" t="inlineStr">
         <is>
           <t>Backfill</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="21.75" customHeight="1" s="51"/>
     <row r="39" ht="21.75" customHeight="1" s="51"/>
     <row r="40" ht="21.75" customHeight="1" s="51"/>
     <row r="41" ht="21.75" customHeight="1" s="51"/>
@@ -4914,7 +4964,7 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46097.57810183834</v>
+        <v>46097.31114975031</v>
       </c>
       <c r="B4" s="114" t="n">
         <v>1.901</v>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -19,7 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -28,7 +28,6 @@
     <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="40">
     <font>
@@ -3185,7 +3184,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46100.31114975031</v>
+        <v>46100.32378609398</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
@@ -3211,7 +3210,7 @@
         <v>-0.1643</v>
       </c>
       <c r="I5" s="105" t="n">
-        <v>2.163</v>
+        <v>2.085</v>
       </c>
       <c r="J5" s="108" t="n">
         <v>22.29</v>
@@ -3224,7 +3223,7 @@
       </c>
       <c r="M5" s="109" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N5" s="110" t="inlineStr">
@@ -4964,31 +4963,31 @@
     </row>
     <row r="4" ht="21.75" customHeight="1" s="51">
       <c r="A4" s="113" t="n">
-        <v>46097.31114975031</v>
+        <v>46097</v>
       </c>
       <c r="B4" s="114" t="n">
-        <v>1.901</v>
+        <v>1.6354</v>
       </c>
       <c r="C4" s="114" t="n">
-        <v>1.793</v>
+        <v>1.6774</v>
       </c>
       <c r="D4" s="114" t="n">
-        <v>1.688</v>
+        <v>1.654</v>
       </c>
       <c r="E4" s="114" t="n">
-        <v>2.115</v>
+        <v>2.1788</v>
       </c>
       <c r="F4" s="114" t="n">
-        <v>1.783</v>
+        <v>1.6545</v>
       </c>
       <c r="G4" s="114" t="n">
-        <v>2.042</v>
+        <v>1.9588</v>
       </c>
       <c r="H4" s="114" t="n">
-        <v>1.748</v>
+        <v>1.8934</v>
       </c>
       <c r="I4" s="115" t="n">
-        <v>0.08749999999999999</v>
+        <v>-0.1363</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -3184,7 +3184,7 @@
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">
       <c r="A5" s="100" t="n">
-        <v>46100.32378609398</v>
+        <v>46100.33126723118</v>
       </c>
       <c r="B5" s="101" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>-0.1643</v>
       </c>
       <c r="I5" s="105" t="n">
-        <v>2.085</v>
+        <v>2.146</v>
       </c>
       <c r="J5" s="108" t="n">
         <v>22.29</v>
@@ -4966,28 +4966,28 @@
         <v>46097</v>
       </c>
       <c r="B4" s="114" t="n">
-        <v>1.6354</v>
+        <v>1.9517</v>
       </c>
       <c r="C4" s="114" t="n">
-        <v>1.6774</v>
+        <v>1.919</v>
       </c>
       <c r="D4" s="114" t="n">
-        <v>1.654</v>
+        <v>1.775</v>
       </c>
       <c r="E4" s="114" t="n">
-        <v>2.1788</v>
+        <v>2.2082</v>
       </c>
       <c r="F4" s="114" t="n">
-        <v>1.6545</v>
+        <v>1.9884</v>
       </c>
       <c r="G4" s="114" t="n">
-        <v>1.9588</v>
+        <v>2.1082</v>
       </c>
       <c r="H4" s="114" t="n">
-        <v>1.8934</v>
+        <v>1.9828</v>
       </c>
       <c r="I4" s="115" t="n">
-        <v>-0.1363</v>
+        <v>-0.0157</v>
       </c>
     </row>
     <row r="5" ht="21.75" customHeight="1" s="51">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -1,67 +1,74 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Daily Tracker" sheetId="1" r:id="rId1"/>
-    <sheet name="Weekly Oil Bulletin" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weekly Oil Bulletin" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="9">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="\+0.000;\-0.000;&quot;-&quot;"/>
-    <numFmt numFmtId="168" formatCode="\+0.0%;\-0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="170" formatCode="+0.000;-0.000;&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="+0.000;-0.000;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="6">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="009CA3AF"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -69,18 +76,135 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -405,1664 +529,1836 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>⛽  Daily Fuel Prices</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>⛽  Daily Fuel Prices</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>🔵 Blue = input  ·  Row 5 = newest</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>🔵 Blue = input  ·  Row 5 = newest</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v>ORLEN PL — EKODIESEL</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>ORLEN LT</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Δ PL vs LT</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>ELVIS DE</v>
-      </c>
-      <c r="J3" t="str">
-        <v>BSH / ST1 SE</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ORLEN PL — EKODIESEL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ORLEN LT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Δ PL vs LT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ELVIS DE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>BSH / ST1 SE</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Day</v>
-      </c>
-      <c r="C4" t="str">
-        <v>PLN/m³</v>
-      </c>
-      <c r="D4" t="str">
-        <v>PLN/EUR</v>
-      </c>
-      <c r="E4" t="str">
-        <v>EUR/l</v>
-      </c>
-      <c r="F4" t="str">
-        <v>EUR/l</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Δ EUR/l</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Δ %</v>
-      </c>
-      <c r="I4" t="str">
-        <v>EUR/l</v>
-      </c>
-      <c r="J4" t="str">
-        <v>SEK/l</v>
-      </c>
-      <c r="K4" t="str">
-        <v>SEK/EUR</v>
-      </c>
-      <c r="L4" t="str">
-        <v>EUR/l</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Notes</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Freq</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PLN/m³</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PLN/EUR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EUR/l</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EUR/l</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Δ EUR/l</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Δ %</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>EUR/l</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>SEK/l</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SEK/EUR</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>EUR/l</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Freq</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C5">
+      <c r="A5" s="1" t="n">
+        <v>46100.38145226741</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>6620</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="4" t="n">
         <v>4.2713</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="5" t="n">
         <v>1.5499</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="6" t="n">
         <v>1.8547</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="7" t="n">
         <v>-0.3048</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="8" t="n">
         <v>-0.1643</v>
       </c>
-      <c r="I5">
-        <v>2.085</v>
-      </c>
-      <c r="J5">
+      <c r="I5" s="6" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J5" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="4" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="5" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M5" t="str">
-        <v>Auto: FX,PL,LT,DE,SE,EU</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>2026-03-18</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>6565</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>4.2593</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1.5413</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>1.864</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>-0.3227</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>-0.1731</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>2.163</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>22.44</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>10.7055</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>2.0961</v>
       </c>
-      <c r="M6" t="str">
-        <v>Auto: FX,PL,LT,DE,SE</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>2026-03-17</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6577</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>4.2683</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>1.5409</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>1.8374</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>-0.2965</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>-0.1614</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>10.769</v>
       </c>
-      <c r="M7" t="str">
-        <v>Auto: FX,PL,LT</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>2026-03-16</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="C8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>6495</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>4.2675</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>1.522</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>1.818</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>-0.296</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>-0.1628</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>2.163</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>21.84</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>10.7545</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>2.0308</v>
       </c>
-      <c r="M8" t="str">
-        <v>Auto: FX,PL,LT</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>2026-03-13</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Fri</v>
-      </c>
-      <c r="C9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>6399</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>1.5029</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>1.7561</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>-0.2532</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>-0.1442</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>2.163</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>21.04</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>1.9644</v>
       </c>
-      <c r="M9" t="str">
-        <v>Auto: FX,PL,LT,DE,SE</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>2026-03-12</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>6192</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>1.5029</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>20.49</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>1.9644</v>
       </c>
-      <c r="M10" t="str">
-        <v>Auto: FX,PL,DE,SE</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>2026-03-11</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>6195</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>4.2523</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>1.5048</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>2.137</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>21.59</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>10.6543</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>1.9748</v>
       </c>
-      <c r="M11" t="str">
-        <v>Auto: FX,PL,DE,SE</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>2026-03-10</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>6359</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>4.2548</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>1.494547334774843</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>1.808</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>-0.1733698369608172</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>2.198</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>21.59</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>10.606</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>1.9838</v>
       </c>
-      <c r="M12" t="str">
-        <v>Auto: FX,PL,DE,SE</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="D13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>4.2785</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>1.792</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>2.175</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>20.99</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>10.6945</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>1.962691102903361</v>
       </c>
-      <c r="M13" t="str">
-        <v>Auto: FX,DE</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>2026-03-06</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Fri</v>
-      </c>
-      <c r="C14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>6150</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>4.2875</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>1.434402332361516</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>1.845</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>-0.2225461613216715</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>2.089</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>19.94</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>10.693</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>1.864771345740204</v>
       </c>
-      <c r="M14" t="str">
-        <v>Auto: FX,DE</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Auto: FX,DE</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>2026-03-05</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>5760</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>4.2725</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>1.34815681685196</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>1.734</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>-0.2225162532572317</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>2.055</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>19.94</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>10.6885</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>1.865556439163587</v>
       </c>
-      <c r="M15" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>2026-03-04</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>5681</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>4.2588</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>1.333943833943834</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>1.738</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>-0.2324834096985995</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>2.011</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>18.64</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>10.6785</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>1.74556351547502</v>
       </c>
-      <c r="M16" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>2026-03-03</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>5237</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>4.2865</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>1.221742680508573</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>1.619</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>-0.2453720318044636</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>1.916</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>17.34</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>10.7265</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>1.61655712487764</v>
       </c>
-      <c r="M17" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="D18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>4.244</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>1.506</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>1.815</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>17.34</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>10.708</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>1.619350018677624</v>
       </c>
-      <c r="M18" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N18" t="str">
-        <v/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="str">
-        <v>2026-02-27</v>
-      </c>
-      <c r="B19" t="str">
-        <v>Fri</v>
-      </c>
-      <c r="C19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>4777</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>4.2243</v>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>1.130838245389769</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="n">
         <v>1.506</v>
       </c>
-      <c r="H19">
+      <c r="H19" t="n">
         <v>-0.2491113908434471</v>
       </c>
-      <c r="I19">
+      <c r="I19" t="n">
         <v>1.748</v>
       </c>
-      <c r="J19">
+      <c r="J19" t="n">
         <v>17.19</v>
       </c>
-      <c r="K19">
+      <c r="K19" t="n">
         <v>10.6643</v>
       </c>
-      <c r="L19">
+      <c r="L19" t="n">
         <v>1.611920144782124</v>
       </c>
-      <c r="M19" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N19" t="str">
-        <v/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="str">
-        <v>2026-02-26</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>4744</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>4.2225</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>1.123505032563647</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>1.492</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>-0.2469805411771802</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>1.726</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>17.34</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>10.673</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>1.624660357912489</v>
       </c>
-      <c r="M20" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N20" t="str">
-        <v/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v>2026-02-25</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>4765</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>4.2233</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>1.128264627187271</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>1.495</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>-0.2453079416807554</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>1.74</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>17.34</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>10.6765</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>1.624127757223809</v>
       </c>
-      <c r="M21" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N21" t="str">
-        <v/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v>2026-02-24</v>
-      </c>
-      <c r="B22" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>4769</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>4.2203</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>1.130014453948772</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>1.505</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>-0.2491598312632747</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>1.745</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>17.24</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>10.688</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>1.613023952095808</v>
       </c>
-      <c r="M22" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N22" t="str">
-        <v/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="B23" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="D23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>4.2173</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>1.492</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>1.742</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>17.24</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>10.6955</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>1.611892852134075</v>
       </c>
-      <c r="M23" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N23" t="str">
-        <v/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="str">
-        <v>2026-02-20</v>
-      </c>
-      <c r="B24" t="str">
-        <v>Fri</v>
-      </c>
-      <c r="C24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>4743</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>4.2238</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>1.122922486860173</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>1.487</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>-0.2448402912843488</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>1.727</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>16.89</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>10.6745</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>1.582275516417631</v>
       </c>
-      <c r="M24" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N24" t="str">
-        <v/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="str">
-        <v>2026-02-19</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>4597</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>4.2215</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>1.088949425559635</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>1.46</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>-0.254144229068743</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>1.713</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>16.64</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>10.6915</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>1.556376560819343</v>
       </c>
-      <c r="M25" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N25" t="str">
-        <v/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="B26" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>4569</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>4.2165</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>1.083600142298115</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>1.443</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>-0.249064350451757</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>1.697</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>16.64</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>10.616</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>1.567445365486059</v>
       </c>
-      <c r="M26" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N26" t="str">
-        <v/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="str">
-        <v>2026-02-17</v>
-      </c>
-      <c r="B27" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>4577</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>4.2138</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>1.086192984954198</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>1.448</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>-0.2498667230979294</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>1.715</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>16.64</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>10.648</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>1.562734785875282</v>
       </c>
-      <c r="M27" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N27" t="str">
-        <v/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="str">
-        <v>2026-02-16</v>
-      </c>
-      <c r="B28" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="D28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>4.2105</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>1.448</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>1.724</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>16.64</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>10.6205</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>1.566781224989407</v>
       </c>
-      <c r="M28" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N28" t="str">
-        <v/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="str">
-        <v>2026-02-13</v>
-      </c>
-      <c r="B29" t="str">
-        <v>Fri</v>
-      </c>
-      <c r="C29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>4593</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>4.215</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>1.089679715302491</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>1.443</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>-0.2448512021465759</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>1.72</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>16.64</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>10.6254</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>1.566058689555217</v>
       </c>
-      <c r="M29" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N29" t="str">
-        <v/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="str">
-        <v>2026-02-12</v>
-      </c>
-      <c r="B30" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>4613</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>4.2158</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>1.094216993215997</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>1.455</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>-0.247960829404813</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>16.64</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>10.567</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>1.574713731428031</v>
       </c>
-      <c r="M30" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N30" t="str">
-        <v/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="str">
-        <v>2026-02-11</v>
-      </c>
-      <c r="B31" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>4609</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>4.2135</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>1.093864957873502</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>1.453</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>-0.2471679574167228</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>16.79</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>10.564</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>1.589360090874669</v>
       </c>
-      <c r="M31" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N31" t="str">
-        <v/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="B32" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>4620</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>4.217</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>1.095565567939293</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>1.456</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>-0.2475511209208149</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>16.94</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>10.6135</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>1.59608046356056</v>
       </c>
-      <c r="M32" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N32" t="str">
-        <v/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="D33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>4.2118</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>1.462</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>16.79</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>10.6505</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>1.576451809774189</v>
       </c>
-      <c r="M33" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N33" t="str">
-        <v/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="str">
-        <v>2026-02-06</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Fri</v>
-      </c>
-      <c r="C34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
         <v>4608</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>4.2185</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>1.092331397416143</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>16.69</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>10.6735</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>1.563685763807561</v>
       </c>
-      <c r="M34" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N34" t="str">
-        <v/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="str">
-        <v>2026-02-05</v>
-      </c>
-      <c r="B35" t="str">
-        <v>Thu</v>
-      </c>
-      <c r="C35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
         <v>4606</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>4.2205</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>1.091339888638787</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>16.69</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>10.641</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>1.568461610750869</v>
       </c>
-      <c r="M35" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N35" t="str">
-        <v/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="str">
-        <v>2026-02-04</v>
-      </c>
-      <c r="B36" t="str">
-        <v>Wed</v>
-      </c>
-      <c r="C36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
         <v>4631</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>4.2235</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>1.096483958801941</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>16.69</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>10.577</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>1.577952160347925</v>
       </c>
-      <c r="M36" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N36" t="str">
-        <v/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="B37" t="str">
-        <v>Tue</v>
-      </c>
-      <c r="C37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
         <v>4622</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>4.2205</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>1.095130908660111</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>16.99</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>10.5485</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>1.610655543442195</v>
       </c>
-      <c r="M37" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N37" t="str">
-        <v/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="str">
-        <v>2026-02-02</v>
-      </c>
-      <c r="B38" t="str">
-        <v>Mon</v>
-      </c>
-      <c r="D38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>4.2173</v>
       </c>
-      <c r="J38">
+      <c r="J38" t="n">
         <v>16.79</v>
       </c>
-      <c r="K38">
+      <c r="K38" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L38">
+      <c r="L38" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M38" t="str">
-        <v>Auto: FX</v>
-      </c>
-      <c r="N38" t="str">
-        <v/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N38"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>📊  EU Weekly Oil Bulletin — Diesel Prices with Taxes</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>📊  EU Weekly Oil Bulletin — Diesel Prices with Taxes</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Source: energy.ec.europa.eu</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Source: energy.ec.europa.eu</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Week Start</v>
-      </c>
-      <c r="B3" t="str">
-        <v>🇱🇹 LT</v>
-      </c>
-      <c r="C3" t="str">
-        <v>🇱🇻 LV</v>
-      </c>
-      <c r="D3" t="str">
-        <v>🇪🇪 EE</v>
-      </c>
-      <c r="E3" t="str">
-        <v>🇩🇰 DK</v>
-      </c>
-      <c r="F3" t="str">
-        <v>🇸🇪 SE</v>
-      </c>
-      <c r="G3" t="str">
-        <v>🇫🇮 FI</v>
-      </c>
-      <c r="H3" t="str">
-        <v>🇪🇺 EU Avg</v>
-      </c>
-      <c r="I3" t="str">
-        <v>LT vs EU Δ</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Notes</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week Start</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>🇱🇹 LT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🇱🇻 LV</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>🇪🇪 EE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🇩🇰 DK</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🇸🇪 SE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>🇫🇮 FI</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>🇪🇺 EU Avg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>LT vs EU Δ</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>2026-03-19</v>
-      </c>
-      <c r="B4">
+      <c r="A4" s="12" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>1.9517</v>
+      </c>
+      <c r="C4" s="13" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="D4" s="13" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="E4" s="13" t="n">
+        <v>2.2082</v>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>1.9884</v>
+      </c>
+      <c r="G4" s="13" t="n">
+        <v>2.1082</v>
+      </c>
+      <c r="H4" s="13" t="n">
+        <v>1.9828</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>-0.0157</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>1.952</v>
       </c>
-      <c r="C4">
+      <c r="C5" t="n">
         <v>1.919</v>
       </c>
-      <c r="D4">
+      <c r="D5" t="n">
         <v>1.775</v>
       </c>
-      <c r="E4">
+      <c r="E5" t="n">
         <v>2.208</v>
       </c>
-      <c r="F4">
+      <c r="F5" t="n">
         <v>1.988</v>
       </c>
-      <c r="G4">
+      <c r="G5" t="n">
         <v>2.108</v>
       </c>
-      <c r="H4">
+      <c r="H5" t="n">
         <v>1.95</v>
       </c>
-      <c r="I4">
-        <v>0.0010256410256410265</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2026-03-09</v>
-      </c>
-      <c r="B5">
+      <c r="I5" t="n">
+        <v>0.001025641025641027</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>1.901</v>
       </c>
-      <c r="C5">
+      <c r="C6" t="n">
         <v>1.793</v>
       </c>
-      <c r="D5">
+      <c r="D6" t="n">
         <v>1.688</v>
       </c>
-      <c r="E5">
+      <c r="E6" t="n">
         <v>2.115</v>
       </c>
-      <c r="F5">
+      <c r="F6" t="n">
         <v>1.783</v>
       </c>
-      <c r="G5">
+      <c r="G6" t="n">
         <v>2.042</v>
       </c>
-      <c r="H5">
+      <c r="H6" t="n">
         <v>1.748</v>
       </c>
-      <c r="I5">
+      <c r="I6" t="n">
         <v>0.08752860411899314</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2026-03-01</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1.641</v>
       </c>
-      <c r="C6">
+      <c r="C7" t="n">
         <v>1.548</v>
       </c>
-      <c r="D6">
+      <c r="D7" t="n">
         <v>1.428</v>
       </c>
-      <c r="E6">
+      <c r="E7" t="n">
         <v>1.794</v>
       </c>
-      <c r="F6">
+      <c r="F7" t="n">
         <v>1.579</v>
       </c>
-      <c r="G6">
+      <c r="G7" t="n">
         <v>1.951</v>
       </c>
-      <c r="H6">
+      <c r="H7" t="n">
         <v>1.572</v>
       </c>
-      <c r="I6">
-        <v>0.043893129770992335</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="B7">
+      <c r="I7" t="n">
+        <v>0.04389312977099234</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>1.637</v>
       </c>
-      <c r="C7">
+      <c r="C8" t="n">
         <v>1.544</v>
       </c>
-      <c r="D7">
+      <c r="D8" t="n">
         <v>1.423</v>
       </c>
-      <c r="E7">
+      <c r="E8" t="n">
         <v>1.79</v>
       </c>
-      <c r="F7">
+      <c r="F8" t="n">
         <v>1.575</v>
       </c>
-      <c r="G7">
+      <c r="G8" t="n">
         <v>1.945</v>
       </c>
-      <c r="H7">
+      <c r="H8" t="n">
         <v>1.568</v>
       </c>
-      <c r="I7">
+      <c r="I8" t="n">
         <v>0.04400510204081629</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2026-02-15</v>
-      </c>
-      <c r="B8">
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>1.632</v>
       </c>
-      <c r="C8">
+      <c r="C9" t="n">
         <v>1.538</v>
       </c>
-      <c r="D8">
+      <c r="D9" t="n">
         <v>1.417</v>
       </c>
-      <c r="E8">
+      <c r="E9" t="n">
         <v>1.786</v>
       </c>
-      <c r="F8">
+      <c r="F9" t="n">
         <v>1.571</v>
       </c>
-      <c r="G8">
+      <c r="G9" t="n">
         <v>1.939</v>
       </c>
-      <c r="H8">
+      <c r="H9" t="n">
         <v>1.564</v>
       </c>
-      <c r="I8">
+      <c r="I9" t="n">
         <v>0.04347826086956511</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="B9">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>1.625</v>
       </c>
-      <c r="C9">
+      <c r="C10" t="n">
         <v>1.532</v>
       </c>
-      <c r="D9">
+      <c r="D10" t="n">
         <v>1.41</v>
       </c>
-      <c r="E9">
+      <c r="E10" t="n">
         <v>1.78</v>
       </c>
-      <c r="F9">
+      <c r="F10" t="n">
         <v>1.568</v>
       </c>
-      <c r="G9">
+      <c r="G10" t="n">
         <v>1.932</v>
       </c>
-      <c r="H9">
+      <c r="H10" t="n">
         <v>1.558</v>
       </c>
-      <c r="I9">
+      <c r="I10" t="n">
         <v>0.04300385109114246</v>
       </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2026-02-01</v>
-      </c>
-      <c r="B10">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>1.618</v>
       </c>
-      <c r="C10">
+      <c r="C11" t="n">
         <v>1.525</v>
       </c>
-      <c r="D10">
+      <c r="D11" t="n">
         <v>1.402</v>
       </c>
-      <c r="E10">
+      <c r="E11" t="n">
         <v>1.772</v>
       </c>
-      <c r="F10">
+      <c r="F11" t="n">
         <v>1.562</v>
       </c>
-      <c r="G10">
+      <c r="G11" t="n">
         <v>1.925</v>
       </c>
-      <c r="H10">
+      <c r="H11" t="n">
         <v>1.553</v>
       </c>
-      <c r="I10">
+      <c r="I11" t="n">
         <v>0.04185447520927248</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J10"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -13,12 +13,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="+0.000;-0.000;&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="+0.000;-0.000;&quot;-&quot;"/>
+    <numFmt numFmtId="168" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -94,9 +94,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,19 +105,19 @@
     <xf numFmtId="4" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -129,9 +129,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -534,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -651,180 +672,183 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46100.38145226741</v>
+      <c r="A5" s="15" t="n">
+        <v>46101.37924015422</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>6737</v>
+      </c>
+      <c r="D5" s="16" t="n">
+        <v>4.2853</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>1.5721</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>1.949</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>-0.3769</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>-0.1934</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="3" t="n">
         <v>6620</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="16" t="n">
         <v>4.2713</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E6" s="17" t="n">
         <v>1.5499</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F6" s="18" t="n">
         <v>1.8547</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G6" s="19" t="n">
         <v>-0.3048</v>
       </c>
-      <c r="H5" s="8" t="n">
+      <c r="H6" s="20" t="n">
         <v>-0.1643</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I6" s="18" t="n">
         <v>2.146</v>
       </c>
-      <c r="J5" s="9" t="n">
+      <c r="J6" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K6" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L6" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J6" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K6" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1614</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.44</v>
       </c>
       <c r="K7" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E8" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F8" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J8" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
       </c>
       <c r="K8" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -835,63 +859,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D9" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I9" t="n">
         <v>2.163</v>
       </c>
       <c r="J9" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K9" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D10" t="n">
         <v>4.2578</v>
@@ -899,8 +923,20 @@
       <c r="E10" t="n">
         <v>1.5029</v>
       </c>
+      <c r="F10" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.163</v>
+      </c>
       <c r="J10" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K10" t="n">
         <v>10.7108</v>
@@ -910,41 +946,38 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5048</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.137</v>
+        <v>1.5029</v>
       </c>
       <c r="J11" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K11" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -955,40 +988,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E12" t="n">
-        <v>1.494547334774843</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-0.1733698369608172</v>
+        <v>1.5048</v>
       </c>
       <c r="I12" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J12" t="n">
         <v>21.59</v>
       </c>
       <c r="K12" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9838</v>
+        <v>1.9748</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -999,75 +1026,75 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6359</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.494547334774843</v>
       </c>
       <c r="F13" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1733698369608172</v>
       </c>
       <c r="I13" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J13" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K13" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L13" t="n">
-        <v>1.962691102903361</v>
+        <v>1.9838</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Auto: FX,DE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1.434402332361516</v>
+        <v>4.2785</v>
       </c>
       <c r="F14" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.2225461613216715</v>
+        <v>1.792</v>
       </c>
       <c r="I14" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J14" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K14" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L14" t="n">
-        <v>1.864771345740204</v>
+        <v>1.962691102903361</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1078,84 +1105,84 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E15" t="n">
-        <v>1.34815681685196</v>
+        <v>1.434402332361516</v>
       </c>
       <c r="F15" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2225162532572317</v>
+        <v>-0.2225461613216715</v>
       </c>
       <c r="I15" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J15" t="n">
         <v>19.94</v>
       </c>
       <c r="K15" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L15" t="n">
-        <v>1.865556439163587</v>
+        <v>1.864771345740204</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,DE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E16" t="n">
-        <v>1.333943833943834</v>
+        <v>1.34815681685196</v>
       </c>
       <c r="F16" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2324834096985995</v>
+        <v>-0.2225162532572317</v>
       </c>
       <c r="I16" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J16" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K16" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L16" t="n">
-        <v>1.74556351547502</v>
+        <v>1.865556439163587</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1166,40 +1193,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E17" t="n">
-        <v>1.221742680508573</v>
+        <v>1.333943833943834</v>
       </c>
       <c r="F17" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2453720318044636</v>
+        <v>-0.2324834096985995</v>
       </c>
       <c r="I17" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J17" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K17" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L17" t="n">
-        <v>1.61655712487764</v>
+        <v>1.74556351547502</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1210,31 +1237,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5237</v>
       </c>
       <c r="D18" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.221742680508573</v>
       </c>
       <c r="F18" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.2453720318044636</v>
       </c>
       <c r="I18" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J18" t="n">
         <v>17.34</v>
       </c>
       <c r="K18" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L18" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1245,40 +1281,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.130838245389769</v>
+        <v>4.244</v>
       </c>
       <c r="F19" t="n">
         <v>1.506</v>
       </c>
-      <c r="H19" t="n">
-        <v>-0.2491113908434471</v>
-      </c>
       <c r="I19" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J19" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K19" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L19" t="n">
-        <v>1.611920144782124</v>
+        <v>1.619350018677624</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1289,40 +1316,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E20" t="n">
-        <v>1.123505032563647</v>
+        <v>1.130838245389769</v>
       </c>
       <c r="F20" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2469805411771802</v>
+        <v>-0.2491113908434471</v>
       </c>
       <c r="I20" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J20" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K20" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L20" t="n">
-        <v>1.624660357912489</v>
+        <v>1.611920144782124</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1333,40 +1360,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E21" t="n">
-        <v>1.128264627187271</v>
+        <v>1.123505032563647</v>
       </c>
       <c r="F21" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2453079416807554</v>
+        <v>-0.2469805411771802</v>
       </c>
       <c r="I21" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J21" t="n">
         <v>17.34</v>
       </c>
       <c r="K21" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L21" t="n">
-        <v>1.624127757223809</v>
+        <v>1.624660357912489</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1377,40 +1404,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E22" t="n">
-        <v>1.130014453948772</v>
+        <v>1.128264627187271</v>
       </c>
       <c r="F22" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2491598312632747</v>
+        <v>-0.2453079416807554</v>
       </c>
       <c r="I22" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J22" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K22" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L22" t="n">
-        <v>1.613023952095808</v>
+        <v>1.624127757223809</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1421,31 +1448,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4769</v>
       </c>
       <c r="D23" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.130014453948772</v>
       </c>
       <c r="F23" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.2491598312632747</v>
       </c>
       <c r="I23" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J23" t="n">
         <v>17.24</v>
       </c>
       <c r="K23" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L23" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1456,40 +1492,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1.122922486860173</v>
+        <v>4.2173</v>
       </c>
       <c r="F24" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-0.2448402912843488</v>
+        <v>1.492</v>
       </c>
       <c r="I24" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J24" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K24" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L24" t="n">
-        <v>1.582275516417631</v>
+        <v>1.611892852134075</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1500,40 +1527,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E25" t="n">
-        <v>1.088949425559635</v>
+        <v>1.122922486860173</v>
       </c>
       <c r="F25" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.254144229068743</v>
+        <v>-0.2448402912843488</v>
       </c>
       <c r="I25" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J25" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K25" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L25" t="n">
-        <v>1.556376560819343</v>
+        <v>1.582275516417631</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1544,40 +1571,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E26" t="n">
-        <v>1.083600142298115</v>
+        <v>1.088949425559635</v>
       </c>
       <c r="F26" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.249064350451757</v>
+        <v>-0.254144229068743</v>
       </c>
       <c r="I26" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J26" t="n">
         <v>16.64</v>
       </c>
       <c r="K26" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L26" t="n">
-        <v>1.567445365486059</v>
+        <v>1.556376560819343</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1588,40 +1615,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E27" t="n">
-        <v>1.086192984954198</v>
+        <v>1.083600142298115</v>
       </c>
       <c r="F27" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2498667230979294</v>
+        <v>-0.249064350451757</v>
       </c>
       <c r="I27" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J27" t="n">
         <v>16.64</v>
       </c>
       <c r="K27" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L27" t="n">
-        <v>1.562734785875282</v>
+        <v>1.567445365486059</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1632,31 +1659,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4577</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.086192984954198</v>
       </c>
       <c r="F28" t="n">
         <v>1.448</v>
       </c>
+      <c r="H28" t="n">
+        <v>-0.2498667230979294</v>
+      </c>
       <c r="I28" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J28" t="n">
         <v>16.64</v>
       </c>
       <c r="K28" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L28" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1667,40 +1703,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.089679715302491</v>
+        <v>4.2105</v>
       </c>
       <c r="F29" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.2448512021465759</v>
+        <v>1.448</v>
       </c>
       <c r="I29" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J29" t="n">
         <v>16.64</v>
       </c>
       <c r="K29" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L29" t="n">
-        <v>1.566058689555217</v>
+        <v>1.566781224989407</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1711,37 +1738,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E30" t="n">
-        <v>1.094216993215997</v>
+        <v>1.089679715302491</v>
       </c>
       <c r="F30" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.247960829404813</v>
+        <v>-0.2448512021465759</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.72</v>
       </c>
       <c r="J30" t="n">
         <v>16.64</v>
       </c>
       <c r="K30" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L30" t="n">
-        <v>1.574713731428031</v>
+        <v>1.566058689555217</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1752,37 +1782,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E31" t="n">
-        <v>1.093864957873502</v>
+        <v>1.094216993215997</v>
       </c>
       <c r="F31" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2471679574167228</v>
+        <v>-0.247960829404813</v>
       </c>
       <c r="J31" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K31" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L31" t="n">
-        <v>1.589360090874669</v>
+        <v>1.574713731428031</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1793,37 +1823,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D32" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E32" t="n">
-        <v>1.095565567939293</v>
+        <v>1.093864957873502</v>
       </c>
       <c r="F32" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2475511209208149</v>
+        <v>-0.2471679574167228</v>
       </c>
       <c r="J32" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K32" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L32" t="n">
-        <v>1.59608046356056</v>
+        <v>1.589360090874669</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1834,28 +1864,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4620</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.095565567939293</v>
       </c>
       <c r="F33" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-0.2475511209208149</v>
       </c>
       <c r="J33" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K33" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L33" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1866,31 +1905,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E34" t="n">
-        <v>1.092331397416143</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.462</v>
       </c>
       <c r="J34" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K34" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L34" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1901,31 +1937,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D35" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E35" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="J35" t="n">
         <v>16.69</v>
       </c>
       <c r="K35" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L35" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -1936,31 +1972,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D36" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E36" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="J36" t="n">
         <v>16.69</v>
       </c>
       <c r="K36" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L36" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -1971,31 +2007,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E37" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="J37" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K37" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L37" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2006,27 +2042,62 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4622</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.095130908660111</v>
+      </c>
+      <c r="J38" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K38" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D39" t="n">
         <v>4.2173</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>16.79</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>
@@ -2113,31 +2184,31 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n">
+      <c r="A4" s="21" t="n">
         <v>46097</v>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="22" t="n">
         <v>1.9517</v>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="22" t="n">
         <v>1.919</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="22" t="n">
         <v>1.775</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="22" t="n">
         <v>2.2082</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="22" t="n">
         <v>1.9884</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="22" t="n">
         <v>2.1082</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="22" t="n">
         <v>1.9828</v>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="23" t="n">
         <v>-0.0157</v>
       </c>
     </row>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,42 +673,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46101.37924015422</v>
+        <v>46104.40028590023</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -723,179 +723,182 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J6" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+        </is>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J7" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K6" s="16" t="n">
+      <c r="K7" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L7" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M7" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
+      <c r="N7" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J7" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D8" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1614</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.44</v>
       </c>
       <c r="K8" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D9" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E9" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F9" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
       </c>
       <c r="K9" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -906,63 +909,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I10" t="n">
         <v>2.163</v>
       </c>
       <c r="J10" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K10" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D11" t="n">
         <v>4.2578</v>
@@ -970,8 +973,20 @@
       <c r="E11" t="n">
         <v>1.5029</v>
       </c>
+      <c r="F11" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.163</v>
+      </c>
       <c r="J11" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K11" t="n">
         <v>10.7108</v>
@@ -981,41 +996,38 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5048</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.137</v>
+        <v>1.5029</v>
       </c>
       <c r="J12" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K12" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1026,40 +1038,34 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E13" t="n">
-        <v>1.494547334774843</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.1733698369608172</v>
+        <v>1.5048</v>
       </c>
       <c r="I13" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J13" t="n">
         <v>21.59</v>
       </c>
       <c r="K13" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9838</v>
+        <v>1.9748</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1070,75 +1076,75 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>6359</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.494547334774843</v>
       </c>
       <c r="F14" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.1733698369608172</v>
       </c>
       <c r="I14" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J14" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K14" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L14" t="n">
-        <v>1.962691102903361</v>
+        <v>1.9838</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Auto: FX,DE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1.434402332361516</v>
+        <v>4.2785</v>
       </c>
       <c r="F15" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.2225461613216715</v>
+        <v>1.792</v>
       </c>
       <c r="I15" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J15" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K15" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L15" t="n">
-        <v>1.864771345740204</v>
+        <v>1.962691102903361</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1149,84 +1155,84 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E16" t="n">
-        <v>1.34815681685196</v>
+        <v>1.434402332361516</v>
       </c>
       <c r="F16" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2225162532572317</v>
+        <v>-0.2225461613216715</v>
       </c>
       <c r="I16" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J16" t="n">
         <v>19.94</v>
       </c>
       <c r="K16" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L16" t="n">
-        <v>1.865556439163587</v>
+        <v>1.864771345740204</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,DE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E17" t="n">
-        <v>1.333943833943834</v>
+        <v>1.34815681685196</v>
       </c>
       <c r="F17" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2324834096985995</v>
+        <v>-0.2225162532572317</v>
       </c>
       <c r="I17" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J17" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K17" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L17" t="n">
-        <v>1.74556351547502</v>
+        <v>1.865556439163587</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1237,40 +1243,40 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E18" t="n">
-        <v>1.221742680508573</v>
+        <v>1.333943833943834</v>
       </c>
       <c r="F18" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2453720318044636</v>
+        <v>-0.2324834096985995</v>
       </c>
       <c r="I18" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J18" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K18" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L18" t="n">
-        <v>1.61655712487764</v>
+        <v>1.74556351547502</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1281,31 +1287,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5237</v>
       </c>
       <c r="D19" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.221742680508573</v>
       </c>
       <c r="F19" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.2453720318044636</v>
       </c>
       <c r="I19" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J19" t="n">
         <v>17.34</v>
       </c>
       <c r="K19" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L19" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1316,40 +1331,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.130838245389769</v>
+        <v>4.244</v>
       </c>
       <c r="F20" t="n">
         <v>1.506</v>
       </c>
-      <c r="H20" t="n">
-        <v>-0.2491113908434471</v>
-      </c>
       <c r="I20" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J20" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K20" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L20" t="n">
-        <v>1.611920144782124</v>
+        <v>1.619350018677624</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1360,40 +1366,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E21" t="n">
-        <v>1.123505032563647</v>
+        <v>1.130838245389769</v>
       </c>
       <c r="F21" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2469805411771802</v>
+        <v>-0.2491113908434471</v>
       </c>
       <c r="I21" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J21" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K21" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L21" t="n">
-        <v>1.624660357912489</v>
+        <v>1.611920144782124</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1404,40 +1410,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E22" t="n">
-        <v>1.128264627187271</v>
+        <v>1.123505032563647</v>
       </c>
       <c r="F22" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2453079416807554</v>
+        <v>-0.2469805411771802</v>
       </c>
       <c r="I22" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J22" t="n">
         <v>17.34</v>
       </c>
       <c r="K22" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L22" t="n">
-        <v>1.624127757223809</v>
+        <v>1.624660357912489</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1448,40 +1454,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D23" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E23" t="n">
-        <v>1.130014453948772</v>
+        <v>1.128264627187271</v>
       </c>
       <c r="F23" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2491598312632747</v>
+        <v>-0.2453079416807554</v>
       </c>
       <c r="I23" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J23" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K23" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L23" t="n">
-        <v>1.613023952095808</v>
+        <v>1.624127757223809</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1492,31 +1498,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4769</v>
       </c>
       <c r="D24" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.130014453948772</v>
       </c>
       <c r="F24" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2491598312632747</v>
       </c>
       <c r="I24" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J24" t="n">
         <v>17.24</v>
       </c>
       <c r="K24" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L24" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1527,40 +1542,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1.122922486860173</v>
+        <v>4.2173</v>
       </c>
       <c r="F25" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-0.2448402912843488</v>
+        <v>1.492</v>
       </c>
       <c r="I25" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J25" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K25" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L25" t="n">
-        <v>1.582275516417631</v>
+        <v>1.611892852134075</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1571,40 +1577,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E26" t="n">
-        <v>1.088949425559635</v>
+        <v>1.122922486860173</v>
       </c>
       <c r="F26" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.254144229068743</v>
+        <v>-0.2448402912843488</v>
       </c>
       <c r="I26" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J26" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K26" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L26" t="n">
-        <v>1.556376560819343</v>
+        <v>1.582275516417631</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1615,40 +1621,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E27" t="n">
-        <v>1.083600142298115</v>
+        <v>1.088949425559635</v>
       </c>
       <c r="F27" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.249064350451757</v>
+        <v>-0.254144229068743</v>
       </c>
       <c r="I27" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J27" t="n">
         <v>16.64</v>
       </c>
       <c r="K27" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L27" t="n">
-        <v>1.567445365486059</v>
+        <v>1.556376560819343</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1659,40 +1665,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E28" t="n">
-        <v>1.086192984954198</v>
+        <v>1.083600142298115</v>
       </c>
       <c r="F28" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2498667230979294</v>
+        <v>-0.249064350451757</v>
       </c>
       <c r="I28" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J28" t="n">
         <v>16.64</v>
       </c>
       <c r="K28" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L28" t="n">
-        <v>1.562734785875282</v>
+        <v>1.567445365486059</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1703,31 +1709,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4577</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.086192984954198</v>
       </c>
       <c r="F29" t="n">
         <v>1.448</v>
       </c>
+      <c r="H29" t="n">
+        <v>-0.2498667230979294</v>
+      </c>
       <c r="I29" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J29" t="n">
         <v>16.64</v>
       </c>
       <c r="K29" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L29" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1738,40 +1753,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1.089679715302491</v>
+        <v>4.2105</v>
       </c>
       <c r="F30" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-0.2448512021465759</v>
+        <v>1.448</v>
       </c>
       <c r="I30" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J30" t="n">
         <v>16.64</v>
       </c>
       <c r="K30" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L30" t="n">
-        <v>1.566058689555217</v>
+        <v>1.566781224989407</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1782,37 +1788,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E31" t="n">
-        <v>1.094216993215997</v>
+        <v>1.089679715302491</v>
       </c>
       <c r="F31" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.247960829404813</v>
+        <v>-0.2448512021465759</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.72</v>
       </c>
       <c r="J31" t="n">
         <v>16.64</v>
       </c>
       <c r="K31" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L31" t="n">
-        <v>1.574713731428031</v>
+        <v>1.566058689555217</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1823,37 +1832,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E32" t="n">
-        <v>1.093864957873502</v>
+        <v>1.094216993215997</v>
       </c>
       <c r="F32" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2471679574167228</v>
+        <v>-0.247960829404813</v>
       </c>
       <c r="J32" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K32" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L32" t="n">
-        <v>1.589360090874669</v>
+        <v>1.574713731428031</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1864,37 +1873,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D33" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E33" t="n">
-        <v>1.095565567939293</v>
+        <v>1.093864957873502</v>
       </c>
       <c r="F33" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2475511209208149</v>
+        <v>-0.2471679574167228</v>
       </c>
       <c r="J33" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K33" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L33" t="n">
-        <v>1.59608046356056</v>
+        <v>1.589360090874669</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1905,28 +1914,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4620</v>
       </c>
       <c r="D34" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.095565567939293</v>
       </c>
       <c r="F34" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.2475511209208149</v>
       </c>
       <c r="J34" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K34" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L34" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1937,31 +1955,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E35" t="n">
-        <v>1.092331397416143</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.462</v>
       </c>
       <c r="J35" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K35" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L35" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -1972,31 +1987,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D36" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E36" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="J36" t="n">
         <v>16.69</v>
       </c>
       <c r="K36" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L36" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2007,31 +2022,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E37" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="J37" t="n">
         <v>16.69</v>
       </c>
       <c r="K37" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L37" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2042,31 +2057,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D38" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E38" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="J38" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K38" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L38" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2077,27 +2092,62 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4622</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.095130908660111</v>
+      </c>
+      <c r="J39" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K39" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D40" t="n">
         <v>4.2173</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J40" t="n">
         <v>16.79</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K40" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L40" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,42 +673,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46104.40028590023</v>
+        <v>46105.39506804097</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7258</v>
+        <v>7171</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2783</v>
+        <v>4.2643</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.6965</v>
+        <v>1.6816</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>2.0362</v>
+        <v>2.0735</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.3397</v>
+        <v>-0.3919</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.1668</v>
+        <v>-0.189</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>24.49</v>
+        <v>24.69</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.7825</v>
+        <v>10.8328</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.2713</v>
+        <v>2.2792</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -723,42 +723,42 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46101.37924015046</v>
+        <v>46104.40028590278</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -773,179 +773,182 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J7" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M7" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+        </is>
+      </c>
+      <c r="N7" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J8" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K7" s="16" t="n">
+      <c r="K8" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L8" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M7" s="10" t="inlineStr">
+      <c r="M8" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
-      <c r="N7" s="11" t="inlineStr">
+      <c r="N8" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J8" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K8" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D9" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1614</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.44</v>
       </c>
       <c r="K9" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E10" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F10" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J10" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
       </c>
       <c r="K10" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -956,63 +959,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I11" t="n">
         <v>2.163</v>
       </c>
       <c r="J11" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K11" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L11" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D12" t="n">
         <v>4.2578</v>
@@ -1020,8 +1023,20 @@
       <c r="E12" t="n">
         <v>1.5029</v>
       </c>
+      <c r="F12" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.163</v>
+      </c>
       <c r="J12" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K12" t="n">
         <v>10.7108</v>
@@ -1031,41 +1046,38 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5048</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.137</v>
+        <v>1.5029</v>
       </c>
       <c r="J13" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K13" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1076,40 +1088,34 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E14" t="n">
-        <v>1.494547334774843</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-0.1733698369608172</v>
+        <v>1.5048</v>
       </c>
       <c r="I14" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J14" t="n">
         <v>21.59</v>
       </c>
       <c r="K14" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9838</v>
+        <v>1.9748</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1120,75 +1126,75 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6359</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.494547334774843</v>
       </c>
       <c r="F15" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.1733698369608172</v>
       </c>
       <c r="I15" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J15" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K15" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L15" t="n">
-        <v>1.962691102903361</v>
+        <v>1.9838</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Auto: FX,DE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.434402332361516</v>
+        <v>4.2785</v>
       </c>
       <c r="F16" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.2225461613216715</v>
+        <v>1.792</v>
       </c>
       <c r="I16" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J16" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K16" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L16" t="n">
-        <v>1.864771345740204</v>
+        <v>1.962691102903361</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1199,84 +1205,84 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E17" t="n">
-        <v>1.34815681685196</v>
+        <v>1.434402332361516</v>
       </c>
       <c r="F17" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2225162532572317</v>
+        <v>-0.2225461613216715</v>
       </c>
       <c r="I17" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J17" t="n">
         <v>19.94</v>
       </c>
       <c r="K17" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L17" t="n">
-        <v>1.865556439163587</v>
+        <v>1.864771345740204</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,DE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E18" t="n">
-        <v>1.333943833943834</v>
+        <v>1.34815681685196</v>
       </c>
       <c r="F18" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2324834096985995</v>
+        <v>-0.2225162532572317</v>
       </c>
       <c r="I18" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J18" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K18" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L18" t="n">
-        <v>1.74556351547502</v>
+        <v>1.865556439163587</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -1287,40 +1293,40 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E19" t="n">
-        <v>1.221742680508573</v>
+        <v>1.333943833943834</v>
       </c>
       <c r="F19" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2453720318044636</v>
+        <v>-0.2324834096985995</v>
       </c>
       <c r="I19" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J19" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K19" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L19" t="n">
-        <v>1.61655712487764</v>
+        <v>1.74556351547502</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1331,31 +1337,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>5237</v>
       </c>
       <c r="D20" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.221742680508573</v>
       </c>
       <c r="F20" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-0.2453720318044636</v>
       </c>
       <c r="I20" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J20" t="n">
         <v>17.34</v>
       </c>
       <c r="K20" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L20" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1366,40 +1381,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.130838245389769</v>
+        <v>4.244</v>
       </c>
       <c r="F21" t="n">
         <v>1.506</v>
       </c>
-      <c r="H21" t="n">
-        <v>-0.2491113908434471</v>
-      </c>
       <c r="I21" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J21" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K21" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L21" t="n">
-        <v>1.611920144782124</v>
+        <v>1.619350018677624</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1410,40 +1416,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E22" t="n">
-        <v>1.123505032563647</v>
+        <v>1.130838245389769</v>
       </c>
       <c r="F22" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2469805411771802</v>
+        <v>-0.2491113908434471</v>
       </c>
       <c r="I22" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J22" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K22" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L22" t="n">
-        <v>1.624660357912489</v>
+        <v>1.611920144782124</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1454,40 +1460,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D23" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E23" t="n">
-        <v>1.128264627187271</v>
+        <v>1.123505032563647</v>
       </c>
       <c r="F23" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2453079416807554</v>
+        <v>-0.2469805411771802</v>
       </c>
       <c r="I23" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J23" t="n">
         <v>17.34</v>
       </c>
       <c r="K23" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L23" t="n">
-        <v>1.624127757223809</v>
+        <v>1.624660357912489</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1498,40 +1504,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D24" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E24" t="n">
-        <v>1.130014453948772</v>
+        <v>1.128264627187271</v>
       </c>
       <c r="F24" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2491598312632747</v>
+        <v>-0.2453079416807554</v>
       </c>
       <c r="I24" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J24" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K24" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L24" t="n">
-        <v>1.613023952095808</v>
+        <v>1.624127757223809</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1542,31 +1548,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>4769</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.130014453948772</v>
       </c>
       <c r="F25" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2491598312632747</v>
       </c>
       <c r="I25" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J25" t="n">
         <v>17.24</v>
       </c>
       <c r="K25" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L25" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1577,40 +1592,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.122922486860173</v>
+        <v>4.2173</v>
       </c>
       <c r="F26" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.2448402912843488</v>
+        <v>1.492</v>
       </c>
       <c r="I26" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J26" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K26" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L26" t="n">
-        <v>1.582275516417631</v>
+        <v>1.611892852134075</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1621,40 +1627,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E27" t="n">
-        <v>1.088949425559635</v>
+        <v>1.122922486860173</v>
       </c>
       <c r="F27" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.254144229068743</v>
+        <v>-0.2448402912843488</v>
       </c>
       <c r="I27" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J27" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K27" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L27" t="n">
-        <v>1.556376560819343</v>
+        <v>1.582275516417631</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1665,40 +1671,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E28" t="n">
-        <v>1.083600142298115</v>
+        <v>1.088949425559635</v>
       </c>
       <c r="F28" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.249064350451757</v>
+        <v>-0.254144229068743</v>
       </c>
       <c r="I28" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J28" t="n">
         <v>16.64</v>
       </c>
       <c r="K28" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L28" t="n">
-        <v>1.567445365486059</v>
+        <v>1.556376560819343</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1709,40 +1715,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E29" t="n">
-        <v>1.086192984954198</v>
+        <v>1.083600142298115</v>
       </c>
       <c r="F29" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2498667230979294</v>
+        <v>-0.249064350451757</v>
       </c>
       <c r="I29" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J29" t="n">
         <v>16.64</v>
       </c>
       <c r="K29" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L29" t="n">
-        <v>1.562734785875282</v>
+        <v>1.567445365486059</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1753,31 +1759,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4577</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.086192984954198</v>
       </c>
       <c r="F30" t="n">
         <v>1.448</v>
       </c>
+      <c r="H30" t="n">
+        <v>-0.2498667230979294</v>
+      </c>
       <c r="I30" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J30" t="n">
         <v>16.64</v>
       </c>
       <c r="K30" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L30" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1788,40 +1803,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1.089679715302491</v>
+        <v>4.2105</v>
       </c>
       <c r="F31" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-0.2448512021465759</v>
+        <v>1.448</v>
       </c>
       <c r="I31" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J31" t="n">
         <v>16.64</v>
       </c>
       <c r="K31" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L31" t="n">
-        <v>1.566058689555217</v>
+        <v>1.566781224989407</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1832,37 +1838,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E32" t="n">
-        <v>1.094216993215997</v>
+        <v>1.089679715302491</v>
       </c>
       <c r="F32" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.247960829404813</v>
+        <v>-0.2448512021465759</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.72</v>
       </c>
       <c r="J32" t="n">
         <v>16.64</v>
       </c>
       <c r="K32" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L32" t="n">
-        <v>1.574713731428031</v>
+        <v>1.566058689555217</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1873,37 +1882,37 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E33" t="n">
-        <v>1.093864957873502</v>
+        <v>1.094216993215997</v>
       </c>
       <c r="F33" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2471679574167228</v>
+        <v>-0.247960829404813</v>
       </c>
       <c r="J33" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L33" t="n">
-        <v>1.589360090874669</v>
+        <v>1.574713731428031</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1914,37 +1923,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D34" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E34" t="n">
-        <v>1.095565567939293</v>
+        <v>1.093864957873502</v>
       </c>
       <c r="F34" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2475511209208149</v>
+        <v>-0.2471679574167228</v>
       </c>
       <c r="J34" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K34" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L34" t="n">
-        <v>1.59608046356056</v>
+        <v>1.589360090874669</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1955,28 +1964,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4620</v>
       </c>
       <c r="D35" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.095565567939293</v>
       </c>
       <c r="F35" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.2475511209208149</v>
       </c>
       <c r="J35" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K35" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L35" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -1987,31 +2005,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D36" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.092331397416143</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.462</v>
       </c>
       <c r="J36" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K36" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L36" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2022,31 +2037,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E37" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="J37" t="n">
         <v>16.69</v>
       </c>
       <c r="K37" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L37" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2057,31 +2072,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D38" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E38" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="J38" t="n">
         <v>16.69</v>
       </c>
       <c r="K38" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L38" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2092,31 +2107,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D39" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E39" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="J39" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K39" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L39" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2127,27 +2142,62 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4622</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.095130908660111</v>
+      </c>
+      <c r="J40" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D41" t="n">
         <v>4.2173</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>16.79</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,46 +673,34 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46105.39506804097</v>
+        <v>46106.29652341043</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7171</v>
-      </c>
-      <c r="D5" s="16" t="n">
-        <v>4.2643</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>1.6816</v>
-      </c>
+        <v>7053</v>
+      </c>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="17" t="n"/>
       <c r="F5" s="18" t="n">
-        <v>2.0735</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>-0.3919</v>
-      </c>
-      <c r="H5" s="20" t="n">
-        <v>-0.189</v>
-      </c>
+        <v>1.9708</v>
+      </c>
+      <c r="G5" s="19" t="n"/>
+      <c r="H5" s="20" t="n"/>
       <c r="I5" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>24.69</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>10.8328</v>
-      </c>
-      <c r="L5" s="17" t="n">
-        <v>2.2792</v>
-      </c>
+        <v>23.64</v>
+      </c>
+      <c r="K5" s="16" t="n"/>
+      <c r="L5" s="17" t="n"/>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+          <t>Auto: PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">
@@ -723,42 +711,42 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46104.40028590278</v>
+        <v>46105.39506804398</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7258</v>
+        <v>7171</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2783</v>
+        <v>4.2643</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.6965</v>
+        <v>1.6816</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>2.0362</v>
+        <v>2.0735</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.3397</v>
+        <v>-0.3919</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.1668</v>
+        <v>-0.189</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>24.49</v>
+        <v>24.69</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.7825</v>
+        <v>10.8328</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.2713</v>
+        <v>2.2792</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -773,42 +761,42 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46101.37924015046</v>
+        <v>46104.40028590278</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -823,179 +811,182 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J8" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+        </is>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J9" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K8" s="16" t="n">
+      <c r="K9" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L9" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M9" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
-      <c r="N8" s="11" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J9" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L9" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D10" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1614</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.44</v>
       </c>
       <c r="K10" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E11" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F11" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J11" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
       </c>
       <c r="K11" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1006,63 +997,63 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I12" t="n">
         <v>2.163</v>
       </c>
       <c r="J12" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K12" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D13" t="n">
         <v>4.2578</v>
@@ -1070,8 +1061,20 @@
       <c r="E13" t="n">
         <v>1.5029</v>
       </c>
+      <c r="F13" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.2532</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1442</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.163</v>
+      </c>
       <c r="J13" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K13" t="n">
         <v>10.7108</v>
@@ -1081,41 +1084,38 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5048</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.137</v>
+        <v>1.5029</v>
       </c>
       <c r="J14" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K14" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9748</v>
+        <v>1.9644</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1126,40 +1126,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E15" t="n">
-        <v>1.494547334774843</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.1733698369608172</v>
+        <v>1.5048</v>
       </c>
       <c r="I15" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J15" t="n">
         <v>21.59</v>
       </c>
       <c r="K15" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9838</v>
+        <v>1.9748</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1170,75 +1164,75 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>6359</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.494547334774843</v>
       </c>
       <c r="F16" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.1733698369608172</v>
       </c>
       <c r="I16" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J16" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K16" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L16" t="n">
-        <v>1.962691102903361</v>
+        <v>1.9838</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Auto: FX,DE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.434402332361516</v>
+        <v>4.2785</v>
       </c>
       <c r="F17" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.2225461613216715</v>
+        <v>1.792</v>
       </c>
       <c r="I17" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J17" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K17" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L17" t="n">
-        <v>1.864771345740204</v>
+        <v>1.962691102903361</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1249,84 +1243,84 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E18" t="n">
-        <v>1.34815681685196</v>
+        <v>1.434402332361516</v>
       </c>
       <c r="F18" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2225162532572317</v>
+        <v>-0.2225461613216715</v>
       </c>
       <c r="I18" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J18" t="n">
         <v>19.94</v>
       </c>
       <c r="K18" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L18" t="n">
-        <v>1.865556439163587</v>
+        <v>1.864771345740204</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,DE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E19" t="n">
-        <v>1.333943833943834</v>
+        <v>1.34815681685196</v>
       </c>
       <c r="F19" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2324834096985995</v>
+        <v>-0.2225162532572317</v>
       </c>
       <c r="I19" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J19" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K19" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L19" t="n">
-        <v>1.74556351547502</v>
+        <v>1.865556439163587</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1337,40 +1331,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E20" t="n">
-        <v>1.221742680508573</v>
+        <v>1.333943833943834</v>
       </c>
       <c r="F20" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2453720318044636</v>
+        <v>-0.2324834096985995</v>
       </c>
       <c r="I20" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J20" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K20" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L20" t="n">
-        <v>1.61655712487764</v>
+        <v>1.74556351547502</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1381,31 +1375,40 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5237</v>
       </c>
       <c r="D21" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.221742680508573</v>
       </c>
       <c r="F21" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.2453720318044636</v>
       </c>
       <c r="I21" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J21" t="n">
         <v>17.34</v>
       </c>
       <c r="K21" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L21" t="n">
-        <v>1.619350018677624</v>
+        <v>1.61655712487764</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1416,40 +1419,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.130838245389769</v>
+        <v>4.244</v>
       </c>
       <c r="F22" t="n">
         <v>1.506</v>
       </c>
-      <c r="H22" t="n">
-        <v>-0.2491113908434471</v>
-      </c>
       <c r="I22" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J22" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K22" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L22" t="n">
-        <v>1.611920144782124</v>
+        <v>1.619350018677624</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1460,40 +1454,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D23" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E23" t="n">
-        <v>1.123505032563647</v>
+        <v>1.130838245389769</v>
       </c>
       <c r="F23" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2469805411771802</v>
+        <v>-0.2491113908434471</v>
       </c>
       <c r="I23" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J23" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K23" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L23" t="n">
-        <v>1.624660357912489</v>
+        <v>1.611920144782124</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1504,40 +1498,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D24" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E24" t="n">
-        <v>1.128264627187271</v>
+        <v>1.123505032563647</v>
       </c>
       <c r="F24" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2453079416807554</v>
+        <v>-0.2469805411771802</v>
       </c>
       <c r="I24" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J24" t="n">
         <v>17.34</v>
       </c>
       <c r="K24" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L24" t="n">
-        <v>1.624127757223809</v>
+        <v>1.624660357912489</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1548,40 +1542,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E25" t="n">
-        <v>1.130014453948772</v>
+        <v>1.128264627187271</v>
       </c>
       <c r="F25" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.2491598312632747</v>
+        <v>-0.2453079416807554</v>
       </c>
       <c r="I25" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J25" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K25" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L25" t="n">
-        <v>1.613023952095808</v>
+        <v>1.624127757223809</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1592,31 +1586,40 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>4769</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.130014453948772</v>
       </c>
       <c r="F26" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.2491598312632747</v>
       </c>
       <c r="I26" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J26" t="n">
         <v>17.24</v>
       </c>
       <c r="K26" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L26" t="n">
-        <v>1.611892852134075</v>
+        <v>1.613023952095808</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1627,40 +1630,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D27" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1.122922486860173</v>
+        <v>4.2173</v>
       </c>
       <c r="F27" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-0.2448402912843488</v>
+        <v>1.492</v>
       </c>
       <c r="I27" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J27" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K27" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L27" t="n">
-        <v>1.582275516417631</v>
+        <v>1.611892852134075</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1671,40 +1665,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E28" t="n">
-        <v>1.088949425559635</v>
+        <v>1.122922486860173</v>
       </c>
       <c r="F28" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.254144229068743</v>
+        <v>-0.2448402912843488</v>
       </c>
       <c r="I28" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J28" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K28" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L28" t="n">
-        <v>1.556376560819343</v>
+        <v>1.582275516417631</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1715,40 +1709,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E29" t="n">
-        <v>1.083600142298115</v>
+        <v>1.088949425559635</v>
       </c>
       <c r="F29" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.249064350451757</v>
+        <v>-0.254144229068743</v>
       </c>
       <c r="I29" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J29" t="n">
         <v>16.64</v>
       </c>
       <c r="K29" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L29" t="n">
-        <v>1.567445365486059</v>
+        <v>1.556376560819343</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1759,40 +1753,40 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E30" t="n">
-        <v>1.086192984954198</v>
+        <v>1.083600142298115</v>
       </c>
       <c r="F30" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2498667230979294</v>
+        <v>-0.249064350451757</v>
       </c>
       <c r="I30" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J30" t="n">
         <v>16.64</v>
       </c>
       <c r="K30" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L30" t="n">
-        <v>1.562734785875282</v>
+        <v>1.567445365486059</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1803,31 +1797,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4577</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.086192984954198</v>
       </c>
       <c r="F31" t="n">
         <v>1.448</v>
       </c>
+      <c r="H31" t="n">
+        <v>-0.2498667230979294</v>
+      </c>
       <c r="I31" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J31" t="n">
         <v>16.64</v>
       </c>
       <c r="K31" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L31" t="n">
-        <v>1.566781224989407</v>
+        <v>1.562734785875282</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1838,40 +1841,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D32" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1.089679715302491</v>
+        <v>4.2105</v>
       </c>
       <c r="F32" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-0.2448512021465759</v>
+        <v>1.448</v>
       </c>
       <c r="I32" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J32" t="n">
         <v>16.64</v>
       </c>
       <c r="K32" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L32" t="n">
-        <v>1.566058689555217</v>
+        <v>1.566781224989407</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1882,37 +1876,40 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E33" t="n">
-        <v>1.094216993215997</v>
+        <v>1.089679715302491</v>
       </c>
       <c r="F33" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.247960829404813</v>
+        <v>-0.2448512021465759</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.72</v>
       </c>
       <c r="J33" t="n">
         <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L33" t="n">
-        <v>1.574713731428031</v>
+        <v>1.566058689555217</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -1923,37 +1920,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D34" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E34" t="n">
-        <v>1.093864957873502</v>
+        <v>1.094216993215997</v>
       </c>
       <c r="F34" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2471679574167228</v>
+        <v>-0.247960829404813</v>
       </c>
       <c r="J34" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K34" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L34" t="n">
-        <v>1.589360090874669</v>
+        <v>1.574713731428031</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -1964,37 +1961,37 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D35" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E35" t="n">
-        <v>1.095565567939293</v>
+        <v>1.093864957873502</v>
       </c>
       <c r="F35" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2475511209208149</v>
+        <v>-0.2471679574167228</v>
       </c>
       <c r="J35" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K35" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L35" t="n">
-        <v>1.59608046356056</v>
+        <v>1.589360090874669</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2005,28 +2002,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4620</v>
       </c>
       <c r="D36" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.095565567939293</v>
       </c>
       <c r="F36" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.2475511209208149</v>
       </c>
       <c r="J36" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K36" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L36" t="n">
-        <v>1.576451809774189</v>
+        <v>1.59608046356056</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2037,31 +2043,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D37" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E37" t="n">
-        <v>1.092331397416143</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.462</v>
       </c>
       <c r="J37" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K37" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L37" t="n">
-        <v>1.563685763807561</v>
+        <v>1.576451809774189</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2072,31 +2075,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D38" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E38" t="n">
-        <v>1.091339888638787</v>
+        <v>1.092331397416143</v>
       </c>
       <c r="J38" t="n">
         <v>16.69</v>
       </c>
       <c r="K38" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L38" t="n">
-        <v>1.568461610750869</v>
+        <v>1.563685763807561</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2107,31 +2110,31 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D39" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E39" t="n">
-        <v>1.096483958801941</v>
+        <v>1.091339888638787</v>
       </c>
       <c r="J39" t="n">
         <v>16.69</v>
       </c>
       <c r="K39" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L39" t="n">
-        <v>1.577952160347925</v>
+        <v>1.568461610750869</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2142,31 +2145,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D40" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E40" t="n">
-        <v>1.095130908660111</v>
+        <v>1.096483958801941</v>
       </c>
       <c r="J40" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K40" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L40" t="n">
-        <v>1.610655543442195</v>
+        <v>1.577952160347925</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2177,27 +2180,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4622</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4.2205</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.095130908660111</v>
+      </c>
+      <c r="J41" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.610655543442195</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Auto: FX</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D42" t="n">
         <v>4.2173</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J42" t="n">
         <v>16.79</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K42" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L42" t="n">
         <v>1.584934157738236</v>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Auto: FX</t>
         </is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -12,13 +12,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -673,7 +672,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.29652341043</v>
+        <v>46106.30551745542</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -672,7 +672,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.30551745542</v>
+        <v>46106.31000573657</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -672,7 +672,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.31000573657</v>
+        <v>46106.31434436814</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -2343,10 +2343,10 @@
         <v>2.1082</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>1.9828</v>
+        <v>1.9495</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>-0.0157</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="5">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -672,7 +672,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.31434436814</v>
+        <v>46106.31835272153</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -682,24 +682,36 @@
       <c r="C5" s="3" t="n">
         <v>7053</v>
       </c>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="17" t="n"/>
+      <c r="D5" s="16" t="n">
+        <v>4.2743</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>1.6501</v>
+      </c>
       <c r="F5" s="18" t="n">
         <v>1.9708</v>
       </c>
-      <c r="G5" s="19" t="n"/>
-      <c r="H5" s="20" t="n"/>
+      <c r="G5" s="19" t="n">
+        <v>-0.3207</v>
+      </c>
+      <c r="H5" s="20" t="n">
+        <v>-0.1627</v>
+      </c>
       <c r="I5" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J5" s="9" t="n">
         <v>23.64</v>
       </c>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="17" t="n"/>
+      <c r="K5" s="16" t="n">
+        <v>10.8238</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <v>2.1841</v>
+      </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
-          <t>Auto: PL,LT,DE,SE,EU</t>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N5" s="11" t="inlineStr">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -672,7 +672,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.31835272153</v>
+        <v>46106.31904905153</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -672,7 +672,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.31904905153</v>
+        <v>46106.31904905092</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2364,217 +2364,186 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.952</v>
+        <v>1.901</v>
       </c>
       <c r="C5" t="n">
-        <v>1.919</v>
+        <v>1.793</v>
       </c>
       <c r="D5" t="n">
-        <v>1.775</v>
+        <v>1.688</v>
       </c>
       <c r="E5" t="n">
-        <v>2.208</v>
+        <v>2.115</v>
       </c>
       <c r="F5" t="n">
-        <v>1.988</v>
+        <v>1.783</v>
       </c>
       <c r="G5" t="n">
-        <v>2.108</v>
+        <v>2.042</v>
       </c>
       <c r="H5" t="n">
-        <v>1.95</v>
+        <v>1.748</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001025641025641027</v>
+        <v>0.08752860411899314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.901</v>
+        <v>1.641</v>
       </c>
       <c r="C6" t="n">
-        <v>1.793</v>
+        <v>1.548</v>
       </c>
       <c r="D6" t="n">
-        <v>1.688</v>
+        <v>1.428</v>
       </c>
       <c r="E6" t="n">
-        <v>2.115</v>
+        <v>1.794</v>
       </c>
       <c r="F6" t="n">
-        <v>1.783</v>
+        <v>1.579</v>
       </c>
       <c r="G6" t="n">
-        <v>2.042</v>
+        <v>1.951</v>
       </c>
       <c r="H6" t="n">
-        <v>1.748</v>
+        <v>1.572</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08752860411899314</v>
+        <v>0.04389312977099234</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.641</v>
+        <v>1.637</v>
       </c>
       <c r="C7" t="n">
-        <v>1.548</v>
+        <v>1.544</v>
       </c>
       <c r="D7" t="n">
-        <v>1.428</v>
+        <v>1.423</v>
       </c>
       <c r="E7" t="n">
-        <v>1.794</v>
+        <v>1.79</v>
       </c>
       <c r="F7" t="n">
-        <v>1.579</v>
+        <v>1.575</v>
       </c>
       <c r="G7" t="n">
-        <v>1.951</v>
+        <v>1.945</v>
       </c>
       <c r="H7" t="n">
-        <v>1.572</v>
+        <v>1.568</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04389312977099234</v>
+        <v>0.04400510204081629</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.637</v>
+        <v>1.632</v>
       </c>
       <c r="C8" t="n">
-        <v>1.544</v>
+        <v>1.538</v>
       </c>
       <c r="D8" t="n">
-        <v>1.423</v>
+        <v>1.417</v>
       </c>
       <c r="E8" t="n">
-        <v>1.79</v>
+        <v>1.786</v>
       </c>
       <c r="F8" t="n">
-        <v>1.575</v>
+        <v>1.571</v>
       </c>
       <c r="G8" t="n">
-        <v>1.945</v>
+        <v>1.939</v>
       </c>
       <c r="H8" t="n">
-        <v>1.568</v>
+        <v>1.564</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04400510204081629</v>
+        <v>0.04347826086956511</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.632</v>
+        <v>1.625</v>
       </c>
       <c r="C9" t="n">
-        <v>1.538</v>
+        <v>1.532</v>
       </c>
       <c r="D9" t="n">
-        <v>1.417</v>
+        <v>1.41</v>
       </c>
       <c r="E9" t="n">
-        <v>1.786</v>
+        <v>1.78</v>
       </c>
       <c r="F9" t="n">
-        <v>1.571</v>
+        <v>1.568</v>
       </c>
       <c r="G9" t="n">
-        <v>1.939</v>
+        <v>1.932</v>
       </c>
       <c r="H9" t="n">
-        <v>1.564</v>
+        <v>1.558</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04347826086956511</v>
+        <v>0.04300385109114246</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.625</v>
+        <v>1.618</v>
       </c>
       <c r="C10" t="n">
-        <v>1.532</v>
+        <v>1.525</v>
       </c>
       <c r="D10" t="n">
-        <v>1.41</v>
+        <v>1.402</v>
       </c>
       <c r="E10" t="n">
-        <v>1.78</v>
+        <v>1.772</v>
       </c>
       <c r="F10" t="n">
-        <v>1.568</v>
+        <v>1.562</v>
       </c>
       <c r="G10" t="n">
-        <v>1.932</v>
+        <v>1.925</v>
       </c>
       <c r="H10" t="n">
-        <v>1.558</v>
+        <v>1.553</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04300385109114246</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.618</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.525</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.402</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1.772</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.562</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.925</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="I11" t="n">
         <v>0.04185447520927248</v>
       </c>
     </row>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -152,6 +152,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,7 +674,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.31904905092</v>
+        <v>46106.33035683677</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -761,7 +763,7 @@
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -811,7 +813,7 @@
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -861,7 +863,7 @@
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
@@ -911,7 +913,7 @@
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE,EU</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -937,16 +939,16 @@
       <c r="D10" t="n">
         <v>4.2593</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="24" t="n">
         <v>1.5413</v>
       </c>
       <c r="F10" t="n">
         <v>1.864</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="25" t="n">
         <v>-0.3227</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="23" t="n">
         <v>-0.1731</v>
       </c>
       <c r="I10" t="n">
@@ -958,7 +960,7 @@
       <c r="K10" t="n">
         <v>10.7055</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="24" t="n">
         <v>2.0961</v>
       </c>
       <c r="M10" t="inlineStr">
@@ -984,24 +986,27 @@
       <c r="D11" t="n">
         <v>4.2683</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="24" t="n">
         <v>1.5409</v>
       </c>
       <c r="F11" t="n">
         <v>1.8374</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="25" t="n">
         <v>-0.2965</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="23" t="n">
         <v>-0.1614</v>
+      </c>
+      <c r="I11" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="K11" t="n">
         <v>10.769</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE</t>
         </is>
       </c>
     </row>
@@ -1022,16 +1027,16 @@
       <c r="D12" t="n">
         <v>4.2675</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="24" t="n">
         <v>1.522</v>
       </c>
       <c r="F12" t="n">
         <v>1.818</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="25" t="n">
         <v>-0.296</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="23" t="n">
         <v>-0.1628</v>
       </c>
       <c r="I12" t="n">
@@ -1043,12 +1048,12 @@
       <c r="K12" t="n">
         <v>10.7545</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12" s="24" t="n">
         <v>2.0308</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1069,16 +1074,16 @@
       <c r="D13" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="24" t="n">
         <v>1.5029</v>
       </c>
       <c r="F13" t="n">
         <v>1.7561</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="25" t="n">
         <v>-0.2532</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="23" t="n">
         <v>-0.1442</v>
       </c>
       <c r="I13" t="n">
@@ -1090,7 +1095,7 @@
       <c r="K13" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13" s="24" t="n">
         <v>1.9644</v>
       </c>
       <c r="M13" t="inlineStr">
@@ -1116,8 +1121,20 @@
       <c r="D14" t="n">
         <v>4.2578</v>
       </c>
-      <c r="E14" t="n">
-        <v>1.5029</v>
+      <c r="E14" s="24" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.3018</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J14" t="n">
         <v>20.49</v>
@@ -1125,12 +1142,12 @@
       <c r="K14" t="n">
         <v>10.7108</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.9644</v>
+      <c r="L14" s="24" t="n">
+        <v>1.913</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1151,8 +1168,8 @@
       <c r="D15" t="n">
         <v>4.2523</v>
       </c>
-      <c r="E15" t="n">
-        <v>1.5048</v>
+      <c r="E15" s="24" t="n">
+        <v>1.4569</v>
       </c>
       <c r="I15" t="n">
         <v>2.137</v>
@@ -1163,8 +1180,8 @@
       <c r="K15" t="n">
         <v>10.6543</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.9748</v>
+      <c r="L15" s="24" t="n">
+        <v>2.0264</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1189,14 +1206,17 @@
       <c r="D16" t="n">
         <v>4.2548</v>
       </c>
-      <c r="E16" t="n">
-        <v>1.494547334774843</v>
+      <c r="E16" s="24" t="n">
+        <v>1.4945</v>
       </c>
       <c r="F16" t="n">
         <v>1.808</v>
       </c>
-      <c r="H16" t="n">
-        <v>-0.1733698369608172</v>
+      <c r="G16" s="25" t="n">
+        <v>-0.3135</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <v>-0.1734</v>
       </c>
       <c r="I16" t="n">
         <v>2.198</v>
@@ -1207,12 +1227,12 @@
       <c r="K16" t="n">
         <v>10.606</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.9838</v>
+      <c r="L16" s="24" t="n">
+        <v>2.0356</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1262,12 @@
       <c r="K17" t="n">
         <v>10.6945</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.962691102903361</v>
+      <c r="L17" s="24" t="n">
+        <v>1.9627</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Auto: FX,DE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1268,14 +1288,17 @@
       <c r="D18" t="n">
         <v>4.2875</v>
       </c>
-      <c r="E18" t="n">
-        <v>1.434402332361516</v>
+      <c r="E18" s="24" t="n">
+        <v>1.4344</v>
       </c>
       <c r="F18" t="n">
         <v>1.845</v>
       </c>
-      <c r="H18" t="n">
-        <v>-0.2225461613216715</v>
+      <c r="G18" s="25" t="n">
+        <v>-0.4106</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-0.2225</v>
       </c>
       <c r="I18" t="n">
         <v>2.089</v>
@@ -1286,12 +1309,12 @@
       <c r="K18" t="n">
         <v>10.693</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.864771345740204</v>
+      <c r="L18" s="24" t="n">
+        <v>1.8648</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Auto: FX,DE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1312,14 +1335,17 @@
       <c r="D19" t="n">
         <v>4.2725</v>
       </c>
-      <c r="E19" t="n">
-        <v>1.34815681685196</v>
+      <c r="E19" s="24" t="n">
+        <v>1.3482</v>
       </c>
       <c r="F19" t="n">
         <v>1.734</v>
       </c>
-      <c r="H19" t="n">
-        <v>-0.2225162532572317</v>
+      <c r="G19" s="25" t="n">
+        <v>-0.3858</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>-0.2225</v>
       </c>
       <c r="I19" t="n">
         <v>2.055</v>
@@ -1330,12 +1356,12 @@
       <c r="K19" t="n">
         <v>10.6885</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.865556439163587</v>
+      <c r="L19" s="24" t="n">
+        <v>1.8656</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1356,14 +1382,17 @@
       <c r="D20" t="n">
         <v>4.2588</v>
       </c>
-      <c r="E20" t="n">
-        <v>1.333943833943834</v>
+      <c r="E20" s="24" t="n">
+        <v>1.3339</v>
       </c>
       <c r="F20" t="n">
         <v>1.738</v>
       </c>
-      <c r="H20" t="n">
-        <v>-0.2324834096985995</v>
+      <c r="G20" s="25" t="n">
+        <v>-0.4041</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>-0.2325</v>
       </c>
       <c r="I20" t="n">
         <v>2.011</v>
@@ -1374,12 +1403,12 @@
       <c r="K20" t="n">
         <v>10.6785</v>
       </c>
-      <c r="L20" t="n">
-        <v>1.74556351547502</v>
+      <c r="L20" s="24" t="n">
+        <v>1.7456</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1400,14 +1429,17 @@
       <c r="D21" t="n">
         <v>4.2865</v>
       </c>
-      <c r="E21" t="n">
-        <v>1.221742680508573</v>
+      <c r="E21" s="24" t="n">
+        <v>1.2217</v>
       </c>
       <c r="F21" t="n">
         <v>1.619</v>
       </c>
-      <c r="H21" t="n">
-        <v>-0.2453720318044636</v>
+      <c r="G21" s="25" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="H21" s="23" t="n">
+        <v>-0.2454</v>
       </c>
       <c r="I21" t="n">
         <v>1.916</v>
@@ -1418,12 +1450,12 @@
       <c r="K21" t="n">
         <v>10.7265</v>
       </c>
-      <c r="L21" t="n">
-        <v>1.61655712487764</v>
+      <c r="L21" s="24" t="n">
+        <v>1.6166</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1485,12 @@
       <c r="K22" t="n">
         <v>10.708</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.619350018677624</v>
+      <c r="L22" s="24" t="n">
+        <v>1.6194</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1479,14 +1511,17 @@
       <c r="D23" t="n">
         <v>4.2243</v>
       </c>
-      <c r="E23" t="n">
-        <v>1.130838245389769</v>
+      <c r="E23" s="24" t="n">
+        <v>1.1308</v>
       </c>
       <c r="F23" t="n">
         <v>1.506</v>
       </c>
-      <c r="H23" t="n">
-        <v>-0.2491113908434471</v>
+      <c r="G23" s="25" t="n">
+        <v>-0.3752</v>
+      </c>
+      <c r="H23" s="23" t="n">
+        <v>-0.2491</v>
       </c>
       <c r="I23" t="n">
         <v>1.748</v>
@@ -1497,12 +1532,12 @@
       <c r="K23" t="n">
         <v>10.6643</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.611920144782124</v>
+      <c r="L23" s="24" t="n">
+        <v>1.6119</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1523,14 +1558,17 @@
       <c r="D24" t="n">
         <v>4.2225</v>
       </c>
-      <c r="E24" t="n">
-        <v>1.123505032563647</v>
+      <c r="E24" s="24" t="n">
+        <v>1.1235</v>
       </c>
       <c r="F24" t="n">
         <v>1.492</v>
       </c>
-      <c r="H24" t="n">
-        <v>-0.2469805411771802</v>
+      <c r="G24" s="25" t="n">
+        <v>-0.3685</v>
+      </c>
+      <c r="H24" s="23" t="n">
+        <v>-0.247</v>
       </c>
       <c r="I24" t="n">
         <v>1.726</v>
@@ -1541,12 +1579,12 @@
       <c r="K24" t="n">
         <v>10.673</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.624660357912489</v>
+      <c r="L24" s="24" t="n">
+        <v>1.6247</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1605,17 @@
       <c r="D25" t="n">
         <v>4.2233</v>
       </c>
-      <c r="E25" t="n">
-        <v>1.128264627187271</v>
+      <c r="E25" s="24" t="n">
+        <v>1.1283</v>
       </c>
       <c r="F25" t="n">
         <v>1.495</v>
       </c>
-      <c r="H25" t="n">
-        <v>-0.2453079416807554</v>
+      <c r="G25" s="25" t="n">
+        <v>-0.3667</v>
+      </c>
+      <c r="H25" s="23" t="n">
+        <v>-0.2453</v>
       </c>
       <c r="I25" t="n">
         <v>1.74</v>
@@ -1585,12 +1626,12 @@
       <c r="K25" t="n">
         <v>10.6765</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.624127757223809</v>
+      <c r="L25" s="24" t="n">
+        <v>1.6241</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1611,14 +1652,17 @@
       <c r="D26" t="n">
         <v>4.2203</v>
       </c>
-      <c r="E26" t="n">
-        <v>1.130014453948772</v>
+      <c r="E26" s="24" t="n">
+        <v>1.13</v>
       </c>
       <c r="F26" t="n">
         <v>1.505</v>
       </c>
-      <c r="H26" t="n">
-        <v>-0.2491598312632747</v>
+      <c r="G26" s="25" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="H26" s="23" t="n">
+        <v>-0.2492</v>
       </c>
       <c r="I26" t="n">
         <v>1.745</v>
@@ -1629,12 +1673,12 @@
       <c r="K26" t="n">
         <v>10.688</v>
       </c>
-      <c r="L26" t="n">
-        <v>1.613023952095808</v>
+      <c r="L26" s="24" t="n">
+        <v>1.613</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1664,12 +1708,12 @@
       <c r="K27" t="n">
         <v>10.6955</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.611892852134075</v>
+      <c r="L27" s="24" t="n">
+        <v>1.6119</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1690,14 +1734,17 @@
       <c r="D28" t="n">
         <v>4.2238</v>
       </c>
-      <c r="E28" t="n">
-        <v>1.122922486860173</v>
+      <c r="E28" s="24" t="n">
+        <v>1.1229</v>
       </c>
       <c r="F28" t="n">
         <v>1.487</v>
       </c>
-      <c r="H28" t="n">
-        <v>-0.2448402912843488</v>
+      <c r="G28" s="25" t="n">
+        <v>-0.3641</v>
+      </c>
+      <c r="H28" s="23" t="n">
+        <v>-0.2449</v>
       </c>
       <c r="I28" t="n">
         <v>1.727</v>
@@ -1708,12 +1755,12 @@
       <c r="K28" t="n">
         <v>10.6745</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.582275516417631</v>
+      <c r="L28" s="24" t="n">
+        <v>1.5823</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1734,14 +1781,17 @@
       <c r="D29" t="n">
         <v>4.2215</v>
       </c>
-      <c r="E29" t="n">
-        <v>1.088949425559635</v>
+      <c r="E29" s="24" t="n">
+        <v>1.0889</v>
       </c>
       <c r="F29" t="n">
         <v>1.46</v>
       </c>
-      <c r="H29" t="n">
-        <v>-0.254144229068743</v>
+      <c r="G29" s="25" t="n">
+        <v>-0.3711</v>
+      </c>
+      <c r="H29" s="23" t="n">
+        <v>-0.2542</v>
       </c>
       <c r="I29" t="n">
         <v>1.713</v>
@@ -1752,12 +1802,12 @@
       <c r="K29" t="n">
         <v>10.6915</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.556376560819343</v>
+      <c r="L29" s="24" t="n">
+        <v>1.5564</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1778,14 +1828,17 @@
       <c r="D30" t="n">
         <v>4.2165</v>
       </c>
-      <c r="E30" t="n">
-        <v>1.083600142298115</v>
+      <c r="E30" s="24" t="n">
+        <v>1.0836</v>
       </c>
       <c r="F30" t="n">
         <v>1.443</v>
       </c>
-      <c r="H30" t="n">
-        <v>-0.249064350451757</v>
+      <c r="G30" s="25" t="n">
+        <v>-0.3594</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <v>-0.2491</v>
       </c>
       <c r="I30" t="n">
         <v>1.697</v>
@@ -1796,12 +1849,12 @@
       <c r="K30" t="n">
         <v>10.616</v>
       </c>
-      <c r="L30" t="n">
-        <v>1.567445365486059</v>
+      <c r="L30" s="24" t="n">
+        <v>1.5674</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1822,14 +1875,17 @@
       <c r="D31" t="n">
         <v>4.2138</v>
       </c>
-      <c r="E31" t="n">
-        <v>1.086192984954198</v>
+      <c r="E31" s="24" t="n">
+        <v>1.0862</v>
       </c>
       <c r="F31" t="n">
         <v>1.448</v>
       </c>
-      <c r="H31" t="n">
-        <v>-0.2498667230979294</v>
+      <c r="G31" s="25" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="H31" s="23" t="n">
+        <v>-0.2499</v>
       </c>
       <c r="I31" t="n">
         <v>1.715</v>
@@ -1840,12 +1896,12 @@
       <c r="K31" t="n">
         <v>10.648</v>
       </c>
-      <c r="L31" t="n">
-        <v>1.562734785875282</v>
+      <c r="L31" s="24" t="n">
+        <v>1.5627</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1931,12 @@
       <c r="K32" t="n">
         <v>10.6205</v>
       </c>
-      <c r="L32" t="n">
-        <v>1.566781224989407</v>
+      <c r="L32" s="24" t="n">
+        <v>1.5668</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1901,14 +1957,17 @@
       <c r="D33" t="n">
         <v>4.215</v>
       </c>
-      <c r="E33" t="n">
-        <v>1.089679715302491</v>
+      <c r="E33" s="24" t="n">
+        <v>1.0897</v>
       </c>
       <c r="F33" t="n">
         <v>1.443</v>
       </c>
-      <c r="H33" t="n">
-        <v>-0.2448512021465759</v>
+      <c r="G33" s="25" t="n">
+        <v>-0.3533</v>
+      </c>
+      <c r="H33" s="23" t="n">
+        <v>-0.2448</v>
       </c>
       <c r="I33" t="n">
         <v>1.72</v>
@@ -1919,12 +1978,12 @@
       <c r="K33" t="n">
         <v>10.6254</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.566058689555217</v>
+      <c r="L33" s="24" t="n">
+        <v>1.5661</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1945,14 +2004,20 @@
       <c r="D34" t="n">
         <v>4.2158</v>
       </c>
-      <c r="E34" t="n">
-        <v>1.094216993215997</v>
+      <c r="E34" s="24" t="n">
+        <v>1.0942</v>
       </c>
       <c r="F34" t="n">
         <v>1.455</v>
       </c>
-      <c r="H34" t="n">
-        <v>-0.247960829404813</v>
+      <c r="G34" s="25" t="n">
+        <v>-0.3608</v>
+      </c>
+      <c r="H34" s="23" t="n">
+        <v>-0.248</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J34" t="n">
         <v>16.64</v>
@@ -1960,12 +2025,12 @@
       <c r="K34" t="n">
         <v>10.567</v>
       </c>
-      <c r="L34" t="n">
-        <v>1.574713731428031</v>
+      <c r="L34" s="24" t="n">
+        <v>1.5747</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -1986,14 +2051,20 @@
       <c r="D35" t="n">
         <v>4.2135</v>
       </c>
-      <c r="E35" t="n">
-        <v>1.093864957873502</v>
+      <c r="E35" s="24" t="n">
+        <v>1.0939</v>
       </c>
       <c r="F35" t="n">
         <v>1.453</v>
       </c>
-      <c r="H35" t="n">
-        <v>-0.2471679574167228</v>
+      <c r="G35" s="25" t="n">
+        <v>-0.3591</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>-0.2471</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J35" t="n">
         <v>16.79</v>
@@ -2001,12 +2072,12 @@
       <c r="K35" t="n">
         <v>10.564</v>
       </c>
-      <c r="L35" t="n">
-        <v>1.589360090874669</v>
+      <c r="L35" s="24" t="n">
+        <v>1.5894</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2027,14 +2098,20 @@
       <c r="D36" t="n">
         <v>4.217</v>
       </c>
-      <c r="E36" t="n">
-        <v>1.095565567939293</v>
+      <c r="E36" s="24" t="n">
+        <v>1.0956</v>
       </c>
       <c r="F36" t="n">
         <v>1.456</v>
       </c>
-      <c r="H36" t="n">
-        <v>-0.2475511209208149</v>
+      <c r="G36" s="25" t="n">
+        <v>-0.3604</v>
+      </c>
+      <c r="H36" s="23" t="n">
+        <v>-0.2475</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J36" t="n">
         <v>16.94</v>
@@ -2042,12 +2119,12 @@
       <c r="K36" t="n">
         <v>10.6135</v>
       </c>
-      <c r="L36" t="n">
-        <v>1.59608046356056</v>
+      <c r="L36" s="24" t="n">
+        <v>1.5961</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2068,18 +2145,21 @@
       <c r="F37" t="n">
         <v>1.462</v>
       </c>
+      <c r="I37" s="24" t="n">
+        <v>2.146</v>
+      </c>
       <c r="J37" t="n">
         <v>16.79</v>
       </c>
       <c r="K37" t="n">
         <v>10.6505</v>
       </c>
-      <c r="L37" t="n">
-        <v>1.576451809774189</v>
+      <c r="L37" s="24" t="n">
+        <v>1.5765</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2100,8 +2180,11 @@
       <c r="D38" t="n">
         <v>4.2185</v>
       </c>
-      <c r="E38" t="n">
-        <v>1.092331397416143</v>
+      <c r="E38" s="24" t="n">
+        <v>1.0923</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J38" t="n">
         <v>16.69</v>
@@ -2109,12 +2192,12 @@
       <c r="K38" t="n">
         <v>10.6735</v>
       </c>
-      <c r="L38" t="n">
-        <v>1.563685763807561</v>
+      <c r="L38" s="24" t="n">
+        <v>1.5637</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2135,8 +2218,11 @@
       <c r="D39" t="n">
         <v>4.2205</v>
       </c>
-      <c r="E39" t="n">
-        <v>1.091339888638787</v>
+      <c r="E39" s="24" t="n">
+        <v>1.0913</v>
+      </c>
+      <c r="I39" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J39" t="n">
         <v>16.69</v>
@@ -2144,12 +2230,12 @@
       <c r="K39" t="n">
         <v>10.641</v>
       </c>
-      <c r="L39" t="n">
-        <v>1.568461610750869</v>
+      <c r="L39" s="24" t="n">
+        <v>1.5685</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2170,8 +2256,11 @@
       <c r="D40" t="n">
         <v>4.2235</v>
       </c>
-      <c r="E40" t="n">
-        <v>1.096483958801941</v>
+      <c r="E40" s="24" t="n">
+        <v>1.0965</v>
+      </c>
+      <c r="I40" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J40" t="n">
         <v>16.69</v>
@@ -2179,12 +2268,12 @@
       <c r="K40" t="n">
         <v>10.577</v>
       </c>
-      <c r="L40" t="n">
-        <v>1.577952160347925</v>
+      <c r="L40" s="24" t="n">
+        <v>1.578</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2205,8 +2294,11 @@
       <c r="D41" t="n">
         <v>4.2205</v>
       </c>
-      <c r="E41" t="n">
-        <v>1.095130908660111</v>
+      <c r="E41" s="24" t="n">
+        <v>1.0951</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J41" t="n">
         <v>16.99</v>
@@ -2214,12 +2306,12 @@
       <c r="K41" t="n">
         <v>10.5485</v>
       </c>
-      <c r="L41" t="n">
-        <v>1.610655543442195</v>
+      <c r="L41" s="24" t="n">
+        <v>1.6107</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
@@ -2237,18 +2329,21 @@
       <c r="D42" t="n">
         <v>4.2173</v>
       </c>
+      <c r="I42" s="24" t="n">
+        <v>2.146</v>
+      </c>
       <c r="J42" t="n">
         <v>16.79</v>
       </c>
       <c r="K42" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L42" t="n">
-        <v>1.584934157738236</v>
+      <c r="L42" s="24" t="n">
+        <v>1.5849</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Auto: FX</t>
+          <t>Auto: FX,DE,SE</t>
         </is>
       </c>
     </row>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -674,7 +674,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.33035683677</v>
+        <v>46106.33123000128</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -674,7 +674,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.33123000128</v>
+        <v>46106.39402475151</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -12,12 +12,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -556,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,42 +675,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46106.39402475151</v>
+        <v>46107.39820906421</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>7053</v>
+        <v>6749</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2718</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.6501</v>
+        <v>1.5799</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>1.9708</v>
+        <v>1.9581</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.3207</v>
+        <v>-0.3782</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.1627</v>
+        <v>-0.1931</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>2.146</v>
+        <v>2.13</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.8238</v>
+        <v>10.7715</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.1841</v>
+        <v>2.1808</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -724,46 +725,46 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46105.39506804398</v>
+        <v>46106.39402475695</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7171</v>
+        <v>7053</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2643</v>
+        <v>4.2743</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.6816</v>
+        <v>1.6501</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>2.0735</v>
+        <v>1.9708</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.3919</v>
+        <v>-0.3207</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.189</v>
+        <v>-0.1627</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>24.69</v>
+        <v>23.64</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.8328</v>
+        <v>10.8238</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.2792</v>
+        <v>2.1841</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N6" s="11" t="inlineStr">
@@ -774,42 +775,42 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46104.40028590278</v>
+        <v>46105.39506804398</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7258</v>
+        <v>7171</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2783</v>
+        <v>4.2643</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.6965</v>
+        <v>1.6816</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>2.0362</v>
+        <v>2.0735</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.3397</v>
+        <v>-0.3919</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.1668</v>
+        <v>-0.189</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>24.49</v>
+        <v>24.69</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>10.7825</v>
+        <v>10.8328</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>2.2713</v>
+        <v>2.2792</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -824,42 +825,42 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46101.37924015046</v>
+        <v>46104.40028590278</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -874,229 +875,232 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J9" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J10" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K10" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L10" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J10" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K10" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L10" s="24" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D11" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E11" s="24" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>-0.1614</v>
-      </c>
-      <c r="I11" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J11" t="n">
+        <v>22.44</v>
       </c>
       <c r="K11" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L11" s="24" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F12" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="K12" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I13" t="n">
         <v>2.163</v>
       </c>
       <c r="J13" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K13" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L13" s="24" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1107,43 +1111,43 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D14" t="n">
         <v>4.2578</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F14" s="24" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F14" t="n">
         <v>1.7561</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.3018</v>
+        <v>-0.2532</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>-0.1719</v>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1442</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.163</v>
       </c>
       <c r="J14" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K14" t="n">
         <v>10.7108</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>1.913</v>
+        <v>1.9644</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1154,210 +1158,210 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>1.4569</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.137</v>
+        <v>1.4543</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.3018</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J15" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K15" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>2.0264</v>
+        <v>1.913</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>1.4945</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.3135</v>
-      </c>
-      <c r="H16" s="23" t="n">
-        <v>-0.1734</v>
+        <v>1.4569</v>
       </c>
       <c r="I16" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J16" t="n">
         <v>21.59</v>
       </c>
       <c r="K16" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>2.0356</v>
+        <v>2.0264</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>6359</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>1.4945</v>
       </c>
       <c r="F17" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.3135</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <v>-0.1734</v>
       </c>
       <c r="I17" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J17" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K17" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>1.9627</v>
+        <v>2.0356</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D18" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>1.4344</v>
+        <v>4.2785</v>
       </c>
       <c r="F18" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.4106</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>-0.2225</v>
+        <v>1.792</v>
       </c>
       <c r="I18" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J18" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K18" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>1.8648</v>
+        <v>1.9627</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>1.3482</v>
+        <v>1.4344</v>
       </c>
       <c r="F19" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>-0.3858</v>
+        <v>-0.4106</v>
       </c>
       <c r="H19" s="23" t="n">
         <v>-0.2225</v>
       </c>
       <c r="I19" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J19" t="n">
         <v>19.94</v>
       </c>
       <c r="K19" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>1.8656</v>
+        <v>1.8648</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -1368,43 +1372,43 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>1.3339</v>
+        <v>1.3482</v>
       </c>
       <c r="F20" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.4041</v>
+        <v>-0.3858</v>
       </c>
       <c r="H20" s="23" t="n">
-        <v>-0.2325</v>
+        <v>-0.2225</v>
       </c>
       <c r="I20" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J20" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K20" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>1.7456</v>
+        <v>1.8656</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1415,43 +1419,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>1.2217</v>
+        <v>1.3339</v>
       </c>
       <c r="F21" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>-0.3973</v>
+        <v>-0.4041</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>-0.2454</v>
+        <v>-0.2325</v>
       </c>
       <c r="I21" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J21" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K21" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>1.6166</v>
+        <v>1.7456</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1462,125 +1466,125 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5237</v>
       </c>
       <c r="D22" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E22" s="24" t="n">
+        <v>1.2217</v>
       </c>
       <c r="F22" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="H22" s="23" t="n">
+        <v>-0.2454</v>
       </c>
       <c r="I22" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J22" t="n">
         <v>17.34</v>
       </c>
       <c r="K22" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>1.6194</v>
+        <v>1.6166</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E23" s="24" t="n">
-        <v>1.1308</v>
+        <v>4.244</v>
       </c>
       <c r="F23" t="n">
         <v>1.506</v>
       </c>
-      <c r="G23" s="25" t="n">
-        <v>-0.3752</v>
-      </c>
-      <c r="H23" s="23" t="n">
-        <v>-0.2491</v>
-      </c>
       <c r="I23" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J23" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K23" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.6194</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D24" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.1235</v>
+        <v>1.1308</v>
       </c>
       <c r="F24" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="G24" s="25" t="n">
-        <v>-0.3685</v>
+        <v>-0.3752</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>-0.247</v>
+        <v>-0.2491</v>
       </c>
       <c r="I24" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J24" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K24" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>1.6247</v>
+        <v>1.6119</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1591,43 +1595,43 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>1.1283</v>
+        <v>1.1235</v>
       </c>
       <c r="F25" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="G25" s="25" t="n">
-        <v>-0.3667</v>
+        <v>-0.3685</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>-0.2453</v>
+        <v>-0.247</v>
       </c>
       <c r="I25" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J25" t="n">
         <v>17.34</v>
       </c>
       <c r="K25" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>1.6241</v>
+        <v>1.6247</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1638,43 +1642,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>1.13</v>
+        <v>1.1283</v>
       </c>
       <c r="F26" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>-0.375</v>
+        <v>-0.3667</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>-0.2492</v>
+        <v>-0.2453</v>
       </c>
       <c r="I26" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J26" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K26" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>1.613</v>
+        <v>1.6241</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1685,125 +1689,125 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4769</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>1.13</v>
       </c>
       <c r="F27" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="G27" s="25" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="H27" s="23" t="n">
+        <v>-0.2492</v>
       </c>
       <c r="I27" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J27" t="n">
         <v>17.24</v>
       </c>
       <c r="K27" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.613</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D28" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E28" s="24" t="n">
-        <v>1.1229</v>
+        <v>4.2173</v>
       </c>
       <c r="F28" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="G28" s="25" t="n">
-        <v>-0.3641</v>
-      </c>
-      <c r="H28" s="23" t="n">
-        <v>-0.2449</v>
+        <v>1.492</v>
       </c>
       <c r="I28" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J28" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K28" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.5823</v>
+        <v>1.6119</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>1.0889</v>
+        <v>1.1229</v>
       </c>
       <c r="F29" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="G29" s="25" t="n">
-        <v>-0.3711</v>
+        <v>-0.3641</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>-0.2542</v>
+        <v>-0.2449</v>
       </c>
       <c r="I29" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J29" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K29" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L29" s="24" t="n">
-        <v>1.5564</v>
+        <v>1.5823</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1814,43 +1818,43 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E30" s="24" t="n">
-        <v>1.0836</v>
+        <v>1.0889</v>
       </c>
       <c r="F30" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>-0.3594</v>
+        <v>-0.3711</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>-0.2491</v>
+        <v>-0.2542</v>
       </c>
       <c r="I30" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J30" t="n">
         <v>16.64</v>
       </c>
       <c r="K30" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L30" s="24" t="n">
-        <v>1.5674</v>
+        <v>1.5564</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1861,43 +1865,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>1.0862</v>
+        <v>1.0836</v>
       </c>
       <c r="F31" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>-0.3618</v>
+        <v>-0.3594</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>-0.2499</v>
+        <v>-0.2491</v>
       </c>
       <c r="I31" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J31" t="n">
         <v>16.64</v>
       </c>
       <c r="K31" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L31" s="24" t="n">
-        <v>1.5627</v>
+        <v>1.5674</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1908,125 +1912,125 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4577</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E32" s="24" t="n">
+        <v>1.0862</v>
       </c>
       <c r="F32" t="n">
         <v>1.448</v>
       </c>
+      <c r="G32" s="25" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="H32" s="23" t="n">
+        <v>-0.2499</v>
+      </c>
       <c r="I32" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J32" t="n">
         <v>16.64</v>
       </c>
       <c r="K32" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L32" s="24" t="n">
-        <v>1.5668</v>
+        <v>1.5627</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D33" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E33" s="24" t="n">
-        <v>1.0897</v>
+        <v>4.2105</v>
       </c>
       <c r="F33" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>-0.3533</v>
-      </c>
-      <c r="H33" s="23" t="n">
-        <v>-0.2448</v>
+        <v>1.448</v>
       </c>
       <c r="I33" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J33" t="n">
         <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L33" s="24" t="n">
-        <v>1.5661</v>
+        <v>1.5668</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D34" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E34" s="24" t="n">
-        <v>1.0942</v>
+        <v>1.0897</v>
       </c>
       <c r="F34" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="G34" s="25" t="n">
-        <v>-0.3608</v>
+        <v>-0.3533</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>-0.248</v>
-      </c>
-      <c r="I34" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.2448</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.72</v>
       </c>
       <c r="J34" t="n">
         <v>16.64</v>
       </c>
       <c r="K34" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>1.5747</v>
+        <v>1.5661</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2037,43 +2041,43 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D35" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>1.0939</v>
+        <v>1.0942</v>
       </c>
       <c r="F35" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="G35" s="25" t="n">
-        <v>-0.3591</v>
+        <v>-0.3608</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>-0.2471</v>
+        <v>-0.248</v>
       </c>
       <c r="I35" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J35" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K35" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>1.5894</v>
+        <v>1.5747</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2084,43 +2088,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D36" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E36" s="24" t="n">
-        <v>1.0956</v>
+        <v>1.0939</v>
       </c>
       <c r="F36" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>-0.3604</v>
+        <v>-0.3591</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>-0.2475</v>
+        <v>-0.2471</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J36" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K36" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L36" s="24" t="n">
-        <v>1.5961</v>
+        <v>1.5894</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2131,95 +2135,104 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>4620</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E37" s="24" t="n">
+        <v>1.0956</v>
       </c>
       <c r="F37" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>-0.3604</v>
+      </c>
+      <c r="H37" s="23" t="n">
+        <v>-0.2475</v>
       </c>
       <c r="I37" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J37" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K37" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L37" s="24" t="n">
-        <v>1.5765</v>
+        <v>1.5961</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D38" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E38" s="24" t="n">
-        <v>1.0923</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.462</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J38" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K38" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>1.5637</v>
+        <v>1.5765</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D39" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E39" s="24" t="n">
-        <v>1.0913</v>
+        <v>1.0923</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>2.146</v>
@@ -2228,10 +2241,10 @@
         <v>16.69</v>
       </c>
       <c r="K39" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L39" s="24" t="n">
-        <v>1.5685</v>
+        <v>1.5637</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2242,22 +2255,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D40" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E40" s="24" t="n">
-        <v>1.0965</v>
+        <v>1.0913</v>
       </c>
       <c r="I40" s="24" t="n">
         <v>2.146</v>
@@ -2266,10 +2279,10 @@
         <v>16.69</v>
       </c>
       <c r="K40" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>1.578</v>
+        <v>1.5685</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2280,34 +2293,34 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D41" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>1.0951</v>
+        <v>1.0965</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J41" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K41" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L41" s="24" t="n">
-        <v>1.6107</v>
+        <v>1.578</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2318,30 +2331,68 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>4622</v>
       </c>
       <c r="D42" t="n">
-        <v>4.2173</v>
+        <v>4.2205</v>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>1.0951</v>
       </c>
       <c r="I42" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J42" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K42" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L42" s="24" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="I43" s="24" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J43" t="n">
         <v>16.79</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K43" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L42" s="24" t="n">
+      <c r="L43" s="24" t="n">
         <v>1.5849</v>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
@@ -2358,7 +2409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,216 +2480,245 @@
     </row>
     <row r="4">
       <c r="A4" s="21" t="n">
-        <v>46097</v>
+        <v>46104</v>
       </c>
       <c r="B4" s="22" t="n">
-        <v>1.9517</v>
+        <v>2.1005</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>1.919</v>
+        <v>2.023</v>
       </c>
       <c r="D4" s="22" t="n">
         <v>1.775</v>
       </c>
       <c r="E4" s="22" t="n">
+        <v>2.3826</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>2.2446</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <v>2.3196</v>
+      </c>
+      <c r="H4" s="22" t="n">
+        <v>2.0347</v>
+      </c>
+      <c r="I4" s="23" t="n">
+        <v>0.0323</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B5" s="22" t="n">
+        <v>1.9517</v>
+      </c>
+      <c r="C5" s="22" t="n">
+        <v>1.919</v>
+      </c>
+      <c r="D5" s="22" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="E5" s="22" t="n">
         <v>2.2082</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="F5" s="22" t="n">
         <v>1.9884</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="G5" s="22" t="n">
         <v>2.1082</v>
       </c>
-      <c r="H4" s="22" t="n">
+      <c r="H5" s="22" t="n">
         <v>1.9495</v>
       </c>
-      <c r="I4" s="23" t="n">
+      <c r="I5" s="23" t="n">
         <v>0.0011</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.901</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1.793</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.688</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.115</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1.783</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.042</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.748</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.08752860411899314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.641</v>
+        <v>1.901</v>
       </c>
       <c r="C6" t="n">
-        <v>1.548</v>
+        <v>1.793</v>
       </c>
       <c r="D6" t="n">
-        <v>1.428</v>
+        <v>1.688</v>
       </c>
       <c r="E6" t="n">
-        <v>1.794</v>
+        <v>2.115</v>
       </c>
       <c r="F6" t="n">
-        <v>1.579</v>
+        <v>1.783</v>
       </c>
       <c r="G6" t="n">
-        <v>1.951</v>
+        <v>2.042</v>
       </c>
       <c r="H6" t="n">
-        <v>1.572</v>
+        <v>1.748</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04389312977099234</v>
+        <v>0.08752860411899314</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.637</v>
+        <v>1.641</v>
       </c>
       <c r="C7" t="n">
-        <v>1.544</v>
+        <v>1.548</v>
       </c>
       <c r="D7" t="n">
-        <v>1.423</v>
+        <v>1.428</v>
       </c>
       <c r="E7" t="n">
-        <v>1.79</v>
+        <v>1.794</v>
       </c>
       <c r="F7" t="n">
-        <v>1.575</v>
+        <v>1.579</v>
       </c>
       <c r="G7" t="n">
-        <v>1.945</v>
+        <v>1.951</v>
       </c>
       <c r="H7" t="n">
-        <v>1.568</v>
+        <v>1.572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04400510204081629</v>
+        <v>0.04389312977099234</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.632</v>
+        <v>1.637</v>
       </c>
       <c r="C8" t="n">
-        <v>1.538</v>
+        <v>1.544</v>
       </c>
       <c r="D8" t="n">
-        <v>1.417</v>
+        <v>1.423</v>
       </c>
       <c r="E8" t="n">
-        <v>1.786</v>
+        <v>1.79</v>
       </c>
       <c r="F8" t="n">
-        <v>1.571</v>
+        <v>1.575</v>
       </c>
       <c r="G8" t="n">
-        <v>1.939</v>
+        <v>1.945</v>
       </c>
       <c r="H8" t="n">
-        <v>1.564</v>
+        <v>1.568</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04347826086956511</v>
+        <v>0.04400510204081629</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.625</v>
+        <v>1.632</v>
       </c>
       <c r="C9" t="n">
-        <v>1.532</v>
+        <v>1.538</v>
       </c>
       <c r="D9" t="n">
-        <v>1.41</v>
+        <v>1.417</v>
       </c>
       <c r="E9" t="n">
-        <v>1.78</v>
+        <v>1.786</v>
       </c>
       <c r="F9" t="n">
-        <v>1.568</v>
+        <v>1.571</v>
       </c>
       <c r="G9" t="n">
-        <v>1.932</v>
+        <v>1.939</v>
       </c>
       <c r="H9" t="n">
-        <v>1.558</v>
+        <v>1.564</v>
       </c>
       <c r="I9" t="n">
-        <v>0.04300385109114246</v>
+        <v>0.04347826086956511</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.932</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.558</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.04300385109114246</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>1.618</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>1.525</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>1.402</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" t="n">
         <v>1.772</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" t="n">
         <v>1.562</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" t="n">
         <v>1.925</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" t="n">
         <v>1.553</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" t="n">
         <v>0.04185447520927248</v>
       </c>
     </row>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46107.39820906421</v>
+        <v>46108.39354064129</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6749</v>
+        <v>6870</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2718</v>
+        <v>4.2743</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.5799</v>
+        <v>1.6073</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>1.9581</v>
+        <v>1.8704</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.3782</v>
+        <v>-0.2631</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.1931</v>
+        <v>-0.1407</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>2.13</v>
+        <v>2.297</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>23.49</v>
+        <v>22.59</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.7715</v>
+        <v>10.8405</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.1808</v>
+        <v>2.0839</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -725,42 +725,42 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46106.39402475695</v>
+        <v>46107.3982090625</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7053</v>
+        <v>6749</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2718</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.6501</v>
+        <v>1.5799</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1.9708</v>
+        <v>1.9581</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.3207</v>
+        <v>-0.3782</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.1627</v>
+        <v>-0.1931</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>2.146</v>
+        <v>2.13</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.8238</v>
+        <v>10.7715</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.1841</v>
+        <v>2.1808</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -775,46 +775,46 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46105.39506804398</v>
+        <v>46106.39402475695</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7171</v>
+        <v>7053</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2643</v>
+        <v>4.2743</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.6816</v>
+        <v>1.6501</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>2.0735</v>
+        <v>1.9708</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.3919</v>
+        <v>-0.3207</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.189</v>
+        <v>-0.1627</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>24.69</v>
+        <v>23.64</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>10.8328</v>
+        <v>10.8238</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>2.2792</v>
+        <v>2.1841</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N7" s="11" t="inlineStr">
@@ -825,42 +825,42 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46104.40028590278</v>
+        <v>46105.39506804398</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7258</v>
+        <v>7171</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4.2783</v>
+        <v>4.2643</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.6965</v>
+        <v>1.6816</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>2.0362</v>
+        <v>2.0735</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.3397</v>
+        <v>-0.3919</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-0.1668</v>
+        <v>-0.189</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>24.49</v>
+        <v>24.69</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>10.7825</v>
+        <v>10.8328</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>2.2713</v>
+        <v>2.2792</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -875,42 +875,42 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46101.37924015046</v>
+        <v>46104.40028590278</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -925,229 +925,232 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J10" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M10" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J11" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K10" s="16" t="n">
+      <c r="K11" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L11" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M10" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="N11" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J11" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K11" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L11" s="24" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D12" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E12" s="24" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G12" s="25" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>-0.1614</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22.44</v>
       </c>
       <c r="K12" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F13" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J13" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
+      </c>
+      <c r="I13" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="K13" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I14" t="n">
         <v>2.163</v>
       </c>
       <c r="J14" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K14" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L14" s="24" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1158,43 +1161,43 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D15" t="n">
         <v>4.2578</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F15" s="24" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F15" t="n">
         <v>1.7561</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.3018</v>
+        <v>-0.2532</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>-0.1719</v>
-      </c>
-      <c r="I15" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1442</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.163</v>
       </c>
       <c r="J15" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K15" t="n">
         <v>10.7108</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>1.913</v>
+        <v>1.9644</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1205,210 +1208,210 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>1.4569</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.137</v>
+        <v>1.4543</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.3018</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="I16" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J16" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K16" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>2.0264</v>
+        <v>1.913</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>1.4945</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.3135</v>
-      </c>
-      <c r="H17" s="23" t="n">
-        <v>-0.1734</v>
+        <v>1.4569</v>
       </c>
       <c r="I17" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J17" t="n">
         <v>21.59</v>
       </c>
       <c r="K17" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>2.0356</v>
+        <v>2.0264</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>6359</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>1.4945</v>
       </c>
       <c r="F18" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.3135</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-0.1734</v>
       </c>
       <c r="I18" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J18" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K18" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>1.9627</v>
+        <v>2.0356</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>1.4344</v>
+        <v>4.2785</v>
       </c>
       <c r="F19" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.4106</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>-0.2225</v>
+        <v>1.792</v>
       </c>
       <c r="I19" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J19" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K19" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>1.8648</v>
+        <v>1.9627</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>1.3482</v>
+        <v>1.4344</v>
       </c>
       <c r="F20" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.3858</v>
+        <v>-0.4106</v>
       </c>
       <c r="H20" s="23" t="n">
         <v>-0.2225</v>
       </c>
       <c r="I20" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J20" t="n">
         <v>19.94</v>
       </c>
       <c r="K20" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>1.8656</v>
+        <v>1.8648</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -1419,43 +1422,43 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>1.3339</v>
+        <v>1.3482</v>
       </c>
       <c r="F21" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>-0.4041</v>
+        <v>-0.3858</v>
       </c>
       <c r="H21" s="23" t="n">
-        <v>-0.2325</v>
+        <v>-0.2225</v>
       </c>
       <c r="I21" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J21" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K21" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>1.7456</v>
+        <v>1.8656</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1466,43 +1469,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>1.2217</v>
+        <v>1.3339</v>
       </c>
       <c r="F22" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>-0.3973</v>
+        <v>-0.4041</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>-0.2454</v>
+        <v>-0.2325</v>
       </c>
       <c r="I22" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J22" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K22" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>1.6166</v>
+        <v>1.7456</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1513,125 +1516,125 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>5237</v>
       </c>
       <c r="D23" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E23" s="24" t="n">
+        <v>1.2217</v>
       </c>
       <c r="F23" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="G23" s="25" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="H23" s="23" t="n">
+        <v>-0.2454</v>
       </c>
       <c r="I23" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J23" t="n">
         <v>17.34</v>
       </c>
       <c r="K23" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>1.6194</v>
+        <v>1.6166</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E24" s="24" t="n">
-        <v>1.1308</v>
+        <v>4.244</v>
       </c>
       <c r="F24" t="n">
         <v>1.506</v>
       </c>
-      <c r="G24" s="25" t="n">
-        <v>-0.3752</v>
-      </c>
-      <c r="H24" s="23" t="n">
-        <v>-0.2491</v>
-      </c>
       <c r="I24" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J24" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K24" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.6194</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D25" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>1.1235</v>
+        <v>1.1308</v>
       </c>
       <c r="F25" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="G25" s="25" t="n">
-        <v>-0.3685</v>
+        <v>-0.3752</v>
       </c>
       <c r="H25" s="23" t="n">
-        <v>-0.247</v>
+        <v>-0.2491</v>
       </c>
       <c r="I25" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J25" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K25" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>1.6247</v>
+        <v>1.6119</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -1642,43 +1645,43 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>1.1283</v>
+        <v>1.1235</v>
       </c>
       <c r="F26" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>-0.3667</v>
+        <v>-0.3685</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>-0.2453</v>
+        <v>-0.247</v>
       </c>
       <c r="I26" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J26" t="n">
         <v>17.34</v>
       </c>
       <c r="K26" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>1.6241</v>
+        <v>1.6247</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1689,43 +1692,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>1.13</v>
+        <v>1.1283</v>
       </c>
       <c r="F27" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>-0.375</v>
+        <v>-0.3667</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>-0.2492</v>
+        <v>-0.2453</v>
       </c>
       <c r="I27" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J27" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K27" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>1.613</v>
+        <v>1.6241</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1736,125 +1739,125 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4769</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E28" s="24" t="n">
+        <v>1.13</v>
       </c>
       <c r="F28" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="G28" s="25" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="H28" s="23" t="n">
+        <v>-0.2492</v>
       </c>
       <c r="I28" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J28" t="n">
         <v>17.24</v>
       </c>
       <c r="K28" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.613</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D29" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E29" s="24" t="n">
-        <v>1.1229</v>
+        <v>4.2173</v>
       </c>
       <c r="F29" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>-0.3641</v>
-      </c>
-      <c r="H29" s="23" t="n">
-        <v>-0.2449</v>
+        <v>1.492</v>
       </c>
       <c r="I29" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J29" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K29" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L29" s="24" t="n">
-        <v>1.5823</v>
+        <v>1.6119</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E30" s="24" t="n">
-        <v>1.0889</v>
+        <v>1.1229</v>
       </c>
       <c r="F30" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>-0.3711</v>
+        <v>-0.3641</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>-0.2542</v>
+        <v>-0.2449</v>
       </c>
       <c r="I30" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J30" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K30" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L30" s="24" t="n">
-        <v>1.5564</v>
+        <v>1.5823</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -1865,43 +1868,43 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>1.0836</v>
+        <v>1.0889</v>
       </c>
       <c r="F31" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>-0.3594</v>
+        <v>-0.3711</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>-0.2491</v>
+        <v>-0.2542</v>
       </c>
       <c r="I31" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J31" t="n">
         <v>16.64</v>
       </c>
       <c r="K31" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L31" s="24" t="n">
-        <v>1.5674</v>
+        <v>1.5564</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1912,43 +1915,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E32" s="24" t="n">
-        <v>1.0862</v>
+        <v>1.0836</v>
       </c>
       <c r="F32" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>-0.3618</v>
+        <v>-0.3594</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>-0.2499</v>
+        <v>-0.2491</v>
       </c>
       <c r="I32" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J32" t="n">
         <v>16.64</v>
       </c>
       <c r="K32" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L32" s="24" t="n">
-        <v>1.5627</v>
+        <v>1.5674</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1959,125 +1962,125 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4577</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E33" s="24" t="n">
+        <v>1.0862</v>
       </c>
       <c r="F33" t="n">
         <v>1.448</v>
       </c>
+      <c r="G33" s="25" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="H33" s="23" t="n">
+        <v>-0.2499</v>
+      </c>
       <c r="I33" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J33" t="n">
         <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L33" s="24" t="n">
-        <v>1.5668</v>
+        <v>1.5627</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D34" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E34" s="24" t="n">
-        <v>1.0897</v>
+        <v>4.2105</v>
       </c>
       <c r="F34" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>-0.3533</v>
-      </c>
-      <c r="H34" s="23" t="n">
-        <v>-0.2448</v>
+        <v>1.448</v>
       </c>
       <c r="I34" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J34" t="n">
         <v>16.64</v>
       </c>
       <c r="K34" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>1.5661</v>
+        <v>1.5668</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D35" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E35" s="24" t="n">
-        <v>1.0942</v>
+        <v>1.0897</v>
       </c>
       <c r="F35" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="G35" s="25" t="n">
-        <v>-0.3608</v>
+        <v>-0.3533</v>
       </c>
       <c r="H35" s="23" t="n">
-        <v>-0.248</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.2448</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.72</v>
       </c>
       <c r="J35" t="n">
         <v>16.64</v>
       </c>
       <c r="K35" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>1.5747</v>
+        <v>1.5661</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2088,43 +2091,43 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D36" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E36" s="24" t="n">
-        <v>1.0939</v>
+        <v>1.0942</v>
       </c>
       <c r="F36" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>-0.3591</v>
+        <v>-0.3608</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>-0.2471</v>
+        <v>-0.248</v>
       </c>
       <c r="I36" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J36" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K36" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L36" s="24" t="n">
-        <v>1.5894</v>
+        <v>1.5747</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2135,43 +2138,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D37" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E37" s="24" t="n">
-        <v>1.0956</v>
+        <v>1.0939</v>
       </c>
       <c r="F37" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>-0.3604</v>
+        <v>-0.3591</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>-0.2475</v>
+        <v>-0.2471</v>
       </c>
       <c r="I37" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J37" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K37" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L37" s="24" t="n">
-        <v>1.5961</v>
+        <v>1.5894</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2182,95 +2185,104 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>4620</v>
       </c>
       <c r="D38" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E38" s="24" t="n">
+        <v>1.0956</v>
       </c>
       <c r="F38" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>-0.3604</v>
+      </c>
+      <c r="H38" s="23" t="n">
+        <v>-0.2475</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J38" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K38" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>1.5765</v>
+        <v>1.5961</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D39" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E39" s="24" t="n">
-        <v>1.0923</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.462</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J39" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K39" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L39" s="24" t="n">
-        <v>1.5637</v>
+        <v>1.5765</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D40" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E40" s="24" t="n">
-        <v>1.0913</v>
+        <v>1.0923</v>
       </c>
       <c r="I40" s="24" t="n">
         <v>2.146</v>
@@ -2279,10 +2291,10 @@
         <v>16.69</v>
       </c>
       <c r="K40" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>1.5685</v>
+        <v>1.5637</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2293,22 +2305,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D41" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>1.0965</v>
+        <v>1.0913</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>2.146</v>
@@ -2317,10 +2329,10 @@
         <v>16.69</v>
       </c>
       <c r="K41" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L41" s="24" t="n">
-        <v>1.578</v>
+        <v>1.5685</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2331,34 +2343,34 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D42" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>1.0951</v>
+        <v>1.0965</v>
       </c>
       <c r="I42" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J42" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K42" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>1.6107</v>
+        <v>1.578</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2369,30 +2381,68 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4622</v>
       </c>
       <c r="D43" t="n">
-        <v>4.2173</v>
+        <v>4.2205</v>
+      </c>
+      <c r="E43" s="24" t="n">
+        <v>1.0951</v>
       </c>
       <c r="I43" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J43" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K43" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L43" s="24" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="I44" s="24" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J44" t="n">
         <v>16.79</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K44" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L43" s="24" t="n">
+      <c r="L44" s="24" t="n">
         <v>1.5849</v>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
@@ -2501,10 +2551,10 @@
         <v>2.3196</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>2.0347</v>
+        <v>2.0634</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>0.0323</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="5">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46108.39354064129</v>
+        <v>46111.33508029572</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6870</v>
+        <v>6761</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2875</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.6073</v>
+        <v>1.5769</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>1.8704</v>
+        <v>1.98</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.2631</v>
+        <v>-0.4031</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.1407</v>
+        <v>-0.2036</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>2.297</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>22.59</v>
+        <v>23.84</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.8405</v>
+        <v>10.878</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.0839</v>
+        <v>2.1916</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -725,42 +725,42 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46107.3982090625</v>
+        <v>46108.39354063657</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6749</v>
+        <v>6870</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2718</v>
+        <v>4.2743</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.5799</v>
+        <v>1.6073</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1.9581</v>
+        <v>1.8704</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.3782</v>
+        <v>-0.2631</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.1931</v>
+        <v>-0.1407</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>2.13</v>
+        <v>2.297</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>23.49</v>
+        <v>22.59</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.7715</v>
+        <v>10.8405</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.1808</v>
+        <v>2.0839</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -775,42 +775,42 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46106.39402475695</v>
+        <v>46107.3982090625</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>7053</v>
+        <v>6749</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2718</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.6501</v>
+        <v>1.5799</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>1.9708</v>
+        <v>1.9581</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.3207</v>
+        <v>-0.3782</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.1627</v>
+        <v>-0.1931</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>2.146</v>
+        <v>2.13</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>10.8238</v>
+        <v>10.7715</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>2.1841</v>
+        <v>2.1808</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -825,46 +825,46 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46105.39506804398</v>
+        <v>46106.39402475695</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7171</v>
+        <v>7053</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4.2643</v>
+        <v>4.2743</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.6816</v>
+        <v>1.6501</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>2.0735</v>
+        <v>1.9708</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.3919</v>
+        <v>-0.3207</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-0.189</v>
+        <v>-0.1627</v>
       </c>
       <c r="I8" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>24.69</v>
+        <v>23.64</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>10.8328</v>
+        <v>10.8238</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>2.2792</v>
+        <v>2.1841</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N8" s="11" t="inlineStr">
@@ -875,42 +875,42 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46104.40028590278</v>
+        <v>46105.39506804398</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>7258</v>
+        <v>7171</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>4.2783</v>
+        <v>4.2643</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1.6965</v>
+        <v>1.6816</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>2.0362</v>
+        <v>2.0735</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-0.3397</v>
+        <v>-0.3919</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.1668</v>
+        <v>-0.189</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>24.49</v>
+        <v>24.69</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>10.7825</v>
+        <v>10.8328</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>2.2713</v>
+        <v>2.2792</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -925,42 +925,42 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46101.37924015046</v>
+        <v>46104.40028590278</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -975,229 +975,232 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J11" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M11" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J12" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K11" s="16" t="n">
+      <c r="K12" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L12" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N11" s="11" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G12" s="25" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J12" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K12" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E13" s="24" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>-0.1614</v>
-      </c>
-      <c r="I13" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22.44</v>
       </c>
       <c r="K13" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L13" s="24" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F14" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J14" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
+      </c>
+      <c r="I14" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="K14" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L14" s="24" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I15" t="n">
         <v>2.163</v>
       </c>
       <c r="J15" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K15" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L15" s="24" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1208,43 +1211,43 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D16" t="n">
         <v>4.2578</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F16" s="24" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F16" t="n">
         <v>1.7561</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>-0.3018</v>
+        <v>-0.2532</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>-0.1719</v>
-      </c>
-      <c r="I16" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1442</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.163</v>
       </c>
       <c r="J16" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K16" t="n">
         <v>10.7108</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>1.913</v>
+        <v>1.9644</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1255,210 +1258,210 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D17" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>1.4569</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.137</v>
+        <v>1.4543</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.3018</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="I17" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J17" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K17" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>2.0264</v>
+        <v>1.913</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>1.4945</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.3135</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>-0.1734</v>
+        <v>1.4569</v>
       </c>
       <c r="I18" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J18" t="n">
         <v>21.59</v>
       </c>
       <c r="K18" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>2.0356</v>
+        <v>2.0264</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6359</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>1.4945</v>
       </c>
       <c r="F19" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.3135</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>-0.1734</v>
       </c>
       <c r="I19" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J19" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K19" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>1.9627</v>
+        <v>2.0356</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D20" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>1.4344</v>
+        <v>4.2785</v>
       </c>
       <c r="F20" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.4106</v>
-      </c>
-      <c r="H20" s="23" t="n">
-        <v>-0.2225</v>
+        <v>1.792</v>
       </c>
       <c r="I20" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J20" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K20" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>1.8648</v>
+        <v>1.9627</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D21" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>1.3482</v>
+        <v>1.4344</v>
       </c>
       <c r="F21" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>-0.3858</v>
+        <v>-0.4106</v>
       </c>
       <c r="H21" s="23" t="n">
         <v>-0.2225</v>
       </c>
       <c r="I21" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J21" t="n">
         <v>19.94</v>
       </c>
       <c r="K21" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>1.8656</v>
+        <v>1.8648</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -1469,43 +1472,43 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>1.3339</v>
+        <v>1.3482</v>
       </c>
       <c r="F22" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>-0.4041</v>
+        <v>-0.3858</v>
       </c>
       <c r="H22" s="23" t="n">
-        <v>-0.2325</v>
+        <v>-0.2225</v>
       </c>
       <c r="I22" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J22" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K22" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>1.7456</v>
+        <v>1.8656</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1516,43 +1519,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D23" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>1.2217</v>
+        <v>1.3339</v>
       </c>
       <c r="F23" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>-0.3973</v>
+        <v>-0.4041</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>-0.2454</v>
+        <v>-0.2325</v>
       </c>
       <c r="I23" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J23" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K23" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>1.6166</v>
+        <v>1.7456</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1563,125 +1566,125 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5237</v>
       </c>
       <c r="D24" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>1.2217</v>
       </c>
       <c r="F24" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="G24" s="25" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="H24" s="23" t="n">
+        <v>-0.2454</v>
       </c>
       <c r="I24" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J24" t="n">
         <v>17.34</v>
       </c>
       <c r="K24" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>1.6194</v>
+        <v>1.6166</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D25" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E25" s="24" t="n">
-        <v>1.1308</v>
+        <v>4.244</v>
       </c>
       <c r="F25" t="n">
         <v>1.506</v>
       </c>
-      <c r="G25" s="25" t="n">
-        <v>-0.3752</v>
-      </c>
-      <c r="H25" s="23" t="n">
-        <v>-0.2491</v>
-      </c>
       <c r="I25" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J25" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K25" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.6194</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D26" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>1.1235</v>
+        <v>1.1308</v>
       </c>
       <c r="F26" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>-0.3685</v>
+        <v>-0.3752</v>
       </c>
       <c r="H26" s="23" t="n">
-        <v>-0.247</v>
+        <v>-0.2491</v>
       </c>
       <c r="I26" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J26" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K26" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>1.6247</v>
+        <v>1.6119</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -1692,43 +1695,43 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>1.1283</v>
+        <v>1.1235</v>
       </c>
       <c r="F27" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>-0.3667</v>
+        <v>-0.3685</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>-0.2453</v>
+        <v>-0.247</v>
       </c>
       <c r="I27" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J27" t="n">
         <v>17.34</v>
       </c>
       <c r="K27" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>1.6241</v>
+        <v>1.6247</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1739,43 +1742,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>1.13</v>
+        <v>1.1283</v>
       </c>
       <c r="F28" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>-0.375</v>
+        <v>-0.3667</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>-0.2492</v>
+        <v>-0.2453</v>
       </c>
       <c r="I28" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J28" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K28" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.613</v>
+        <v>1.6241</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1786,125 +1789,125 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4769</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>1.13</v>
       </c>
       <c r="F29" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="G29" s="25" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="H29" s="23" t="n">
+        <v>-0.2492</v>
       </c>
       <c r="I29" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J29" t="n">
         <v>17.24</v>
       </c>
       <c r="K29" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L29" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.613</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D30" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E30" s="24" t="n">
-        <v>1.1229</v>
+        <v>4.2173</v>
       </c>
       <c r="F30" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="G30" s="25" t="n">
-        <v>-0.3641</v>
-      </c>
-      <c r="H30" s="23" t="n">
-        <v>-0.2449</v>
+        <v>1.492</v>
       </c>
       <c r="I30" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J30" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K30" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L30" s="24" t="n">
-        <v>1.5823</v>
+        <v>1.6119</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D31" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E31" s="24" t="n">
-        <v>1.0889</v>
+        <v>1.1229</v>
       </c>
       <c r="F31" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>-0.3711</v>
+        <v>-0.3641</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>-0.2542</v>
+        <v>-0.2449</v>
       </c>
       <c r="I31" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J31" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K31" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L31" s="24" t="n">
-        <v>1.5564</v>
+        <v>1.5823</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -1915,43 +1918,43 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E32" s="24" t="n">
-        <v>1.0836</v>
+        <v>1.0889</v>
       </c>
       <c r="F32" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>-0.3594</v>
+        <v>-0.3711</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>-0.2491</v>
+        <v>-0.2542</v>
       </c>
       <c r="I32" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J32" t="n">
         <v>16.64</v>
       </c>
       <c r="K32" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L32" s="24" t="n">
-        <v>1.5674</v>
+        <v>1.5564</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1962,43 +1965,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E33" s="24" t="n">
-        <v>1.0862</v>
+        <v>1.0836</v>
       </c>
       <c r="F33" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="G33" s="25" t="n">
-        <v>-0.3618</v>
+        <v>-0.3594</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>-0.2499</v>
+        <v>-0.2491</v>
       </c>
       <c r="I33" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J33" t="n">
         <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L33" s="24" t="n">
-        <v>1.5627</v>
+        <v>1.5674</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2009,125 +2012,125 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4577</v>
       </c>
       <c r="D34" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E34" s="24" t="n">
+        <v>1.0862</v>
       </c>
       <c r="F34" t="n">
         <v>1.448</v>
       </c>
+      <c r="G34" s="25" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="H34" s="23" t="n">
+        <v>-0.2499</v>
+      </c>
       <c r="I34" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J34" t="n">
         <v>16.64</v>
       </c>
       <c r="K34" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>1.5668</v>
+        <v>1.5627</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D35" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E35" s="24" t="n">
-        <v>1.0897</v>
+        <v>4.2105</v>
       </c>
       <c r="F35" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="G35" s="25" t="n">
-        <v>-0.3533</v>
-      </c>
-      <c r="H35" s="23" t="n">
-        <v>-0.2448</v>
+        <v>1.448</v>
       </c>
       <c r="I35" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J35" t="n">
         <v>16.64</v>
       </c>
       <c r="K35" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>1.5661</v>
+        <v>1.5668</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D36" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E36" s="24" t="n">
-        <v>1.0942</v>
+        <v>1.0897</v>
       </c>
       <c r="F36" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="G36" s="25" t="n">
-        <v>-0.3608</v>
+        <v>-0.3533</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>-0.248</v>
-      </c>
-      <c r="I36" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.2448</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.72</v>
       </c>
       <c r="J36" t="n">
         <v>16.64</v>
       </c>
       <c r="K36" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L36" s="24" t="n">
-        <v>1.5747</v>
+        <v>1.5661</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2138,43 +2141,43 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E37" s="24" t="n">
-        <v>1.0939</v>
+        <v>1.0942</v>
       </c>
       <c r="F37" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>-0.3591</v>
+        <v>-0.3608</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>-0.2471</v>
+        <v>-0.248</v>
       </c>
       <c r="I37" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J37" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K37" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L37" s="24" t="n">
-        <v>1.5894</v>
+        <v>1.5747</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2185,43 +2188,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D38" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E38" s="24" t="n">
-        <v>1.0956</v>
+        <v>1.0939</v>
       </c>
       <c r="F38" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="G38" s="25" t="n">
-        <v>-0.3604</v>
+        <v>-0.3591</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>-0.2475</v>
+        <v>-0.2471</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J38" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K38" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>1.5961</v>
+        <v>1.5894</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2232,95 +2235,104 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4620</v>
       </c>
       <c r="D39" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E39" s="24" t="n">
+        <v>1.0956</v>
       </c>
       <c r="F39" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="G39" s="25" t="n">
+        <v>-0.3604</v>
+      </c>
+      <c r="H39" s="23" t="n">
+        <v>-0.2475</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J39" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K39" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L39" s="24" t="n">
-        <v>1.5765</v>
+        <v>1.5961</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D40" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E40" s="24" t="n">
-        <v>1.0923</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.462</v>
       </c>
       <c r="I40" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J40" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K40" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>1.5637</v>
+        <v>1.5765</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D41" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E41" s="24" t="n">
-        <v>1.0913</v>
+        <v>1.0923</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>2.146</v>
@@ -2329,10 +2341,10 @@
         <v>16.69</v>
       </c>
       <c r="K41" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L41" s="24" t="n">
-        <v>1.5685</v>
+        <v>1.5637</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2343,22 +2355,22 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D42" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>1.0965</v>
+        <v>1.0913</v>
       </c>
       <c r="I42" s="24" t="n">
         <v>2.146</v>
@@ -2367,10 +2379,10 @@
         <v>16.69</v>
       </c>
       <c r="K42" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>1.578</v>
+        <v>1.5685</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2381,34 +2393,34 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D43" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>1.0951</v>
+        <v>1.0965</v>
       </c>
       <c r="I43" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J43" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K43" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L43" s="24" t="n">
-        <v>1.6107</v>
+        <v>1.578</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2419,30 +2431,68 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4622</v>
       </c>
       <c r="D44" t="n">
-        <v>4.2173</v>
+        <v>4.2205</v>
+      </c>
+      <c r="E44" s="24" t="n">
+        <v>1.0951</v>
       </c>
       <c r="I44" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J44" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K44" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L44" s="24" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J45" t="n">
         <v>16.79</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K45" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L44" s="24" t="n">
+      <c r="L45" s="24" t="n">
         <v>1.5849</v>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>
@@ -2539,7 +2589,7 @@
         <v>2.023</v>
       </c>
       <c r="D4" s="22" t="n">
-        <v>1.775</v>
+        <v>1.974</v>
       </c>
       <c r="E4" s="22" t="n">
         <v>2.3826</v>
@@ -2551,10 +2601,10 @@
         <v>2.3196</v>
       </c>
       <c r="H4" s="22" t="n">
-        <v>2.0634</v>
+        <v>2.0643</v>
       </c>
       <c r="I4" s="23" t="n">
-        <v>0.018</v>
+        <v>0.0175</v>
       </c>
     </row>
     <row r="5">

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -12,13 +12,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
-    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -675,7 +674,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46111.33508029572</v>
+        <v>46111.34078255336</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -674,7 +674,7 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46111.34078255336</v>
+        <v>46111.413462762</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -12,12 +12,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="+0.000;-0.000;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="+0.0%;-0.0%;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -556,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,42 +675,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46111.413462762</v>
+        <v>46112.40250203417</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6761</v>
+        <v>6796</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2875</v>
+        <v>4.2883</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.5769</v>
+        <v>1.5848</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>1.98</v>
+        <v>2.0011</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.4031</v>
+        <v>-0.4163</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.2036</v>
+        <v>-0.208</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>2.297</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>23.84</v>
+        <v>24.14</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.878</v>
+        <v>10.906</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.1916</v>
+        <v>2.2135</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -724,42 +725,42 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46108.39354063657</v>
+        <v>46111.41346276621</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6870</v>
+        <v>6761</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2875</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.6073</v>
+        <v>1.5769</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1.8704</v>
+        <v>1.98</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.2631</v>
+        <v>-0.4031</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.1407</v>
+        <v>-0.2036</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>2.297</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>22.59</v>
+        <v>23.84</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.8405</v>
+        <v>10.878</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.0839</v>
+        <v>2.1916</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -774,42 +775,42 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46107.3982090625</v>
+        <v>46108.39354063657</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6749</v>
+        <v>6870</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2718</v>
+        <v>4.2743</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.5799</v>
+        <v>1.6073</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>1.9581</v>
+        <v>1.8704</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.3782</v>
+        <v>-0.2631</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.1931</v>
+        <v>-0.1407</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>2.13</v>
+        <v>2.297</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>23.49</v>
+        <v>22.59</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>10.7715</v>
+        <v>10.8405</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>2.1808</v>
+        <v>2.0839</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -824,42 +825,42 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46106.39402475695</v>
+        <v>46107.3982090625</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>7053</v>
+        <v>6749</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2718</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.6501</v>
+        <v>1.5799</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1.9708</v>
+        <v>1.9581</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.3207</v>
+        <v>-0.3782</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-0.1627</v>
+        <v>-0.1931</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>2.146</v>
+        <v>2.13</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>10.8238</v>
+        <v>10.7715</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>2.1841</v>
+        <v>2.1808</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -874,46 +875,46 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46105.39506804398</v>
+        <v>46106.39402475695</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>7171</v>
+        <v>7053</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>4.2643</v>
+        <v>4.2743</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1.6816</v>
+        <v>1.6501</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>2.0735</v>
+        <v>1.9708</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-0.3919</v>
+        <v>-0.3207</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.189</v>
+        <v>-0.1627</v>
       </c>
       <c r="I9" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>24.69</v>
+        <v>23.64</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>10.8328</v>
+        <v>10.8238</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>2.2792</v>
+        <v>2.1841</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE,EU</t>
         </is>
       </c>
       <c r="N9" s="11" t="inlineStr">
@@ -924,42 +925,42 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46104.40028590278</v>
+        <v>46105.39506804398</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7258</v>
+        <v>7171</v>
       </c>
       <c r="D10" s="16" t="n">
-        <v>4.2783</v>
+        <v>4.2643</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1.6965</v>
+        <v>1.6816</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>2.0362</v>
+        <v>2.0735</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>-0.3397</v>
+        <v>-0.3919</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>-0.1668</v>
+        <v>-0.189</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>24.49</v>
+        <v>24.69</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>10.7825</v>
+        <v>10.8328</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>2.2713</v>
+        <v>2.2792</v>
       </c>
       <c r="M10" s="10" t="inlineStr">
         <is>
@@ -974,42 +975,42 @@
     </row>
     <row r="11">
       <c r="A11" s="15" t="n">
-        <v>46101.37924015046</v>
+        <v>46104.40028590278</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6737</v>
+        <v>7258</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>4.2853</v>
+        <v>4.2783</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>1.5721</v>
+        <v>1.6965</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>1.949</v>
+        <v>2.0362</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>-0.3769</v>
+        <v>-0.3397</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>-0.1934</v>
+        <v>-0.1668</v>
       </c>
       <c r="I11" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>23.44</v>
+        <v>24.49</v>
       </c>
       <c r="K11" s="16" t="n">
-        <v>10.8065</v>
+        <v>10.7825</v>
       </c>
       <c r="L11" s="17" t="n">
-        <v>2.1691</v>
+        <v>2.2713</v>
       </c>
       <c r="M11" s="10" t="inlineStr">
         <is>
@@ -1024,229 +1025,232 @@
     </row>
     <row r="12">
       <c r="A12" s="15" t="n">
-        <v>46100.38145226852</v>
+        <v>46101.37924015046</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>6620</v>
+        <v>6737</v>
       </c>
       <c r="D12" s="16" t="n">
-        <v>4.2713</v>
+        <v>4.2853</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>1.5499</v>
+        <v>1.5721</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>1.8547</v>
+        <v>1.949</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>-0.3048</v>
+        <v>-0.3769</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>-0.1643</v>
+        <v>-0.1934</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>2.146</v>
       </c>
       <c r="J12" s="9" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>10.8065</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <v>2.1691</v>
+      </c>
+      <c r="M12" s="10" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,LT,DE,SE</t>
+        </is>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n">
+        <v>46100.38145226852</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>6620</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>4.2713</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>1.5499</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>1.8547</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>-0.3048</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-0.1643</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J13" s="9" t="n">
         <v>22.29</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K13" s="16" t="n">
         <v>10.7778</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L13" s="17" t="n">
         <v>2.0681</v>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N13" s="11" t="inlineStr">
         <is>
           <t>Auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>6565</v>
-      </c>
-      <c r="D13" t="n">
-        <v>4.2593</v>
-      </c>
-      <c r="E13" s="24" t="n">
-        <v>1.5413</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1.864</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>-0.3227</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J13" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10.7055</v>
-      </c>
-      <c r="L13" s="24" t="n">
-        <v>2.0961</v>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6577</v>
+        <v>6565</v>
       </c>
       <c r="D14" t="n">
-        <v>4.2683</v>
+        <v>4.2593</v>
       </c>
       <c r="E14" s="24" t="n">
-        <v>1.5409</v>
+        <v>1.5413</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8374</v>
+        <v>1.864</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.2965</v>
+        <v>-0.3227</v>
       </c>
       <c r="H14" s="23" t="n">
-        <v>-0.1614</v>
-      </c>
-      <c r="I14" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1731</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.163</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22.44</v>
       </c>
       <c r="K14" t="n">
-        <v>10.769</v>
+        <v>10.7055</v>
+      </c>
+      <c r="L14" s="24" t="n">
+        <v>2.0961</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6495</v>
+        <v>6577</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2675</v>
+        <v>4.2683</v>
       </c>
       <c r="E15" s="24" t="n">
-        <v>1.522</v>
+        <v>1.5409</v>
       </c>
       <c r="F15" t="n">
-        <v>1.818</v>
+        <v>1.8374</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.296</v>
+        <v>-0.2965</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>-0.1628</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.163</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21.84</v>
+        <v>-0.1614</v>
+      </c>
+      <c r="I15" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="K15" t="n">
-        <v>10.7545</v>
-      </c>
-      <c r="L15" s="24" t="n">
-        <v>2.0308</v>
+        <v>10.769</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6399</v>
+        <v>6495</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2578</v>
+        <v>4.2675</v>
       </c>
       <c r="E16" s="24" t="n">
-        <v>1.5029</v>
+        <v>1.522</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7561</v>
+        <v>1.818</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>-0.2532</v>
+        <v>-0.296</v>
       </c>
       <c r="H16" s="23" t="n">
-        <v>-0.1442</v>
+        <v>-0.1628</v>
       </c>
       <c r="I16" t="n">
         <v>2.163</v>
       </c>
       <c r="J16" t="n">
-        <v>21.04</v>
+        <v>21.84</v>
       </c>
       <c r="K16" t="n">
-        <v>10.7108</v>
+        <v>10.7545</v>
       </c>
       <c r="L16" s="24" t="n">
-        <v>1.9644</v>
+        <v>2.0308</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1257,43 +1261,43 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6192</v>
+        <v>6399</v>
       </c>
       <c r="D17" t="n">
         <v>4.2578</v>
       </c>
       <c r="E17" s="24" t="n">
-        <v>1.4543</v>
-      </c>
-      <c r="F17" s="24" t="n">
+        <v>1.5029</v>
+      </c>
+      <c r="F17" t="n">
         <v>1.7561</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>-0.3018</v>
+        <v>-0.2532</v>
       </c>
       <c r="H17" s="23" t="n">
-        <v>-0.1719</v>
-      </c>
-      <c r="I17" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.1442</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.163</v>
       </c>
       <c r="J17" t="n">
-        <v>20.49</v>
+        <v>21.04</v>
       </c>
       <c r="K17" t="n">
         <v>10.7108</v>
       </c>
       <c r="L17" s="24" t="n">
-        <v>1.913</v>
+        <v>1.9644</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1304,210 +1308,210 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6195</v>
+        <v>6192</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2523</v>
+        <v>4.2578</v>
       </c>
       <c r="E18" s="24" t="n">
-        <v>1.4569</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.137</v>
+        <v>1.4543</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>1.7561</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.3018</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-0.1719</v>
+      </c>
+      <c r="I18" s="24" t="n">
+        <v>2.146</v>
       </c>
       <c r="J18" t="n">
-        <v>21.59</v>
+        <v>20.49</v>
       </c>
       <c r="K18" t="n">
-        <v>10.6543</v>
+        <v>10.7108</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>2.0264</v>
+        <v>1.913</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6359</v>
+        <v>6195</v>
       </c>
       <c r="D19" t="n">
-        <v>4.2548</v>
+        <v>4.2523</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>1.4945</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.808</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.3135</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>-0.1734</v>
+        <v>1.4569</v>
       </c>
       <c r="I19" t="n">
-        <v>2.198</v>
+        <v>2.137</v>
       </c>
       <c r="J19" t="n">
         <v>21.59</v>
       </c>
       <c r="K19" t="n">
-        <v>10.606</v>
+        <v>10.6543</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>2.0356</v>
+        <v>2.0264</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,PL,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>6359</v>
       </c>
       <c r="D20" t="n">
-        <v>4.2785</v>
+        <v>4.2548</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>1.4945</v>
       </c>
       <c r="F20" t="n">
-        <v>1.792</v>
+        <v>1.808</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.3135</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>-0.1734</v>
       </c>
       <c r="I20" t="n">
-        <v>2.175</v>
+        <v>2.198</v>
       </c>
       <c r="J20" t="n">
-        <v>20.99</v>
+        <v>21.59</v>
       </c>
       <c r="K20" t="n">
-        <v>10.6945</v>
+        <v>10.606</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>1.9627</v>
+        <v>2.0356</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>6150</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>4.2875</v>
-      </c>
-      <c r="E21" s="24" t="n">
-        <v>1.4344</v>
+        <v>4.2785</v>
       </c>
       <c r="F21" t="n">
-        <v>1.845</v>
-      </c>
-      <c r="G21" s="25" t="n">
-        <v>-0.4106</v>
-      </c>
-      <c r="H21" s="23" t="n">
-        <v>-0.2225</v>
+        <v>1.792</v>
       </c>
       <c r="I21" t="n">
-        <v>2.089</v>
+        <v>2.175</v>
       </c>
       <c r="J21" t="n">
-        <v>19.94</v>
+        <v>20.99</v>
       </c>
       <c r="K21" t="n">
-        <v>10.693</v>
+        <v>10.6945</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>1.8648</v>
+        <v>1.9627</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5760</v>
+        <v>6150</v>
       </c>
       <c r="D22" t="n">
-        <v>4.2725</v>
+        <v>4.2875</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>1.3482</v>
+        <v>1.4344</v>
       </c>
       <c r="F22" t="n">
-        <v>1.734</v>
+        <v>1.845</v>
       </c>
       <c r="G22" s="25" t="n">
-        <v>-0.3858</v>
+        <v>-0.4106</v>
       </c>
       <c r="H22" s="23" t="n">
         <v>-0.2225</v>
       </c>
       <c r="I22" t="n">
-        <v>2.055</v>
+        <v>2.089</v>
       </c>
       <c r="J22" t="n">
         <v>19.94</v>
       </c>
       <c r="K22" t="n">
-        <v>10.6885</v>
+        <v>10.693</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>1.8656</v>
+        <v>1.8648</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -1518,43 +1522,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5681</v>
+        <v>5760</v>
       </c>
       <c r="D23" t="n">
-        <v>4.2588</v>
+        <v>4.2725</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>1.3339</v>
+        <v>1.3482</v>
       </c>
       <c r="F23" t="n">
-        <v>1.738</v>
+        <v>1.734</v>
       </c>
       <c r="G23" s="25" t="n">
-        <v>-0.4041</v>
+        <v>-0.3858</v>
       </c>
       <c r="H23" s="23" t="n">
-        <v>-0.2325</v>
+        <v>-0.2225</v>
       </c>
       <c r="I23" t="n">
-        <v>2.011</v>
+        <v>2.055</v>
       </c>
       <c r="J23" t="n">
-        <v>18.64</v>
+        <v>19.94</v>
       </c>
       <c r="K23" t="n">
-        <v>10.6785</v>
+        <v>10.6885</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>1.7456</v>
+        <v>1.8656</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -1565,43 +1569,43 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5237</v>
+        <v>5681</v>
       </c>
       <c r="D24" t="n">
-        <v>4.2865</v>
+        <v>4.2588</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>1.2217</v>
+        <v>1.3339</v>
       </c>
       <c r="F24" t="n">
-        <v>1.619</v>
+        <v>1.738</v>
       </c>
       <c r="G24" s="25" t="n">
-        <v>-0.3973</v>
+        <v>-0.4041</v>
       </c>
       <c r="H24" s="23" t="n">
-        <v>-0.2454</v>
+        <v>-0.2325</v>
       </c>
       <c r="I24" t="n">
-        <v>1.916</v>
+        <v>2.011</v>
       </c>
       <c r="J24" t="n">
-        <v>17.34</v>
+        <v>18.64</v>
       </c>
       <c r="K24" t="n">
-        <v>10.7265</v>
+        <v>10.6785</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>1.6166</v>
+        <v>1.7456</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -1612,125 +1616,125 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5237</v>
       </c>
       <c r="D25" t="n">
-        <v>4.244</v>
+        <v>4.2865</v>
+      </c>
+      <c r="E25" s="24" t="n">
+        <v>1.2217</v>
       </c>
       <c r="F25" t="n">
-        <v>1.506</v>
+        <v>1.619</v>
+      </c>
+      <c r="G25" s="25" t="n">
+        <v>-0.3973</v>
+      </c>
+      <c r="H25" s="23" t="n">
+        <v>-0.2454</v>
       </c>
       <c r="I25" t="n">
-        <v>1.815</v>
+        <v>1.916</v>
       </c>
       <c r="J25" t="n">
         <v>17.34</v>
       </c>
       <c r="K25" t="n">
-        <v>10.708</v>
+        <v>10.7265</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>1.6194</v>
+        <v>1.6166</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4777</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D26" t="n">
-        <v>4.2243</v>
-      </c>
-      <c r="E26" s="24" t="n">
-        <v>1.1308</v>
+        <v>4.244</v>
       </c>
       <c r="F26" t="n">
         <v>1.506</v>
       </c>
-      <c r="G26" s="25" t="n">
-        <v>-0.3752</v>
-      </c>
-      <c r="H26" s="23" t="n">
-        <v>-0.2491</v>
-      </c>
       <c r="I26" t="n">
-        <v>1.748</v>
+        <v>1.815</v>
       </c>
       <c r="J26" t="n">
-        <v>17.19</v>
+        <v>17.34</v>
       </c>
       <c r="K26" t="n">
-        <v>10.6643</v>
+        <v>10.708</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.6194</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4744</v>
+        <v>4777</v>
       </c>
       <c r="D27" t="n">
-        <v>4.2225</v>
+        <v>4.2243</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>1.1235</v>
+        <v>1.1308</v>
       </c>
       <c r="F27" t="n">
-        <v>1.492</v>
+        <v>1.506</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>-0.3685</v>
+        <v>-0.3752</v>
       </c>
       <c r="H27" s="23" t="n">
-        <v>-0.247</v>
+        <v>-0.2491</v>
       </c>
       <c r="I27" t="n">
-        <v>1.726</v>
+        <v>1.748</v>
       </c>
       <c r="J27" t="n">
-        <v>17.34</v>
+        <v>17.19</v>
       </c>
       <c r="K27" t="n">
-        <v>10.673</v>
+        <v>10.6643</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>1.6247</v>
+        <v>1.6119</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -1741,43 +1745,43 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4765</v>
+        <v>4744</v>
       </c>
       <c r="D28" t="n">
-        <v>4.2233</v>
+        <v>4.2225</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>1.1283</v>
+        <v>1.1235</v>
       </c>
       <c r="F28" t="n">
-        <v>1.495</v>
+        <v>1.492</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>-0.3667</v>
+        <v>-0.3685</v>
       </c>
       <c r="H28" s="23" t="n">
-        <v>-0.2453</v>
+        <v>-0.247</v>
       </c>
       <c r="I28" t="n">
-        <v>1.74</v>
+        <v>1.726</v>
       </c>
       <c r="J28" t="n">
         <v>17.34</v>
       </c>
       <c r="K28" t="n">
-        <v>10.6765</v>
+        <v>10.673</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>1.6241</v>
+        <v>1.6247</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -1788,43 +1792,43 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4769</v>
+        <v>4765</v>
       </c>
       <c r="D29" t="n">
-        <v>4.2203</v>
+        <v>4.2233</v>
       </c>
       <c r="E29" s="24" t="n">
-        <v>1.13</v>
+        <v>1.1283</v>
       </c>
       <c r="F29" t="n">
-        <v>1.505</v>
+        <v>1.495</v>
       </c>
       <c r="G29" s="25" t="n">
-        <v>-0.375</v>
+        <v>-0.3667</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>-0.2492</v>
+        <v>-0.2453</v>
       </c>
       <c r="I29" t="n">
-        <v>1.745</v>
+        <v>1.74</v>
       </c>
       <c r="J29" t="n">
-        <v>17.24</v>
+        <v>17.34</v>
       </c>
       <c r="K29" t="n">
-        <v>10.688</v>
+        <v>10.6765</v>
       </c>
       <c r="L29" s="24" t="n">
-        <v>1.613</v>
+        <v>1.6241</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -1835,125 +1839,125 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4769</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2173</v>
+        <v>4.2203</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>1.13</v>
       </c>
       <c r="F30" t="n">
-        <v>1.492</v>
+        <v>1.505</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>-0.375</v>
+      </c>
+      <c r="H30" s="23" t="n">
+        <v>-0.2492</v>
       </c>
       <c r="I30" t="n">
-        <v>1.742</v>
+        <v>1.745</v>
       </c>
       <c r="J30" t="n">
         <v>17.24</v>
       </c>
       <c r="K30" t="n">
-        <v>10.6955</v>
+        <v>10.688</v>
       </c>
       <c r="L30" s="24" t="n">
-        <v>1.6119</v>
+        <v>1.613</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4743</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D31" t="n">
-        <v>4.2238</v>
-      </c>
-      <c r="E31" s="24" t="n">
-        <v>1.1229</v>
+        <v>4.2173</v>
       </c>
       <c r="F31" t="n">
-        <v>1.487</v>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>-0.3641</v>
-      </c>
-      <c r="H31" s="23" t="n">
-        <v>-0.2449</v>
+        <v>1.492</v>
       </c>
       <c r="I31" t="n">
-        <v>1.727</v>
+        <v>1.742</v>
       </c>
       <c r="J31" t="n">
-        <v>16.89</v>
+        <v>17.24</v>
       </c>
       <c r="K31" t="n">
-        <v>10.6745</v>
+        <v>10.6955</v>
       </c>
       <c r="L31" s="24" t="n">
-        <v>1.5823</v>
+        <v>1.6119</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4597</v>
+        <v>4743</v>
       </c>
       <c r="D32" t="n">
-        <v>4.2215</v>
+        <v>4.2238</v>
       </c>
       <c r="E32" s="24" t="n">
-        <v>1.0889</v>
+        <v>1.1229</v>
       </c>
       <c r="F32" t="n">
-        <v>1.46</v>
+        <v>1.487</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>-0.3711</v>
+        <v>-0.3641</v>
       </c>
       <c r="H32" s="23" t="n">
-        <v>-0.2542</v>
+        <v>-0.2449</v>
       </c>
       <c r="I32" t="n">
-        <v>1.713</v>
+        <v>1.727</v>
       </c>
       <c r="J32" t="n">
-        <v>16.64</v>
+        <v>16.89</v>
       </c>
       <c r="K32" t="n">
-        <v>10.6915</v>
+        <v>10.6745</v>
       </c>
       <c r="L32" s="24" t="n">
-        <v>1.5564</v>
+        <v>1.5823</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -1964,43 +1968,43 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4569</v>
+        <v>4597</v>
       </c>
       <c r="D33" t="n">
-        <v>4.2165</v>
+        <v>4.2215</v>
       </c>
       <c r="E33" s="24" t="n">
-        <v>1.0836</v>
+        <v>1.0889</v>
       </c>
       <c r="F33" t="n">
-        <v>1.443</v>
+        <v>1.46</v>
       </c>
       <c r="G33" s="25" t="n">
-        <v>-0.3594</v>
+        <v>-0.3711</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>-0.2491</v>
+        <v>-0.2542</v>
       </c>
       <c r="I33" t="n">
-        <v>1.697</v>
+        <v>1.713</v>
       </c>
       <c r="J33" t="n">
         <v>16.64</v>
       </c>
       <c r="K33" t="n">
-        <v>10.616</v>
+        <v>10.6915</v>
       </c>
       <c r="L33" s="24" t="n">
-        <v>1.5674</v>
+        <v>1.5564</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2011,43 +2015,43 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4577</v>
+        <v>4569</v>
       </c>
       <c r="D34" t="n">
-        <v>4.2138</v>
+        <v>4.2165</v>
       </c>
       <c r="E34" s="24" t="n">
-        <v>1.0862</v>
+        <v>1.0836</v>
       </c>
       <c r="F34" t="n">
-        <v>1.448</v>
+        <v>1.443</v>
       </c>
       <c r="G34" s="25" t="n">
-        <v>-0.3618</v>
+        <v>-0.3594</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>-0.2499</v>
+        <v>-0.2491</v>
       </c>
       <c r="I34" t="n">
-        <v>1.715</v>
+        <v>1.697</v>
       </c>
       <c r="J34" t="n">
         <v>16.64</v>
       </c>
       <c r="K34" t="n">
-        <v>10.648</v>
+        <v>10.616</v>
       </c>
       <c r="L34" s="24" t="n">
-        <v>1.5627</v>
+        <v>1.5674</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2058,125 +2062,125 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4577</v>
       </c>
       <c r="D35" t="n">
-        <v>4.2105</v>
+        <v>4.2138</v>
+      </c>
+      <c r="E35" s="24" t="n">
+        <v>1.0862</v>
       </c>
       <c r="F35" t="n">
         <v>1.448</v>
       </c>
+      <c r="G35" s="25" t="n">
+        <v>-0.3618</v>
+      </c>
+      <c r="H35" s="23" t="n">
+        <v>-0.2499</v>
+      </c>
       <c r="I35" t="n">
-        <v>1.724</v>
+        <v>1.715</v>
       </c>
       <c r="J35" t="n">
         <v>16.64</v>
       </c>
       <c r="K35" t="n">
-        <v>10.6205</v>
+        <v>10.648</v>
       </c>
       <c r="L35" s="24" t="n">
-        <v>1.5668</v>
+        <v>1.5627</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>4593</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D36" t="n">
-        <v>4.215</v>
-      </c>
-      <c r="E36" s="24" t="n">
-        <v>1.0897</v>
+        <v>4.2105</v>
       </c>
       <c r="F36" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="G36" s="25" t="n">
-        <v>-0.3533</v>
-      </c>
-      <c r="H36" s="23" t="n">
-        <v>-0.2448</v>
+        <v>1.448</v>
       </c>
       <c r="I36" t="n">
-        <v>1.72</v>
+        <v>1.724</v>
       </c>
       <c r="J36" t="n">
         <v>16.64</v>
       </c>
       <c r="K36" t="n">
-        <v>10.6254</v>
+        <v>10.6205</v>
       </c>
       <c r="L36" s="24" t="n">
-        <v>1.5661</v>
+        <v>1.5668</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,LT,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4613</v>
+        <v>4593</v>
       </c>
       <c r="D37" t="n">
-        <v>4.2158</v>
+        <v>4.215</v>
       </c>
       <c r="E37" s="24" t="n">
-        <v>1.0942</v>
+        <v>1.0897</v>
       </c>
       <c r="F37" t="n">
-        <v>1.455</v>
+        <v>1.443</v>
       </c>
       <c r="G37" s="25" t="n">
-        <v>-0.3608</v>
+        <v>-0.3533</v>
       </c>
       <c r="H37" s="23" t="n">
-        <v>-0.248</v>
-      </c>
-      <c r="I37" s="24" t="n">
-        <v>2.146</v>
+        <v>-0.2448</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.72</v>
       </c>
       <c r="J37" t="n">
         <v>16.64</v>
       </c>
       <c r="K37" t="n">
-        <v>10.567</v>
+        <v>10.6254</v>
       </c>
       <c r="L37" s="24" t="n">
-        <v>1.5747</v>
+        <v>1.5661</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2187,43 +2191,43 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4609</v>
+        <v>4613</v>
       </c>
       <c r="D38" t="n">
-        <v>4.2135</v>
+        <v>4.2158</v>
       </c>
       <c r="E38" s="24" t="n">
-        <v>1.0939</v>
+        <v>1.0942</v>
       </c>
       <c r="F38" t="n">
-        <v>1.453</v>
+        <v>1.455</v>
       </c>
       <c r="G38" s="25" t="n">
-        <v>-0.3591</v>
+        <v>-0.3608</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>-0.2471</v>
+        <v>-0.248</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J38" t="n">
-        <v>16.79</v>
+        <v>16.64</v>
       </c>
       <c r="K38" t="n">
-        <v>10.564</v>
+        <v>10.567</v>
       </c>
       <c r="L38" s="24" t="n">
-        <v>1.5894</v>
+        <v>1.5747</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2234,43 +2238,43 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4620</v>
+        <v>4609</v>
       </c>
       <c r="D39" t="n">
-        <v>4.217</v>
+        <v>4.2135</v>
       </c>
       <c r="E39" s="24" t="n">
-        <v>1.0956</v>
+        <v>1.0939</v>
       </c>
       <c r="F39" t="n">
-        <v>1.456</v>
+        <v>1.453</v>
       </c>
       <c r="G39" s="25" t="n">
-        <v>-0.3604</v>
+        <v>-0.3591</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>-0.2475</v>
+        <v>-0.2471</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J39" t="n">
-        <v>16.94</v>
+        <v>16.79</v>
       </c>
       <c r="K39" t="n">
-        <v>10.6135</v>
+        <v>10.564</v>
       </c>
       <c r="L39" s="24" t="n">
-        <v>1.5961</v>
+        <v>1.5894</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2281,95 +2285,104 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>4620</v>
       </c>
       <c r="D40" t="n">
-        <v>4.2118</v>
+        <v>4.217</v>
+      </c>
+      <c r="E40" s="24" t="n">
+        <v>1.0956</v>
       </c>
       <c r="F40" t="n">
-        <v>1.462</v>
+        <v>1.456</v>
+      </c>
+      <c r="G40" s="25" t="n">
+        <v>-0.3604</v>
+      </c>
+      <c r="H40" s="23" t="n">
+        <v>-0.2475</v>
       </c>
       <c r="I40" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J40" t="n">
-        <v>16.79</v>
+        <v>16.94</v>
       </c>
       <c r="K40" t="n">
-        <v>10.6505</v>
+        <v>10.6135</v>
       </c>
       <c r="L40" s="24" t="n">
-        <v>1.5765</v>
+        <v>1.5961</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Auto: FX,LT,DE,SE</t>
+          <t>Auto: FX,PL,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>4608</v>
+          <t>Mon</t>
+        </is>
       </c>
       <c r="D41" t="n">
-        <v>4.2185</v>
-      </c>
-      <c r="E41" s="24" t="n">
-        <v>1.0923</v>
+        <v>4.2118</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.462</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J41" t="n">
-        <v>16.69</v>
+        <v>16.79</v>
       </c>
       <c r="K41" t="n">
-        <v>10.6735</v>
+        <v>10.6505</v>
       </c>
       <c r="L41" s="24" t="n">
-        <v>1.5637</v>
+        <v>1.5765</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Auto: FX,PL,DE,SE</t>
+          <t>Auto: FX,LT,DE,SE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4606</v>
+        <v>4608</v>
       </c>
       <c r="D42" t="n">
-        <v>4.2205</v>
+        <v>4.2185</v>
       </c>
       <c r="E42" s="24" t="n">
-        <v>1.0913</v>
+        <v>1.0923</v>
       </c>
       <c r="I42" s="24" t="n">
         <v>2.146</v>
@@ -2378,10 +2391,10 @@
         <v>16.69</v>
       </c>
       <c r="K42" t="n">
-        <v>10.641</v>
+        <v>10.6735</v>
       </c>
       <c r="L42" s="24" t="n">
-        <v>1.5685</v>
+        <v>1.5637</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -2392,22 +2405,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4631</v>
+        <v>4606</v>
       </c>
       <c r="D43" t="n">
-        <v>4.2235</v>
+        <v>4.2205</v>
       </c>
       <c r="E43" s="24" t="n">
-        <v>1.0965</v>
+        <v>1.0913</v>
       </c>
       <c r="I43" s="24" t="n">
         <v>2.146</v>
@@ -2416,10 +2429,10 @@
         <v>16.69</v>
       </c>
       <c r="K43" t="n">
-        <v>10.577</v>
+        <v>10.641</v>
       </c>
       <c r="L43" s="24" t="n">
-        <v>1.578</v>
+        <v>1.5685</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -2430,34 +2443,34 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4622</v>
+        <v>4631</v>
       </c>
       <c r="D44" t="n">
-        <v>4.2205</v>
+        <v>4.2235</v>
       </c>
       <c r="E44" s="24" t="n">
-        <v>1.0951</v>
+        <v>1.0965</v>
       </c>
       <c r="I44" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J44" t="n">
-        <v>16.99</v>
+        <v>16.69</v>
       </c>
       <c r="K44" t="n">
-        <v>10.5485</v>
+        <v>10.577</v>
       </c>
       <c r="L44" s="24" t="n">
-        <v>1.6107</v>
+        <v>1.578</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -2468,30 +2481,68 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Mon</t>
-        </is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4622</v>
       </c>
       <c r="D45" t="n">
-        <v>4.2173</v>
+        <v>4.2205</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>1.0951</v>
       </c>
       <c r="I45" s="24" t="n">
         <v>2.146</v>
       </c>
       <c r="J45" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10.5485</v>
+      </c>
+      <c r="L45" s="24" t="n">
+        <v>1.6107</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Auto: FX,PL,DE,SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.2173</v>
+      </c>
+      <c r="I46" s="24" t="n">
+        <v>2.146</v>
+      </c>
+      <c r="J46" t="n">
         <v>16.79</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K46" t="n">
         <v>10.5935</v>
       </c>
-      <c r="L45" s="24" t="n">
+      <c r="L46" s="24" t="n">
         <v>1.5849</v>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Auto: FX,DE,SE</t>
         </is>

--- a/fuel_tracker.xlsx
+++ b/fuel_tracker.xlsx
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,42 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46112.40250203417</v>
+        <v>46113.4067401887</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tue</t>
+          <t>Wed</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>6796</v>
+        <v>6782</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>4.2883</v>
+        <v>4.289</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>1.5848</v>
+        <v>1.5813</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>2.0011</v>
+        <v>2.0183</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.4163</v>
+        <v>-0.437</v>
       </c>
       <c r="H5" s="20" t="n">
-        <v>-0.208</v>
+        <v>-0.2165</v>
       </c>
       <c r="I5" s="18" t="n">
         <v>2.297</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>24.14</v>
+        <v>24.34</v>
       </c>
       <c r="K5" s="16" t="n">
-        <v>10.906</v>
+        <v>10.943</v>
       </c>
       <c r="L5" s="17" t="n">
-        <v>2.2135</v>
+        <v>2.2243</v>
       </c>
       <c r="M5" s="10" t="inlineStr">
         <is>
@@ -725,42 +725,42 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46111.41346276621</v>
+        <v>46112.40250203704</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Mon</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6761</v>
+        <v>6796</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>4.2875</v>
+        <v>4.2883</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>1.5769</v>
+        <v>1.5848</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1.98</v>
+        <v>2.0011</v>
       </c>
       <c r="G6" s="19" t="n">
-        <v>-0.4031</v>
+        <v>-0.4163</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>-0.2036</v>
+        <v>-0.208</v>
       </c>
       <c r="I6" s="18" t="n">
         <v>2.297</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>23.84</v>
+        <v>24.14</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>10.878</v>
+        <v>10.906</v>
       </c>
       <c r="L6" s="17" t="n">
-        <v>2.1916</v>
+        <v>2.2135</v>
       </c>
       <c r="M6" s="10" t="inlineStr">
         <is>
@@ -775,42 +775,42 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46108.39354063657</v>
+        <v>46111.41346276621</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Mon</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>6870</v>
+        <v>6761</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2875</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>1.6073</v>
+        <v>1.5769</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>1.8704</v>
+        <v>1.98</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.2631</v>
+        <v>-0.4031</v>
       </c>
       <c r="H7" s="20" t="n">
-        <v>-0.1407</v>
+        <v>-0.2036</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>2.297</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>22.59</v>
+        <v>23.84</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>10.8405</v>
+        <v>10.878</v>
       </c>
       <c r="L7" s="17" t="n">
-        <v>2.0839</v>
+        <v>2.1916</v>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
@@ -825,42 +825,42 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46107.3982090625</v>
+        <v>46108.39354063657</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Thu</t>
+          <t>Fri</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6749</v>
+        <v>6870</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>4.2718</v>
+        <v>4.2743</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1.5799</v>
+        <v>1.6073</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>1.9581</v>
+        <v>1.8704</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>-0.3782</v>
+        <v>-0.2631</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>-0.1931</v>
+        <v>-0.1407</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>2.13</v>
+        <v>2.297</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>23.49</v>
+        <v>22.59</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>10.7715</v>
+        <v>10.8405</v>
       </c>
       <c r="L8" s="17" t="n">
-        <v>2.1808</v>
+        <v>2.0839</v>
       </c>
       <c r="M8" s="10" t="inlineStr">
         <is>
@@ -875,42 +875,42 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46106.39402475695</v>
+        <v>46107.3982090625</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Wed</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>7053</v>
+        <v>6749</v>
       </c>
       <c r="D9" s="16" t="n">
-        <v>4.2743</v>
+        <v>4.2718</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1.6501</v>
+        <v>1.5799</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>1.9708</v>
+        <v>1.9581</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-0.3207</v>
+        <v>-0.3782</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.1627</v>
+        <v>-0.1931</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>2.146</v>
+        <v>2.13</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>23.64</v>
+        <v>23.49</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>10.8238</v>
+        <v>10.7715</v>
       </c>
       <c r="L9" s="17" t="n">
-        <v>2.1841</v>
+        <v>2.1808</v>
       </c>
       <c r="M9" s="10" t="inlineStr">
         <is>
@@ -925,46 +925,46 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46105.39506804398</v>
+        <v>46106.39402475695</v>
       </c>
       <